--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F951C955-688C-4C03-8E39-91919928D5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6D54EB-DDAA-4C2D-8312-A82ED282B970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="394">
   <si>
     <t>6.6.0 敌人数据一览</t>
   </si>
@@ -857,17 +857,7 @@
     <t>瘟疫圣诞老人</t>
   </si>
   <si>
-    <t>47.7±0.6</t>
-  </si>
-  <si>
-    <t>35 冰</t>
-  </si>
-  <si>
     <t>概率冰冻</t>
-  </si>
-  <si>
-    <t>红猎第十一季
-(克劳斯指挥官 vs 瘟疫圣诞老人)</t>
   </si>
   <si>
     <t>群生领主</t>
@@ -1207,6 +1197,49 @@
   </si>
   <si>
     <t>站着靠近会逃走，蹲着不会</t>
+  </si>
+  <si>
+    <t>银矿</t>
+  </si>
+  <si>
+    <t>修博尔触碰的矿工</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害减免50%受到的寒冷伤害；1.嗜血。攻击时能恢复等同于其所造成的伤害的生命值。2.破甲。攻击时无视玩家部分护甲。</t>
+  </si>
+  <si>
+    <t>西方银矿</t>
+  </si>
+  <si>
+    <t>修博尔触碰的工兵</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害减免50%受到的寒冷伤害；1.投掷炸弹。对玩家所在区域投掷炸弹，投掷时有前摇和预警，若被命中则受到500点物理伤害并被眩晕。2.自爆。死亡时自爆，对附近造成750点伤害。3.走位。会主动远离玩家，跟玩家拉开距离</t>
+  </si>
+  <si>
+    <t>修博尔触碰的监工</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害减免50%受到的寒冷伤害；1.普通攻击。距离它较近时，它将使用近战攻击；距离较远时使用远程攻击，远程攻击有概率对玩家造成恐惧效果。2.流血。造成持续1分钟的流血效果，共20段流血伤害（8）。3.呼唤。呼叫附近的矿工和工兵。4.召唤。召唤一个骷髅战士攻击玩家。</t>
+  </si>
+  <si>
+    <t>不稳定的骨傀儡</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害减免50%受到的寒冷伤害；1.不稳。骨傀儡约每2秒受到50点真实伤害，约每10秒恢复250点生命值。若骨傀儡被冻结，则它将无法恢复生命值。2.加速。骨傀儡造成的伤害降低100点，但是攻击速度大大提高。3.重组。骨傀儡死后，将在一段时间内复活，无法彻底杀死。</t>
+  </si>
+  <si>
+    <t>100 冰</t>
+  </si>
+  <si>
+    <t>克劳斯司令（友军）</t>
+  </si>
+  <si>
+    <t>(克劳斯指挥官 vs 瘟疫圣诞老人)</t>
+  </si>
+  <si>
+    <t>在激活圣诞树buff后，可免疫冻伤和75%寒冷伤害；攻击力视其武器而定。
+克劳斯司令的武器也有耐久度。武器可在营地处升级。友方单位，帮助对抗瘟疫圣诞老人</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m\,\ d\,\ yy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1263,8 +1296,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1343,8 +1382,20 @@
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A86E8"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1611,13 +1662,178 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1783,6 +1999,63 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1794,6 +2067,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF4A86E8"/>
       <color rgb="FF351C75"/>
     </mruColors>
   </colors>
@@ -2071,7 +2345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="35.3984375" customWidth="1"/>
@@ -3560,7 +3834,7 @@
     </row>
     <row r="65" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>191</v>
+        <v>380</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>2</v>
@@ -3584,1645 +3858,1789 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" ht="36.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="B66" s="5">
+        <v>330</v>
+      </c>
+      <c r="C66" s="5">
+        <v>150</v>
+      </c>
+      <c r="D66" s="5">
+        <v>48</v>
+      </c>
+      <c r="E66" s="5">
+        <v>100</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="G66" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="43.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="57" t="s">
+        <v>384</v>
+      </c>
+      <c r="B67" s="60">
+        <v>450</v>
+      </c>
+      <c r="C67" s="63">
+        <v>0</v>
+      </c>
+      <c r="D67" s="60">
+        <v>0</v>
+      </c>
+      <c r="E67" s="60">
+        <v>500</v>
+      </c>
+      <c r="F67" s="73"/>
+      <c r="G67" s="67" t="s">
+        <v>385</v>
+      </c>
+      <c r="H67" s="58" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="58.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="56" t="s">
+        <v>386</v>
+      </c>
+      <c r="B68" s="61">
+        <v>500</v>
+      </c>
+      <c r="C68" s="64">
+        <v>150</v>
+      </c>
+      <c r="D68" s="61">
+        <v>48</v>
+      </c>
+      <c r="E68" s="61">
+        <v>180</v>
+      </c>
+      <c r="F68" s="71"/>
+      <c r="G68" s="68" t="s">
+        <v>387</v>
+      </c>
+      <c r="H68" s="59" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="58.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A69" s="56" t="s">
+        <v>388</v>
+      </c>
+      <c r="B69" s="62">
+        <v>1000</v>
+      </c>
+      <c r="C69" s="65">
+        <v>150</v>
+      </c>
+      <c r="D69" s="62">
+        <v>48</v>
+      </c>
+      <c r="E69" s="62">
+        <v>200</v>
+      </c>
+      <c r="F69" s="72"/>
+      <c r="G69" s="69" t="s">
+        <v>389</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" s="66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A71" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B71" s="12">
         <v>25</v>
       </c>
-      <c r="C66" s="12">
-        <v>0</v>
-      </c>
-      <c r="D66" s="12">
-        <v>0</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="12" t="s">
+      <c r="C71" s="12">
+        <v>0</v>
+      </c>
+      <c r="D71" s="12">
+        <v>0</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H66" s="15" t="s">
+      <c r="H71" s="15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A67" s="4" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A72" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B72" s="5">
         <v>400</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C72" s="5">
         <v>140</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E72" s="5">
         <v>26</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A68" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B68" s="5">
-        <v>400</v>
-      </c>
-      <c r="C68" s="5">
-        <v>140</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E68" s="5">
-        <v>19</v>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A69" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B69" s="5">
-        <v>400</v>
-      </c>
-      <c r="C69" s="5">
-        <v>140</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E69" s="5">
-        <v>35</v>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A70" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="B70" s="9">
-        <v>400</v>
-      </c>
-      <c r="C70" s="5">
-        <v>140</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E70" s="9">
-        <v>59</v>
-      </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A71" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B71" s="5">
-        <v>200</v>
-      </c>
-      <c r="C71" s="5">
-        <v>0</v>
-      </c>
-      <c r="D71" s="5">
-        <v>0</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A72" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B72" s="9">
-        <v>400</v>
-      </c>
-      <c r="C72" s="9">
-        <v>105</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="E72" s="9">
-        <v>34</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="11"/>
-      <c r="H72" s="10" t="s">
-        <v>206</v>
+      <c r="H72" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="18" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B73" s="5">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="C73" s="5">
-        <v>0</v>
-      </c>
-      <c r="D73" s="5">
-        <v>0</v>
+        <v>140</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="E73" s="5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F73" s="6"/>
-      <c r="G73" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="G73" s="11"/>
       <c r="H73" s="7" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="18" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B74" s="5">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="C74" s="5">
-        <v>280</v>
-      </c>
-      <c r="D74" s="5">
-        <v>63</v>
+        <v>140</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="E74" s="5">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F74" s="6"/>
-      <c r="G74" s="32"/>
+      <c r="G74" s="11"/>
       <c r="H74" s="7" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B75" s="5">
-        <v>40</v>
+        <v>200</v>
+      </c>
+      <c r="B75" s="9">
+        <v>400</v>
       </c>
       <c r="C75" s="5">
-        <v>0</v>
-      </c>
-      <c r="D75" s="5">
-        <v>0</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>213</v>
+        <v>140</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E75" s="9">
+        <v>59</v>
       </c>
       <c r="F75" s="6"/>
-      <c r="G75" s="32"/>
+      <c r="G75" s="11"/>
       <c r="H75" s="7" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A76" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="B76" s="9">
-        <v>120</v>
-      </c>
-      <c r="C76" s="9">
-        <v>50</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E76" s="9">
-        <v>30</v>
+      <c r="A76" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B76" s="5">
+        <v>200</v>
+      </c>
+      <c r="C76" s="5">
+        <v>0</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="F76" s="6"/>
-      <c r="G76" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>218</v>
+      <c r="G76" s="11"/>
+      <c r="H76" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A77" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B77" s="5">
-        <v>110</v>
-      </c>
-      <c r="C77" s="5">
-        <v>475</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E77" s="5">
-        <v>15</v>
+      <c r="A77" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B77" s="9">
+        <v>400</v>
+      </c>
+      <c r="C77" s="9">
+        <v>105</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" s="9">
+        <v>34</v>
       </c>
       <c r="F77" s="6"/>
-      <c r="G77" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>222</v>
+      <c r="G77" s="11"/>
+      <c r="H77" s="10" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A78" s="4" t="s">
-        <v>223</v>
+      <c r="A78" s="18" t="s">
+        <v>207</v>
       </c>
       <c r="B78" s="5">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="C78" s="5">
-        <v>475</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>224</v>
+        <v>0</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0</v>
       </c>
       <c r="E78" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="5" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H78" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A79" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" s="5">
+        <v>550</v>
+      </c>
+      <c r="C79" s="5">
+        <v>280</v>
+      </c>
+      <c r="D79" s="5">
+        <v>63</v>
+      </c>
+      <c r="E79" s="5">
+        <v>70</v>
+      </c>
+      <c r="F79" s="6"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A80" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" s="5">
+        <v>40</v>
+      </c>
+      <c r="C80" s="5">
+        <v>0</v>
+      </c>
+      <c r="D80" s="5">
+        <v>0</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F80" s="6"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A81" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" s="9">
+        <v>120</v>
+      </c>
+      <c r="C81" s="9">
+        <v>50</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E81" s="9">
+        <v>30</v>
+      </c>
+      <c r="F81" s="6"/>
+      <c r="G81" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A82" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B82" s="5">
+        <v>110</v>
+      </c>
+      <c r="C82" s="5">
+        <v>475</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E82" s="5">
+        <v>15</v>
+      </c>
+      <c r="F82" s="6"/>
+      <c r="G82" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H82" s="7" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A79" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B79" s="9">
-        <v>300</v>
-      </c>
-      <c r="C79" s="9">
-        <v>0</v>
-      </c>
-      <c r="D79" s="9">
-        <v>0</v>
-      </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A80" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="B80" s="9">
-        <v>300</v>
-      </c>
-      <c r="C80" s="9">
-        <v>80</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="E80" s="9">
-        <v>40</v>
-      </c>
-      <c r="F80" s="6"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="10" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A81" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B81" s="5">
-        <v>300</v>
-      </c>
-      <c r="C81" s="5">
-        <v>40</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E81" s="5">
-        <v>20</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A82" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="B82" s="5">
-        <v>600</v>
-      </c>
-      <c r="C82" s="5">
-        <v>40</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E82" s="5">
-        <v>24</v>
-      </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A83" s="22" t="s">
-        <v>238</v>
+      <c r="A83" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="B83" s="5">
-        <v>450</v>
+        <v>185</v>
       </c>
       <c r="C83" s="5">
-        <v>370</v>
+        <v>475</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E83" s="6"/>
+        <v>224</v>
+      </c>
+      <c r="E83" s="5">
+        <v>50</v>
+      </c>
       <c r="F83" s="6"/>
       <c r="G83" s="5" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="22" t="s">
-        <v>242</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A84" s="21" t="s">
+        <v>226</v>
       </c>
       <c r="B84" s="9">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="C84" s="9">
-        <v>50</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E84" s="9">
-        <v>55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D84" s="9">
+        <v>0</v>
+      </c>
+      <c r="E84" s="6"/>
       <c r="F84" s="6"/>
-      <c r="G84" s="24" t="s">
-        <v>243</v>
+      <c r="G84" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A85" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="B85" s="5">
-        <v>10000</v>
-      </c>
-      <c r="C85" s="5">
-        <v>200</v>
+      <c r="A85" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B85" s="9">
+        <v>300</v>
+      </c>
+      <c r="C85" s="9">
+        <v>80</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E85" s="5">
+        <v>230</v>
+      </c>
+      <c r="E85" s="9">
         <v>40</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="11"/>
       <c r="H85" s="10" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A86" s="29" t="s">
-        <v>247</v>
+      <c r="A86" s="20" t="s">
+        <v>232</v>
       </c>
       <c r="B86" s="5">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="C86" s="5">
-        <v>0</v>
-      </c>
-      <c r="D86" s="5">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="E86" s="5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F86" s="6"/>
-      <c r="G86" s="5" t="s">
-        <v>248</v>
-      </c>
+      <c r="G86" s="11"/>
       <c r="H86" s="7" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A87" s="23" t="s">
-        <v>250</v>
+      <c r="A87" s="29" t="s">
+        <v>235</v>
       </c>
       <c r="B87" s="5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="C87" s="5">
         <v>40</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E87" s="5">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="11"/>
       <c r="H87" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A88" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B88" s="33">
-        <v>1700</v>
-      </c>
-      <c r="C88" s="33">
-        <v>340</v>
-      </c>
-      <c r="D88" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="E88" s="33">
-        <v>90</v>
-      </c>
-      <c r="F88" s="34"/>
-      <c r="G88" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="H88" s="36" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H89" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A88" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B88" s="5">
+        <v>450</v>
+      </c>
+      <c r="C88" s="5">
+        <v>370</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="B89" s="9">
+        <v>2500</v>
+      </c>
+      <c r="C89" s="9">
+        <v>50</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E89" s="9">
+        <v>55</v>
+      </c>
+      <c r="F89" s="6"/>
+      <c r="G89" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A90" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="B90" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C90" s="5">
+        <v>200</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E90" s="5">
+        <v>40</v>
+      </c>
+      <c r="F90" s="6"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A91" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="B91" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0</v>
+      </c>
+      <c r="E91" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A90" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="B90" s="5">
-        <v>50</v>
-      </c>
-      <c r="C90" s="5">
-        <v>0</v>
-      </c>
-      <c r="D90" s="5">
-        <v>0</v>
-      </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A91" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="B91" s="9">
-        <v>400</v>
-      </c>
-      <c r="C91" s="9">
-        <v>50</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E91" s="9">
-        <v>65</v>
-      </c>
       <c r="F91" s="6"/>
-      <c r="G91" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>264</v>
+      <c r="G91" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A92" s="18" t="s">
-        <v>265</v>
+      <c r="A92" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="B92" s="5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="C92" s="5">
-        <v>0</v>
-      </c>
-      <c r="D92" s="5">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="E92" s="5">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="11"/>
       <c r="H92" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A93" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B93" s="5">
-        <v>60</v>
-      </c>
-      <c r="C93" s="5">
-        <v>0</v>
-      </c>
-      <c r="D93" s="5">
-        <v>0</v>
-      </c>
-      <c r="E93" s="32"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A94" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="B94" s="5">
-        <v>600</v>
-      </c>
-      <c r="C94" s="5">
-        <v>0</v>
-      </c>
-      <c r="D94" s="5">
-        <v>0</v>
-      </c>
-      <c r="E94" s="5">
-        <v>20</v>
-      </c>
-      <c r="F94" s="38"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A95" s="20" t="s">
-        <v>269</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A93" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B93" s="33">
+        <v>1700</v>
+      </c>
+      <c r="C93" s="33">
+        <v>340</v>
+      </c>
+      <c r="D93" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="E93" s="33">
+        <v>90</v>
+      </c>
+      <c r="F93" s="34"/>
+      <c r="G93" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="H93" s="36" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A95" s="18" t="s">
+        <v>258</v>
       </c>
       <c r="B95" s="5">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="C95" s="5">
-        <v>150</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E95" s="5">
+        <v>0</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0</v>
+      </c>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A96" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B96" s="9">
+        <v>400</v>
+      </c>
+      <c r="C96" s="9">
         <v>50</v>
       </c>
-      <c r="F95" s="39" t="s">
-        <v>271</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="H95" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A96" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="B96" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C96" s="9">
-        <v>55</v>
-      </c>
       <c r="D96" s="9" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E96" s="9">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A97" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B97" s="5">
+        <v>75</v>
+      </c>
+      <c r="C97" s="5">
+        <v>0</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0</v>
+      </c>
+      <c r="E97" s="5">
+        <v>9</v>
+      </c>
+      <c r="F97" s="6"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A98" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B98" s="5">
+        <v>60</v>
+      </c>
+      <c r="C98" s="5">
+        <v>0</v>
+      </c>
+      <c r="D98" s="5">
+        <v>0</v>
+      </c>
+      <c r="E98" s="32"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="A99" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="B99" s="5">
+        <v>5000</v>
+      </c>
+      <c r="C99" s="5">
+        <v>180</v>
+      </c>
+      <c r="D99" s="5">
+        <v>52</v>
+      </c>
+      <c r="E99" s="32"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="74" t="s">
+        <v>393</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A100" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B100" s="5">
+        <v>600</v>
+      </c>
+      <c r="C100" s="5">
+        <v>0</v>
+      </c>
+      <c r="D100" s="5">
+        <v>0</v>
+      </c>
+      <c r="E100" s="5">
+        <v>20</v>
+      </c>
+      <c r="F100" s="38"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="B101" s="5">
+        <v>4000</v>
+      </c>
+      <c r="C101" s="5">
+        <v>150</v>
+      </c>
+      <c r="D101" s="5">
+        <v>48</v>
+      </c>
+      <c r="E101" s="5">
+        <v>100</v>
+      </c>
+      <c r="F101" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H101" s="19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A102" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="B102" s="9">
+        <v>1000</v>
+      </c>
+      <c r="C102" s="9">
+        <v>55</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E102" s="9">
+        <v>9</v>
+      </c>
+      <c r="F102" s="6"/>
+      <c r="G102" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A103" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="B103" s="9">
+        <v>800</v>
+      </c>
+      <c r="C103" s="9">
+        <v>100</v>
+      </c>
+      <c r="D103" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H96" s="10" t="s">
+      <c r="E103" s="9">
+        <v>20</v>
+      </c>
+      <c r="F103" s="6"/>
+      <c r="G103" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A104" s="22" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A97" s="29" t="s">
+      <c r="B104" s="9">
+        <v>150</v>
+      </c>
+      <c r="C104" s="9">
+        <v>0</v>
+      </c>
+      <c r="D104" s="9">
+        <v>0</v>
+      </c>
+      <c r="E104" s="9">
+        <v>35</v>
+      </c>
+      <c r="F104" s="6"/>
+      <c r="G104" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="B97" s="9">
-        <v>800</v>
-      </c>
-      <c r="C97" s="9">
-        <v>100</v>
-      </c>
-      <c r="D97" s="9" t="s">
+      <c r="H104" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E97" s="9">
-        <v>20</v>
-      </c>
-      <c r="F97" s="6"/>
-      <c r="G97" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A98" s="22" t="s">
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A105" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="B98" s="9">
-        <v>150</v>
-      </c>
-      <c r="C98" s="9">
-        <v>0</v>
-      </c>
-      <c r="D98" s="9">
-        <v>0</v>
-      </c>
-      <c r="E98" s="9">
-        <v>35</v>
-      </c>
-      <c r="F98" s="6"/>
-      <c r="G98" s="9" t="s">
+      <c r="B105" s="9">
+        <v>700</v>
+      </c>
+      <c r="C105" s="9">
+        <v>0</v>
+      </c>
+      <c r="D105" s="9">
+        <v>0</v>
+      </c>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="H98" s="7" t="s">
+      <c r="H105" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A106" s="40" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A99" s="22" t="s">
+      <c r="B106" s="9">
+        <v>2000</v>
+      </c>
+      <c r="C106" s="9">
+        <v>0</v>
+      </c>
+      <c r="D106" s="9">
+        <v>0</v>
+      </c>
+      <c r="E106" s="9">
+        <v>57</v>
+      </c>
+      <c r="F106" s="6"/>
+      <c r="G106" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="B99" s="9">
-        <v>700</v>
-      </c>
-      <c r="C99" s="9">
-        <v>0</v>
-      </c>
-      <c r="D99" s="9">
-        <v>0</v>
-      </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="9" t="s">
+      <c r="H106" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A107" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="H99" s="10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A100" s="40" t="s">
+      <c r="B107" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A108" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B100" s="9">
-        <v>2000</v>
-      </c>
-      <c r="C100" s="9">
-        <v>0</v>
-      </c>
-      <c r="D100" s="9">
-        <v>0</v>
-      </c>
-      <c r="E100" s="9">
-        <v>57</v>
-      </c>
-      <c r="F100" s="6"/>
-      <c r="G100" s="24" t="s">
+      <c r="B108" s="5">
+        <v>400</v>
+      </c>
+      <c r="C108" s="5">
+        <v>0</v>
+      </c>
+      <c r="D108" s="9">
+        <v>0</v>
+      </c>
+      <c r="E108" s="5">
+        <v>99</v>
+      </c>
+      <c r="F108" s="6"/>
+      <c r="G108" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="H100" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A101" s="1" t="s">
+      <c r="H108" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A109" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A102" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B102" s="5">
-        <v>400</v>
-      </c>
-      <c r="C102" s="5">
-        <v>0</v>
-      </c>
-      <c r="D102" s="9">
-        <v>0</v>
-      </c>
-      <c r="E102" s="5">
-        <v>99</v>
-      </c>
-      <c r="F102" s="6"/>
-      <c r="G102" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A103" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B103" s="5">
+      <c r="B109" s="5">
         <v>80</v>
       </c>
-      <c r="C103" s="5">
-        <v>0</v>
-      </c>
-      <c r="D103" s="9">
-        <v>0</v>
-      </c>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A104" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B104" s="5">
-        <v>70</v>
-      </c>
-      <c r="C104" s="5">
-        <v>0</v>
-      </c>
-      <c r="D104" s="9">
-        <v>0</v>
-      </c>
-      <c r="E104" s="5">
-        <v>14</v>
-      </c>
-      <c r="F104" s="6"/>
-      <c r="G104" s="11"/>
-      <c r="H104" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A105" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B105" s="5">
-        <v>180</v>
-      </c>
-      <c r="C105" s="5">
-        <v>35</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E105" s="5">
-        <v>54</v>
-      </c>
-      <c r="F105" s="6"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A106" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B106" s="5">
-        <v>40</v>
-      </c>
-      <c r="C106" s="5">
-        <v>0</v>
-      </c>
-      <c r="D106" s="9">
-        <v>0</v>
-      </c>
-      <c r="E106" s="5">
-        <v>5</v>
-      </c>
-      <c r="F106" s="6"/>
-      <c r="G106" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A107" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B107" s="5">
-        <v>100</v>
-      </c>
-      <c r="C107" s="5">
-        <v>0</v>
-      </c>
-      <c r="D107" s="9">
-        <v>0</v>
-      </c>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A108" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A109" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>303</v>
-      </c>
       <c r="C109" s="5">
         <v>0</v>
       </c>
-      <c r="D109" s="5">
-        <v>0</v>
-      </c>
-      <c r="E109" s="41" t="s">
-        <v>304</v>
-      </c>
+      <c r="D109" s="9">
+        <v>0</v>
+      </c>
+      <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="5" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C110" s="42">
-        <v>14914</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E110" s="42">
-        <v>43929</v>
-      </c>
-      <c r="F110" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>312</v>
+      <c r="A110" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B110" s="5">
+        <v>70</v>
+      </c>
+      <c r="C110" s="5">
+        <v>0</v>
+      </c>
+      <c r="D110" s="9">
+        <v>0</v>
+      </c>
+      <c r="E110" s="5">
+        <v>14</v>
+      </c>
+      <c r="F110" s="6"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="7" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A111" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C111" s="42">
-        <v>14914</v>
+      <c r="A111" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B111" s="5">
+        <v>180</v>
+      </c>
+      <c r="C111" s="5">
+        <v>35</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E111" s="42">
-        <v>43929</v>
-      </c>
-      <c r="F111" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>312</v>
+        <v>292</v>
+      </c>
+      <c r="E111" s="5">
+        <v>54</v>
+      </c>
+      <c r="F111" s="6"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="7" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A112" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C112" s="42">
-        <v>14914</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E112" s="42">
-        <v>43929</v>
-      </c>
-      <c r="F112" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G112" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="H112" s="10" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A113" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C113" s="42">
-        <v>14914</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E113" s="42">
-        <v>43929</v>
-      </c>
-      <c r="F113" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G113" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A114" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C114" s="42">
-        <v>14914</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E114" s="42">
-        <v>43929</v>
-      </c>
-      <c r="F114" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G114" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="H114" s="10" t="s">
-        <v>319</v>
+      <c r="A112" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B112" s="5">
+        <v>40</v>
+      </c>
+      <c r="C112" s="5">
+        <v>0</v>
+      </c>
+      <c r="D112" s="9">
+        <v>0</v>
+      </c>
+      <c r="E112" s="5">
+        <v>5</v>
+      </c>
+      <c r="F112" s="6"/>
+      <c r="G112" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A113" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B113" s="5">
+        <v>100</v>
+      </c>
+      <c r="C113" s="5">
+        <v>0</v>
+      </c>
+      <c r="D113" s="9">
+        <v>0</v>
+      </c>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A114" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A115" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C115" s="42">
-        <v>14914</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E115" s="42">
-        <v>43929</v>
-      </c>
-      <c r="F115" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G115" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>319</v>
+      <c r="A115" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C115" s="5">
+        <v>0</v>
+      </c>
+      <c r="D115" s="5">
+        <v>0</v>
+      </c>
+      <c r="E115" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="F115" s="6"/>
+      <c r="G115" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="22" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C116" s="42">
         <v>14914</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E116" s="42">
         <v>43929</v>
       </c>
       <c r="F116" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="G116" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="H116" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A117" s="22" t="s">
-        <v>326</v>
-      </c>
       <c r="B117" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C117" s="42">
         <v>14914</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E117" s="42">
         <v>43929</v>
       </c>
       <c r="F117" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G117" s="24" t="s">
-        <v>327</v>
+        <v>307</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>311</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="22" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C118" s="42">
         <v>14914</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E118" s="42">
         <v>43929</v>
       </c>
       <c r="F118" s="43" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G118" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C119" s="42">
+        <v>14914</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E119" s="42">
+        <v>43929</v>
+      </c>
+      <c r="F119" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A120" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C120" s="42">
+        <v>14914</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E120" s="42">
+        <v>43929</v>
+      </c>
+      <c r="F120" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="H120" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C121" s="42">
+        <v>14914</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E121" s="42">
+        <v>43929</v>
+      </c>
+      <c r="F121" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A122" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C122" s="42">
+        <v>14914</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E122" s="42">
+        <v>43929</v>
+      </c>
+      <c r="F122" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A123" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C123" s="42">
+        <v>14914</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E123" s="42">
+        <v>43929</v>
+      </c>
+      <c r="F123" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G123" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C124" s="42">
+        <v>14914</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E124" s="42">
+        <v>43929</v>
+      </c>
+      <c r="F124" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="74.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A125" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="H118" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" ht="74.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A119" s="40" t="s">
+      <c r="D125" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="E125" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="F125" s="44" t="s">
         <v>332</v>
       </c>
-      <c r="D119" s="5" t="s">
+      <c r="G125" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="H125" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="40.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A126" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="F119" s="44" t="s">
+      <c r="B126" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="G119" s="24" t="s">
+      <c r="C126" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="H119" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" ht="40.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A120" s="40" t="s">
+      <c r="D126" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="B120" s="9" t="s">
+      <c r="E126" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="C120" s="9" t="s">
+      <c r="F126" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="D120" s="9" t="s">
+      <c r="G126" s="24" t="s">
         <v>340</v>
       </c>
-      <c r="E120" s="9" t="s">
+      <c r="H126" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A127" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F120" s="43" t="s">
-        <v>342</v>
-      </c>
-      <c r="G120" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="H120" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A121" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B121" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D127" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E127" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F121" s="2" t="s">
+      <c r="F127" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="G127" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H121" s="3" t="s">
+      <c r="H127" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A122" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B122" s="5">
-        <v>120</v>
-      </c>
-      <c r="C122" s="5">
-        <v>220</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E122" s="5">
-        <v>30</v>
-      </c>
-      <c r="F122" s="39" t="s">
-        <v>347</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A123" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B123" s="5">
-        <v>120</v>
-      </c>
-      <c r="C123" s="5">
-        <v>295</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="E123" s="5">
-        <v>90</v>
-      </c>
-      <c r="F123" s="6"/>
-      <c r="G123" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A124" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B124" s="5">
-        <v>200</v>
-      </c>
-      <c r="C124" s="5">
-        <v>295</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="E124" s="5">
-        <v>180</v>
-      </c>
-      <c r="F124" s="6"/>
-      <c r="G124" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A125" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B125" s="5">
-        <v>200</v>
-      </c>
-      <c r="C125" s="5">
-        <v>230</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E125" s="5">
-        <v>98</v>
-      </c>
-      <c r="F125" s="6"/>
-      <c r="G125" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A126" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B126" s="5">
-        <v>200</v>
-      </c>
-      <c r="C126" s="5">
-        <v>405</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="E126" s="5">
-        <v>132</v>
-      </c>
-      <c r="F126" s="6"/>
-      <c r="G126" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A127" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B127" s="45">
-        <v>200</v>
-      </c>
-      <c r="C127" s="45">
-        <v>330</v>
-      </c>
-      <c r="D127" s="45" t="s">
-        <v>361</v>
-      </c>
-      <c r="E127" s="45">
-        <v>24</v>
-      </c>
-      <c r="F127" s="13"/>
-      <c r="G127" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B128" s="45">
-        <v>200</v>
-      </c>
-      <c r="C128" s="45">
+        <v>342</v>
+      </c>
+      <c r="B128" s="5">
+        <v>120</v>
+      </c>
+      <c r="C128" s="5">
         <v>220</v>
       </c>
-      <c r="D128" s="45" t="s">
-        <v>346</v>
-      </c>
-      <c r="E128" s="45">
-        <v>100</v>
-      </c>
-      <c r="F128" s="13"/>
-      <c r="G128" s="45" t="s">
-        <v>364</v>
+      <c r="D128" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E128" s="5">
+        <v>30</v>
+      </c>
+      <c r="F128" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B129" s="45">
-        <v>200</v>
-      </c>
-      <c r="C129" s="45">
-        <v>320</v>
-      </c>
-      <c r="D129" s="45" t="s">
-        <v>366</v>
-      </c>
-      <c r="E129" s="45">
-        <v>128</v>
-      </c>
-      <c r="F129" s="13"/>
-      <c r="G129" s="45" t="s">
-        <v>367</v>
+        <v>346</v>
+      </c>
+      <c r="B129" s="5">
+        <v>120</v>
+      </c>
+      <c r="C129" s="5">
+        <v>295</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E129" s="5">
+        <v>90</v>
+      </c>
+      <c r="F129" s="6"/>
+      <c r="G129" s="9" t="s">
+        <v>348</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B130" s="45">
+        <v>349</v>
+      </c>
+      <c r="B130" s="5">
         <v>200</v>
       </c>
-      <c r="C130" s="45">
-        <v>640</v>
-      </c>
-      <c r="D130" s="45" t="s">
-        <v>369</v>
-      </c>
-      <c r="E130" s="45">
-        <v>70</v>
-      </c>
-      <c r="F130" s="13"/>
-      <c r="G130" s="45" t="s">
-        <v>370</v>
+      <c r="C130" s="5">
+        <v>295</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E130" s="5">
+        <v>180</v>
+      </c>
+      <c r="F130" s="6"/>
+      <c r="G130" s="9" t="s">
+        <v>350</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="37.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A131" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="B131" s="46">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A131" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B131" s="5">
         <v>200</v>
       </c>
-      <c r="C131" s="46">
-        <v>1060</v>
-      </c>
-      <c r="D131" s="46" t="s">
-        <v>372</v>
-      </c>
-      <c r="E131" s="46">
-        <v>83</v>
-      </c>
-      <c r="F131" s="31"/>
-      <c r="G131" s="47" t="s">
-        <v>373</v>
+      <c r="C131" s="5">
+        <v>230</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E131" s="5">
+        <v>98</v>
+      </c>
+      <c r="F131" s="6"/>
+      <c r="G131" s="9" t="s">
+        <v>353</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A132" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="B132" s="45">
-        <v>250</v>
-      </c>
-      <c r="C132" s="45">
-        <v>585</v>
-      </c>
-      <c r="D132" s="45" t="s">
-        <v>375</v>
-      </c>
-      <c r="E132" s="45">
-        <v>100</v>
-      </c>
-      <c r="F132" s="13"/>
-      <c r="G132" s="48" t="s">
-        <v>376</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B132" s="5">
+        <v>200</v>
+      </c>
+      <c r="C132" s="5">
+        <v>405</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E132" s="5">
+        <v>132</v>
+      </c>
+      <c r="F132" s="6"/>
+      <c r="G132" s="5" t="s">
+        <v>356</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="41.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A133" s="20" t="s">
-        <v>377</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A133" s="4" t="s">
+        <v>357</v>
       </c>
       <c r="B133" s="45">
         <v>200</v>
       </c>
       <c r="C133" s="45">
+        <v>330</v>
+      </c>
+      <c r="D133" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="E133" s="45">
+        <v>24</v>
+      </c>
+      <c r="F133" s="13"/>
+      <c r="G133" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A134" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B134" s="45">
+        <v>200</v>
+      </c>
+      <c r="C134" s="45">
+        <v>220</v>
+      </c>
+      <c r="D134" s="45" t="s">
+        <v>343</v>
+      </c>
+      <c r="E134" s="45">
+        <v>100</v>
+      </c>
+      <c r="F134" s="13"/>
+      <c r="G134" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A135" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B135" s="45">
+        <v>200</v>
+      </c>
+      <c r="C135" s="45">
+        <v>320</v>
+      </c>
+      <c r="D135" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="E135" s="45">
+        <v>128</v>
+      </c>
+      <c r="F135" s="13"/>
+      <c r="G135" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A136" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B136" s="45">
+        <v>200</v>
+      </c>
+      <c r="C136" s="45">
+        <v>640</v>
+      </c>
+      <c r="D136" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="E136" s="45">
+        <v>70</v>
+      </c>
+      <c r="F136" s="13"/>
+      <c r="G136" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="37.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A137" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="B137" s="46">
+        <v>200</v>
+      </c>
+      <c r="C137" s="46">
+        <v>1060</v>
+      </c>
+      <c r="D137" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="E137" s="46">
+        <v>83</v>
+      </c>
+      <c r="F137" s="31"/>
+      <c r="G137" s="47" t="s">
+        <v>370</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="39.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A138" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B138" s="45">
+        <v>250</v>
+      </c>
+      <c r="C138" s="45">
+        <v>585</v>
+      </c>
+      <c r="D138" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="E138" s="45">
+        <v>100</v>
+      </c>
+      <c r="F138" s="13"/>
+      <c r="G138" s="48" t="s">
+        <v>373</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="41.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A139" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="B139" s="45">
+        <v>200</v>
+      </c>
+      <c r="C139" s="45">
         <v>805</v>
       </c>
-      <c r="D133" s="45" t="s">
+      <c r="D139" s="45" t="s">
+        <v>375</v>
+      </c>
+      <c r="E139" s="45">
+        <v>60</v>
+      </c>
+      <c r="F139" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="G139" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A140" s="50" t="s">
         <v>378</v>
       </c>
-      <c r="E133" s="45">
-        <v>60</v>
-      </c>
-      <c r="F133" s="49" t="s">
+      <c r="B140" s="51">
+        <v>500</v>
+      </c>
+      <c r="C140" s="51">
+        <v>0</v>
+      </c>
+      <c r="D140" s="51">
+        <v>0</v>
+      </c>
+      <c r="E140" s="52"/>
+      <c r="F140" s="52"/>
+      <c r="G140" s="51" t="s">
         <v>379</v>
       </c>
-      <c r="G133" s="48" t="s">
-        <v>380</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A134" s="50" t="s">
-        <v>381</v>
-      </c>
-      <c r="B134" s="51">
-        <v>500</v>
-      </c>
-      <c r="C134" s="51">
-        <v>0</v>
-      </c>
-      <c r="D134" s="51">
-        <v>0</v>
-      </c>
-      <c r="E134" s="52"/>
-      <c r="F134" s="52"/>
-      <c r="G134" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="H134" s="53" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
+      <c r="H140" s="53" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -5232,20 +5650,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5468,6 +5886,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38D30046-78DC-4E5E-85B0-443BB565BBA5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{782B16F9-C146-46D4-84C5-C24998C80642}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5480,14 +5906,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
     <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38D30046-78DC-4E5E-85B0-443BB565BBA5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B07A180-342A-42F9-96DA-BC4262C0D49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7229F010-A207-46A2-A3EE-5678F8F96151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="652">
   <si>
     <t>家里</t>
   </si>
@@ -2025,6 +2025,9 @@
   </si>
   <si>
     <t>15，20，35</t>
+  </si>
+  <si>
+    <t>待测 衰败</t>
   </si>
 </sst>
 </file>
@@ -5901,7 +5904,7 @@
         <v>645</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>342</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7229F010-A207-46A2-A3EE-5678F8F96151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A731013A-D8A2-40F1-B383-7C9AABB17EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="659">
   <si>
     <t>家里</t>
   </si>
@@ -2028,6 +2028,27 @@
   </si>
   <si>
     <t>待测 衰败</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.嗜血。攻击时能恢复等同于其所造成的伤害的生命值。2.破甲。攻击时无视玩家部分护甲。</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.投掷炸弹。对玩家所在区域投掷炸弹，投掷时有前摇和预警，若被命中则受到500点物理伤害并被眩晕。2.自爆。死亡时自爆，对附近造成750点伤害。3.走位。会主动远离玩家，跟玩家拉开距离</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.普通攻击。距离它较近时使用近战攻击；距离较远时使用远程攻击，远程攻击有概率对玩家造成恐惧效果。2.流血。造成持续55秒的流血效果（可叠加），共20段流血伤害（8）。3.呼唤。呼叫附近的矿工和工兵。4.召唤。随机召唤一个骷髅战士(200HP)攻击玩家。</t>
+  </si>
+  <si>
+    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.不稳。骨傀儡约每2秒受到50点真实伤害，约每10秒恢复250点生命值。若骨傀儡被冻结，则它将无法恢复生命值。2.加速。骨傀儡造成的伤害降低100点（快速攻击100），但是攻击速度大大提高。3.重组。骨傀儡死后将在一段时间内复活，无法彻底杀死；可闪避，降低玩家攻速；击败后会清除仇恨值并回归原位置。</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>无限</t>
+  </si>
+  <si>
+    <t>取决于爆炸距离</t>
   </si>
 </sst>
 </file>
@@ -2761,7 +2782,9 @@
       <c r="C3" s="2">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -3357,8 +3380,12 @@
       <c r="A33" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="D33" s="2">
         <v>24</v>
       </c>
@@ -3500,7 +3527,9 @@
       <c r="C40" s="2">
         <v>0</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" s="2" t="s">
+        <v>658</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
         <v>103</v>
@@ -4070,7 +4099,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>171</v>
+        <v>652</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>172</v>
@@ -4091,7 +4120,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>174</v>
+        <v>653</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>172</v>
@@ -4112,13 +4141,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>176</v>
+        <v>654</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="14" t="s">
         <v>177</v>
       </c>
@@ -4133,7 +4162,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>178</v>
+        <v>655</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>172</v>
@@ -4489,7 +4518,9 @@
       <c r="C87" s="2">
         <v>0</v>
       </c>
-      <c r="D87" s="2"/>
+      <c r="D87" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
         <v>221</v>
@@ -4531,7 +4562,9 @@
       <c r="C89" s="2">
         <v>0</v>
       </c>
-      <c r="D89" s="2"/>
+      <c r="D89" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
         <v>11</v>
@@ -4828,7 +4861,9 @@
       <c r="C104" s="2">
         <v>0</v>
       </c>
-      <c r="D104" s="2"/>
+      <c r="D104" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
         <v>258</v>
@@ -4999,7 +5034,9 @@
       <c r="C113" s="2">
         <v>69</v>
       </c>
-      <c r="D113" s="2"/>
+      <c r="D113" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
         <v>276</v>
@@ -5125,7 +5162,9 @@
       <c r="C119" s="2">
         <v>0</v>
       </c>
-      <c r="D119" s="2"/>
+      <c r="D119" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
         <v>292</v>
@@ -5257,8 +5296,12 @@
       <c r="B126" s="2">
         <v>200</v>
       </c>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
+      <c r="C126" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>645</v>
+      </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="13" t="s">
@@ -5275,7 +5318,9 @@
       <c r="C127" s="2">
         <v>0</v>
       </c>
-      <c r="D127" s="2"/>
+      <c r="D127" s="2" t="s">
+        <v>645</v>
+      </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
         <v>308</v>
@@ -5294,7 +5339,9 @@
       <c r="C128" s="2">
         <v>52</v>
       </c>
-      <c r="D128" s="2"/>
+      <c r="D128" s="2" t="s">
+        <v>645</v>
+      </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
         <v>310</v>
@@ -5485,7 +5532,9 @@
       <c r="C137" s="2">
         <v>0</v>
       </c>
-      <c r="D137" s="2"/>
+      <c r="D137" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
         <v>332</v>
@@ -5563,7 +5612,9 @@
       <c r="C141" s="2">
         <v>0</v>
       </c>
-      <c r="D141" s="2"/>
+      <c r="D141" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
         <v>340</v>
@@ -5929,7 +5980,9 @@
       <c r="E157" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F157" s="4"/>
+      <c r="F157" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G157" s="11" t="s">
         <v>6</v>
       </c>
@@ -6119,7 +6172,9 @@
       <c r="C167" s="2">
         <v>55</v>
       </c>
-      <c r="D167" s="2"/>
+      <c r="D167" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
         <v>407</v>
@@ -6216,7 +6271,9 @@
       <c r="C172" s="2">
         <v>0</v>
       </c>
-      <c r="D172" s="2"/>
+      <c r="D172" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
         <v>418</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A731013A-D8A2-40F1-B383-7C9AABB17EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BB0228-6BA0-4A59-AFDC-ED605C21B511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="661">
   <si>
     <t>家里</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>中毒5*8次</t>
-  </si>
-  <si>
-    <t>后妈；5级图</t>
   </si>
   <si>
     <t>麻风病人</t>
@@ -163,10 +160,6 @@
   </si>
   <si>
     <t>伤害取决于所持武器（15-27）</t>
-  </si>
-  <si>
-    <t>荒废墓穴；后妈；夜晚地窖；
-死灵法师；死亡村庄</t>
   </si>
   <si>
     <t>天灭者</t>
@@ -2049,6 +2042,19 @@
   </si>
   <si>
     <t>取决于爆炸距离</t>
+  </si>
+  <si>
+    <t>继母艾莎+5级图的蝙蝠</t>
+  </si>
+  <si>
+    <t>继母艾莎</t>
+  </si>
+  <si>
+    <t>继母艾莎；5级图</t>
+  </si>
+  <si>
+    <t>荒废墓穴；继母艾莎；夜晚地窖；
+死灵法师；死亡村庄</t>
   </si>
 </sst>
 </file>
@@ -2740,7 +2746,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2783,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -2915,7 +2921,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>22</v>
+        <v>657</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -2931,12 +2937,12 @@
         <v>23</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>24</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>50</v>
@@ -2950,12 +2956,12 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2">
         <v>200</v>
@@ -2969,12 +2975,12 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
         <v>300</v>
@@ -2993,7 +2999,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
         <v>100</v>
@@ -3004,15 +3010,15 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
         <v>90</v>
@@ -3031,7 +3037,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2">
         <v>80</v>
@@ -3044,15 +3050,15 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
         <v>125</v>
@@ -3066,12 +3072,12 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
         <v>95</v>
@@ -3084,15 +3090,15 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2">
         <v>90</v>
@@ -3106,12 +3112,12 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2">
         <v>70</v>
@@ -3120,19 +3126,19 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>47</v>
+        <v>660</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2">
         <v>300</v>
@@ -3146,46 +3152,46 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2">
         <v>100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>9</v>
@@ -3193,7 +3199,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2">
         <v>90</v>
@@ -3206,7 +3212,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>9</v>
@@ -3214,7 +3220,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2">
         <v>140</v>
@@ -3227,15 +3233,15 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2">
         <v>200</v>
@@ -3248,15 +3254,15 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B27" s="2">
         <v>300</v>
@@ -3269,15 +3275,15 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B28" s="2">
         <v>2800</v>
@@ -3286,17 +3292,17 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" s="2">
         <v>1000</v>
@@ -3307,15 +3313,15 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B30" s="2">
         <v>900</v>
@@ -3328,15 +3334,15 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A31" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B31" s="2">
         <v>760</v>
@@ -3349,15 +3355,15 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A32" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B32" s="2">
         <v>2000</v>
@@ -3370,36 +3376,36 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -3422,7 +3428,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B35" s="2">
         <v>50</v>
@@ -3436,12 +3442,12 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B36" s="2">
         <v>55</v>
@@ -3455,12 +3461,12 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B37" s="2">
         <v>50</v>
@@ -3474,12 +3480,12 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B38" s="2">
         <v>65</v>
@@ -3492,15 +3498,15 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" s="2">
         <v>175</v>
@@ -3514,12 +3520,12 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B40" s="2">
         <v>10</v>
@@ -3528,19 +3534,19 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B41" s="2">
         <v>400</v>
@@ -3554,12 +3560,12 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B42" s="2">
         <v>100</v>
@@ -3573,12 +3579,12 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B43" s="2">
         <v>400</v>
@@ -3591,15 +3597,15 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -3612,15 +3618,15 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -3633,15 +3639,15 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -3654,15 +3660,15 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B47" s="2">
         <v>400</v>
@@ -3675,15 +3681,15 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B48" s="2">
         <v>600</v>
@@ -3696,36 +3702,36 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A49" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G48" s="13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="81" x14ac:dyDescent="0.45">
-      <c r="A49" s="15" t="s">
+      <c r="C49" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="D49" s="2">
         <v>150</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B50" s="2">
         <v>1750</v>
@@ -3738,15 +3744,15 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B51" s="2">
         <v>900</v>
@@ -3759,15 +3765,15 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B52" s="2">
         <v>1750</v>
@@ -3780,15 +3786,15 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B53" s="2">
         <v>1600</v>
@@ -3801,15 +3807,15 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1</v>
@@ -3832,7 +3838,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -3845,15 +3851,15 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B56" s="2">
         <v>90</v>
@@ -3866,15 +3872,15 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B57" s="2">
         <v>200</v>
@@ -3887,15 +3893,15 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B58" s="2">
         <v>180</v>
@@ -3908,15 +3914,15 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B59" s="2">
         <v>250</v>
@@ -3929,15 +3935,15 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B60" s="2">
         <v>350</v>
@@ -3950,15 +3956,15 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B61" s="2">
         <v>350</v>
@@ -3971,15 +3977,15 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B62" s="2">
         <v>300</v>
@@ -3992,15 +3998,15 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B63" s="2">
         <v>300</v>
@@ -4013,15 +4019,15 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B64" s="2">
         <v>175</v>
@@ -4034,15 +4040,15 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A65" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B65" s="2">
         <v>10000</v>
@@ -4055,15 +4061,15 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>1</v>
@@ -4086,7 +4092,7 @@
     </row>
     <row r="67" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A67" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B67" s="2">
         <v>335</v>
@@ -4099,15 +4105,15 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B68" s="2">
         <v>450</v>
@@ -4120,15 +4126,15 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A69" s="14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B69" s="2">
         <v>550</v>
@@ -4141,15 +4147,15 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B70" s="2">
         <v>1000</v>
@@ -4162,15 +4168,15 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>1</v>
@@ -4193,7 +4199,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B72" s="2">
         <v>60</v>
@@ -4207,12 +4213,12 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B73" s="2">
         <v>70</v>
@@ -4226,12 +4232,12 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B74" s="2">
         <v>30</v>
@@ -4244,15 +4250,15 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>1</v>
@@ -4275,7 +4281,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B76" s="2">
         <v>800</v>
@@ -4284,19 +4290,19 @@
         <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B77" s="2">
         <v>700</v>
@@ -4308,18 +4314,18 @@
         <v>30</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B78" s="2">
         <v>800</v>
@@ -4328,21 +4334,21 @@
         <v>23</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="G78" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B79" s="2">
         <v>800</v>
@@ -4355,18 +4361,18 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -4376,18 +4382,18 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -4397,18 +4403,18 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C82" s="2">
         <v>24</v>
@@ -4418,60 +4424,60 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C83" s="2">
         <v>55</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" s="17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C84" s="2">
         <v>38</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C85" s="2">
         <v>38</v>
@@ -4481,18 +4487,18 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A86" s="16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C86" s="2">
         <v>60</v>
@@ -4502,15 +4508,15 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" s="16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -4519,19 +4525,19 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>1</v>
@@ -4554,7 +4560,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B89" s="2">
         <v>25</v>
@@ -4563,19 +4569,19 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B90" s="2">
         <v>400</v>
@@ -4589,12 +4595,12 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -4608,12 +4614,12 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -4627,12 +4633,12 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -4646,12 +4652,12 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B94" s="2">
         <v>200</v>
@@ -4660,19 +4666,19 @@
         <v>0</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B95" s="2">
         <v>400</v>
@@ -4686,12 +4692,12 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B96" s="2">
         <v>60</v>
@@ -4704,15 +4710,15 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B97" s="2">
         <v>2000</v>
@@ -4726,12 +4732,12 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B98" s="2">
         <v>550</v>
@@ -4745,12 +4751,12 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B99" s="2">
         <v>40</v>
@@ -4759,38 +4765,38 @@
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D100" s="2">
         <v>62</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B101" s="2">
         <v>150</v>
@@ -4803,15 +4809,15 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G101" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B102" s="2">
         <v>110</v>
@@ -4824,15 +4830,15 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B103" s="2">
         <v>185</v>
@@ -4845,15 +4851,15 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
@@ -4862,19 +4868,19 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B105" s="2">
         <v>300</v>
@@ -4888,18 +4894,18 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B106" s="2">
         <v>500</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D106" s="2">
         <v>36</v>
@@ -4907,15 +4913,15 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -4926,18 +4932,18 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D108" s="2">
         <v>72</v>
@@ -4945,31 +4951,31 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B110" s="2">
         <v>300</v>
@@ -4983,12 +4989,12 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B111" s="2">
         <v>600</v>
@@ -5002,12 +5008,12 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" s="16" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B112" s="2">
         <v>1000</v>
@@ -5021,12 +5027,12 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B113" s="2">
         <v>450</v>
@@ -5035,19 +5041,19 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A114" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B114" s="2">
         <v>2500</v>
@@ -5060,15 +5066,15 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B115" s="2">
         <v>9000</v>
@@ -5081,15 +5087,15 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B116" s="2">
         <v>10500</v>
@@ -5098,19 +5104,19 @@
         <v>0</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="16" t="s">
-        <v>287</v>
+        <v>658</v>
       </c>
       <c r="B117" s="2">
         <v>1700</v>
@@ -5123,15 +5129,15 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>1</v>
@@ -5154,7 +5160,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B119" s="2">
         <v>50</v>
@@ -5163,19 +5169,19 @@
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B120" s="2">
         <v>900</v>
@@ -5189,12 +5195,12 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B121" s="2">
         <v>400</v>
@@ -5207,15 +5213,15 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B122" s="2">
         <v>75</v>
@@ -5229,12 +5235,12 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -5248,12 +5254,12 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B124" s="2">
         <v>100</v>
@@ -5265,12 +5271,12 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B125" s="2">
         <v>45</v>
@@ -5283,34 +5289,34 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B127" s="2">
         <v>550</v>
@@ -5319,19 +5325,19 @@
         <v>0</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A128" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B128" s="2">
         <v>1500</v>
@@ -5340,19 +5346,19 @@
         <v>52</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B129" s="2">
         <v>1500</v>
@@ -5364,18 +5370,18 @@
         <v>100</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B130" s="2">
         <v>1000</v>
@@ -5388,15 +5394,15 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" s="15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B131" s="2">
         <v>750</v>
@@ -5409,15 +5415,15 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G131" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B132" s="2">
         <v>150</v>
@@ -5430,15 +5436,15 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B133" s="2">
         <v>720</v>
@@ -5451,15 +5457,15 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A134" s="16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B134" s="2">
         <v>2000</v>
@@ -5472,15 +5478,15 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>1</v>
@@ -5503,7 +5509,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B136" s="2">
         <v>400</v>
@@ -5516,15 +5522,15 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B137" s="2">
         <v>80</v>
@@ -5533,19 +5539,19 @@
         <v>0</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B138" s="2">
         <v>70</v>
@@ -5559,12 +5565,12 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B139" s="2">
         <v>180</v>
@@ -5578,12 +5584,12 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A140" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B140" s="2">
         <v>40</v>
@@ -5596,15 +5602,15 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B141" s="2">
         <v>100</v>
@@ -5613,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>1</v>
@@ -5648,325 +5654,325 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A145" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C145" s="2" t="s">
+      <c r="D145" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E145" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D145" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E145" s="6" t="s">
+      <c r="F145" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G145" s="13" t="s">
         <v>354</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="G145" s="13" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A146" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E146" s="6" t="s">
+      <c r="G146" s="13" t="s">
         <v>354</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A147" s="15" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C147" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E147" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E147" s="6" t="s">
+      <c r="F147" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G147" s="13" t="s">
         <v>354</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G147" s="13" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G148" s="13" t="s">
         <v>362</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G148" s="13" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="15" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C149" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E149" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="F149" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="15" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C150" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E150" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="F150" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="15" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C151" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E151" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D151" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="F151" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="15" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C152" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E152" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="F152" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="15" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C153" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E153" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="F153" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A154" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="D154" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E154" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="F154" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="D154" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="G154" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A155" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="D155" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E155" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="F155" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="G155" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="16" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>1</v>
@@ -5989,7 +5995,7 @@
     </row>
     <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B158" s="2">
         <v>120</v>
@@ -6001,18 +6007,18 @@
         <v>30</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G158" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B159" s="2">
         <v>120</v>
@@ -6025,13 +6031,13 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G159" s="21"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B160" s="2">
         <v>200</v>
@@ -6044,13 +6050,13 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G160" s="21"/>
     </row>
     <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B161" s="2">
         <v>200</v>
@@ -6063,13 +6069,13 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G161" s="21"/>
     </row>
     <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B162" s="2">
         <v>200</v>
@@ -6082,13 +6088,13 @@
       </c>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G162" s="21"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B163" s="2">
         <v>200</v>
@@ -6101,13 +6107,13 @@
       </c>
       <c r="E163" s="2"/>
       <c r="F163" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G163" s="21"/>
     </row>
     <row r="164" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B164" s="2">
         <v>200</v>
@@ -6120,13 +6126,13 @@
       </c>
       <c r="E164" s="2"/>
       <c r="F164" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G164" s="21"/>
     </row>
     <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="12" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B165" s="2">
         <v>200</v>
@@ -6139,13 +6145,13 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G165" s="21"/>
     </row>
     <row r="166" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B166" s="2">
         <v>200</v>
@@ -6158,13 +6164,13 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G166" s="21"/>
     </row>
     <row r="167" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B167" s="2">
         <v>120</v>
@@ -6173,17 +6179,17 @@
         <v>55</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G167" s="21"/>
     </row>
     <row r="168" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B168" s="2">
         <v>200</v>
@@ -6196,13 +6202,13 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G168" s="21"/>
     </row>
     <row r="169" spans="1:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A169" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B169" s="2">
         <v>250</v>
@@ -6215,13 +6221,13 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G169" s="21"/>
     </row>
     <row r="170" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A170" s="14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6233,16 +6239,16 @@
         <v>60</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G170" s="21"/>
     </row>
     <row r="171" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A171" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B171" s="2">
         <v>250</v>
@@ -6254,16 +6260,16 @@
         <v>60</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G171" s="21"/>
     </row>
     <row r="172" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B172" s="2">
         <v>500</v>
@@ -6272,17 +6278,17 @@
         <v>0</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G172" s="21"/>
     </row>
     <row r="173" spans="1:7" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B173" s="19">
         <v>500</v>
@@ -6295,7 +6301,7 @@
       </c>
       <c r="E173" s="19"/>
       <c r="F173" s="19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G173" s="22"/>
     </row>
@@ -6323,24 +6329,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -6349,15 +6355,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -6366,32 +6372,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -6400,7 +6406,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -6408,3589 +6414,3589 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BB0228-6BA0-4A59-AFDC-ED605C21B511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10921FBF-DE31-45CF-A1D2-C82AE0D00A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="682">
   <si>
     <t>家里</t>
   </si>
@@ -915,12 +915,6 @@
     <t>巨型骷髅</t>
   </si>
   <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>万圣节活动地图</t>
-  </si>
-  <si>
     <t>被遗忘的灵魂</t>
   </si>
   <si>
@@ -928,9 +922,6 @@
   </si>
   <si>
     <t>复仇的灵魂</t>
-  </si>
-  <si>
-    <t>万圣节维尔格莱夫废墟</t>
   </si>
   <si>
     <t>冰行者</t>
@@ -2055,6 +2046,82 @@
   <si>
     <t>荒废墓穴；继母艾莎；夜晚地窖；
 死灵法师；死亡村庄</t>
+  </si>
+  <si>
+    <t>韦格劳废墟</t>
+  </si>
+  <si>
+    <t>不定</t>
+  </si>
+  <si>
+    <t>随机持有石斧石镐，或者木棒作为武器</t>
+  </si>
+  <si>
+    <t>万圣节韦格劳废墟</t>
+  </si>
+  <si>
+    <t>远程攻击</t>
+  </si>
+  <si>
+    <t>坟墓守卫</t>
+  </si>
+  <si>
+    <t>不是魔王</t>
+  </si>
+  <si>
+    <t>免疫冰伤，受到双倍火伤</t>
+  </si>
+  <si>
+    <t>随机持有一种中级武器</t>
+  </si>
+  <si>
+    <t>骷髅炼金师</t>
+  </si>
+  <si>
+    <t>投掷南瓜炸弹，造成35点范围真实伤害，并造成恐惧效果；当你靠近它时，它会逃跑</t>
+  </si>
+  <si>
+    <t>被咒者奥塔</t>
+  </si>
+  <si>
+    <t>高抵抗衰败伤害；高抵抗寒冷伤害	每隔一段时间，召唤两个骷髅新兵，或一个骷髅炼金师；不是魔王</t>
+  </si>
+  <si>
+    <t>骷髅射手-古墓</t>
+  </si>
+  <si>
+    <t>骷髅新兵-古墓</t>
+  </si>
+  <si>
+    <t>小骷髅-万圣节</t>
+  </si>
+  <si>
+    <t>骷髅射手-万圣节</t>
+  </si>
+  <si>
+    <t>骷髅新兵-万圣节</t>
+  </si>
+  <si>
+    <t>骷髅战士射手-万圣节</t>
+  </si>
+  <si>
+    <t>骷髅战士近战-万圣节</t>
+  </si>
+  <si>
+    <t>武器为复合弓</t>
+  </si>
+  <si>
+    <t>武器为一把高级武器</t>
+  </si>
+  <si>
+    <t>低语噩梦</t>
+  </si>
+  <si>
+    <t>免疫冰伤，受到双倍火伤；
+1.灵魂复苏：释放超大范围圆形斩击，若命中则造成140点物理伤害，并召唤3个被遗忘的灵魂；
+2.噩梦之斩：释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕；
+3.低语触碰：低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）；
+不是魔王</t>
   </si>
 </sst>
 </file>
@@ -2430,11 +2497,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFBBC04"/>
       <color rgb="FF4A86E8"/>
       <color rgb="FF0B5394"/>
       <color rgb="FFFF6D01"/>
       <color rgb="FF351C75"/>
-      <color rgb="FFFBBC04"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2733,7 +2800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
@@ -2746,7 +2813,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2789,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -2921,7 +2988,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -2937,7 +3004,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3133,7 +3200,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3387,10 +3454,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3534,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4105,7 +4172,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>170</v>
@@ -4126,7 +4193,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>170</v>
@@ -4147,7 +4214,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>170</v>
@@ -4168,7 +4235,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>170</v>
@@ -4390,7 +4457,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>199</v>
+        <v>671</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>200</v>
@@ -4411,7 +4478,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>202</v>
+        <v>672</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>203</v>
@@ -4525,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -4569,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -4778,10 +4845,10 @@
         <v>245</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D100" s="2">
         <v>62</v>
@@ -4868,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
@@ -4921,7 +4988,7 @@
         <v>263</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -4940,10 +5007,10 @@
         <v>265</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D108" s="2">
         <v>72</v>
@@ -4959,13 +5026,13 @@
         <v>266</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5041,7 +5108,7 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
@@ -5116,7 +5183,7 @@
     </row>
     <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="16" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B117" s="2">
         <v>1700</v>
@@ -5137,7 +5204,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
-        <v>288</v>
+        <v>658</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>1</v>
@@ -5160,1154 +5227,1350 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>289</v>
+        <v>673</v>
       </c>
       <c r="B119" s="2">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C119" s="2">
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>290</v>
+        <v>660</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>291</v>
+        <v>661</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A120" s="14" t="s">
-        <v>71</v>
+      <c r="A120" s="12" t="s">
+        <v>674</v>
       </c>
       <c r="B120" s="2">
-        <v>900</v>
+        <v>45</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
       </c>
       <c r="D120" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
+      <c r="F120" s="2" t="s">
+        <v>662</v>
+      </c>
       <c r="G120" s="13" t="s">
-        <v>72</v>
+        <v>661</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A121" s="14" t="s">
-        <v>292</v>
+      <c r="A121" s="12" t="s">
+        <v>675</v>
       </c>
       <c r="B121" s="2">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="C121" s="2">
-        <v>24</v>
-      </c>
-      <c r="D121" s="2">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>659</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A122" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G121" s="13" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A122" s="12" t="s">
-        <v>295</v>
-      </c>
       <c r="B122" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C122" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D122" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
+      <c r="F122" s="2" t="s">
+        <v>665</v>
+      </c>
       <c r="G122" s="13" t="s">
-        <v>296</v>
+        <v>661</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B123" s="2">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="C123" s="2">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D123" s="2">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
+      <c r="F123" s="2" t="s">
+        <v>665</v>
+      </c>
       <c r="G123" s="13" t="s">
-        <v>298</v>
+        <v>661</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>299</v>
+        <v>676</v>
       </c>
       <c r="B124" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
       </c>
-      <c r="D124" s="2"/>
+      <c r="D124" s="2" t="s">
+        <v>659</v>
+      </c>
       <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
+      <c r="F124" s="2" t="s">
+        <v>678</v>
+      </c>
       <c r="G124" s="13" t="s">
-        <v>300</v>
+        <v>661</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>301</v>
+        <v>677</v>
       </c>
       <c r="B125" s="2">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="C125" s="2">
         <v>0</v>
       </c>
-      <c r="D125" s="2">
-        <v>5</v>
+      <c r="D125" s="2" t="s">
+        <v>659</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>302</v>
+        <v>679</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>303</v>
+        <v>661</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A126" s="12" t="s">
-        <v>304</v>
+      <c r="A126" s="14" t="s">
+        <v>663</v>
       </c>
       <c r="B126" s="2">
+        <v>215</v>
+      </c>
+      <c r="C126" s="2">
+        <v>9</v>
+      </c>
+      <c r="D126" s="2">
+        <v>10</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G126" s="13" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A127" s="14" t="s">
+        <v>667</v>
+      </c>
+      <c r="B127" s="2">
         <v>200</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A127" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B127" s="2">
-        <v>550</v>
-      </c>
       <c r="C127" s="2">
-        <v>0</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>643</v>
+        <v>24</v>
+      </c>
+      <c r="D127" s="2">
+        <v>35</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>306</v>
+        <v>668</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A128" s="12" t="s">
-        <v>307</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A128" s="15" t="s">
+        <v>669</v>
       </c>
       <c r="B128" s="2">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="C128" s="2">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>308</v>
+        <v>670</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A129" s="14" t="s">
-        <v>310</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+      <c r="A129" s="15" t="s">
+        <v>680</v>
       </c>
       <c r="B129" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C129" s="2">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D129" s="2">
-        <v>100</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>311</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>312</v>
+        <v>681</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>309</v>
+        <v>661</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A130" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="B130" s="2">
-        <v>1000</v>
-      </c>
-      <c r="C130" s="2">
-        <v>23</v>
-      </c>
-      <c r="D130" s="2">
-        <v>9</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="G130" s="13" t="s">
-        <v>315</v>
+      <c r="A130" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G130" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A131" s="15" t="s">
-        <v>316</v>
+      <c r="A131" s="12" t="s">
+        <v>289</v>
       </c>
       <c r="B131" s="2">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="C131" s="2">
-        <v>38</v>
-      </c>
-      <c r="D131" s="2">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>651</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="G131" s="13" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A132" s="15" t="s">
-        <v>318</v>
+      <c r="A132" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="B132" s="2">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
       </c>
       <c r="D132" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E132" s="2"/>
-      <c r="F132" s="2" t="s">
-        <v>319</v>
-      </c>
+      <c r="F132" s="2"/>
       <c r="G132" s="13" t="s">
-        <v>320</v>
+        <v>72</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A133" s="15" t="s">
-        <v>321</v>
+      <c r="A133" s="12" t="s">
+        <v>296</v>
       </c>
       <c r="B133" s="2">
-        <v>720</v>
+        <v>100</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
-      <c r="D133" s="2">
-        <v>23</v>
-      </c>
+      <c r="D133" s="2"/>
       <c r="E133" s="2"/>
-      <c r="F133" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="F133" s="2"/>
       <c r="G133" s="13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A134" s="16" t="s">
-        <v>324</v>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A134" s="12" t="s">
+        <v>298</v>
       </c>
       <c r="B134" s="2">
-        <v>2000</v>
+        <v>45</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
       </c>
       <c r="D134" s="2">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A135" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G135" s="11" t="s">
-        <v>6</v>
+      <c r="A135" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B135" s="2">
+        <v>200</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="13" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B136" s="2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
-      <c r="D136" s="2">
-        <v>99</v>
+      <c r="D136" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="B137" s="2">
-        <v>80</v>
+        <v>1500</v>
       </c>
       <c r="C137" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A138" s="12" t="s">
-        <v>331</v>
+      <c r="A138" s="14" t="s">
+        <v>307</v>
       </c>
       <c r="B138" s="2">
-        <v>70</v>
+        <v>1500</v>
       </c>
       <c r="C138" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D138" s="2">
-        <v>14</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="G138" s="13" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A139" s="12" t="s">
-        <v>333</v>
+      <c r="A139" s="15" t="s">
+        <v>310</v>
       </c>
       <c r="B139" s="2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="C139" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D139" s="2">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
+      <c r="F139" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="G139" s="13" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A140" s="12" t="s">
-        <v>334</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A140" s="15" t="s">
+        <v>313</v>
       </c>
       <c r="B140" s="2">
-        <v>40</v>
+        <v>750</v>
       </c>
       <c r="C140" s="2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D140" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A141" s="12" t="s">
-        <v>337</v>
+      <c r="A141" s="15" t="s">
+        <v>315</v>
       </c>
       <c r="B141" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C141" s="2">
         <v>0</v>
       </c>
-      <c r="D141" s="2" t="s">
-        <v>654</v>
+      <c r="D141" s="2">
+        <v>35</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A142" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G142" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A143" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>345</v>
+      <c r="A142" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B142" s="2">
+        <v>720</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2">
+        <v>23</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G142" s="13" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A143" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B143" s="2">
+        <v>2000</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>645</v>
+      <c r="D143" s="2">
+        <v>57</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G143" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A144" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G144" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A145" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B145" s="2">
+        <v>400</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2">
+        <v>99</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G145" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A146" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B146" s="2">
+        <v>80</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G146" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A147" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B147" s="2">
+        <v>70</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2">
+        <v>14</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A148" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="2">
+        <v>180</v>
+      </c>
+      <c r="C148" s="2">
+        <v>15</v>
+      </c>
+      <c r="D148" s="2">
+        <v>54</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A149" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B149" s="2">
+        <v>40</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2">
+        <v>5</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G149" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A150" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B150" s="2">
+        <v>100</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G150" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A151" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A152" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G152" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A153" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G153" s="13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A154" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="C154" s="2" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A144" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="B144" s="2" t="s">
+      <c r="D154" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G154" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A155" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="G144" s="13" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A145" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="B145" s="2" t="s">
+      <c r="E155" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G145" s="13" t="s">
+      <c r="F155" s="2" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A146" s="15" t="s">
+      <c r="G155" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A156" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A147" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G147" s="13" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A148" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G148" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A149" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="G149" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A150" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G150" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A151" s="15" t="s">
-        <v>638</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="G151" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A152" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="G152" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A153" s="15" t="s">
-        <v>640</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G153" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A154" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G154" s="13" t="s">
+      <c r="B156" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="54" x14ac:dyDescent="0.45">
-      <c r="A155" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G155" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A156" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="E156" s="8" t="s">
-        <v>649</v>
+      <c r="E156" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A157" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="B157" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A157" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G157" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A158" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G158" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A159" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G159" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A160" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G160" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A161" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="G161" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A162" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G162" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A163" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G163" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="54" x14ac:dyDescent="0.45">
+      <c r="A164" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G164" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A165" s="16" t="s">
+        <v>639</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G165" s="13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A166" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C166" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="D166" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E166" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="F166" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G157" s="11" t="s">
+      <c r="G166" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A158" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="B158" s="2">
-        <v>120</v>
-      </c>
-      <c r="C158" s="2">
-        <v>57</v>
-      </c>
-      <c r="D158" s="2">
-        <v>30</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="G158" s="20" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A159" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="B159" s="2">
-        <v>120</v>
-      </c>
-      <c r="C159" s="2">
-        <v>62</v>
-      </c>
-      <c r="D159" s="2">
-        <v>90</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="G159" s="21"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A160" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="B160" s="2">
-        <v>200</v>
-      </c>
-      <c r="C160" s="2">
-        <v>69</v>
-      </c>
-      <c r="D160" s="2">
-        <v>180</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="G160" s="21"/>
-    </row>
-    <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A161" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="B161" s="2">
-        <v>200</v>
-      </c>
-      <c r="C161" s="2">
-        <v>48</v>
-      </c>
-      <c r="D161" s="2">
-        <v>98</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G161" s="21"/>
-    </row>
-    <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A162" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="B162" s="2">
-        <v>200</v>
-      </c>
-      <c r="C162" s="2">
-        <v>59</v>
-      </c>
-      <c r="D162" s="2">
-        <v>132</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="G162" s="21"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A163" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="B163" s="2">
-        <v>200</v>
-      </c>
-      <c r="C163" s="2">
-        <v>40</v>
-      </c>
-      <c r="D163" s="2">
-        <v>24</v>
-      </c>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="G163" s="21"/>
-    </row>
-    <row r="164" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A164" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="B164" s="2">
-        <v>200</v>
-      </c>
-      <c r="C164" s="2">
-        <v>57</v>
-      </c>
-      <c r="D164" s="2">
-        <v>100</v>
-      </c>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G164" s="21"/>
-    </row>
-    <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A165" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="B165" s="2">
-        <v>200</v>
-      </c>
-      <c r="C165" s="2">
-        <v>65</v>
-      </c>
-      <c r="D165" s="2">
-        <v>128</v>
-      </c>
-      <c r="E165" s="2"/>
-      <c r="F165" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G165" s="21"/>
-    </row>
-    <row r="166" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A166" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="B166" s="2">
-        <v>200</v>
-      </c>
-      <c r="C166" s="2">
-        <v>77</v>
-      </c>
-      <c r="D166" s="2">
-        <v>70</v>
-      </c>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="G166" s="21"/>
     </row>
     <row r="167" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="12" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="B167" s="2">
         <v>120</v>
       </c>
       <c r="C167" s="2">
-        <v>55</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="E167" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D167" s="2">
+        <v>30</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>383</v>
+      </c>
       <c r="F167" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G167" s="21"/>
+        <v>384</v>
+      </c>
+      <c r="G167" s="20" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="168" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A168" s="14" t="s">
-        <v>406</v>
+      <c r="A168" s="12" t="s">
+        <v>385</v>
       </c>
       <c r="B168" s="2">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C168" s="2">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D168" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="G168" s="21"/>
     </row>
-    <row r="169" spans="1:7" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A169" s="14" t="s">
-        <v>408</v>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A169" s="12" t="s">
+        <v>387</v>
       </c>
       <c r="B169" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C169" s="2">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D169" s="2">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="G169" s="21"/>
     </row>
-    <row r="170" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A170" s="14" t="s">
-        <v>410</v>
+    <row r="170" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A170" s="12" t="s">
+        <v>389</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
       </c>
       <c r="C170" s="2">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="D170" s="2">
-        <v>60</v>
-      </c>
-      <c r="E170" s="7" t="s">
-        <v>192</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="G170" s="21"/>
     </row>
-    <row r="171" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A171" s="14" t="s">
-        <v>412</v>
+    <row r="171" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A171" s="12" t="s">
+        <v>391</v>
       </c>
       <c r="B171" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C171" s="2">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D171" s="2">
-        <v>60</v>
-      </c>
-      <c r="E171" s="9" t="s">
-        <v>413</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="G171" s="21"/>
     </row>
-    <row r="172" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A172" s="14" t="s">
-        <v>415</v>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A172" s="12" t="s">
+        <v>393</v>
       </c>
       <c r="B172" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="C172" s="2">
-        <v>0</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>654</v>
+        <v>40</v>
+      </c>
+      <c r="D172" s="2">
+        <v>24</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="G172" s="21"/>
     </row>
-    <row r="173" spans="1:7" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A173" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="B173" s="19">
+    <row r="173" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A173" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B173" s="2">
+        <v>200</v>
+      </c>
+      <c r="C173" s="2">
+        <v>57</v>
+      </c>
+      <c r="D173" s="2">
+        <v>100</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G173" s="21"/>
+    </row>
+    <row r="174" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A174" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B174" s="2">
+        <v>200</v>
+      </c>
+      <c r="C174" s="2">
+        <v>65</v>
+      </c>
+      <c r="D174" s="2">
+        <v>128</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G174" s="21"/>
+    </row>
+    <row r="175" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A175" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B175" s="2">
+        <v>200</v>
+      </c>
+      <c r="C175" s="2">
+        <v>77</v>
+      </c>
+      <c r="D175" s="2">
+        <v>70</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="G175" s="21"/>
+    </row>
+    <row r="176" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A176" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B176" s="2">
+        <v>120</v>
+      </c>
+      <c r="C176" s="2">
+        <v>55</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G176" s="21"/>
+    </row>
+    <row r="177" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A177" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="B177" s="2">
+        <v>200</v>
+      </c>
+      <c r="C177" s="2">
+        <v>86</v>
+      </c>
+      <c r="D177" s="2">
+        <v>83</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G177" s="21"/>
+    </row>
+    <row r="178" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A178" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B178" s="2">
+        <v>250</v>
+      </c>
+      <c r="C178" s="2">
+        <v>77</v>
+      </c>
+      <c r="D178" s="2">
+        <v>100</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G178" s="21"/>
+    </row>
+    <row r="179" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A179" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B179" s="2">
+        <v>200</v>
+      </c>
+      <c r="C179" s="2">
+        <v>82</v>
+      </c>
+      <c r="D179" s="2">
+        <v>60</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G179" s="21"/>
+    </row>
+    <row r="180" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A180" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B180" s="2">
+        <v>250</v>
+      </c>
+      <c r="C180" s="2">
+        <v>83</v>
+      </c>
+      <c r="D180" s="2">
+        <v>60</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="G180" s="21"/>
+    </row>
+    <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A181" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="B181" s="2">
         <v>500</v>
       </c>
-      <c r="C173" s="19">
+      <c r="C181" s="2">
+        <v>0</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G181" s="21"/>
+    </row>
+    <row r="182" spans="1:7" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A182" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="B182" s="19">
+        <v>500</v>
+      </c>
+      <c r="C182" s="19">
         <v>87</v>
       </c>
-      <c r="D173" s="19">
+      <c r="D182" s="19">
         <v>130</v>
       </c>
-      <c r="E173" s="19"/>
-      <c r="F173" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="G173" s="22"/>
-    </row>
+      <c r="E182" s="19"/>
+      <c r="F182" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="G182" s="22"/>
+    </row>
+    <row r="186" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G158:G173"/>
+    <mergeCell ref="G167:G182"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -6329,24 +6592,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -6355,15 +6618,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -6372,32 +6635,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -6406,7 +6669,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -6414,7 +6677,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -6423,15 +6686,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6440,15 +6703,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -6457,7 +6720,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -6465,7 +6728,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -6474,15 +6737,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -6491,7 +6754,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -6499,7 +6762,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -6508,7 +6771,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -6516,7 +6779,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -6525,15 +6788,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>59</v>
@@ -6542,15 +6805,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>59</v>
@@ -6559,7 +6822,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>60</v>
@@ -6567,7 +6830,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -6576,15 +6839,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>65</v>
@@ -6593,15 +6856,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>65</v>
@@ -6610,7 +6873,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>66</v>
@@ -6618,7 +6881,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>71</v>
@@ -6627,15 +6890,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -6644,15 +6907,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -6661,7 +6924,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>77</v>
@@ -6669,7 +6932,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -6678,15 +6941,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -6695,7 +6958,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>80</v>
@@ -6703,7 +6966,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -6712,15 +6975,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -6737,7 +7000,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>89</v>
@@ -6746,15 +7009,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -6763,15 +7026,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>98</v>
@@ -6780,15 +7043,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>103</v>
@@ -6797,15 +7060,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>107</v>
@@ -6814,15 +7077,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>110</v>
@@ -6831,15 +7094,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>110</v>
@@ -6856,7 +7119,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>110</v>
@@ -6865,7 +7128,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>112</v>
@@ -6873,7 +7136,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>113</v>
@@ -6882,15 +7145,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>113</v>
@@ -6899,7 +7162,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>114</v>
@@ -6907,7 +7170,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>116</v>
@@ -6916,15 +7179,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>116</v>
@@ -6933,7 +7196,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>117</v>
@@ -6941,7 +7204,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>118</v>
@@ -6950,15 +7213,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>118</v>
@@ -6967,7 +7230,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>119</v>
@@ -6975,7 +7238,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>120</v>
@@ -6984,15 +7247,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>122</v>
@@ -7001,7 +7264,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>124</v>
@@ -7009,7 +7272,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>122</v>
@@ -7018,7 +7281,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>125</v>
@@ -7026,7 +7289,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>126</v>
@@ -7035,15 +7298,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>126</v>
@@ -7052,7 +7315,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>127</v>
@@ -7060,7 +7323,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>129</v>
@@ -7069,15 +7332,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>129</v>
@@ -7086,15 +7349,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>132</v>
@@ -7103,15 +7366,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>132</v>
@@ -7120,15 +7383,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>135</v>
@@ -7137,15 +7400,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>135</v>
@@ -7154,15 +7417,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>135</v>
@@ -7171,7 +7434,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>136</v>
@@ -7179,7 +7442,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>139</v>
@@ -7188,15 +7451,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>142</v>
@@ -7205,7 +7468,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>143</v>
@@ -7213,7 +7476,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>145</v>
@@ -7230,7 +7493,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>150</v>
@@ -7239,7 +7502,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>151</v>
@@ -7247,7 +7510,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>153</v>
@@ -7256,15 +7519,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>155</v>
@@ -7273,15 +7536,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>157</v>
@@ -7290,15 +7553,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>160</v>
@@ -7307,15 +7570,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>160</v>
@@ -7324,7 +7587,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>161</v>
@@ -7332,7 +7595,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>163</v>
@@ -7341,15 +7604,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>163</v>
@@ -7358,7 +7621,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>164</v>
@@ -7366,24 +7629,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>168</v>
@@ -7392,15 +7655,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>168</v>
@@ -7409,7 +7672,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>169</v>
@@ -7417,7 +7680,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>171</v>
@@ -7426,7 +7689,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>172</v>
@@ -7434,7 +7697,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>173</v>
@@ -7443,15 +7706,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>173</v>
@@ -7460,7 +7723,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>174</v>
@@ -7468,7 +7731,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>175</v>
@@ -7477,15 +7740,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>175</v>
@@ -7494,7 +7757,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>176</v>
@@ -7502,262 +7765,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>183</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>194</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>196</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>202</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>221</v>
@@ -7766,7 +8029,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>222</v>
@@ -7774,7 +8037,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>223</v>
@@ -7783,15 +8046,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>225</v>
@@ -7800,15 +8063,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>227</v>
@@ -7817,15 +8080,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>228</v>
@@ -7834,15 +8097,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>229</v>
@@ -7851,7 +8114,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>231</v>
@@ -7859,7 +8122,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>233</v>
@@ -7868,49 +8131,49 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>238</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>245</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>247</v>
@@ -7919,15 +8182,15 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>247</v>
@@ -7936,15 +8199,15 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>247</v>
@@ -7953,7 +8216,7 @@
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>248</v>
@@ -7961,7 +8224,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>250</v>
@@ -7970,15 +8233,15 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>250</v>
@@ -7987,7 +8250,7 @@
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>251</v>
@@ -7995,7 +8258,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>253</v>
@@ -8004,15 +8267,15 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>253</v>
@@ -8021,7 +8284,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>254</v>
@@ -8029,7 +8292,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>255</v>
@@ -8038,7 +8301,7 @@
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>256</v>
@@ -8046,7 +8309,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>258</v>
@@ -8055,83 +8318,83 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>263</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>266</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>267</v>
@@ -8140,15 +8403,15 @@
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>269</v>
@@ -8157,15 +8420,15 @@
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>271</v>
@@ -8174,15 +8437,15 @@
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>273</v>
@@ -8191,15 +8454,15 @@
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>276</v>
@@ -8208,15 +8471,15 @@
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>276</v>
@@ -8225,7 +8488,7 @@
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>277</v>
@@ -8233,7 +8496,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>278</v>
@@ -8242,15 +8505,15 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>278</v>
@@ -8259,15 +8522,15 @@
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>278</v>
@@ -8276,7 +8539,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>279</v>
@@ -8284,7 +8547,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>281</v>
@@ -8293,15 +8556,15 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>281</v>
@@ -8310,7 +8573,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>282</v>
@@ -8318,7 +8581,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>281</v>
@@ -8327,7 +8590,7 @@
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>283</v>
@@ -8335,7 +8598,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>285</v>
@@ -8344,15 +8607,15 @@
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>289</v>
@@ -8361,7 +8624,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>290</v>
@@ -8369,7 +8632,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>71</v>
@@ -8378,15 +8641,15 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>292</v>
@@ -8395,228 +8658,228 @@
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>80</v>
@@ -8624,1379 +8887,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10921FBF-DE31-45CF-A1D2-C82AE0D00A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF257E74-150C-47EA-81A9-9E411C44DA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="684">
   <si>
     <t>家里</t>
   </si>
@@ -525,12 +525,6 @@
   </si>
   <si>
     <t>领主卡恩</t>
-  </si>
-  <si>
-    <t>狂暴时伤害持续翻倍；远程投掷固定180伤害；
-飞钩500伤害，命中减速90%并造成流血5*8；
-狂暴恢复400HP；喝酒恢复150HP(不打断可回满血)；
-起跳20伤害附带3.5秒眩晕，并净化玩家身上的增益效果</t>
   </si>
   <si>
     <t>银矿</t>
@@ -2122,6 +2116,20 @@
 2.噩梦之斩：释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕；
 3.低语触碰：低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）；
 不是魔王</t>
+  </si>
+  <si>
+    <t>铁钉盾举盾，概率格挡2次命中；概率回血40；治疗绷带*4；元素伤害减半</t>
+  </si>
+  <si>
+    <t>通攻击：距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
+钩索：出现预警范围，短暂蓄力后若未脱离范围则被勾到卡恩身边并受到500点物理伤害。若被勾路径上有铁蒺藜，则受到额外伤害。
+净化：当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
+饮血：距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
+震地：卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒；是魔王</t>
+  </si>
+  <si>
+    <t>120（近战）
+180（远程）</t>
   </si>
 </sst>
 </file>
@@ -2806,14 +2814,14 @@
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
     <col min="2" max="4" width="16" style="5" customWidth="1"/>
     <col min="5" max="5" width="12" style="5" customWidth="1"/>
-    <col min="6" max="6" width="66.3984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="68.796875" style="5" customWidth="1"/>
     <col min="7" max="7" width="32.06640625" style="5" customWidth="1"/>
     <col min="8" max="16384" width="9.06640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2856,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -2988,7 +2996,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3004,7 +3012,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3200,7 +3208,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3454,10 +3462,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3601,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4113,7 +4121,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="54" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A65" s="16" t="s">
         <v>165</v>
       </c>
@@ -4123,12 +4131,12 @@
       <c r="C65" s="2">
         <v>0</v>
       </c>
-      <c r="D65" s="2">
-        <v>120</v>
+      <c r="D65" s="2" t="s">
+        <v>683</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>166</v>
+        <v>682</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>138</v>
@@ -4136,7 +4144,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>1</v>
@@ -4159,7 +4167,7 @@
     </row>
     <row r="67" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A67" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B67" s="2">
         <v>335</v>
@@ -4172,15 +4180,15 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B68" s="2">
         <v>450</v>
@@ -4193,15 +4201,15 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A69" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B69" s="2">
         <v>550</v>
@@ -4214,15 +4222,15 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B70" s="2">
         <v>1000</v>
@@ -4235,15 +4243,15 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>1</v>
@@ -4266,7 +4274,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B72" s="2">
         <v>60</v>
@@ -4280,12 +4288,12 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B73" s="2">
         <v>70</v>
@@ -4299,12 +4307,12 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B74" s="2">
         <v>30</v>
@@ -4317,15 +4325,15 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>1</v>
@@ -4348,7 +4356,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B76" s="2">
         <v>800</v>
@@ -4357,19 +4365,19 @@
         <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G76" s="13" t="s">
         <v>185</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B77" s="2">
         <v>700</v>
@@ -4381,18 +4389,18 @@
         <v>30</v>
       </c>
       <c r="E77" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="G77" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B78" s="2">
         <v>800</v>
@@ -4401,21 +4409,21 @@
         <v>23</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E78" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="F78" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="G78" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B79" s="2">
         <v>800</v>
@@ -4428,18 +4436,18 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -4449,18 +4457,18 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -4470,18 +4478,18 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C82" s="2">
         <v>24</v>
@@ -4491,60 +4499,60 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="C83" s="2">
         <v>55</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="C84" s="2">
         <v>38</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C85" s="2">
         <v>38</v>
@@ -4554,18 +4562,18 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A86" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C86" s="2">
         <v>60</v>
@@ -4575,15 +4583,15 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -4592,19 +4600,19 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>1</v>
@@ -4627,7 +4635,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B89" s="2">
         <v>25</v>
@@ -4636,19 +4644,19 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B90" s="2">
         <v>400</v>
@@ -4662,12 +4670,12 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -4681,12 +4689,12 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -4700,12 +4708,12 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -4719,12 +4727,12 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B94" s="2">
         <v>200</v>
@@ -4733,19 +4741,19 @@
         <v>0</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G94" s="13" t="s">
         <v>231</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B95" s="2">
         <v>400</v>
@@ -4759,12 +4767,12 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B96" s="2">
         <v>60</v>
@@ -4777,15 +4785,15 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G96" s="13" t="s">
         <v>236</v>
-      </c>
-      <c r="G96" s="13" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B97" s="2">
         <v>2000</v>
@@ -4799,12 +4807,12 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B98" s="2">
         <v>550</v>
@@ -4818,12 +4826,12 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B99" s="2">
         <v>40</v>
@@ -4832,38 +4840,38 @@
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D100" s="2">
         <v>62</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B101" s="2">
         <v>150</v>
@@ -4876,15 +4884,15 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G101" s="13" t="s">
         <v>248</v>
-      </c>
-      <c r="G101" s="13" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B102" s="2">
         <v>110</v>
@@ -4897,15 +4905,15 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G102" s="13" t="s">
         <v>251</v>
-      </c>
-      <c r="G102" s="13" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B103" s="2">
         <v>185</v>
@@ -4918,15 +4926,15 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
@@ -4935,19 +4943,19 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G104" s="13" t="s">
         <v>256</v>
-      </c>
-      <c r="G104" s="13" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B105" s="2">
         <v>300</v>
@@ -4961,18 +4969,18 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B106" s="2">
         <v>500</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D106" s="2">
         <v>36</v>
@@ -4980,15 +4988,15 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -4999,18 +5007,18 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D108" s="2">
         <v>72</v>
@@ -5018,31 +5026,31 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B110" s="2">
         <v>300</v>
@@ -5056,12 +5064,12 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B111" s="2">
         <v>600</v>
@@ -5075,12 +5083,12 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B112" s="2">
         <v>1000</v>
@@ -5094,12 +5102,12 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B113" s="2">
         <v>450</v>
@@ -5108,19 +5116,19 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G113" s="13" t="s">
         <v>274</v>
-      </c>
-      <c r="G113" s="13" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A114" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B114" s="2">
         <v>2500</v>
@@ -5133,15 +5141,15 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B115" s="2">
         <v>9000</v>
@@ -5154,15 +5162,15 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G115" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B116" s="2">
         <v>10500</v>
@@ -5171,19 +5179,19 @@
         <v>0</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G116" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="G116" s="13" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="16" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B117" s="2">
         <v>1700</v>
@@ -5196,15 +5204,15 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G117" s="13" t="s">
         <v>286</v>
-      </c>
-      <c r="G117" s="13" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>1</v>
@@ -5227,7 +5235,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B119" s="2">
         <v>75</v>
@@ -5236,19 +5244,19 @@
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="G119" s="13" t="s">
         <v>660</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B120" s="2">
         <v>45</v>
@@ -5261,15 +5269,15 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B121" s="2">
         <v>100</v>
@@ -5278,19 +5286,19 @@
         <v>0</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B122" s="2">
         <v>150</v>
@@ -5303,15 +5311,15 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B123" s="2">
         <v>300</v>
@@ -5324,15 +5332,15 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B124" s="2">
         <v>150</v>
@@ -5341,19 +5349,19 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B125" s="2">
         <v>200</v>
@@ -5362,19 +5370,19 @@
         <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="14" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B126" s="2">
         <v>215</v>
@@ -5387,15 +5395,15 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B127" s="2">
         <v>200</v>
@@ -5408,15 +5416,15 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A128" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B128" s="2">
         <v>600</v>
@@ -5425,19 +5433,19 @@
         <v>66</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A129" s="15" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B129" s="2">
         <v>2000</v>
@@ -5450,15 +5458,15 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>1</v>
@@ -5481,7 +5489,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B131" s="2">
         <v>50</v>
@@ -5490,14 +5498,14 @@
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G131" s="13" t="s">
         <v>290</v>
-      </c>
-      <c r="G131" s="13" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
@@ -5521,7 +5529,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B133" s="2">
         <v>100</v>
@@ -5529,16 +5537,18 @@
       <c r="C133" s="2">
         <v>0</v>
       </c>
-      <c r="D133" s="2"/>
+      <c r="D133" s="2" t="s">
+        <v>639</v>
+      </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B134" s="2">
         <v>45</v>
@@ -5551,34 +5561,34 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G134" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="G134" s="13" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B135" s="2">
         <v>200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B136" s="2">
         <v>600</v>
@@ -5587,19 +5597,19 @@
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
@@ -5608,19 +5618,19 @@
         <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G137" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="G137" s="13" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B138" s="2">
         <v>1500</v>
@@ -5632,18 +5642,18 @@
         <v>100</v>
       </c>
       <c r="E138" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F138" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="G138" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B139" s="2">
         <v>1000</v>
@@ -5656,15 +5666,15 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G139" s="13" t="s">
         <v>311</v>
-      </c>
-      <c r="G139" s="13" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B140" s="2">
         <v>750</v>
@@ -5680,12 +5690,12 @@
         <v>80</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B141" s="2">
         <v>150</v>
@@ -5698,15 +5708,15 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G141" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="G141" s="13" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B142" s="2">
         <v>720</v>
@@ -5719,15 +5729,15 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G142" s="13" t="s">
         <v>319</v>
-      </c>
-      <c r="G142" s="13" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A143" s="16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B143" s="2">
         <v>2000</v>
@@ -5740,15 +5750,15 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>1</v>
@@ -5771,7 +5781,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B145" s="2">
         <v>400</v>
@@ -5784,15 +5794,15 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B146" s="2">
         <v>80</v>
@@ -5801,19 +5811,19 @@
         <v>0</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B147" s="2">
         <v>70</v>
@@ -5827,12 +5837,12 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B148" s="2">
         <v>180</v>
@@ -5846,12 +5856,12 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B149" s="2">
         <v>40</v>
@@ -5864,15 +5874,15 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G149" s="13" t="s">
         <v>332</v>
-      </c>
-      <c r="G149" s="13" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B150" s="2">
         <v>100</v>
@@ -5881,19 +5891,19 @@
         <v>0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -5916,325 +5926,325 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="C152" s="2">
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G152" s="13" t="s">
         <v>343</v>
-      </c>
-      <c r="G152" s="13" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G153" s="13" t="s">
         <v>337</v>
-      </c>
-      <c r="G153" s="13" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E154" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F154" s="2" t="s">
+      <c r="G154" s="13" t="s">
         <v>350</v>
-      </c>
-      <c r="G154" s="13" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="15" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D155" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="G156" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="G157" s="13" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="15" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="D162" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E163" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E163" s="7" t="s">
+      <c r="F163" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="G163" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="D164" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E164" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E164" s="6" t="s">
+      <c r="F164" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="F164" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="G164" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="C165" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F165" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G165" s="13" t="s">
         <v>337</v>
-      </c>
-      <c r="G165" s="13" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -6257,7 +6267,7 @@
     </row>
     <row r="167" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B167" s="2">
         <v>120</v>
@@ -6266,21 +6276,21 @@
         <v>57</v>
       </c>
       <c r="D167" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E167" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F167" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="G167" s="20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B168" s="2">
         <v>120</v>
@@ -6289,17 +6299,17 @@
         <v>62</v>
       </c>
       <c r="D168" s="2">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G168" s="21"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B169" s="2">
         <v>200</v>
@@ -6312,13 +6322,13 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G169" s="21"/>
     </row>
     <row r="170" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6327,17 +6337,17 @@
         <v>48</v>
       </c>
       <c r="D170" s="2">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G170" s="21"/>
     </row>
     <row r="171" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
@@ -6346,17 +6356,17 @@
         <v>59</v>
       </c>
       <c r="D171" s="2">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G171" s="21"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
@@ -6369,13 +6379,13 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G172" s="21"/>
     </row>
     <row r="173" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
@@ -6388,13 +6398,13 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G173" s="21"/>
     </row>
     <row r="174" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
@@ -6407,13 +6417,13 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="G174" s="21"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A175" s="12" t="s">
         <v>398</v>
-      </c>
-      <c r="G174" s="21"/>
-    </row>
-    <row r="175" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A175" s="12" t="s">
-        <v>399</v>
       </c>
       <c r="B175" s="2">
         <v>200</v>
@@ -6426,13 +6436,13 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>400</v>
+        <v>681</v>
       </c>
       <c r="G175" s="21"/>
     </row>
     <row r="176" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B176" s="2">
         <v>120</v>
@@ -6441,17 +6451,17 @@
         <v>55</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G176" s="21"/>
     </row>
     <row r="177" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B177" s="2">
         <v>200</v>
@@ -6464,13 +6474,13 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G177" s="21"/>
     </row>
     <row r="178" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B178" s="2">
         <v>250</v>
@@ -6483,13 +6493,13 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G178" s="21"/>
     </row>
     <row r="179" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B179" s="2">
         <v>200</v>
@@ -6501,16 +6511,16 @@
         <v>60</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G179" s="21"/>
     </row>
     <row r="180" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A180" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B180" s="2">
         <v>250</v>
@@ -6522,16 +6532,16 @@
         <v>60</v>
       </c>
       <c r="E180" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="G180" s="21"/>
     </row>
     <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B181" s="2">
         <v>500</v>
@@ -6540,17 +6550,17 @@
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G181" s="21"/>
     </row>
     <row r="182" spans="1:7" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B182" s="19">
         <v>500</v>
@@ -6563,7 +6573,7 @@
       </c>
       <c r="E182" s="19"/>
       <c r="F182" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G182" s="22"/>
     </row>
@@ -6592,24 +6602,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -6618,15 +6628,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -6635,32 +6645,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -6669,7 +6679,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -6677,7 +6687,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -6686,15 +6696,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6703,15 +6713,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -6720,7 +6730,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -6728,7 +6738,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -6737,15 +6747,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -6754,7 +6764,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -6762,7 +6772,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -6771,7 +6781,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -6779,7 +6789,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -6788,15 +6798,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>59</v>
@@ -6805,15 +6815,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>59</v>
@@ -6822,7 +6832,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>60</v>
@@ -6830,7 +6840,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -6839,15 +6849,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>65</v>
@@ -6856,15 +6866,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>65</v>
@@ -6873,7 +6883,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>66</v>
@@ -6881,7 +6891,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>71</v>
@@ -6890,15 +6900,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -6907,15 +6917,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -6924,7 +6934,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>77</v>
@@ -6932,7 +6942,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -6941,15 +6951,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -6958,7 +6968,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>80</v>
@@ -6966,7 +6976,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -6975,15 +6985,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -7000,7 +7010,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>89</v>
@@ -7009,15 +7019,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -7026,15 +7036,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>98</v>
@@ -7043,15 +7053,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>103</v>
@@ -7060,15 +7070,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>107</v>
@@ -7077,15 +7087,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>110</v>
@@ -7094,15 +7104,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>110</v>
@@ -7119,7 +7129,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>110</v>
@@ -7128,7 +7138,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>112</v>
@@ -7136,7 +7146,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>113</v>
@@ -7145,15 +7155,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>113</v>
@@ -7162,7 +7172,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>114</v>
@@ -7170,7 +7180,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>116</v>
@@ -7179,15 +7189,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>116</v>
@@ -7196,7 +7206,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>117</v>
@@ -7204,7 +7214,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>118</v>
@@ -7213,15 +7223,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>118</v>
@@ -7230,7 +7240,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>119</v>
@@ -7238,7 +7248,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>120</v>
@@ -7247,15 +7257,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>122</v>
@@ -7264,7 +7274,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>124</v>
@@ -7272,7 +7282,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>122</v>
@@ -7281,7 +7291,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>125</v>
@@ -7289,7 +7299,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>126</v>
@@ -7298,15 +7308,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>126</v>
@@ -7315,7 +7325,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>127</v>
@@ -7323,7 +7333,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>129</v>
@@ -7332,15 +7342,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>129</v>
@@ -7349,15 +7359,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>132</v>
@@ -7366,15 +7376,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>132</v>
@@ -7383,15 +7393,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>135</v>
@@ -7400,15 +7410,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>135</v>
@@ -7417,15 +7427,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>135</v>
@@ -7434,7 +7444,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>136</v>
@@ -7442,7 +7452,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>139</v>
@@ -7451,15 +7461,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>142</v>
@@ -7468,7 +7478,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>143</v>
@@ -7476,7 +7486,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>145</v>
@@ -7493,7 +7503,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>150</v>
@@ -7502,7 +7512,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>151</v>
@@ -7510,7 +7520,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>153</v>
@@ -7519,15 +7529,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>155</v>
@@ -7536,15 +7546,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>157</v>
@@ -7553,15 +7563,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>160</v>
@@ -7570,15 +7580,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>160</v>
@@ -7587,7 +7597,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>161</v>
@@ -7595,7 +7605,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>163</v>
@@ -7604,15 +7614,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>163</v>
@@ -7621,7 +7631,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>164</v>
@@ -7629,1010 +7639,1010 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D70" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D71" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D72" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D73" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D74" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D75" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D76" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D77" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D79" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D80" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D81" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D82" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D83" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D84" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D92" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D105" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>71</v>
@@ -8641,245 +8651,245 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D124" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>80</v>
@@ -8887,1379 +8897,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D144" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D145" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D207" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D214" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF257E74-150C-47EA-81A9-9E411C44DA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF62679-36F3-4AF6-BBB2-3DD536DF0643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="683">
   <si>
     <t>家里</t>
   </si>
@@ -1191,9 +1191,6 @@
   </si>
   <si>
     <t>大车炮台弓箭手</t>
-  </si>
-  <si>
-    <t>30 冰</t>
   </si>
   <si>
     <t>武器：冰弓（冻伤20）；减速；保持距离；概率回血40；治疗绷带*4；元素伤害减半</t>
@@ -2821,7 +2818,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2864,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -2996,7 +2993,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3012,7 +3009,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3208,7 +3205,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3462,10 +3459,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3609,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -3783,7 +3780,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" ht="54" x14ac:dyDescent="0.45">
       <c r="A49" s="15" t="s">
         <v>122</v>
       </c>
@@ -4132,11 +4129,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>138</v>
@@ -4180,7 +4177,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>169</v>
@@ -4201,7 +4198,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>169</v>
@@ -4222,7 +4219,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>169</v>
@@ -4243,7 +4240,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>169</v>
@@ -4465,7 +4462,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>199</v>
@@ -4486,7 +4483,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>202</v>
@@ -4600,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -4644,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -4853,10 +4850,10 @@
         <v>244</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D100" s="2">
         <v>62</v>
@@ -4943,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
@@ -4996,7 +4993,7 @@
         <v>262</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -5015,10 +5012,10 @@
         <v>264</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D108" s="2">
         <v>72</v>
@@ -5034,13 +5031,13 @@
         <v>265</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5116,7 +5113,7 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
@@ -5126,7 +5123,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="54" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A114" s="15" t="s">
         <v>275</v>
       </c>
@@ -5191,7 +5188,7 @@
     </row>
     <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B117" s="2">
         <v>1700</v>
@@ -5212,7 +5209,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>1</v>
@@ -5235,7 +5232,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B119" s="2">
         <v>75</v>
@@ -5244,19 +5241,19 @@
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="G119" s="13" t="s">
         <v>659</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B120" s="2">
         <v>45</v>
@@ -5269,15 +5266,15 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B121" s="2">
         <v>100</v>
@@ -5286,14 +5283,14 @@
         <v>0</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
@@ -5311,10 +5308,10 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
@@ -5332,15 +5329,15 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B124" s="2">
         <v>150</v>
@@ -5349,19 +5346,19 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B125" s="2">
         <v>200</v>
@@ -5370,19 +5367,19 @@
         <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="14" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B126" s="2">
         <v>215</v>
@@ -5395,15 +5392,15 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B127" s="2">
         <v>200</v>
@@ -5416,15 +5413,15 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A128" s="15" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B128" s="2">
         <v>600</v>
@@ -5433,19 +5430,19 @@
         <v>66</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A129" s="15" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B129" s="2">
         <v>2000</v>
@@ -5458,10 +5455,10 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
@@ -5498,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
@@ -5538,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
@@ -5575,10 +5572,10 @@
         <v>200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
@@ -5597,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
@@ -5618,7 +5615,7 @@
         <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
@@ -5811,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
@@ -5891,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
@@ -5935,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
@@ -5950,13 +5947,13 @@
         <v>338</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
@@ -5977,7 +5974,7 @@
         <v>346</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>348</v>
@@ -6000,7 +5997,7 @@
         <v>346</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>348</v>
@@ -6023,7 +6020,7 @@
         <v>346</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>348</v>
@@ -6046,7 +6043,7 @@
         <v>346</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>348</v>
@@ -6060,7 +6057,7 @@
     </row>
     <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="15" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>345</v>
@@ -6069,7 +6066,7 @@
         <v>346</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>348</v>
@@ -6083,7 +6080,7 @@
     </row>
     <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>345</v>
@@ -6092,7 +6089,7 @@
         <v>346</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>348</v>
@@ -6106,7 +6103,7 @@
     </row>
     <row r="160" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>345</v>
@@ -6115,7 +6112,7 @@
         <v>346</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>348</v>
@@ -6129,7 +6126,7 @@
     </row>
     <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>345</v>
@@ -6138,7 +6135,7 @@
         <v>346</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>348</v>
@@ -6152,7 +6149,7 @@
     </row>
     <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>345</v>
@@ -6161,7 +6158,7 @@
         <v>346</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>348</v>
@@ -6184,7 +6181,7 @@
         <v>371</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>372</v>
@@ -6207,7 +6204,7 @@
         <v>376</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>377</v>
@@ -6221,19 +6218,19 @@
     </row>
     <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="C165" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>336</v>
@@ -6279,10 +6276,10 @@
         <v>40</v>
       </c>
       <c r="E167" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="G167" s="20" t="s">
         <v>380</v>
@@ -6290,7 +6287,7 @@
     </row>
     <row r="168" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B168" s="2">
         <v>120</v>
@@ -6303,13 +6300,13 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G168" s="21"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B169" s="2">
         <v>200</v>
@@ -6322,13 +6319,13 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G169" s="21"/>
     </row>
     <row r="170" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6341,13 +6338,13 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G170" s="21"/>
     </row>
     <row r="171" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
@@ -6360,13 +6357,13 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G171" s="21"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
@@ -6379,13 +6376,13 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G172" s="21"/>
     </row>
     <row r="173" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
@@ -6398,13 +6395,13 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G173" s="21"/>
     </row>
     <row r="174" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
@@ -6417,13 +6414,13 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G174" s="21"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B175" s="2">
         <v>200</v>
@@ -6436,13 +6433,13 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G175" s="21"/>
     </row>
     <row r="176" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B176" s="2">
         <v>120</v>
@@ -6451,17 +6448,17 @@
         <v>55</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G176" s="21"/>
     </row>
     <row r="177" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B177" s="2">
         <v>200</v>
@@ -6474,13 +6471,13 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G177" s="21"/>
     </row>
     <row r="178" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B178" s="2">
         <v>250</v>
@@ -6493,13 +6490,13 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G178" s="21"/>
     </row>
     <row r="179" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B179" s="2">
         <v>200</v>
@@ -6514,13 +6511,13 @@
         <v>191</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G179" s="21"/>
     </row>
     <row r="180" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A180" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B180" s="2">
         <v>250</v>
@@ -6532,16 +6529,16 @@
         <v>60</v>
       </c>
       <c r="E180" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="G180" s="21"/>
     </row>
     <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B181" s="2">
         <v>500</v>
@@ -6550,17 +6547,17 @@
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G181" s="21"/>
     </row>
     <row r="182" spans="1:7" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" s="18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B182" s="19">
         <v>500</v>
@@ -6573,7 +6570,7 @@
       </c>
       <c r="E182" s="19"/>
       <c r="F182" s="19" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G182" s="22"/>
     </row>
@@ -6602,24 +6599,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -6628,15 +6625,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -6645,32 +6642,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -6679,7 +6676,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -6687,7 +6684,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -6696,15 +6693,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6713,15 +6710,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -6730,7 +6727,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -6738,7 +6735,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -6747,15 +6744,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -6764,7 +6761,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -6772,7 +6769,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -6781,7 +6778,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -6789,7 +6786,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -6798,15 +6795,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>59</v>
@@ -6815,15 +6812,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>59</v>
@@ -6832,7 +6829,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>60</v>
@@ -6840,7 +6837,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -6849,15 +6846,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>65</v>
@@ -6866,15 +6863,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>65</v>
@@ -6883,7 +6880,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>66</v>
@@ -6891,7 +6888,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>71</v>
@@ -6900,15 +6897,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -6917,15 +6914,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -6934,7 +6931,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>77</v>
@@ -6942,7 +6939,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -6951,15 +6948,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -6968,7 +6965,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>80</v>
@@ -6976,7 +6973,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -6985,15 +6982,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -7010,7 +7007,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>89</v>
@@ -7019,15 +7016,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -7036,15 +7033,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>98</v>
@@ -7053,15 +7050,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>103</v>
@@ -7070,15 +7067,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>107</v>
@@ -7087,15 +7084,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>110</v>
@@ -7104,15 +7101,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>110</v>
@@ -7129,7 +7126,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>110</v>
@@ -7138,7 +7135,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>112</v>
@@ -7146,7 +7143,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>113</v>
@@ -7155,15 +7152,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>113</v>
@@ -7172,7 +7169,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>114</v>
@@ -7180,7 +7177,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>116</v>
@@ -7189,15 +7186,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>116</v>
@@ -7206,7 +7203,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>117</v>
@@ -7214,7 +7211,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>118</v>
@@ -7223,15 +7220,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>118</v>
@@ -7240,7 +7237,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>119</v>
@@ -7248,7 +7245,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>120</v>
@@ -7257,15 +7254,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>122</v>
@@ -7274,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>124</v>
@@ -7282,7 +7279,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>122</v>
@@ -7291,7 +7288,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>125</v>
@@ -7299,7 +7296,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>126</v>
@@ -7308,15 +7305,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>126</v>
@@ -7325,7 +7322,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>127</v>
@@ -7333,7 +7330,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>129</v>
@@ -7342,15 +7339,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>129</v>
@@ -7359,15 +7356,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>132</v>
@@ -7376,15 +7373,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>132</v>
@@ -7393,15 +7390,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>135</v>
@@ -7410,15 +7407,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>135</v>
@@ -7427,15 +7424,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>135</v>
@@ -7444,7 +7441,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>136</v>
@@ -7452,7 +7449,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>139</v>
@@ -7461,15 +7458,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>142</v>
@@ -7478,7 +7475,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>143</v>
@@ -7486,7 +7483,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>145</v>
@@ -7503,7 +7500,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>150</v>
@@ -7512,7 +7509,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>151</v>
@@ -7520,7 +7517,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>153</v>
@@ -7529,15 +7526,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>155</v>
@@ -7546,15 +7543,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>157</v>
@@ -7563,15 +7560,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>160</v>
@@ -7580,15 +7577,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>160</v>
@@ -7597,7 +7594,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>161</v>
@@ -7605,7 +7602,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>163</v>
@@ -7614,15 +7611,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>163</v>
@@ -7631,7 +7628,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>164</v>
@@ -7639,24 +7636,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>167</v>
@@ -7665,15 +7662,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>167</v>
@@ -7682,7 +7679,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>168</v>
@@ -7690,7 +7687,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>170</v>
@@ -7699,7 +7696,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>171</v>
@@ -7707,7 +7704,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>172</v>
@@ -7716,15 +7713,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>172</v>
@@ -7733,7 +7730,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>173</v>
@@ -7741,7 +7738,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>174</v>
@@ -7750,15 +7747,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>174</v>
@@ -7767,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>175</v>
@@ -7775,262 +7772,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>182</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>220</v>
@@ -8039,7 +8036,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>221</v>
@@ -8047,7 +8044,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>222</v>
@@ -8056,15 +8053,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>224</v>
@@ -8073,15 +8070,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>226</v>
@@ -8090,15 +8087,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>227</v>
@@ -8107,15 +8104,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>228</v>
@@ -8124,7 +8121,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>230</v>
@@ -8132,7 +8129,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>232</v>
@@ -8141,49 +8138,49 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>237</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>246</v>
@@ -8192,15 +8189,15 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>246</v>
@@ -8209,15 +8206,15 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>246</v>
@@ -8226,7 +8223,7 @@
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>247</v>
@@ -8234,7 +8231,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>249</v>
@@ -8243,15 +8240,15 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>249</v>
@@ -8260,7 +8257,7 @@
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>250</v>
@@ -8268,7 +8265,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>252</v>
@@ -8277,15 +8274,15 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>252</v>
@@ -8294,7 +8291,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>253</v>
@@ -8302,7 +8299,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>254</v>
@@ -8311,7 +8308,7 @@
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>255</v>
@@ -8319,7 +8316,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>257</v>
@@ -8328,83 +8325,83 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>259</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>264</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>266</v>
@@ -8413,15 +8410,15 @@
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>268</v>
@@ -8430,15 +8427,15 @@
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>270</v>
@@ -8447,15 +8444,15 @@
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>272</v>
@@ -8464,15 +8461,15 @@
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>275</v>
@@ -8481,15 +8478,15 @@
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>275</v>
@@ -8498,7 +8495,7 @@
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>276</v>
@@ -8506,7 +8503,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>277</v>
@@ -8515,15 +8512,15 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>277</v>
@@ -8532,15 +8529,15 @@
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>277</v>
@@ -8549,7 +8546,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>278</v>
@@ -8557,7 +8554,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>280</v>
@@ -8566,15 +8563,15 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>280</v>
@@ -8583,7 +8580,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>281</v>
@@ -8591,7 +8588,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>280</v>
@@ -8600,7 +8597,7 @@
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>282</v>
@@ -8608,7 +8605,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>284</v>
@@ -8617,15 +8614,15 @@
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>288</v>
@@ -8634,7 +8631,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>289</v>
@@ -8642,7 +8639,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>71</v>
@@ -8651,15 +8648,15 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>291</v>
@@ -8668,15 +8665,15 @@
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>292</v>
@@ -8685,7 +8682,7 @@
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>293</v>
@@ -8693,24 +8690,24 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>295</v>
@@ -8719,66 +8716,66 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>300</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>301</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>303</v>
@@ -8787,15 +8784,15 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>306</v>
@@ -8804,15 +8801,15 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>309</v>
@@ -8821,15 +8818,15 @@
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>309</v>
@@ -8838,7 +8835,7 @@
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>310</v>
@@ -8846,7 +8843,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>312</v>
@@ -8855,15 +8852,15 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>312</v>
@@ -8872,15 +8869,15 @@
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>312</v>
@@ -8889,7 +8886,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>80</v>
@@ -8897,7 +8894,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>312</v>
@@ -8914,7 +8911,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>317</v>
@@ -8923,15 +8920,15 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>317</v>
@@ -8940,15 +8937,15 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>317</v>
@@ -8957,7 +8954,7 @@
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>318</v>
@@ -8965,7 +8962,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>317</v>
@@ -8982,7 +8979,7 @@
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>320</v>
@@ -8991,7 +8988,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>321</v>
@@ -8999,7 +8996,7 @@
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>325</v>
@@ -9008,7 +9005,7 @@
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>326</v>
@@ -9016,7 +9013,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>329</v>
@@ -9025,49 +9022,49 @@
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>335</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>340</v>
@@ -9076,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>341</v>
@@ -9084,7 +9081,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>340</v>
@@ -9093,7 +9090,7 @@
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>342</v>
@@ -9101,7 +9098,7 @@
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>344</v>
@@ -9110,7 +9107,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>345</v>
@@ -9118,7 +9115,7 @@
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>344</v>
@@ -9127,7 +9124,7 @@
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>346</v>
@@ -9135,7 +9132,7 @@
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>344</v>
@@ -9144,7 +9141,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>347</v>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>344</v>
@@ -9161,7 +9158,7 @@
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>349</v>
@@ -9169,7 +9166,7 @@
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>351</v>
@@ -9178,7 +9175,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>345</v>
@@ -9186,7 +9183,7 @@
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>351</v>
@@ -9195,7 +9192,7 @@
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>346</v>
@@ -9203,7 +9200,7 @@
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>351</v>
@@ -9212,7 +9209,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>352</v>
@@ -9220,7 +9217,7 @@
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>351</v>
@@ -9229,7 +9226,7 @@
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>353</v>
@@ -9237,7 +9234,7 @@
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>354</v>
@@ -9246,7 +9243,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>345</v>
@@ -9254,7 +9251,7 @@
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>354</v>
@@ -9263,7 +9260,7 @@
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>346</v>
@@ -9271,7 +9268,7 @@
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>354</v>
@@ -9280,7 +9277,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>352</v>
@@ -9288,7 +9285,7 @@
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>354</v>
@@ -9297,7 +9294,7 @@
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>355</v>
@@ -9305,7 +9302,7 @@
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>356</v>
@@ -9314,7 +9311,7 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>345</v>
@@ -9322,7 +9319,7 @@
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>356</v>
@@ -9331,7 +9328,7 @@
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>346</v>
@@ -9339,7 +9336,7 @@
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>356</v>
@@ -9348,7 +9345,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>352</v>
@@ -9356,7 +9353,7 @@
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>356</v>
@@ -9365,7 +9362,7 @@
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>357</v>
@@ -9373,7 +9370,7 @@
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>359</v>
@@ -9382,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>345</v>
@@ -9390,7 +9387,7 @@
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>359</v>
@@ -9399,7 +9396,7 @@
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>346</v>
@@ -9407,7 +9404,7 @@
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>359</v>
@@ -9416,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>352</v>
@@ -9424,7 +9421,7 @@
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>359</v>
@@ -9433,7 +9430,7 @@
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>360</v>
@@ -9441,7 +9438,7 @@
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>361</v>
@@ -9450,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>345</v>
@@ -9458,7 +9455,7 @@
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>361</v>
@@ -9467,7 +9464,7 @@
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>346</v>
@@ -9475,7 +9472,7 @@
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>361</v>
@@ -9484,7 +9481,7 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>352</v>
@@ -9492,7 +9489,7 @@
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>361</v>
@@ -9501,7 +9498,7 @@
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>362</v>
@@ -9509,7 +9506,7 @@
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>363</v>
@@ -9518,7 +9515,7 @@
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>345</v>
@@ -9526,7 +9523,7 @@
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>363</v>
@@ -9535,7 +9532,7 @@
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>346</v>
@@ -9543,7 +9540,7 @@
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>363</v>
@@ -9552,7 +9549,7 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>352</v>
@@ -9560,7 +9557,7 @@
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>363</v>
@@ -9569,7 +9566,7 @@
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>364</v>
@@ -9577,7 +9574,7 @@
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>365</v>
@@ -9586,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>345</v>
@@ -9594,7 +9591,7 @@
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>365</v>
@@ -9603,7 +9600,7 @@
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>346</v>
@@ -9611,7 +9608,7 @@
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>365</v>
@@ -9620,7 +9617,7 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>352</v>
@@ -9628,7 +9625,7 @@
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>365</v>
@@ -9637,7 +9634,7 @@
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>366</v>
@@ -9645,7 +9642,7 @@
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>367</v>
@@ -9654,7 +9651,7 @@
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>345</v>
@@ -9662,7 +9659,7 @@
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>367</v>
@@ -9671,7 +9668,7 @@
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>346</v>
@@ -9679,7 +9676,7 @@
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>367</v>
@@ -9688,7 +9685,7 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>352</v>
@@ -9696,7 +9693,7 @@
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>367</v>
@@ -9705,7 +9702,7 @@
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>368</v>
@@ -9713,7 +9710,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>369</v>
@@ -9722,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>370</v>
@@ -9730,7 +9727,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>369</v>
@@ -9739,7 +9736,7 @@
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>371</v>
@@ -9747,7 +9744,7 @@
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>369</v>
@@ -9756,7 +9753,7 @@
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>373</v>
@@ -9764,7 +9761,7 @@
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>374</v>
@@ -9773,7 +9770,7 @@
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>376</v>
@@ -9781,7 +9778,7 @@
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>374</v>
@@ -9790,7 +9787,7 @@
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>378</v>
@@ -9798,7 +9795,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>381</v>
@@ -9807,15 +9804,15 @@
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>381</v>
@@ -9824,452 +9821,452 @@
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="D207" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="D214" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF62679-36F3-4AF6-BBB2-3DD536DF0643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0C52B9-8098-4CCF-842F-E273E5B68741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="690">
   <si>
     <t>家里</t>
   </si>
@@ -1291,11 +1291,6 @@
     <t>咸味中尉（英雄模式）</t>
   </si>
   <si>
-    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
-复活药1瓶；治疗2*苦药酒；
-可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
@@ -2127,6 +2122,32 @@
   <si>
     <t>120（近战）
 180（远程）</t>
+  </si>
+  <si>
+    <t>15 冰</t>
+  </si>
+  <si>
+    <t>45 火</t>
+  </si>
+  <si>
+    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
+复活药1瓶；治疗2*苦药酒；他的武器可以禁疗；
+可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
+  </si>
+  <si>
+    <t>中尉咸味（英雄模式）</t>
+  </si>
+  <si>
+    <t>中尉咸味（普通模式）</t>
+  </si>
+  <si>
+    <t>领主第三个小弟-吉杜尔</t>
+  </si>
+  <si>
+    <t>领主第二个小弟-郭隆德</t>
+  </si>
+  <si>
+    <t>领主第一个小弟-阿托鲁斯</t>
   </si>
 </sst>
 </file>
@@ -2818,7 +2839,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2861,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -2993,7 +3014,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3009,7 +3030,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3205,7 +3226,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3459,10 +3480,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3606,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -3677,7 +3698,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="14" t="s">
-        <v>110</v>
+        <v>689</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -3698,7 +3719,7 @@
     </row>
     <row r="45" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="14" t="s">
-        <v>113</v>
+        <v>688</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -3719,7 +3740,7 @@
     </row>
     <row r="46" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="14" t="s">
-        <v>116</v>
+        <v>687</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4129,11 +4150,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>138</v>
@@ -4177,7 +4198,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>169</v>
@@ -4198,7 +4219,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>169</v>
@@ -4219,7 +4240,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>169</v>
@@ -4240,7 +4261,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>169</v>
@@ -4462,7 +4483,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>199</v>
@@ -4483,7 +4504,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>202</v>
@@ -4597,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -4641,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -4850,10 +4871,10 @@
         <v>244</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D100" s="2">
         <v>62</v>
@@ -4940,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
@@ -4993,7 +5014,7 @@
         <v>262</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -5012,10 +5033,10 @@
         <v>264</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D108" s="2">
         <v>72</v>
@@ -5031,13 +5052,13 @@
         <v>265</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5113,7 +5134,7 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
@@ -5188,7 +5209,7 @@
     </row>
     <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="16" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B117" s="2">
         <v>1700</v>
@@ -5209,7 +5230,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>1</v>
@@ -5232,7 +5253,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B119" s="2">
         <v>75</v>
@@ -5241,19 +5262,19 @@
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="G119" s="13" t="s">
         <v>658</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B120" s="2">
         <v>45</v>
@@ -5266,15 +5287,15 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B121" s="2">
         <v>100</v>
@@ -5283,14 +5304,14 @@
         <v>0</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
@@ -5308,10 +5329,10 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
@@ -5329,15 +5350,15 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B124" s="2">
         <v>150</v>
@@ -5346,19 +5367,19 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B125" s="2">
         <v>200</v>
@@ -5367,19 +5388,19 @@
         <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="14" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B126" s="2">
         <v>215</v>
@@ -5392,15 +5413,15 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B127" s="2">
         <v>200</v>
@@ -5413,15 +5434,15 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A128" s="15" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B128" s="2">
         <v>600</v>
@@ -5430,19 +5451,19 @@
         <v>66</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A129" s="15" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B129" s="2">
         <v>2000</v>
@@ -5455,10 +5476,10 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
@@ -5495,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
@@ -5535,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
@@ -5572,10 +5593,10 @@
         <v>200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
@@ -5594,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
@@ -5615,7 +5636,7 @@
         <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
@@ -5808,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
@@ -5888,7 +5909,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
@@ -5932,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
@@ -5947,13 +5968,13 @@
         <v>338</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
@@ -5974,7 +5995,7 @@
         <v>346</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>348</v>
@@ -5997,7 +6018,7 @@
         <v>346</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>348</v>
@@ -6020,7 +6041,7 @@
         <v>346</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>348</v>
@@ -6043,7 +6064,7 @@
         <v>346</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>348</v>
@@ -6057,7 +6078,7 @@
     </row>
     <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>345</v>
@@ -6066,7 +6087,7 @@
         <v>346</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>348</v>
@@ -6080,7 +6101,7 @@
     </row>
     <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>345</v>
@@ -6089,7 +6110,7 @@
         <v>346</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>348</v>
@@ -6103,7 +6124,7 @@
     </row>
     <row r="160" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>345</v>
@@ -6112,7 +6133,7 @@
         <v>346</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>348</v>
@@ -6126,7 +6147,7 @@
     </row>
     <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>345</v>
@@ -6135,7 +6156,7 @@
         <v>346</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>348</v>
@@ -6149,7 +6170,7 @@
     </row>
     <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>345</v>
@@ -6158,7 +6179,7 @@
         <v>346</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>348</v>
@@ -6181,7 +6202,7 @@
         <v>371</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>372</v>
@@ -6204,7 +6225,7 @@
         <v>376</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>377</v>
@@ -6218,19 +6239,19 @@
     </row>
     <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="C165" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>336</v>
@@ -6433,7 +6454,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G175" s="21"/>
     </row>
@@ -6448,7 +6469,7 @@
         <v>55</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
@@ -6505,10 +6526,10 @@
         <v>82</v>
       </c>
       <c r="D179" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>191</v>
+        <v>682</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>406</v>
@@ -6538,7 +6559,7 @@
     </row>
     <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="14" t="s">
-        <v>410</v>
+        <v>686</v>
       </c>
       <c r="B181" s="2">
         <v>500</v>
@@ -6547,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
@@ -6555,9 +6576,9 @@
       </c>
       <c r="G181" s="21"/>
     </row>
-    <row r="182" spans="1:7" ht="34.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:7" ht="48.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" s="18" t="s">
-        <v>412</v>
+        <v>685</v>
       </c>
       <c r="B182" s="19">
         <v>500</v>
@@ -6568,9 +6589,11 @@
       <c r="D182" s="19">
         <v>130</v>
       </c>
-      <c r="E182" s="19"/>
+      <c r="E182" s="6" t="s">
+        <v>683</v>
+      </c>
       <c r="F182" s="19" t="s">
-        <v>413</v>
+        <v>684</v>
       </c>
       <c r="G182" s="22"/>
     </row>
@@ -6599,24 +6622,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -6625,15 +6648,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -6642,32 +6665,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -6676,7 +6699,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -6684,7 +6707,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -6693,15 +6716,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6710,15 +6733,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -6727,7 +6750,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -6735,7 +6758,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -6744,15 +6767,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -6761,7 +6784,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -6769,7 +6792,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -6778,7 +6801,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -6786,7 +6809,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -6795,15 +6818,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>59</v>
@@ -6812,15 +6835,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>59</v>
@@ -6829,7 +6852,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>60</v>
@@ -6837,7 +6860,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -6846,15 +6869,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>65</v>
@@ -6863,15 +6886,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>65</v>
@@ -6880,7 +6903,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>66</v>
@@ -6888,7 +6911,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>71</v>
@@ -6897,15 +6920,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -6914,15 +6937,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -6931,7 +6954,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>77</v>
@@ -6939,7 +6962,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -6948,15 +6971,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -6965,7 +6988,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>80</v>
@@ -6973,7 +6996,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -6982,15 +7005,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -7007,7 +7030,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>89</v>
@@ -7016,15 +7039,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -7033,15 +7056,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>98</v>
@@ -7050,15 +7073,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>103</v>
@@ -7067,15 +7090,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>107</v>
@@ -7084,15 +7107,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>110</v>
@@ -7101,15 +7124,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>110</v>
@@ -7126,7 +7149,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>110</v>
@@ -7135,7 +7158,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>112</v>
@@ -7143,7 +7166,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>113</v>
@@ -7152,15 +7175,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>113</v>
@@ -7169,7 +7192,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>114</v>
@@ -7177,7 +7200,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>116</v>
@@ -7186,15 +7209,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>116</v>
@@ -7203,7 +7226,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>117</v>
@@ -7211,7 +7234,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>118</v>
@@ -7220,15 +7243,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>118</v>
@@ -7237,7 +7260,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>119</v>
@@ -7245,7 +7268,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>120</v>
@@ -7254,15 +7277,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>122</v>
@@ -7271,7 +7294,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>124</v>
@@ -7279,7 +7302,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>122</v>
@@ -7288,7 +7311,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>125</v>
@@ -7296,7 +7319,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>126</v>
@@ -7305,15 +7328,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>126</v>
@@ -7322,7 +7345,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>127</v>
@@ -7330,7 +7353,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>129</v>
@@ -7339,15 +7362,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>129</v>
@@ -7356,15 +7379,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>132</v>
@@ -7373,15 +7396,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>132</v>
@@ -7390,15 +7413,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>135</v>
@@ -7407,15 +7430,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>135</v>
@@ -7424,15 +7447,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>135</v>
@@ -7441,7 +7464,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>136</v>
@@ -7449,7 +7472,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>139</v>
@@ -7458,15 +7481,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>142</v>
@@ -7475,7 +7498,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>143</v>
@@ -7483,7 +7506,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>145</v>
@@ -7500,7 +7523,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>150</v>
@@ -7509,7 +7532,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>151</v>
@@ -7517,7 +7540,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>153</v>
@@ -7526,15 +7549,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>155</v>
@@ -7543,15 +7566,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>157</v>
@@ -7560,15 +7583,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>160</v>
@@ -7577,15 +7600,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>160</v>
@@ -7594,7 +7617,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>161</v>
@@ -7602,7 +7625,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>163</v>
@@ -7611,15 +7634,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>163</v>
@@ -7628,7 +7651,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>164</v>
@@ -7636,24 +7659,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>167</v>
@@ -7662,15 +7685,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>167</v>
@@ -7679,7 +7702,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>168</v>
@@ -7687,7 +7710,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>170</v>
@@ -7696,7 +7719,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>171</v>
@@ -7704,7 +7727,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>172</v>
@@ -7713,15 +7736,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>172</v>
@@ -7730,7 +7753,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>173</v>
@@ -7738,7 +7761,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>174</v>
@@ -7747,15 +7770,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>174</v>
@@ -7764,7 +7787,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>175</v>
@@ -7772,262 +7795,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>182</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>220</v>
@@ -8036,7 +8059,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>221</v>
@@ -8044,7 +8067,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>222</v>
@@ -8053,15 +8076,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>224</v>
@@ -8070,15 +8093,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>226</v>
@@ -8087,15 +8110,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>227</v>
@@ -8104,15 +8127,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>228</v>
@@ -8121,7 +8144,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>230</v>
@@ -8129,7 +8152,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>232</v>
@@ -8138,49 +8161,49 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>237</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>246</v>
@@ -8189,15 +8212,15 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>246</v>
@@ -8206,15 +8229,15 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>246</v>
@@ -8223,7 +8246,7 @@
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>247</v>
@@ -8231,7 +8254,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>249</v>
@@ -8240,15 +8263,15 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>249</v>
@@ -8257,7 +8280,7 @@
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>250</v>
@@ -8265,7 +8288,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>252</v>
@@ -8274,15 +8297,15 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>252</v>
@@ -8291,7 +8314,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>253</v>
@@ -8299,7 +8322,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>254</v>
@@ -8308,7 +8331,7 @@
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>255</v>
@@ -8316,7 +8339,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>257</v>
@@ -8325,83 +8348,83 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>259</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>264</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>266</v>
@@ -8410,15 +8433,15 @@
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>268</v>
@@ -8427,15 +8450,15 @@
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>270</v>
@@ -8444,15 +8467,15 @@
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>272</v>
@@ -8461,15 +8484,15 @@
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>275</v>
@@ -8478,15 +8501,15 @@
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>275</v>
@@ -8495,7 +8518,7 @@
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>276</v>
@@ -8503,7 +8526,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>277</v>
@@ -8512,15 +8535,15 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>277</v>
@@ -8529,15 +8552,15 @@
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>277</v>
@@ -8546,7 +8569,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>278</v>
@@ -8554,7 +8577,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>280</v>
@@ -8563,15 +8586,15 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>280</v>
@@ -8580,7 +8603,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>281</v>
@@ -8588,7 +8611,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>280</v>
@@ -8597,7 +8620,7 @@
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>282</v>
@@ -8605,7 +8628,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>284</v>
@@ -8614,15 +8637,15 @@
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>288</v>
@@ -8631,7 +8654,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>289</v>
@@ -8639,7 +8662,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>71</v>
@@ -8648,15 +8671,15 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>291</v>
@@ -8665,15 +8688,15 @@
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>292</v>
@@ -8682,7 +8705,7 @@
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>293</v>
@@ -8690,24 +8713,24 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>295</v>
@@ -8716,66 +8739,66 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>300</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>301</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>303</v>
@@ -8784,15 +8807,15 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>306</v>
@@ -8801,15 +8824,15 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>309</v>
@@ -8818,15 +8841,15 @@
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>309</v>
@@ -8835,7 +8858,7 @@
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>310</v>
@@ -8843,7 +8866,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>312</v>
@@ -8852,15 +8875,15 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>312</v>
@@ -8869,15 +8892,15 @@
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>312</v>
@@ -8886,7 +8909,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>80</v>
@@ -8894,7 +8917,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>312</v>
@@ -8911,7 +8934,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>317</v>
@@ -8920,15 +8943,15 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>317</v>
@@ -8937,15 +8960,15 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>317</v>
@@ -8954,7 +8977,7 @@
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>318</v>
@@ -8962,7 +8985,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>317</v>
@@ -8979,7 +9002,7 @@
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>320</v>
@@ -8988,7 +9011,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>321</v>
@@ -8996,7 +9019,7 @@
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>325</v>
@@ -9005,7 +9028,7 @@
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>326</v>
@@ -9013,7 +9036,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>329</v>
@@ -9022,49 +9045,49 @@
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>335</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>340</v>
@@ -9073,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>341</v>
@@ -9081,7 +9104,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>340</v>
@@ -9090,7 +9113,7 @@
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>342</v>
@@ -9098,7 +9121,7 @@
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>344</v>
@@ -9107,7 +9130,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>345</v>
@@ -9115,7 +9138,7 @@
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>344</v>
@@ -9124,7 +9147,7 @@
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>346</v>
@@ -9132,7 +9155,7 @@
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>344</v>
@@ -9141,7 +9164,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>347</v>
@@ -9149,7 +9172,7 @@
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>344</v>
@@ -9158,7 +9181,7 @@
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>349</v>
@@ -9166,7 +9189,7 @@
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>351</v>
@@ -9175,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>345</v>
@@ -9183,7 +9206,7 @@
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>351</v>
@@ -9192,7 +9215,7 @@
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>346</v>
@@ -9200,7 +9223,7 @@
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>351</v>
@@ -9209,7 +9232,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>352</v>
@@ -9217,7 +9240,7 @@
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>351</v>
@@ -9226,7 +9249,7 @@
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>353</v>
@@ -9234,7 +9257,7 @@
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>354</v>
@@ -9243,7 +9266,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>345</v>
@@ -9251,7 +9274,7 @@
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>354</v>
@@ -9260,7 +9283,7 @@
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>346</v>
@@ -9268,7 +9291,7 @@
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>354</v>
@@ -9277,7 +9300,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>352</v>
@@ -9285,7 +9308,7 @@
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>354</v>
@@ -9294,7 +9317,7 @@
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>355</v>
@@ -9302,7 +9325,7 @@
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>356</v>
@@ -9311,7 +9334,7 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>345</v>
@@ -9319,7 +9342,7 @@
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>356</v>
@@ -9328,7 +9351,7 @@
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>346</v>
@@ -9336,7 +9359,7 @@
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>356</v>
@@ -9345,7 +9368,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>352</v>
@@ -9353,7 +9376,7 @@
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>356</v>
@@ -9362,7 +9385,7 @@
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>357</v>
@@ -9370,7 +9393,7 @@
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>359</v>
@@ -9379,7 +9402,7 @@
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>345</v>
@@ -9387,7 +9410,7 @@
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>359</v>
@@ -9396,7 +9419,7 @@
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>346</v>
@@ -9404,7 +9427,7 @@
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>359</v>
@@ -9413,7 +9436,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>352</v>
@@ -9421,7 +9444,7 @@
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>359</v>
@@ -9430,7 +9453,7 @@
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>360</v>
@@ -9438,7 +9461,7 @@
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>361</v>
@@ -9447,7 +9470,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>345</v>
@@ -9455,7 +9478,7 @@
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>361</v>
@@ -9464,7 +9487,7 @@
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>346</v>
@@ -9472,7 +9495,7 @@
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>361</v>
@@ -9481,7 +9504,7 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>352</v>
@@ -9489,7 +9512,7 @@
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>361</v>
@@ -9498,7 +9521,7 @@
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>362</v>
@@ -9506,7 +9529,7 @@
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>363</v>
@@ -9515,7 +9538,7 @@
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>345</v>
@@ -9523,7 +9546,7 @@
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>363</v>
@@ -9532,7 +9555,7 @@
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>346</v>
@@ -9540,7 +9563,7 @@
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>363</v>
@@ -9549,7 +9572,7 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>352</v>
@@ -9557,7 +9580,7 @@
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>363</v>
@@ -9566,7 +9589,7 @@
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>364</v>
@@ -9574,7 +9597,7 @@
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>365</v>
@@ -9583,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>345</v>
@@ -9591,7 +9614,7 @@
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>365</v>
@@ -9600,7 +9623,7 @@
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>346</v>
@@ -9608,7 +9631,7 @@
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>365</v>
@@ -9617,7 +9640,7 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>352</v>
@@ -9625,7 +9648,7 @@
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>365</v>
@@ -9634,7 +9657,7 @@
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>366</v>
@@ -9642,7 +9665,7 @@
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>367</v>
@@ -9651,7 +9674,7 @@
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>345</v>
@@ -9659,7 +9682,7 @@
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>367</v>
@@ -9668,7 +9691,7 @@
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>346</v>
@@ -9676,7 +9699,7 @@
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>367</v>
@@ -9685,7 +9708,7 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>352</v>
@@ -9693,7 +9716,7 @@
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>367</v>
@@ -9702,7 +9725,7 @@
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>368</v>
@@ -9710,7 +9733,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>369</v>
@@ -9719,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>370</v>
@@ -9727,7 +9750,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>369</v>
@@ -9736,7 +9759,7 @@
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>371</v>
@@ -9744,7 +9767,7 @@
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>369</v>
@@ -9753,7 +9776,7 @@
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>373</v>
@@ -9761,7 +9784,7 @@
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>374</v>
@@ -9770,7 +9793,7 @@
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>376</v>
@@ -9778,7 +9801,7 @@
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>374</v>
@@ -9787,7 +9810,7 @@
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>378</v>
@@ -9795,7 +9818,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>381</v>
@@ -9804,15 +9827,15 @@
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>381</v>
@@ -9821,7 +9844,7 @@
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>382</v>
@@ -9829,7 +9852,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>383</v>
@@ -9838,15 +9861,15 @@
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>383</v>
@@ -9855,7 +9878,7 @@
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>384</v>
@@ -9863,7 +9886,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>385</v>
@@ -9872,15 +9895,15 @@
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>385</v>
@@ -9889,7 +9912,7 @@
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>386</v>
@@ -9897,7 +9920,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>387</v>
@@ -9906,15 +9929,15 @@
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>387</v>
@@ -9923,7 +9946,7 @@
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>388</v>
@@ -9931,7 +9954,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>389</v>
@@ -9940,15 +9963,15 @@
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>389</v>
@@ -9957,7 +9980,7 @@
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>390</v>
@@ -9965,7 +9988,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>391</v>
@@ -9974,15 +9997,15 @@
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>391</v>
@@ -9991,7 +10014,7 @@
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>392</v>
@@ -9999,7 +10022,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>393</v>
@@ -10008,15 +10031,15 @@
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>393</v>
@@ -10025,7 +10048,7 @@
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>394</v>
@@ -10033,7 +10056,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>395</v>
@@ -10042,15 +10065,15 @@
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>395</v>
@@ -10059,7 +10082,7 @@
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>396</v>
@@ -10067,7 +10090,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>397</v>
@@ -10076,15 +10099,15 @@
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>397</v>
@@ -10093,7 +10116,7 @@
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>398</v>
@@ -10101,24 +10124,24 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>399</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>401</v>
@@ -10127,15 +10150,15 @@
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>401</v>
@@ -10144,7 +10167,7 @@
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>402</v>
@@ -10152,7 +10175,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>403</v>
@@ -10161,15 +10184,15 @@
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>403</v>
@@ -10178,7 +10201,7 @@
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>404</v>
@@ -10186,7 +10209,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>405</v>
@@ -10195,15 +10218,15 @@
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>405</v>
@@ -10212,7 +10235,7 @@
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>406</v>
@@ -10220,24 +10243,24 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>410</v>
@@ -10246,7 +10269,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>411</v>
@@ -10254,19 +10277,19 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>412</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0C52B9-8098-4CCF-842F-E273E5B68741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F13AFF0-9FE8-423C-80F4-ABD283FE88BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2113,41 +2113,41 @@
     <t>铁钉盾举盾，概率格挡2次命中；概率回血40；治疗绷带*4；元素伤害减半</t>
   </si>
   <si>
-    <t>通攻击：距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
+    <t>120（近战）
+180（远程）</t>
+  </si>
+  <si>
+    <t>15 冰</t>
+  </si>
+  <si>
+    <t>45 火</t>
+  </si>
+  <si>
+    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
+复活药1瓶；治疗2*苦药酒；他的武器可以禁疗；
+可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
+  </si>
+  <si>
+    <t>中尉咸味（英雄模式）</t>
+  </si>
+  <si>
+    <t>中尉咸味（普通模式）</t>
+  </si>
+  <si>
+    <t>领主第三个小弟-吉杜尔</t>
+  </si>
+  <si>
+    <t>领主第二个小弟-郭隆德</t>
+  </si>
+  <si>
+    <t>领主第一个小弟-阿托鲁斯</t>
+  </si>
+  <si>
+    <t>普通攻击：距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
 钩索：出现预警范围，短暂蓄力后若未脱离范围则被勾到卡恩身边并受到500点物理伤害。若被勾路径上有铁蒺藜，则受到额外伤害。
 净化：当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
 饮血：距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
 震地：卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒；是魔王</t>
-  </si>
-  <si>
-    <t>120（近战）
-180（远程）</t>
-  </si>
-  <si>
-    <t>15 冰</t>
-  </si>
-  <si>
-    <t>45 火</t>
-  </si>
-  <si>
-    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
-复活药1瓶；治疗2*苦药酒；他的武器可以禁疗；
-可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
-  </si>
-  <si>
-    <t>中尉咸味（英雄模式）</t>
-  </si>
-  <si>
-    <t>中尉咸味（普通模式）</t>
-  </si>
-  <si>
-    <t>领主第三个小弟-吉杜尔</t>
-  </si>
-  <si>
-    <t>领主第二个小弟-郭隆德</t>
-  </si>
-  <si>
-    <t>领主第一个小弟-阿托鲁斯</t>
   </si>
 </sst>
 </file>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="14" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="45" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="46" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4150,11 +4150,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>138</v>
@@ -6529,7 +6529,7 @@
         <v>64</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>406</v>
@@ -6559,7 +6559,7 @@
     </row>
     <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B181" s="2">
         <v>500</v>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="182" spans="1:7" ht="48.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" s="18" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B182" s="19">
         <v>500</v>
@@ -6590,10 +6590,10 @@
         <v>130</v>
       </c>
       <c r="E182" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="F182" s="19" t="s">
         <v>683</v>
-      </c>
-      <c r="F182" s="19" t="s">
-        <v>684</v>
       </c>
       <c r="G182" s="22"/>
     </row>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F13AFF0-9FE8-423C-80F4-ABD283FE88BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F708CA-2056-4692-9FEF-59A1B08A69B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="701">
   <si>
     <t>家里</t>
   </si>
@@ -1184,12 +1184,6 @@
     <t>大车炮台</t>
   </si>
   <si>
-    <t>【场地机制】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
-【英雄模式增益】玩家生命值增加40点；帐篷敌人不致命；敌人更容易受到火焰/冰冻/衰败伤害。
-【英雄模式玩家负面】无法使用食物、卷轴、狼和猫、任何药水（含投掷型）；回复能力降低3倍；生命值减少40点；防御力降低25%。
-【英雄模式敌方强化】敌人生命值和回复能力增强；免疫冰冻、眩晕和恐惧；移动速度提高40%；视野范围增加30%；20%概率使用复活药（两条命）；造成的伤害增加20%。</t>
-  </si>
-  <si>
     <t>大车炮台弓箭手</t>
   </si>
   <si>
@@ -1276,10 +1270,6 @@
   </si>
   <si>
     <t>40 雷</t>
-  </si>
-  <si>
-    <t>装备：鸳鸯钺，雷霆套装（造成40点伤害）；
-复活药1瓶；治疗2*苦药酒；无名教派异界之力可以免疫闪电并回血；元素伤害减半</t>
   </si>
   <si>
     <t>中尉咸味---裸体中尉</t>
@@ -2110,9 +2100,6 @@
 不是魔王</t>
   </si>
   <si>
-    <t>铁钉盾举盾，概率格挡2次命中；概率回血40；治疗绷带*4；元素伤害减半</t>
-  </si>
-  <si>
     <t>120（近战）
 180（远程）</t>
   </si>
@@ -2121,11 +2108,6 @@
   </si>
   <si>
     <t>45 火</t>
-  </si>
-  <si>
-    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
-复活药1瓶；治疗2*苦药酒；他的武器可以禁疗；
-可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
   </si>
   <si>
     <t>中尉咸味（英雄模式）</t>
@@ -2149,12 +2131,70 @@
 饮血：距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
 震地：卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒；是魔王</t>
   </si>
+  <si>
+    <t>武器：冰弓（冻伤20）；减速；保持距离；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>武器：渡鸦弩；远程高伤害，最低45；保持距离；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>武器：磨5长剑；概率回血40；治疗绷带*4；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>武器：萨姆风刃；攻速和跑步速度提高；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>武器：尖刺三叉戟；概率流血5*4次；概率中毒12*5次；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>概率瞬杀；夜晚攻速增加20%；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>概率破甲并造成双倍伤害（破甲秒杀200伤害）；不受陷阱伤害；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>嗜血；咒术套装；造成流血4*5次；恐惧无效；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>铁钉盾举盾，概率格挡2次命中；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
+  </si>
+  <si>
+    <t>装备：粉碎者，圣殿盾牌，圣殿骑士盔甲；概率眩晕；
+复活药剂1瓶（复活1次）；元素伤害减半；受伤后回血,单次上限100(超出部分每5秒补一次),累计400</t>
+  </si>
+  <si>
+    <t>装备：罪恶凝视之刃，罪恶骑士套装；概率恐惧；概率造成50纯伤害；
+复活药1瓶（复活一次）；元素伤害减半；受伤后回血,单次上限100(超出部分每5秒补一次),累计400</t>
+  </si>
+  <si>
+    <t>装备：冰斧，冰盾，雪地猎人套装；
+概率冻结；概率格挡伤害2秒；减慢攻速和移动速度；
+复活药1瓶（复活一次）；元素伤害减半；受伤后回血,单次上限100(超出部分每5秒补一次),累计400</t>
+  </si>
+  <si>
+    <t>装备：鸳鸯钺，雷霆套装（造成40点伤害）；
+复活药1瓶；无名教派异界之力可以免疫闪电并回血；元素伤害减半
+受伤后回血,单次上限100(超出部分每5秒补一次),累计400</t>
+  </si>
+  <si>
+    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
+复活药1瓶；他的武器可以禁疗；受伤后回血,单次上限100(超出部分每5秒补一次),累计400
+可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
+  </si>
+  <si>
+    <t>【场地机制】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
+【英雄模式增益】玩家生命值增加40点；帐篷敌人不致命；敌人更容易受到火焰/冰冻/衰败伤害。
+【英雄模式玩家负面】无法使用食物、卷轴、狼和猫、任何药水（含投掷型）；回复能力降低3倍；生命值减少40点；防御力降低25%。
+【英雄模式敌方强化】敌人生命值和回复能力增强；免疫冰冻、眩晕和恐惧；移动速度提高40%；视野范围增加30%；20%概率使用复活药（两条命）；造成的伤害增加20%。
+【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
+【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2183,11 +2223,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2458,7 +2493,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2479,25 +2514,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2513,6 +2545,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2838,15 +2873,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="25"/>
+      <c r="A1" s="22" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -2882,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -3014,7 +3049,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3030,7 +3065,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3226,7 +3261,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3480,10 +3515,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3627,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -3698,7 +3733,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="14" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -3719,7 +3754,7 @@
     </row>
     <row r="45" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="14" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -3740,7 +3775,7 @@
     </row>
     <row r="46" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="14" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4150,11 +4185,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>138</v>
@@ -4198,7 +4233,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>169</v>
@@ -4219,7 +4254,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>169</v>
@@ -4240,7 +4275,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>169</v>
@@ -4261,7 +4296,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>169</v>
@@ -4483,7 +4518,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>199</v>
@@ -4504,7 +4539,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>202</v>
@@ -4618,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -4662,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -4871,10 +4906,10 @@
         <v>244</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D100" s="2">
         <v>62</v>
@@ -4961,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
@@ -5014,7 +5049,7 @@
         <v>262</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -5033,10 +5068,10 @@
         <v>264</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D108" s="2">
         <v>72</v>
@@ -5052,13 +5087,13 @@
         <v>265</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5134,7 +5169,7 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
@@ -5209,7 +5244,7 @@
     </row>
     <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B117" s="2">
         <v>1700</v>
@@ -5230,7 +5265,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>1</v>
@@ -5253,7 +5288,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B119" s="2">
         <v>75</v>
@@ -5262,19 +5297,19 @@
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B120" s="2">
         <v>45</v>
@@ -5287,15 +5322,15 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B121" s="2">
         <v>100</v>
@@ -5304,14 +5339,14 @@
         <v>0</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
@@ -5329,10 +5364,10 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
@@ -5350,15 +5385,15 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B124" s="2">
         <v>150</v>
@@ -5367,19 +5402,19 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B125" s="2">
         <v>200</v>
@@ -5388,19 +5423,19 @@
         <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="14" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B126" s="2">
         <v>215</v>
@@ -5413,15 +5448,15 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B127" s="2">
         <v>200</v>
@@ -5434,15 +5469,15 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A128" s="15" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B128" s="2">
         <v>600</v>
@@ -5451,19 +5486,19 @@
         <v>66</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A129" s="15" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B129" s="2">
         <v>2000</v>
@@ -5476,10 +5511,10 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
@@ -5516,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
@@ -5556,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
@@ -5593,10 +5628,10 @@
         <v>200</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
@@ -5615,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
@@ -5636,7 +5671,7 @@
         <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
@@ -5829,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
@@ -5909,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
@@ -5953,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
@@ -5968,13 +6003,13 @@
         <v>338</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
@@ -5995,7 +6030,7 @@
         <v>346</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>348</v>
@@ -6018,7 +6053,7 @@
         <v>346</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>348</v>
@@ -6041,7 +6076,7 @@
         <v>346</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>348</v>
@@ -6064,7 +6099,7 @@
         <v>346</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>348</v>
@@ -6078,7 +6113,7 @@
     </row>
     <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="15" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>345</v>
@@ -6087,7 +6122,7 @@
         <v>346</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>348</v>
@@ -6101,7 +6136,7 @@
     </row>
     <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="15" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>345</v>
@@ -6110,7 +6145,7 @@
         <v>346</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>348</v>
@@ -6124,7 +6159,7 @@
     </row>
     <row r="160" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="15" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>345</v>
@@ -6133,7 +6168,7 @@
         <v>346</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>348</v>
@@ -6147,7 +6182,7 @@
     </row>
     <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>345</v>
@@ -6156,7 +6191,7 @@
         <v>346</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>348</v>
@@ -6170,7 +6205,7 @@
     </row>
     <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="15" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>345</v>
@@ -6179,7 +6214,7 @@
         <v>346</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>348</v>
@@ -6202,7 +6237,7 @@
         <v>371</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>372</v>
@@ -6225,7 +6260,7 @@
         <v>376</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>377</v>
@@ -6239,19 +6274,19 @@
     </row>
     <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="16" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>336</v>
@@ -6285,7 +6320,7 @@
     </row>
     <row r="167" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B167" s="2">
         <v>120</v>
@@ -6300,15 +6335,15 @@
         <v>191</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G167" s="20" t="s">
-        <v>380</v>
+        <v>686</v>
+      </c>
+      <c r="G167" s="25" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B168" s="2">
         <v>120</v>
@@ -6321,13 +6356,13 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="G168" s="20"/>
+    </row>
+    <row r="169" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A169" s="12" t="s">
         <v>384</v>
-      </c>
-      <c r="G168" s="21"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A169" s="12" t="s">
-        <v>385</v>
       </c>
       <c r="B169" s="2">
         <v>200</v>
@@ -6340,13 +6375,13 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G169" s="21"/>
+        <v>688</v>
+      </c>
+      <c r="G169" s="20"/>
     </row>
     <row r="170" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6359,13 +6394,13 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G170" s="21"/>
+        <v>689</v>
+      </c>
+      <c r="G170" s="20"/>
     </row>
     <row r="171" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
@@ -6378,13 +6413,13 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="G171" s="20"/>
+    </row>
+    <row r="172" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A172" s="12" t="s">
         <v>390</v>
-      </c>
-      <c r="G171" s="21"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A172" s="12" t="s">
-        <v>391</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
@@ -6397,13 +6432,13 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="G172" s="21"/>
+        <v>691</v>
+      </c>
+      <c r="G172" s="20"/>
     </row>
     <row r="173" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
@@ -6416,13 +6451,13 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G173" s="21"/>
+        <v>692</v>
+      </c>
+      <c r="G173" s="20"/>
     </row>
     <row r="174" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
@@ -6435,13 +6470,13 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="G174" s="20"/>
+    </row>
+    <row r="175" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="A175" s="12" t="s">
         <v>396</v>
-      </c>
-      <c r="G174" s="21"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A175" s="12" t="s">
-        <v>397</v>
       </c>
       <c r="B175" s="2">
         <v>200</v>
@@ -6454,13 +6489,13 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="G175" s="21"/>
+        <v>694</v>
+      </c>
+      <c r="G175" s="20"/>
     </row>
     <row r="176" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B176" s="2">
         <v>120</v>
@@ -6469,17 +6504,17 @@
         <v>55</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G176" s="20"/>
+    </row>
+    <row r="177" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A177" s="14" t="s">
         <v>400</v>
-      </c>
-      <c r="G176" s="21"/>
-    </row>
-    <row r="177" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A177" s="14" t="s">
-        <v>401</v>
       </c>
       <c r="B177" s="2">
         <v>200</v>
@@ -6492,13 +6527,13 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="G177" s="20"/>
+    </row>
+    <row r="178" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A178" s="14" t="s">
         <v>402</v>
-      </c>
-      <c r="G177" s="21"/>
-    </row>
-    <row r="178" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A178" s="14" t="s">
-        <v>403</v>
       </c>
       <c r="B178" s="2">
         <v>250</v>
@@ -6511,13 +6546,13 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="G178" s="20"/>
+    </row>
+    <row r="179" spans="1:7" ht="54" x14ac:dyDescent="0.45">
+      <c r="A179" s="14" t="s">
         <v>404</v>
-      </c>
-      <c r="G178" s="21"/>
-    </row>
-    <row r="179" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A179" s="14" t="s">
-        <v>405</v>
       </c>
       <c r="B179" s="2">
         <v>200</v>
@@ -6529,16 +6564,16 @@
         <v>64</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G179" s="21"/>
+        <v>697</v>
+      </c>
+      <c r="G179" s="20"/>
     </row>
     <row r="180" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A180" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B180" s="2">
         <v>250</v>
@@ -6550,16 +6585,16 @@
         <v>60</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="G180" s="21"/>
+        <v>698</v>
+      </c>
+      <c r="G180" s="20"/>
     </row>
     <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="14" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B181" s="2">
         <v>500</v>
@@ -6568,17 +6603,17 @@
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="G181" s="21"/>
-    </row>
-    <row r="182" spans="1:7" ht="48.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>409</v>
+      </c>
+      <c r="G181" s="20"/>
+    </row>
+    <row r="182" spans="1:7" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" s="18" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B182" s="19">
         <v>500</v>
@@ -6590,12 +6625,12 @@
         <v>130</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F182" s="19" t="s">
-        <v>683</v>
-      </c>
-      <c r="G182" s="22"/>
+        <v>699</v>
+      </c>
+      <c r="G182" s="21"/>
     </row>
     <row r="186" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
@@ -6603,7 +6638,7 @@
     <mergeCell ref="G167:G182"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6622,24 +6657,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -6648,15 +6683,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -6665,32 +6700,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -6699,7 +6734,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -6707,7 +6742,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -6716,15 +6751,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -6733,15 +6768,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -6750,7 +6785,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -6758,7 +6793,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -6767,15 +6802,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -6784,7 +6819,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -6792,7 +6827,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -6801,7 +6836,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -6809,7 +6844,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -6818,15 +6853,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>59</v>
@@ -6835,15 +6870,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>59</v>
@@ -6852,7 +6887,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>60</v>
@@ -6860,7 +6895,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>62</v>
@@ -6869,15 +6904,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>65</v>
@@ -6886,15 +6921,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>65</v>
@@ -6903,7 +6938,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>66</v>
@@ -6911,7 +6946,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>71</v>
@@ -6920,15 +6955,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
@@ -6937,15 +6972,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -6954,7 +6989,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>77</v>
@@ -6962,7 +6997,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -6971,15 +7006,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -6988,7 +7023,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>80</v>
@@ -6996,7 +7031,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>82</v>
@@ -7005,15 +7040,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>82</v>
@@ -7030,7 +7065,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>89</v>
@@ -7039,15 +7074,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>93</v>
@@ -7056,15 +7091,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>98</v>
@@ -7073,15 +7108,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>103</v>
@@ -7090,15 +7125,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>107</v>
@@ -7107,15 +7142,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>110</v>
@@ -7124,15 +7159,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>110</v>
@@ -7149,7 +7184,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>110</v>
@@ -7158,7 +7193,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>112</v>
@@ -7166,7 +7201,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>113</v>
@@ -7175,15 +7210,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>113</v>
@@ -7192,7 +7227,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>114</v>
@@ -7200,7 +7235,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>116</v>
@@ -7209,15 +7244,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>116</v>
@@ -7226,7 +7261,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>117</v>
@@ -7234,7 +7269,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>118</v>
@@ -7243,15 +7278,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>118</v>
@@ -7260,7 +7295,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>119</v>
@@ -7268,7 +7303,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>120</v>
@@ -7277,15 +7312,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>122</v>
@@ -7294,7 +7329,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>124</v>
@@ -7302,7 +7337,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>122</v>
@@ -7311,7 +7346,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>125</v>
@@ -7319,7 +7354,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>126</v>
@@ -7328,15 +7363,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>126</v>
@@ -7345,7 +7380,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>127</v>
@@ -7353,7 +7388,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>129</v>
@@ -7362,15 +7397,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>129</v>
@@ -7379,15 +7414,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>132</v>
@@ -7396,15 +7431,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>132</v>
@@ -7413,15 +7448,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>135</v>
@@ -7430,15 +7465,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>135</v>
@@ -7447,15 +7482,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>135</v>
@@ -7464,7 +7499,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>136</v>
@@ -7472,7 +7507,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>139</v>
@@ -7481,15 +7516,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>142</v>
@@ -7498,7 +7533,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>143</v>
@@ -7506,7 +7541,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>145</v>
@@ -7523,7 +7558,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>150</v>
@@ -7532,7 +7567,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>151</v>
@@ -7540,7 +7575,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>153</v>
@@ -7549,15 +7584,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>155</v>
@@ -7566,15 +7601,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>157</v>
@@ -7583,15 +7618,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>160</v>
@@ -7600,15 +7635,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>160</v>
@@ -7617,7 +7652,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>161</v>
@@ -7625,7 +7660,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>163</v>
@@ -7634,15 +7669,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>163</v>
@@ -7651,7 +7686,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>164</v>
@@ -7659,24 +7694,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>167</v>
@@ -7685,15 +7720,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>167</v>
@@ -7702,7 +7737,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>168</v>
@@ -7710,7 +7745,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>170</v>
@@ -7719,7 +7754,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>171</v>
@@ -7727,7 +7762,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>172</v>
@@ -7736,15 +7771,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>172</v>
@@ -7753,7 +7788,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>173</v>
@@ -7761,7 +7796,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>174</v>
@@ -7770,15 +7805,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>174</v>
@@ -7787,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>175</v>
@@ -7795,262 +7830,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>182</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>220</v>
@@ -8059,7 +8094,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>221</v>
@@ -8067,7 +8102,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>222</v>
@@ -8076,15 +8111,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>224</v>
@@ -8093,15 +8128,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>226</v>
@@ -8110,15 +8145,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>227</v>
@@ -8127,15 +8162,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>228</v>
@@ -8144,7 +8179,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>230</v>
@@ -8152,7 +8187,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>232</v>
@@ -8161,49 +8196,49 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>237</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>246</v>
@@ -8212,15 +8247,15 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>246</v>
@@ -8229,15 +8264,15 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>246</v>
@@ -8246,7 +8281,7 @@
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>247</v>
@@ -8254,7 +8289,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>249</v>
@@ -8263,15 +8298,15 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>249</v>
@@ -8280,7 +8315,7 @@
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>250</v>
@@ -8288,7 +8323,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>252</v>
@@ -8297,15 +8332,15 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>252</v>
@@ -8314,7 +8349,7 @@
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>253</v>
@@ -8322,7 +8357,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>254</v>
@@ -8331,7 +8366,7 @@
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>255</v>
@@ -8339,7 +8374,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>257</v>
@@ -8348,83 +8383,83 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>259</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>264</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>265</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>266</v>
@@ -8433,15 +8468,15 @@
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>268</v>
@@ -8450,15 +8485,15 @@
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>270</v>
@@ -8467,15 +8502,15 @@
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>272</v>
@@ -8484,15 +8519,15 @@
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>275</v>
@@ -8501,15 +8536,15 @@
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>275</v>
@@ -8518,7 +8553,7 @@
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>276</v>
@@ -8526,7 +8561,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>277</v>
@@ -8535,15 +8570,15 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>277</v>
@@ -8552,15 +8587,15 @@
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>277</v>
@@ -8569,7 +8604,7 @@
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>278</v>
@@ -8577,7 +8612,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>280</v>
@@ -8586,15 +8621,15 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>280</v>
@@ -8603,7 +8638,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>281</v>
@@ -8611,7 +8646,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>280</v>
@@ -8620,7 +8655,7 @@
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>282</v>
@@ -8628,7 +8663,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>284</v>
@@ -8637,15 +8672,15 @@
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>288</v>
@@ -8654,7 +8689,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>289</v>
@@ -8662,7 +8697,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>71</v>
@@ -8671,15 +8706,15 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>291</v>
@@ -8688,15 +8723,15 @@
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>292</v>
@@ -8705,7 +8740,7 @@
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>293</v>
@@ -8713,24 +8748,24 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>295</v>
@@ -8739,66 +8774,66 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>297</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>300</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>301</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>303</v>
@@ -8807,15 +8842,15 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>306</v>
@@ -8824,15 +8859,15 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>309</v>
@@ -8841,15 +8876,15 @@
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>309</v>
@@ -8858,7 +8893,7 @@
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>310</v>
@@ -8866,7 +8901,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>312</v>
@@ -8875,15 +8910,15 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>312</v>
@@ -8892,15 +8927,15 @@
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>312</v>
@@ -8909,7 +8944,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>80</v>
@@ -8917,7 +8952,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>312</v>
@@ -8934,7 +8969,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>317</v>
@@ -8943,15 +8978,15 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>317</v>
@@ -8960,15 +8995,15 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>317</v>
@@ -8977,7 +9012,7 @@
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>318</v>
@@ -8985,7 +9020,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>317</v>
@@ -9002,7 +9037,7 @@
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>320</v>
@@ -9011,7 +9046,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>321</v>
@@ -9019,7 +9054,7 @@
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>325</v>
@@ -9028,7 +9063,7 @@
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>326</v>
@@ -9036,7 +9071,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>329</v>
@@ -9045,49 +9080,49 @@
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>335</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>340</v>
@@ -9096,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>341</v>
@@ -9104,7 +9139,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>340</v>
@@ -9113,7 +9148,7 @@
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>342</v>
@@ -9121,7 +9156,7 @@
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>344</v>
@@ -9130,7 +9165,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>345</v>
@@ -9138,7 +9173,7 @@
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>344</v>
@@ -9147,7 +9182,7 @@
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>346</v>
@@ -9155,7 +9190,7 @@
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>344</v>
@@ -9164,7 +9199,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>347</v>
@@ -9172,7 +9207,7 @@
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>344</v>
@@ -9181,7 +9216,7 @@
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>349</v>
@@ -9189,7 +9224,7 @@
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>351</v>
@@ -9198,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>345</v>
@@ -9206,7 +9241,7 @@
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>351</v>
@@ -9215,7 +9250,7 @@
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>346</v>
@@ -9223,7 +9258,7 @@
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>351</v>
@@ -9232,7 +9267,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>352</v>
@@ -9240,7 +9275,7 @@
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>351</v>
@@ -9249,7 +9284,7 @@
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>353</v>
@@ -9257,7 +9292,7 @@
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>354</v>
@@ -9266,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>345</v>
@@ -9274,7 +9309,7 @@
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>354</v>
@@ -9283,7 +9318,7 @@
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>346</v>
@@ -9291,7 +9326,7 @@
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>354</v>
@@ -9300,7 +9335,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>352</v>
@@ -9308,7 +9343,7 @@
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>354</v>
@@ -9317,7 +9352,7 @@
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>355</v>
@@ -9325,7 +9360,7 @@
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>356</v>
@@ -9334,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>345</v>
@@ -9342,7 +9377,7 @@
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>356</v>
@@ -9351,7 +9386,7 @@
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>346</v>
@@ -9359,7 +9394,7 @@
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>356</v>
@@ -9368,7 +9403,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>352</v>
@@ -9376,7 +9411,7 @@
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>356</v>
@@ -9385,7 +9420,7 @@
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>357</v>
@@ -9393,7 +9428,7 @@
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>359</v>
@@ -9402,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>345</v>
@@ -9410,7 +9445,7 @@
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>359</v>
@@ -9419,7 +9454,7 @@
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>346</v>
@@ -9427,7 +9462,7 @@
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>359</v>
@@ -9436,7 +9471,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>352</v>
@@ -9444,7 +9479,7 @@
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>359</v>
@@ -9453,7 +9488,7 @@
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>360</v>
@@ -9461,7 +9496,7 @@
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>361</v>
@@ -9470,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>345</v>
@@ -9478,7 +9513,7 @@
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>361</v>
@@ -9487,7 +9522,7 @@
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>346</v>
@@ -9495,7 +9530,7 @@
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>361</v>
@@ -9504,7 +9539,7 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>352</v>
@@ -9512,7 +9547,7 @@
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>361</v>
@@ -9521,7 +9556,7 @@
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>362</v>
@@ -9529,7 +9564,7 @@
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>363</v>
@@ -9538,7 +9573,7 @@
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>345</v>
@@ -9546,7 +9581,7 @@
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>363</v>
@@ -9555,7 +9590,7 @@
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>346</v>
@@ -9563,7 +9598,7 @@
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>363</v>
@@ -9572,7 +9607,7 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>352</v>
@@ -9580,7 +9615,7 @@
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>363</v>
@@ -9589,7 +9624,7 @@
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>364</v>
@@ -9597,7 +9632,7 @@
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>365</v>
@@ -9606,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>345</v>
@@ -9614,7 +9649,7 @@
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>365</v>
@@ -9623,7 +9658,7 @@
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>346</v>
@@ -9631,7 +9666,7 @@
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>365</v>
@@ -9640,7 +9675,7 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>352</v>
@@ -9648,7 +9683,7 @@
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>365</v>
@@ -9657,7 +9692,7 @@
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>366</v>
@@ -9665,7 +9700,7 @@
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>367</v>
@@ -9674,7 +9709,7 @@
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>345</v>
@@ -9682,7 +9717,7 @@
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>367</v>
@@ -9691,7 +9726,7 @@
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>346</v>
@@ -9699,7 +9734,7 @@
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>367</v>
@@ -9708,7 +9743,7 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>352</v>
@@ -9716,7 +9751,7 @@
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>367</v>
@@ -9725,7 +9760,7 @@
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>368</v>
@@ -9733,7 +9768,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>369</v>
@@ -9742,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>370</v>
@@ -9750,7 +9785,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>369</v>
@@ -9759,7 +9794,7 @@
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>371</v>
@@ -9767,7 +9802,7 @@
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>369</v>
@@ -9776,7 +9811,7 @@
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>373</v>
@@ -9784,7 +9819,7 @@
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>374</v>
@@ -9793,7 +9828,7 @@
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>376</v>
@@ -9801,7 +9836,7 @@
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>374</v>
@@ -9810,7 +9845,7 @@
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>378</v>
@@ -9818,478 +9853,478 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F708CA-2056-4692-9FEF-59A1B08A69B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E16C20E-6D3A-4455-99CB-EBBED853B755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="敌人生命护甲和伤害" sheetId="1" r:id="rId1"/>
     <sheet name="变更记录" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="705">
   <si>
     <t>家里</t>
   </si>
@@ -2182,12 +2195,37 @@
 可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
   </si>
   <si>
+    <t>场地机制</t>
+  </si>
+  <si>
     <t>【场地机制】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
-【英雄模式增益】玩家生命值增加40点；帐篷敌人不致命；敌人更容易受到火焰/冰冻/衰败伤害。
-【英雄模式玩家负面】无法使用食物、卷轴、狼和猫、任何药水（含投掷型）；回复能力降低3倍；生命值减少40点；防御力降低25%。
-【英雄模式敌方强化】敌人生命值和回复能力增强；免疫冰冻、眩晕和恐惧；移动速度提高40%；视野范围增加30%；20%概率使用复活药（两条命）；造成的伤害增加20%。
+【英雄模式玩家增益】玩家生命值增加40点；帐篷敌人不致命；敌人更容易受到火焰/冰冻/衰败伤害；玩家治疗效果提高20%
+【英雄模式玩家减益】无法使用食物、卷轴、狼和猫、任何药水（含投掷型）；回复能力降低3倍；生命值减少40点；防御力降低25%；无法使用陷阱或符文
+【英雄模式敌方强化】敌人生命值和回复能力增强；免疫冰冻、眩晕和恐惧；移动速度提高40%；视野范围增加30%；20%概率使用复活药（两条命）；造成的伤害增加20%；防御力提升25%
 【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
 【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。</t>
+  </si>
+  <si>
+    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，猎头者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，掷斧者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
+【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫
+【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
+（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
+（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
+（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
+【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破</t>
+  </si>
+  <si>
+    <t>【治疗效果降低】矿井内受黑暗力量影响,所有治疗手段效果压到三分之一，圣殿骑士套装可以免疫这个减益
+【玩家死亡】玩家死亡会回到码头，而不是河对岸的城堡，并且可以回去捡尸体
+【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血</t>
+  </si>
+  <si>
+    <t>【英雄模式的减益】英雄模式下的地牢会有4种随机减益，前2种为固定减益，后2种为随机减益
+（1）一条命：固定减益，死亡后无法返回地下城捡尸体
+（2）瘟疫崛起：固定减益，敌人可以复活
+（3）全速奔跑：随即减益，敌人移动速度增加35%
+（4）超自然反应：随机减益，敌人有15%的机会躲避攻击
+（5）生锈的锁：</t>
   </si>
 </sst>
 </file>
@@ -2312,7 +2350,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -2469,11 +2507,222 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2511,9 +2760,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2547,7 +2793,82 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2861,7 +3182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
@@ -2869,21 +3190,23 @@
     <col min="5" max="5" width="12" style="5" customWidth="1"/>
     <col min="6" max="6" width="68.796875" style="5" customWidth="1"/>
     <col min="7" max="7" width="32.06640625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="5"/>
+    <col min="8" max="8" width="65.1328125" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="A1" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="24"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -2899,14 +3222,17 @@
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="27" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H2" s="26" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
@@ -2920,14 +3246,15 @@
         <v>646</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="28" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H3" s="35"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
@@ -2943,14 +3270,17 @@
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="27" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H4" s="26" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="12" t="s">
         <v>10</v>
       </c>
@@ -2962,14 +3292,15 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H5" s="35"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="12" t="s">
         <v>13</v>
       </c>
@@ -2983,12 +3314,13 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="13" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H6" s="35"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
@@ -3002,12 +3334,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H7" s="35"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
         <v>17</v>
       </c>
@@ -3021,12 +3354,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="13" t="s">
+      <c r="F8" s="25"/>
+      <c r="G8" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H8" s="35"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
@@ -3040,14 +3374,15 @@
         <v>60</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="28" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H9" s="35"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
         <v>649</v>
       </c>
@@ -3061,14 +3396,15 @@
         <v>40</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="28" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H10" s="35"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
@@ -3082,12 +3418,13 @@
         <v>6</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="13" t="s">
+      <c r="F11" s="25"/>
+      <c r="G11" s="28" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H11" s="35"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
         <v>26</v>
       </c>
@@ -3101,12 +3438,13 @@
         <v>49</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="13" t="s">
+      <c r="F12" s="25"/>
+      <c r="G12" s="28" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H12" s="35"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
         <v>28</v>
       </c>
@@ -3120,12 +3458,13 @@
         <v>70</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="13" t="s">
+      <c r="F13" s="25"/>
+      <c r="G13" s="28" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H13" s="35"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
         <v>29</v>
       </c>
@@ -3137,14 +3476,15 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="28" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H14" s="35"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
         <v>32</v>
       </c>
@@ -3158,12 +3498,13 @@
         <v>9</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="13" t="s">
+      <c r="F15" s="25"/>
+      <c r="G15" s="28" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H15" s="35"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
         <v>33</v>
       </c>
@@ -3177,14 +3518,15 @@
         <v>63</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="H16" s="35"/>
+    </row>
+    <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
         <v>36</v>
       </c>
@@ -3198,12 +3540,13 @@
         <v>20</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="13" t="s">
+      <c r="F17" s="25"/>
+      <c r="G17" s="28" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="H17" s="35"/>
+    </row>
+    <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
         <v>38</v>
       </c>
@@ -3217,14 +3560,15 @@
         <v>32</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="28" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H18" s="35"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="12" t="s">
         <v>41</v>
       </c>
@@ -3238,12 +3582,13 @@
         <v>15</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="13" t="s">
+      <c r="F19" s="25"/>
+      <c r="G19" s="28" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="12" t="s">
         <v>43</v>
       </c>
@@ -3257,14 +3602,15 @@
         <v>44</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="28" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H20" s="35"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
         <v>46</v>
       </c>
@@ -3278,12 +3624,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="25"/>
+      <c r="G21" s="28" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H21" s="35"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
         <v>48</v>
       </c>
@@ -3297,15 +3644,16 @@
         <v>50</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="14" t="s">
+      <c r="H22" s="35"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" s="13" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="2">
@@ -3318,15 +3666,16 @@
         <v>55</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="28" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="14" t="s">
+      <c r="H23" s="35"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="2">
@@ -3339,15 +3688,16 @@
         <v>10</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="28" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="14" t="s">
+      <c r="H24" s="35"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="2">
@@ -3360,15 +3710,16 @@
         <v>50</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="28" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="14" t="s">
+      <c r="H25" s="35"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26" s="13" t="s">
         <v>62</v>
       </c>
       <c r="B26" s="2">
@@ -3384,12 +3735,13 @@
       <c r="F26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="14" t="s">
+      <c r="H26" s="35"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B27" s="2">
@@ -3405,12 +3757,13 @@
       <c r="F27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="25" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="14" t="s">
+      <c r="H27" s="35"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A28" s="13" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="2">
@@ -3424,12 +3777,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="25" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="15" t="s">
+      <c r="H28" s="35"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" s="14" t="s">
         <v>73</v>
       </c>
       <c r="B29" s="2">
@@ -3443,12 +3797,13 @@
       <c r="F29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="25" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="15" t="s">
+      <c r="H29" s="35"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A30" s="14" t="s">
         <v>76</v>
       </c>
       <c r="B30" s="2">
@@ -3464,12 +3819,13 @@
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="25" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="54" x14ac:dyDescent="0.45">
-      <c r="A31" s="15" t="s">
+      <c r="H30" s="35"/>
+    </row>
+    <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A31" s="14" t="s">
         <v>79</v>
       </c>
       <c r="B31" s="2">
@@ -3485,12 +3841,13 @@
       <c r="F31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="25" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="54" x14ac:dyDescent="0.45">
-      <c r="A32" s="15" t="s">
+      <c r="H31" s="35"/>
+    </row>
+    <row r="32" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A32" s="14" t="s">
         <v>82</v>
       </c>
       <c r="B32" s="2">
@@ -3506,12 +3863,13 @@
       <c r="F32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="25" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="16" t="s">
+      <c r="H32" s="35"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A33" s="15" t="s">
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -3527,11 +3885,12 @@
       <c r="F33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="25" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H33" s="35"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
         <v>88</v>
       </c>
@@ -3553,8 +3912,11 @@
       <c r="G34" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H34" s="11" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="12" t="s">
         <v>89</v>
       </c>
@@ -3569,11 +3931,14 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="25" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H35" s="46" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="12" t="s">
         <v>91</v>
       </c>
@@ -3588,11 +3953,12 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="25" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H36" s="47"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="12" t="s">
         <v>93</v>
       </c>
@@ -3607,11 +3973,12 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="25" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H37" s="47"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="12" t="s">
         <v>95</v>
       </c>
@@ -3628,11 +3995,12 @@
       <c r="F38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="25" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H38" s="47"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="12" t="s">
         <v>98</v>
       </c>
@@ -3647,11 +4015,12 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="25" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H39" s="47"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="12" t="s">
         <v>100</v>
       </c>
@@ -3668,11 +4037,12 @@
       <c r="F40" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="25" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H40" s="47"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="12" t="s">
         <v>103</v>
       </c>
@@ -3687,11 +4057,12 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="25" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H41" s="47"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="12" t="s">
         <v>105</v>
       </c>
@@ -3706,12 +4077,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="25" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="14" t="s">
+      <c r="H42" s="47"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" s="13" t="s">
         <v>107</v>
       </c>
       <c r="B43" s="2">
@@ -3727,12 +4099,13 @@
       <c r="F43" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="25" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="14" t="s">
+      <c r="H43" s="47"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A44" s="13" t="s">
         <v>684</v>
       </c>
       <c r="B44" s="2">
@@ -3748,12 +4121,13 @@
       <c r="F44" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="25" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A45" s="14" t="s">
+      <c r="H44" s="47"/>
+    </row>
+    <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A45" s="13" t="s">
         <v>683</v>
       </c>
       <c r="B45" s="2">
@@ -3769,12 +4143,13 @@
       <c r="F45" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="25" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A46" s="14" t="s">
+      <c r="H45" s="47"/>
+    </row>
+    <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A46" s="13" t="s">
         <v>682</v>
       </c>
       <c r="B46" s="2">
@@ -3790,12 +4165,13 @@
       <c r="F46" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="25" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A47" s="14" t="s">
+      <c r="H46" s="47"/>
+    </row>
+    <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A47" s="13" t="s">
         <v>118</v>
       </c>
       <c r="B47" s="2">
@@ -3811,12 +4187,13 @@
       <c r="F47" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="25" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="14" t="s">
+      <c r="H47" s="47"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A48" s="13" t="s">
         <v>120</v>
       </c>
       <c r="B48" s="2">
@@ -3832,12 +4209,13 @@
       <c r="F48" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="25" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="54" x14ac:dyDescent="0.45">
-      <c r="A49" s="15" t="s">
+      <c r="H48" s="47"/>
+    </row>
+    <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A49" s="14" t="s">
         <v>122</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -3853,12 +4231,13 @@
       <c r="F49" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G49" s="13" t="s">
+      <c r="G49" s="25" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="15" t="s">
+      <c r="H49" s="47"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50" s="14" t="s">
         <v>126</v>
       </c>
       <c r="B50" s="2">
@@ -3874,12 +4253,13 @@
       <c r="F50" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="25" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A51" s="15" t="s">
+      <c r="H50" s="47"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B51" s="2">
@@ -3895,12 +4275,13 @@
       <c r="F51" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="25" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A52" s="15" t="s">
+      <c r="H51" s="47"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B52" s="2">
@@ -3916,12 +4297,13 @@
       <c r="F52" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="25" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A53" s="15" t="s">
+      <c r="H52" s="47"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53" s="14" t="s">
         <v>135</v>
       </c>
       <c r="B53" s="2">
@@ -3937,11 +4319,12 @@
       <c r="F53" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="G53" s="25" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H53" s="48"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
         <v>138</v>
       </c>
@@ -3963,8 +4346,11 @@
       <c r="G54" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H54" s="11" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="12" t="s">
         <v>139</v>
       </c>
@@ -3981,11 +4367,14 @@
       <c r="F55" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="25" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H55" s="46" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="12" t="s">
         <v>142</v>
       </c>
@@ -4002,11 +4391,12 @@
       <c r="F56" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="25" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H56" s="47"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="12" t="s">
         <v>145</v>
       </c>
@@ -4023,11 +4413,12 @@
       <c r="F57" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="25" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H57" s="47"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="12" t="s">
         <v>148</v>
       </c>
@@ -4044,11 +4435,12 @@
       <c r="F58" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="G58" s="25" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H58" s="47"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
         <v>150</v>
       </c>
@@ -4065,11 +4457,12 @@
       <c r="F59" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G59" s="13" t="s">
+      <c r="G59" s="25" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H59" s="47"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="12" t="s">
         <v>153</v>
       </c>
@@ -4086,11 +4479,12 @@
       <c r="F60" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G60" s="13" t="s">
+      <c r="G60" s="25" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H60" s="47"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="12" t="s">
         <v>155</v>
       </c>
@@ -4107,12 +4501,13 @@
       <c r="F61" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G61" s="13" t="s">
+      <c r="G61" s="25" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A62" s="14" t="s">
+      <c r="H61" s="47"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A62" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B62" s="2">
@@ -4128,12 +4523,13 @@
       <c r="F62" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="G62" s="25" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A63" s="14" t="s">
+      <c r="H62" s="47"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A63" s="13" t="s">
         <v>160</v>
       </c>
       <c r="B63" s="2">
@@ -4149,12 +4545,13 @@
       <c r="F63" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G63" s="13" t="s">
+      <c r="G63" s="25" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A64" s="14" t="s">
+      <c r="H63" s="47"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A64" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B64" s="2">
@@ -4170,12 +4567,13 @@
       <c r="F64" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G64" s="13" t="s">
+      <c r="G64" s="25" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="162" x14ac:dyDescent="0.45">
-      <c r="A65" s="16" t="s">
+      <c r="H64" s="47"/>
+    </row>
+    <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
+      <c r="A65" s="15" t="s">
         <v>165</v>
       </c>
       <c r="B65" s="2">
@@ -4191,11 +4589,12 @@
       <c r="F65" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="G65" s="13" t="s">
+      <c r="G65" s="25" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H65" s="48"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
         <v>166</v>
       </c>
@@ -4217,8 +4616,11 @@
       <c r="G66" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="H66" s="30" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A67" s="12" t="s">
         <v>167</v>
       </c>
@@ -4235,11 +4637,14 @@
       <c r="F67" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="G67" s="13" t="s">
+      <c r="G67" s="25" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="54" x14ac:dyDescent="0.45">
+      <c r="H67" s="49" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
         <v>170</v>
       </c>
@@ -4256,12 +4661,13 @@
       <c r="F68" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="G68" s="13" t="s">
+      <c r="G68" s="25" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A69" s="14" t="s">
+      <c r="H68" s="47"/>
+    </row>
+    <row r="69" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A69" s="13" t="s">
         <v>172</v>
       </c>
       <c r="B69" s="2">
@@ -4277,12 +4683,13 @@
       <c r="F69" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="G69" s="13" t="s">
+      <c r="G69" s="25" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="14" t="s">
+      <c r="H69" s="47"/>
+    </row>
+    <row r="70" spans="1:8" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="13" t="s">
         <v>174</v>
       </c>
       <c r="B70" s="2">
@@ -4298,11 +4705,12 @@
       <c r="F70" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="G70" s="25" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H70" s="47"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
         <v>176</v>
       </c>
@@ -4324,8 +4732,11 @@
       <c r="G71" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H71" s="31" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="12" t="s">
         <v>177</v>
       </c>
@@ -4340,11 +4751,12 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="25" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H72" s="35"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
         <v>178</v>
       </c>
@@ -4359,11 +4771,12 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="13" t="s">
+      <c r="G73" s="25" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H73" s="35"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
         <v>179</v>
       </c>
@@ -4380,11 +4793,12 @@
       <c r="F74" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G74" s="13" t="s">
+      <c r="G74" s="25" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H74" s="35"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
         <v>181</v>
       </c>
@@ -4406,8 +4820,11 @@
       <c r="G75" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H75" s="11" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" s="12" t="s">
         <v>182</v>
       </c>
@@ -4424,11 +4841,12 @@
       <c r="F76" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H76" s="35"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
         <v>186</v>
       </c>
@@ -4447,11 +4865,12 @@
       <c r="F77" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G77" s="13" t="s">
+      <c r="G77" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H77" s="35"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
         <v>189</v>
       </c>
@@ -4470,11 +4889,12 @@
       <c r="F78" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G78" s="13" t="s">
+      <c r="G78" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H78" s="35"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
         <v>193</v>
       </c>
@@ -4491,11 +4911,12 @@
       <c r="F79" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G79" s="13" t="s">
+      <c r="G79" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H79" s="35"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
         <v>195</v>
       </c>
@@ -4512,11 +4933,12 @@
       <c r="F80" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G80" s="13" t="s">
+      <c r="G80" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H80" s="35"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
         <v>666</v>
       </c>
@@ -4533,11 +4955,12 @@
       <c r="F81" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G81" s="13" t="s">
+      <c r="G81" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H81" s="35"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
         <v>667</v>
       </c>
@@ -4554,12 +4977,13 @@
       <c r="F82" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G82" s="13" t="s">
+      <c r="G82" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A83" s="17" t="s">
+      <c r="H82" s="35"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A83" s="16" t="s">
         <v>204</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -4575,12 +4999,13 @@
       <c r="F83" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G83" s="13" t="s">
+      <c r="G83" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A84" s="17" t="s">
+      <c r="H83" s="35"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A84" s="16" t="s">
         <v>208</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -4596,12 +5021,13 @@
       <c r="F84" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G84" s="13" t="s">
+      <c r="G84" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A85" s="17" t="s">
+      <c r="H84" s="35"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A85" s="16" t="s">
         <v>212</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -4617,12 +5043,13 @@
       <c r="F85" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G85" s="13" t="s">
+      <c r="G85" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A86" s="16" t="s">
+      <c r="H85" s="35"/>
+    </row>
+    <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A86" s="15" t="s">
         <v>214</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -4638,12 +5065,13 @@
       <c r="F86" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G86" s="13" t="s">
+      <c r="G86" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A87" s="16" t="s">
+      <c r="H86" s="35"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A87" s="15" t="s">
         <v>217</v>
       </c>
       <c r="B87" s="2">
@@ -4659,11 +5087,12 @@
       <c r="F87" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G87" s="13" t="s">
+      <c r="G87" s="25" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H87" s="35"/>
+    </row>
+    <row r="88" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
         <v>219</v>
       </c>
@@ -4685,8 +5114,11 @@
       <c r="G88" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H88" s="30" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" s="12" t="s">
         <v>220</v>
       </c>
@@ -4703,11 +5135,12 @@
       <c r="F89" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G89" s="13" t="s">
+      <c r="G89" s="25" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H89" s="35"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
         <v>222</v>
       </c>
@@ -4722,11 +5155,12 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
-      <c r="G90" s="13" t="s">
+      <c r="G90" s="25" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H90" s="35"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
         <v>224</v>
       </c>
@@ -4741,11 +5175,12 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="13" t="s">
+      <c r="G91" s="25" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H91" s="35"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
         <v>226</v>
       </c>
@@ -4760,11 +5195,12 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="13" t="s">
+      <c r="G92" s="25" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H92" s="35"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
         <v>227</v>
       </c>
@@ -4779,11 +5215,12 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="13" t="s">
+      <c r="G93" s="25" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H93" s="35"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
         <v>228</v>
       </c>
@@ -4800,11 +5237,12 @@
       <c r="F94" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="G94" s="13" t="s">
+      <c r="G94" s="25" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H94" s="35"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
         <v>232</v>
       </c>
@@ -4819,11 +5257,12 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="13" t="s">
+      <c r="G95" s="25" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H95" s="35"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
         <v>234</v>
       </c>
@@ -4840,11 +5279,12 @@
       <c r="F96" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G96" s="13" t="s">
+      <c r="G96" s="25" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H96" s="35"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
         <v>237</v>
       </c>
@@ -4859,11 +5299,12 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="13" t="s">
+      <c r="G97" s="25" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H97" s="35"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
         <v>239</v>
       </c>
@@ -4878,11 +5319,12 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="13" t="s">
+      <c r="G98" s="25" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H98" s="35"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
         <v>241</v>
       </c>
@@ -4897,11 +5339,12 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="13" t="s">
+      <c r="G99" s="25" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H99" s="35"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
         <v>244</v>
       </c>
@@ -4918,11 +5361,12 @@
       <c r="F100" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G100" s="13" t="s">
+      <c r="G100" s="25" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H100" s="35"/>
+    </row>
+    <row r="101" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
         <v>246</v>
       </c>
@@ -4939,11 +5383,12 @@
       <c r="F101" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="25" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H101" s="35"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
         <v>249</v>
       </c>
@@ -4960,11 +5405,12 @@
       <c r="F102" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G102" s="13" t="s">
+      <c r="G102" s="25" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H102" s="35"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
         <v>252</v>
       </c>
@@ -4981,12 +5427,13 @@
       <c r="F103" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G103" s="13" t="s">
+      <c r="G103" s="25" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A104" s="14" t="s">
+      <c r="H103" s="35"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A104" s="13" t="s">
         <v>254</v>
       </c>
       <c r="B104" s="2">
@@ -5002,12 +5449,13 @@
       <c r="F104" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="G104" s="13" t="s">
+      <c r="G104" s="25" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A105" s="14" t="s">
+      <c r="H104" s="35"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A105" s="13" t="s">
         <v>257</v>
       </c>
       <c r="B105" s="2">
@@ -5021,11 +5469,12 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="13" t="s">
+      <c r="G105" s="25" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="H105" s="35"/>
+    </row>
+    <row r="106" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
         <v>259</v>
       </c>
@@ -5040,11 +5489,12 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="13" t="s">
+      <c r="G106" s="25" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H106" s="35"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
         <v>262</v>
       </c>
@@ -5059,11 +5509,12 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="13" t="s">
+      <c r="G107" s="25" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H107" s="35"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
         <v>264</v>
       </c>
@@ -5078,11 +5529,12 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="13" t="s">
+      <c r="G108" s="25" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H108" s="35"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
         <v>265</v>
       </c>
@@ -5097,12 +5549,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="13" t="s">
+      <c r="G109" s="25" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A110" s="14" t="s">
+      <c r="H109" s="35"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A110" s="13" t="s">
         <v>266</v>
       </c>
       <c r="B110" s="2">
@@ -5116,12 +5569,13 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="13" t="s">
+      <c r="G110" s="25" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A111" s="15" t="s">
+      <c r="H110" s="35"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A111" s="14" t="s">
         <v>268</v>
       </c>
       <c r="B111" s="2">
@@ -5135,12 +5589,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="13" t="s">
+      <c r="G111" s="25" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A112" s="16" t="s">
+      <c r="H111" s="35"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A112" s="15" t="s">
         <v>270</v>
       </c>
       <c r="B112" s="2">
@@ -5154,12 +5609,13 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="13" t="s">
+      <c r="G112" s="25" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A113" s="15" t="s">
+      <c r="H112" s="35"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" s="14" t="s">
         <v>272</v>
       </c>
       <c r="B113" s="2">
@@ -5175,12 +5631,13 @@
       <c r="F113" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G113" s="13" t="s">
+      <c r="G113" s="25" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A114" s="15" t="s">
+      <c r="H113" s="35"/>
+    </row>
+    <row r="114" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A114" s="14" t="s">
         <v>275</v>
       </c>
       <c r="B114" s="2">
@@ -5196,12 +5653,13 @@
       <c r="F114" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="G114" s="13" t="s">
+      <c r="G114" s="25" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A115" s="15" t="s">
+      <c r="H114" s="35"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A115" s="14" t="s">
         <v>277</v>
       </c>
       <c r="B115" s="2">
@@ -5217,12 +5675,13 @@
       <c r="F115" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G115" s="13" t="s">
+      <c r="G115" s="25" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A116" s="15" t="s">
+      <c r="H115" s="35"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116" s="14" t="s">
         <v>280</v>
       </c>
       <c r="B116" s="2">
@@ -5238,12 +5697,13 @@
       <c r="F116" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G116" s="13" t="s">
+      <c r="G116" s="25" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A117" s="16" t="s">
+      <c r="H116" s="35"/>
+    </row>
+    <row r="117" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A117" s="15" t="s">
         <v>650</v>
       </c>
       <c r="B117" s="2">
@@ -5259,11 +5719,12 @@
       <c r="F117" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G117" s="13" t="s">
+      <c r="G117" s="25" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H117" s="35"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
         <v>653</v>
       </c>
@@ -5285,8 +5746,11 @@
       <c r="G118" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H118" s="31" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
         <v>668</v>
       </c>
@@ -5303,11 +5767,12 @@
       <c r="F119" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G119" s="13" t="s">
+      <c r="G119" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H119" s="35"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
         <v>669</v>
       </c>
@@ -5324,11 +5789,12 @@
       <c r="F120" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="G120" s="13" t="s">
+      <c r="G120" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H120" s="35"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
         <v>670</v>
       </c>
@@ -5345,11 +5811,12 @@
       <c r="F121" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="G121" s="13" t="s">
+      <c r="G121" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H121" s="35"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
         <v>292</v>
       </c>
@@ -5366,11 +5833,12 @@
       <c r="F122" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G122" s="13" t="s">
+      <c r="G122" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H122" s="35"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
         <v>294</v>
       </c>
@@ -5387,11 +5855,12 @@
       <c r="F123" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G123" s="13" t="s">
+      <c r="G123" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H123" s="35"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
         <v>671</v>
       </c>
@@ -5408,11 +5877,12 @@
       <c r="F124" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="G124" s="13" t="s">
+      <c r="G124" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H124" s="35"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
         <v>672</v>
       </c>
@@ -5429,12 +5899,13 @@
       <c r="F125" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="G125" s="13" t="s">
+      <c r="G125" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A126" s="14" t="s">
+      <c r="H125" s="35"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126" s="13" t="s">
         <v>658</v>
       </c>
       <c r="B126" s="2">
@@ -5450,12 +5921,13 @@
       <c r="F126" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="G126" s="13" t="s">
+      <c r="G126" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A127" s="14" t="s">
+      <c r="H126" s="35"/>
+    </row>
+    <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A127" s="13" t="s">
         <v>662</v>
       </c>
       <c r="B127" s="2">
@@ -5471,12 +5943,13 @@
       <c r="F127" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="G127" s="13" t="s">
+      <c r="G127" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A128" s="15" t="s">
+      <c r="H127" s="35"/>
+    </row>
+    <row r="128" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A128" s="14" t="s">
         <v>664</v>
       </c>
       <c r="B128" s="2">
@@ -5492,12 +5965,13 @@
       <c r="F128" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="G128" s="13" t="s">
+      <c r="G128" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="108" x14ac:dyDescent="0.45">
-      <c r="A129" s="15" t="s">
+      <c r="H128" s="35"/>
+    </row>
+    <row r="129" spans="1:8" ht="108" x14ac:dyDescent="0.45">
+      <c r="A129" s="14" t="s">
         <v>675</v>
       </c>
       <c r="B129" s="2">
@@ -5513,11 +5987,12 @@
       <c r="F129" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="G129" s="13" t="s">
+      <c r="G129" s="25" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H129" s="35"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="10" t="s">
         <v>287</v>
       </c>
@@ -5539,8 +6014,11 @@
       <c r="G130" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H130" s="30" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="12" t="s">
         <v>288</v>
       </c>
@@ -5557,12 +6035,13 @@
       <c r="F131" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G131" s="13" t="s">
+      <c r="G131" s="25" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A132" s="14" t="s">
+      <c r="H131" s="35"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B132" s="2">
@@ -5576,11 +6055,12 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="13" t="s">
+      <c r="G132" s="25" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H132" s="35"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="12" t="s">
         <v>295</v>
       </c>
@@ -5595,11 +6075,12 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="13" t="s">
+      <c r="G133" s="25" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H133" s="35"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
         <v>297</v>
       </c>
@@ -5616,11 +6097,12 @@
       <c r="F134" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G134" s="13" t="s">
+      <c r="G134" s="25" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H134" s="35"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
         <v>300</v>
       </c>
@@ -5635,11 +6117,12 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="13" t="s">
+      <c r="G135" s="25" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H135" s="35"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
         <v>301</v>
       </c>
@@ -5656,11 +6139,12 @@
       <c r="F136" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G136" s="13" t="s">
+      <c r="G136" s="25" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="H136" s="35"/>
+    </row>
+    <row r="137" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
         <v>303</v>
       </c>
@@ -5677,12 +6161,13 @@
       <c r="F137" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G137" s="13" t="s">
+      <c r="G137" s="25" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A138" s="14" t="s">
+      <c r="H137" s="35"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A138" s="13" t="s">
         <v>306</v>
       </c>
       <c r="B138" s="2">
@@ -5700,12 +6185,13 @@
       <c r="F138" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G138" s="13" t="s">
+      <c r="G138" s="25" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A139" s="15" t="s">
+      <c r="H138" s="35"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A139" s="14" t="s">
         <v>309</v>
       </c>
       <c r="B139" s="2">
@@ -5721,12 +6207,13 @@
       <c r="F139" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G139" s="13" t="s">
+      <c r="G139" s="25" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A140" s="15" t="s">
+      <c r="H139" s="35"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A140" s="14" t="s">
         <v>312</v>
       </c>
       <c r="B140" s="2">
@@ -5742,12 +6229,13 @@
       <c r="F140" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G140" s="13" t="s">
+      <c r="G140" s="25" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A141" s="15" t="s">
+      <c r="H140" s="35"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A141" s="14" t="s">
         <v>314</v>
       </c>
       <c r="B141" s="2">
@@ -5763,12 +6251,13 @@
       <c r="F141" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="G141" s="13" t="s">
+      <c r="G141" s="25" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A142" s="15" t="s">
+      <c r="H141" s="35"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A142" s="14" t="s">
         <v>317</v>
       </c>
       <c r="B142" s="2">
@@ -5784,12 +6273,13 @@
       <c r="F142" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="G142" s="13" t="s">
+      <c r="G142" s="25" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A143" s="16" t="s">
+      <c r="H142" s="35"/>
+    </row>
+    <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A143" s="15" t="s">
         <v>320</v>
       </c>
       <c r="B143" s="2">
@@ -5805,11 +6295,12 @@
       <c r="F143" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="G143" s="25" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H143" s="35"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
         <v>322</v>
       </c>
@@ -5831,8 +6322,11 @@
       <c r="G144" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H144" s="32" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="12" t="s">
         <v>323</v>
       </c>
@@ -5849,11 +6343,12 @@
       <c r="F145" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G145" s="13" t="s">
+      <c r="G145" s="25" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H145" s="35"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
         <v>325</v>
       </c>
@@ -5870,11 +6365,12 @@
       <c r="F146" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G146" s="13" t="s">
+      <c r="G146" s="25" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H146" s="35"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
         <v>327</v>
       </c>
@@ -5889,11 +6385,12 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="13" t="s">
+      <c r="G147" s="25" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H147" s="35"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
         <v>329</v>
       </c>
@@ -5908,11 +6405,12 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="13" t="s">
+      <c r="G148" s="25" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="H148" s="35"/>
+    </row>
+    <row r="149" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
         <v>330</v>
       </c>
@@ -5929,11 +6427,12 @@
       <c r="F149" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="G149" s="13" t="s">
+      <c r="G149" s="25" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H149" s="35"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="12" t="s">
         <v>333</v>
       </c>
@@ -5950,11 +6449,12 @@
       <c r="F150" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="G150" s="13" t="s">
+      <c r="G150" s="25" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H150" s="35"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
         <v>339</v>
       </c>
@@ -5976,8 +6476,11 @@
       <c r="G151" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H151" s="32" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="12" t="s">
         <v>340</v>
       </c>
@@ -5994,11 +6497,12 @@
       <c r="F152" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G152" s="13" t="s">
+      <c r="G152" s="25" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="H152" s="35"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="12" t="s">
         <v>338</v>
       </c>
@@ -6015,12 +6519,13 @@
       <c r="F153" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G153" s="13" t="s">
+      <c r="G153" s="25" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A154" s="15" t="s">
+      <c r="H153" s="35"/>
+    </row>
+    <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A154" s="14" t="s">
         <v>344</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -6038,12 +6543,13 @@
       <c r="F154" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G154" s="13" t="s">
+      <c r="G154" s="25" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A155" s="15" t="s">
+      <c r="H154" s="35"/>
+    </row>
+    <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A155" s="14" t="s">
         <v>351</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -6061,12 +6567,13 @@
       <c r="F155" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G155" s="13" t="s">
+      <c r="G155" s="25" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A156" s="15" t="s">
+      <c r="H155" s="35"/>
+    </row>
+    <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A156" s="14" t="s">
         <v>354</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -6084,12 +6591,13 @@
       <c r="F156" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="G156" s="13" t="s">
+      <c r="G156" s="25" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A157" s="15" t="s">
+      <c r="H156" s="35"/>
+    </row>
+    <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A157" s="14" t="s">
         <v>356</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -6107,12 +6615,13 @@
       <c r="F157" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="G157" s="13" t="s">
+      <c r="G157" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A158" s="15" t="s">
+      <c r="H157" s="35"/>
+    </row>
+    <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A158" s="14" t="s">
         <v>633</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -6130,12 +6639,13 @@
       <c r="F158" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G158" s="13" t="s">
+      <c r="G158" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A159" s="15" t="s">
+      <c r="H158" s="35"/>
+    </row>
+    <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A159" s="14" t="s">
         <v>629</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -6153,12 +6663,13 @@
       <c r="F159" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G159" s="13" t="s">
+      <c r="G159" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A160" s="15" t="s">
+      <c r="H159" s="35"/>
+    </row>
+    <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A160" s="14" t="s">
         <v>630</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -6176,12 +6687,13 @@
       <c r="F160" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="G160" s="13" t="s">
+      <c r="G160" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A161" s="15" t="s">
+      <c r="H160" s="35"/>
+    </row>
+    <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A161" s="14" t="s">
         <v>631</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -6199,12 +6711,13 @@
       <c r="F161" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="G161" s="13" t="s">
+      <c r="G161" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A162" s="15" t="s">
+      <c r="H161" s="35"/>
+    </row>
+    <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A162" s="14" t="s">
         <v>632</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -6222,12 +6735,13 @@
       <c r="F162" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G162" s="13" t="s">
+      <c r="G162" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A163" s="16" t="s">
+      <c r="H162" s="35"/>
+    </row>
+    <row r="163" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A163" s="15" t="s">
         <v>369</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -6245,12 +6759,13 @@
       <c r="F163" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G163" s="13" t="s">
+      <c r="G163" s="25" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="54" x14ac:dyDescent="0.45">
-      <c r="A164" s="16" t="s">
+      <c r="H163" s="35"/>
+    </row>
+    <row r="164" spans="1:10" ht="54" x14ac:dyDescent="0.45">
+      <c r="A164" s="15" t="s">
         <v>374</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -6268,12 +6783,13 @@
       <c r="F164" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G164" s="13" t="s">
+      <c r="G164" s="25" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A165" s="16" t="s">
+      <c r="H164" s="35"/>
+    </row>
+    <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A165" s="15" t="s">
         <v>634</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -6291,57 +6807,64 @@
       <c r="F165" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G165" s="13" t="s">
+      <c r="G165" s="25" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A166" s="10" t="s">
+      <c r="H165" s="35"/>
+    </row>
+    <row r="166" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A166" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="D166" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E166" s="4" t="s">
+      <c r="E166" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F166" s="4" t="s">
+      <c r="F166" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="11" t="s">
+      <c r="G166" s="30" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A167" s="12" t="s">
+      <c r="H166" s="32" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A167" s="39" t="s">
         <v>380</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167" s="40">
         <v>120</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167" s="40">
         <v>57</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="40">
         <v>40</v>
       </c>
-      <c r="E167" s="7" t="s">
+      <c r="E167" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="F167" s="40" t="s">
         <v>686</v>
       </c>
-      <c r="G167" s="25" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G167" s="43" t="s">
+        <v>379</v>
+      </c>
+      <c r="H167" s="42" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
         <v>382</v>
       </c>
@@ -6358,9 +6881,10 @@
       <c r="F168" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="G168" s="20"/>
-    </row>
-    <row r="169" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G168" s="44"/>
+      <c r="H168" s="19"/>
+    </row>
+    <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
         <v>384</v>
       </c>
@@ -6377,9 +6901,10 @@
       <c r="F169" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="G169" s="20"/>
-    </row>
-    <row r="170" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G169" s="44"/>
+      <c r="H169" s="19"/>
+    </row>
+    <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
         <v>386</v>
       </c>
@@ -6396,9 +6921,10 @@
       <c r="F170" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="G170" s="20"/>
-    </row>
-    <row r="171" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G170" s="44"/>
+      <c r="H170" s="19"/>
+    </row>
+    <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
         <v>388</v>
       </c>
@@ -6415,9 +6941,10 @@
       <c r="F171" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="G171" s="20"/>
-    </row>
-    <row r="172" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G171" s="44"/>
+      <c r="H171" s="19"/>
+    </row>
+    <row r="172" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A172" s="12" t="s">
         <v>390</v>
       </c>
@@ -6434,9 +6961,10 @@
       <c r="F172" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="G172" s="20"/>
-    </row>
-    <row r="173" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G172" s="44"/>
+      <c r="H172" s="19"/>
+    </row>
+    <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
         <v>392</v>
       </c>
@@ -6453,9 +6981,11 @@
       <c r="F173" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="G173" s="20"/>
-    </row>
-    <row r="174" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G173" s="44"/>
+      <c r="H173" s="19"/>
+      <c r="J173" s="33"/>
+    </row>
+    <row r="174" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="12" t="s">
         <v>394</v>
       </c>
@@ -6472,9 +7002,10 @@
       <c r="F174" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="G174" s="20"/>
-    </row>
-    <row r="175" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G174" s="44"/>
+      <c r="H174" s="19"/>
+    </row>
+    <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
         <v>396</v>
       </c>
@@ -6491,9 +7022,10 @@
       <c r="F175" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="G175" s="20"/>
-    </row>
-    <row r="176" spans="1:7" ht="27" x14ac:dyDescent="0.45">
+      <c r="G175" s="44"/>
+      <c r="H175" s="19"/>
+    </row>
+    <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
         <v>398</v>
       </c>
@@ -6510,10 +7042,11 @@
       <c r="F176" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G176" s="20"/>
-    </row>
-    <row r="177" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A177" s="14" t="s">
+      <c r="G176" s="44"/>
+      <c r="H176" s="19"/>
+    </row>
+    <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A177" s="13" t="s">
         <v>400</v>
       </c>
       <c r="B177" s="2">
@@ -6529,10 +7062,11 @@
       <c r="F177" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="G177" s="20"/>
-    </row>
-    <row r="178" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A178" s="14" t="s">
+      <c r="G177" s="44"/>
+      <c r="H177" s="19"/>
+    </row>
+    <row r="178" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A178" s="13" t="s">
         <v>402</v>
       </c>
       <c r="B178" s="2">
@@ -6548,10 +7082,11 @@
       <c r="F178" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="G178" s="20"/>
-    </row>
-    <row r="179" spans="1:7" ht="54" x14ac:dyDescent="0.45">
-      <c r="A179" s="14" t="s">
+      <c r="G178" s="44"/>
+      <c r="H178" s="19"/>
+    </row>
+    <row r="179" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A179" s="13" t="s">
         <v>404</v>
       </c>
       <c r="B179" s="2">
@@ -6569,10 +7104,11 @@
       <c r="F179" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="G179" s="20"/>
-    </row>
-    <row r="180" spans="1:7" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A180" s="14" t="s">
+      <c r="G179" s="44"/>
+      <c r="H179" s="19"/>
+    </row>
+    <row r="180" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A180" s="13" t="s">
         <v>406</v>
       </c>
       <c r="B180" s="2">
@@ -6590,10 +7126,11 @@
       <c r="F180" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="G180" s="20"/>
-    </row>
-    <row r="181" spans="1:7" ht="27" x14ac:dyDescent="0.45">
-      <c r="A181" s="14" t="s">
+      <c r="G180" s="44"/>
+      <c r="H180" s="19"/>
+    </row>
+    <row r="181" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A181" s="13" t="s">
         <v>681</v>
       </c>
       <c r="B181" s="2">
@@ -6609,34 +7146,40 @@
       <c r="F181" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="G181" s="20"/>
-    </row>
-    <row r="182" spans="1:7" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A182" s="18" t="s">
+      <c r="G181" s="44"/>
+      <c r="H181" s="19"/>
+    </row>
+    <row r="182" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A182" s="17" t="s">
         <v>680</v>
       </c>
-      <c r="B182" s="19">
+      <c r="B182" s="18">
         <v>500</v>
       </c>
-      <c r="C182" s="19">
+      <c r="C182" s="18">
         <v>87</v>
       </c>
-      <c r="D182" s="19">
+      <c r="D182" s="18">
         <v>130</v>
       </c>
-      <c r="E182" s="6" t="s">
+      <c r="E182" s="36" t="s">
         <v>679</v>
       </c>
-      <c r="F182" s="19" t="s">
+      <c r="F182" s="18" t="s">
         <v>699</v>
       </c>
-      <c r="G182" s="21"/>
-    </row>
-    <row r="186" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="G182" s="45"/>
+      <c r="H182" s="20"/>
+    </row>
+    <row r="186" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="G167:G182"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="H167:H182"/>
+    <mergeCell ref="H35:H53"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="H55:H65"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E16C20E-6D3A-4455-99CB-EBBED853B755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D341240-8CF9-4BBC-9FE9-2A3FFB992ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2220,12 +2220,16 @@
 【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血</t>
   </si>
   <si>
-    <t>【英雄模式的减益】英雄模式下的地牢会有4种随机减益，前2种为固定减益，后2种为随机减益
+    <t>【地牢介绍】被弃地下城一共有三层，第二层比第一层多了狂热者和狂怒亵渎，然后第三层主要是领主和他的四个小弟；被弃地下城有普通模式和英雄模式，普通模式玩家死亡后可以返回捡尸体，地点冷却时间为8小时，而英雄模式玩家死亡后无法返回，物品将永远丢失，地点冷却时间为4小时
+【英雄模式的减益】英雄模式下的地牢会有4种随机减益，前2种为固定减益，后2种为随机减益
 （1）一条命：固定减益，死亡后无法返回地下城捡尸体
 （2）瘟疫崛起：固定减益，敌人可以复活
 （3）全速奔跑：随即减益，敌人移动速度增加35%
 （4）超自然反应：随机减益，敌人有15%的机会躲避攻击
-（5）生锈的锁：</t>
+（5）疯子的笑声：随机减益，陷阱数量增加
+（6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
+（7）被感染的空气：随机减益，角色最大生命值降低30
+（8）鹰眼：随机减益，敌人视野增加35%</t>
   </si>
 </sst>
 </file>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D341240-8CF9-4BBC-9FE9-2A3FFB992ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30143CDC-BF08-4B15-A546-D217D1FCDEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2224,7 +2224,7 @@
 【英雄模式的减益】英雄模式下的地牢会有4种随机减益，前2种为固定减益，后2种为随机减益
 （1）一条命：固定减益，死亡后无法返回地下城捡尸体
 （2）瘟疫崛起：固定减益，敌人可以复活
-（3）全速奔跑：随即减益，敌人移动速度增加35%
+（3）全速奔跑：随机减益，敌人移动速度增加35%
 （4）超自然反应：随机减益，敌人有15%的机会躲避攻击
 （5）疯子的笑声：随机减益，陷阱数量增加
 （6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
@@ -2782,21 +2782,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2806,10 +2791,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2826,9 +2811,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2851,9 +2833,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2861,6 +2840,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3199,16 +3199,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="39" t="s">
         <v>628</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -3226,13 +3226,13 @@
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="21" t="s">
         <v>700</v>
       </c>
     </row>
@@ -3250,13 +3250,13 @@
         <v>646</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="35"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
@@ -3274,13 +3274,13 @@
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="21" t="s">
         <v>700</v>
       </c>
     </row>
@@ -3296,13 +3296,13 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="12" t="s">
@@ -3318,11 +3318,11 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="28" t="s">
+      <c r="F6" s="20"/>
+      <c r="G6" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
@@ -3338,11 +3338,11 @@
         <v>6</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="28" t="s">
+      <c r="F7" s="20"/>
+      <c r="G7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
@@ -3358,11 +3358,11 @@
         <v>16</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="28" t="s">
+      <c r="F8" s="20"/>
+      <c r="G8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
@@ -3378,13 +3378,13 @@
         <v>60</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
@@ -3400,13 +3400,13 @@
         <v>40</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="23" t="s">
         <v>651</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
@@ -3422,11 +3422,11 @@
         <v>6</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="28" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
@@ -3442,11 +3442,11 @@
         <v>49</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="28" t="s">
+      <c r="F12" s="20"/>
+      <c r="G12" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
@@ -3462,11 +3462,11 @@
         <v>70</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="28" t="s">
+      <c r="F13" s="20"/>
+      <c r="G13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
@@ -3480,13 +3480,13 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
@@ -3502,11 +3502,11 @@
         <v>9</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="28" t="s">
+      <c r="F15" s="20"/>
+      <c r="G15" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="35"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
@@ -3522,13 +3522,13 @@
         <v>63</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="G16" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
@@ -3544,11 +3544,11 @@
         <v>20</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="28" t="s">
+      <c r="F17" s="20"/>
+      <c r="G17" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="35"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
@@ -3564,13 +3564,13 @@
         <v>32</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="12" t="s">
@@ -3586,11 +3586,11 @@
         <v>15</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="28" t="s">
+      <c r="F19" s="20"/>
+      <c r="G19" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="12" t="s">
@@ -3606,13 +3606,13 @@
         <v>44</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="23" t="s">
         <v>652</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
@@ -3628,11 +3628,11 @@
         <v>10</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="20"/>
+      <c r="G21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="35"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
@@ -3648,13 +3648,13 @@
         <v>50</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="28" t="s">
+      <c r="G22" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="35"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
@@ -3670,13 +3670,13 @@
         <v>55</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="35"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
@@ -3692,13 +3692,13 @@
         <v>10</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="28" t="s">
+      <c r="G24" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H24" s="35"/>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
@@ -3714,13 +3714,13 @@
         <v>50</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="28" t="s">
+      <c r="G25" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H25" s="35"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
@@ -3739,10 +3739,10 @@
       <c r="F26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="35"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
@@ -3761,10 +3761,10 @@
       <c r="F27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H27" s="35"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
@@ -3781,10 +3781,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="35"/>
+      <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="14" t="s">
@@ -3801,10 +3801,10 @@
       <c r="F29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="25" t="s">
+      <c r="G29" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="35"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="14" t="s">
@@ -3823,10 +3823,10 @@
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G30" s="25" t="s">
+      <c r="G30" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H30" s="35"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A31" s="14" t="s">
@@ -3845,10 +3845,10 @@
       <c r="F31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="H31" s="35"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A32" s="14" t="s">
@@ -3867,10 +3867,10 @@
       <c r="F32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="25" t="s">
+      <c r="G32" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="35"/>
+      <c r="H32" s="29"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="15" t="s">
@@ -3889,10 +3889,10 @@
       <c r="F33" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H33" s="35"/>
+      <c r="H33" s="29"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="25" t="s">
+      <c r="G35" s="20" t="s">
         <v>90</v>
       </c>
       <c r="H35" s="46" t="s">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="25" t="s">
+      <c r="G36" s="20" t="s">
         <v>92</v>
       </c>
       <c r="H36" s="47"/>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="25" t="s">
+      <c r="G37" s="20" t="s">
         <v>94</v>
       </c>
       <c r="H37" s="47"/>
@@ -3999,7 +3999,7 @@
       <c r="F38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="25" t="s">
+      <c r="G38" s="20" t="s">
         <v>97</v>
       </c>
       <c r="H38" s="47"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="25" t="s">
+      <c r="G39" s="20" t="s">
         <v>99</v>
       </c>
       <c r="H39" s="47"/>
@@ -4041,7 +4041,7 @@
       <c r="F40" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="25" t="s">
+      <c r="G40" s="20" t="s">
         <v>102</v>
       </c>
       <c r="H40" s="47"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="25" t="s">
+      <c r="G41" s="20" t="s">
         <v>104</v>
       </c>
       <c r="H41" s="47"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="25" t="s">
+      <c r="G42" s="20" t="s">
         <v>106</v>
       </c>
       <c r="H42" s="47"/>
@@ -4103,7 +4103,7 @@
       <c r="F43" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="25" t="s">
+      <c r="G43" s="20" t="s">
         <v>109</v>
       </c>
       <c r="H43" s="47"/>
@@ -4125,7 +4125,7 @@
       <c r="F44" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G44" s="25" t="s">
+      <c r="G44" s="20" t="s">
         <v>112</v>
       </c>
       <c r="H44" s="47"/>
@@ -4147,7 +4147,7 @@
       <c r="F45" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G45" s="25" t="s">
+      <c r="G45" s="20" t="s">
         <v>115</v>
       </c>
       <c r="H45" s="47"/>
@@ -4169,7 +4169,7 @@
       <c r="F46" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="25" t="s">
+      <c r="G46" s="20" t="s">
         <v>115</v>
       </c>
       <c r="H46" s="47"/>
@@ -4191,7 +4191,7 @@
       <c r="F47" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="25" t="s">
+      <c r="G47" s="20" t="s">
         <v>115</v>
       </c>
       <c r="H47" s="47"/>
@@ -4213,7 +4213,7 @@
       <c r="F48" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="25" t="s">
+      <c r="G48" s="20" t="s">
         <v>92</v>
       </c>
       <c r="H48" s="47"/>
@@ -4235,7 +4235,7 @@
       <c r="F49" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G49" s="25" t="s">
+      <c r="G49" s="20" t="s">
         <v>115</v>
       </c>
       <c r="H49" s="47"/>
@@ -4257,7 +4257,7 @@
       <c r="F50" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G50" s="25" t="s">
+      <c r="G50" s="20" t="s">
         <v>128</v>
       </c>
       <c r="H50" s="47"/>
@@ -4279,7 +4279,7 @@
       <c r="F51" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="25" t="s">
+      <c r="G51" s="20" t="s">
         <v>131</v>
       </c>
       <c r="H51" s="47"/>
@@ -4301,7 +4301,7 @@
       <c r="F52" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G52" s="25" t="s">
+      <c r="G52" s="20" t="s">
         <v>134</v>
       </c>
       <c r="H52" s="47"/>
@@ -4323,7 +4323,7 @@
       <c r="F53" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G53" s="25" t="s">
+      <c r="G53" s="20" t="s">
         <v>137</v>
       </c>
       <c r="H53" s="48"/>
@@ -4371,7 +4371,7 @@
       <c r="F55" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G55" s="25" t="s">
+      <c r="G55" s="20" t="s">
         <v>141</v>
       </c>
       <c r="H55" s="46" t="s">
@@ -4395,7 +4395,7 @@
       <c r="F56" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G56" s="25" t="s">
+      <c r="G56" s="20" t="s">
         <v>144</v>
       </c>
       <c r="H56" s="47"/>
@@ -4417,7 +4417,7 @@
       <c r="F57" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G57" s="25" t="s">
+      <c r="G57" s="20" t="s">
         <v>147</v>
       </c>
       <c r="H57" s="47"/>
@@ -4439,7 +4439,7 @@
       <c r="F58" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G58" s="25" t="s">
+      <c r="G58" s="20" t="s">
         <v>149</v>
       </c>
       <c r="H58" s="47"/>
@@ -4461,7 +4461,7 @@
       <c r="F59" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G59" s="25" t="s">
+      <c r="G59" s="20" t="s">
         <v>152</v>
       </c>
       <c r="H59" s="47"/>
@@ -4483,7 +4483,7 @@
       <c r="F60" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G60" s="25" t="s">
+      <c r="G60" s="20" t="s">
         <v>144</v>
       </c>
       <c r="H60" s="47"/>
@@ -4505,7 +4505,7 @@
       <c r="F61" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G61" s="25" t="s">
+      <c r="G61" s="20" t="s">
         <v>147</v>
       </c>
       <c r="H61" s="47"/>
@@ -4527,7 +4527,7 @@
       <c r="F62" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G62" s="25" t="s">
+      <c r="G62" s="20" t="s">
         <v>159</v>
       </c>
       <c r="H62" s="47"/>
@@ -4549,7 +4549,7 @@
       <c r="F63" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G63" s="25" t="s">
+      <c r="G63" s="20" t="s">
         <v>162</v>
       </c>
       <c r="H63" s="47"/>
@@ -4571,7 +4571,7 @@
       <c r="F64" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G64" s="25" t="s">
+      <c r="G64" s="20" t="s">
         <v>147</v>
       </c>
       <c r="H64" s="47"/>
@@ -4593,7 +4593,7 @@
       <c r="F65" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="G65" s="25" t="s">
+      <c r="G65" s="20" t="s">
         <v>138</v>
       </c>
       <c r="H65" s="48"/>
@@ -4620,7 +4620,7 @@
       <c r="G66" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H66" s="30" t="s">
+      <c r="H66" s="25" t="s">
         <v>700</v>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       <c r="F67" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="G67" s="25" t="s">
+      <c r="G67" s="20" t="s">
         <v>169</v>
       </c>
       <c r="H67" s="49" t="s">
@@ -4665,7 +4665,7 @@
       <c r="F68" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="G68" s="25" t="s">
+      <c r="G68" s="20" t="s">
         <v>169</v>
       </c>
       <c r="H68" s="47"/>
@@ -4687,7 +4687,7 @@
       <c r="F69" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="G69" s="25" t="s">
+      <c r="G69" s="20" t="s">
         <v>169</v>
       </c>
       <c r="H69" s="47"/>
@@ -4709,7 +4709,7 @@
       <c r="F70" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="G70" s="25" t="s">
+      <c r="G70" s="20" t="s">
         <v>169</v>
       </c>
       <c r="H70" s="47"/>
@@ -4736,7 +4736,7 @@
       <c r="G71" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H71" s="31" t="s">
+      <c r="H71" s="26" t="s">
         <v>700</v>
       </c>
     </row>
@@ -4755,10 +4755,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="25" t="s">
+      <c r="G72" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="H72" s="35"/>
+      <c r="H72" s="29"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
@@ -4775,10 +4775,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="25" t="s">
+      <c r="G73" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="H73" s="35"/>
+      <c r="H73" s="29"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
@@ -4797,10 +4797,10 @@
       <c r="F74" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G74" s="25" t="s">
+      <c r="G74" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="H74" s="35"/>
+      <c r="H74" s="29"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
@@ -4845,10 +4845,10 @@
       <c r="F76" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G76" s="25" t="s">
+      <c r="G76" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H76" s="35"/>
+      <c r="H76" s="29"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
@@ -4869,10 +4869,10 @@
       <c r="F77" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G77" s="25" t="s">
+      <c r="G77" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H77" s="35"/>
+      <c r="H77" s="29"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
@@ -4893,10 +4893,10 @@
       <c r="F78" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G78" s="25" t="s">
+      <c r="G78" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H78" s="35"/>
+      <c r="H78" s="29"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
@@ -4915,10 +4915,10 @@
       <c r="F79" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G79" s="25" t="s">
+      <c r="G79" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H79" s="35"/>
+      <c r="H79" s="29"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
@@ -4937,10 +4937,10 @@
       <c r="F80" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G80" s="25" t="s">
+      <c r="G80" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H80" s="35"/>
+      <c r="H80" s="29"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
@@ -4959,10 +4959,10 @@
       <c r="F81" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G81" s="25" t="s">
+      <c r="G81" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H81" s="35"/>
+      <c r="H81" s="29"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
@@ -4981,10 +4981,10 @@
       <c r="F82" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G82" s="25" t="s">
+      <c r="G82" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H82" s="35"/>
+      <c r="H82" s="29"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="16" t="s">
@@ -5003,10 +5003,10 @@
       <c r="F83" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G83" s="25" t="s">
+      <c r="G83" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H83" s="35"/>
+      <c r="H83" s="29"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="16" t="s">
@@ -5025,10 +5025,10 @@
       <c r="F84" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G84" s="25" t="s">
+      <c r="G84" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H84" s="35"/>
+      <c r="H84" s="29"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="16" t="s">
@@ -5047,10 +5047,10 @@
       <c r="F85" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G85" s="25" t="s">
+      <c r="G85" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H85" s="35"/>
+      <c r="H85" s="29"/>
     </row>
     <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A86" s="15" t="s">
@@ -5069,10 +5069,10 @@
       <c r="F86" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G86" s="25" t="s">
+      <c r="G86" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H86" s="35"/>
+      <c r="H86" s="29"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
@@ -5091,10 +5091,10 @@
       <c r="F87" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G87" s="25" t="s">
+      <c r="G87" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H87" s="35"/>
+      <c r="H87" s="29"/>
     </row>
     <row r="88" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
@@ -5118,7 +5118,7 @@
       <c r="G88" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H88" s="30" t="s">
+      <c r="H88" s="25" t="s">
         <v>700</v>
       </c>
     </row>
@@ -5139,10 +5139,10 @@
       <c r="F89" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G89" s="25" t="s">
+      <c r="G89" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="H89" s="35"/>
+      <c r="H89" s="29"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
@@ -5159,10 +5159,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
-      <c r="G90" s="25" t="s">
+      <c r="G90" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="H90" s="35"/>
+      <c r="H90" s="29"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
@@ -5179,10 +5179,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="25" t="s">
+      <c r="G91" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="H91" s="35"/>
+      <c r="H91" s="29"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
@@ -5199,10 +5199,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="25" t="s">
+      <c r="G92" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="H92" s="35"/>
+      <c r="H92" s="29"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
@@ -5219,10 +5219,10 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="25" t="s">
+      <c r="G93" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="H93" s="35"/>
+      <c r="H93" s="29"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
@@ -5241,10 +5241,10 @@
       <c r="F94" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="G94" s="25" t="s">
+      <c r="G94" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="H94" s="35"/>
+      <c r="H94" s="29"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
@@ -5261,10 +5261,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="25" t="s">
+      <c r="G95" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="H95" s="35"/>
+      <c r="H95" s="29"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
@@ -5283,10 +5283,10 @@
       <c r="F96" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G96" s="25" t="s">
+      <c r="G96" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="H96" s="35"/>
+      <c r="H96" s="29"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
@@ -5303,10 +5303,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="25" t="s">
+      <c r="G97" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="H97" s="35"/>
+      <c r="H97" s="29"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
@@ -5323,10 +5323,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="25" t="s">
+      <c r="G98" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="H98" s="35"/>
+      <c r="H98" s="29"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
@@ -5343,10 +5343,10 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
-      <c r="G99" s="25" t="s">
+      <c r="G99" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="H99" s="35"/>
+      <c r="H99" s="29"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
@@ -5365,10 +5365,10 @@
       <c r="F100" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G100" s="25" t="s">
+      <c r="G100" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="H100" s="35"/>
+      <c r="H100" s="29"/>
     </row>
     <row r="101" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
@@ -5387,10 +5387,10 @@
       <c r="F101" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G101" s="25" t="s">
+      <c r="G101" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="H101" s="35"/>
+      <c r="H101" s="29"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
@@ -5409,10 +5409,10 @@
       <c r="F102" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G102" s="25" t="s">
+      <c r="G102" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="H102" s="35"/>
+      <c r="H102" s="29"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
@@ -5431,10 +5431,10 @@
       <c r="F103" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G103" s="25" t="s">
+      <c r="G103" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="H103" s="35"/>
+      <c r="H103" s="29"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="13" t="s">
@@ -5453,10 +5453,10 @@
       <c r="F104" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="G104" s="25" t="s">
+      <c r="G104" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="H104" s="35"/>
+      <c r="H104" s="29"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="13" t="s">
@@ -5473,10 +5473,10 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="25" t="s">
+      <c r="G105" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="H105" s="35"/>
+      <c r="H105" s="29"/>
     </row>
     <row r="106" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
@@ -5493,10 +5493,10 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="25" t="s">
+      <c r="G106" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="H106" s="35"/>
+      <c r="H106" s="29"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
@@ -5513,10 +5513,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="25" t="s">
+      <c r="G107" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="H107" s="35"/>
+      <c r="H107" s="29"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
@@ -5533,10 +5533,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="25" t="s">
+      <c r="G108" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="H108" s="35"/>
+      <c r="H108" s="29"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
@@ -5553,10 +5553,10 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="25" t="s">
+      <c r="G109" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="H109" s="35"/>
+      <c r="H109" s="29"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
@@ -5573,10 +5573,10 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="25" t="s">
+      <c r="G110" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="H110" s="35"/>
+      <c r="H110" s="29"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
@@ -5593,10 +5593,10 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="25" t="s">
+      <c r="G111" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="H111" s="35"/>
+      <c r="H111" s="29"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="15" t="s">
@@ -5613,10 +5613,10 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="25" t="s">
+      <c r="G112" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="H112" s="35"/>
+      <c r="H112" s="29"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" s="14" t="s">
@@ -5635,10 +5635,10 @@
       <c r="F113" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G113" s="25" t="s">
+      <c r="G113" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="H113" s="35"/>
+      <c r="H113" s="29"/>
     </row>
     <row r="114" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A114" s="14" t="s">
@@ -5657,10 +5657,10 @@
       <c r="F114" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="G114" s="25" t="s">
+      <c r="G114" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="H114" s="35"/>
+      <c r="H114" s="29"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
@@ -5679,10 +5679,10 @@
       <c r="F115" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G115" s="25" t="s">
+      <c r="G115" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="H115" s="35"/>
+      <c r="H115" s="29"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
@@ -5701,10 +5701,10 @@
       <c r="F116" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G116" s="25" t="s">
+      <c r="G116" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="H116" s="35"/>
+      <c r="H116" s="29"/>
     </row>
     <row r="117" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A117" s="15" t="s">
@@ -5723,10 +5723,10 @@
       <c r="F117" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G117" s="25" t="s">
+      <c r="G117" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="H117" s="35"/>
+      <c r="H117" s="29"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="10" t="s">
@@ -5750,7 +5750,7 @@
       <c r="G118" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H118" s="31" t="s">
+      <c r="H118" s="26" t="s">
         <v>700</v>
       </c>
     </row>
@@ -5771,10 +5771,10 @@
       <c r="F119" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G119" s="25" t="s">
+      <c r="G119" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H119" s="35"/>
+      <c r="H119" s="29"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
@@ -5793,10 +5793,10 @@
       <c r="F120" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="G120" s="25" t="s">
+      <c r="G120" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H120" s="35"/>
+      <c r="H120" s="29"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
@@ -5815,10 +5815,10 @@
       <c r="F121" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="G121" s="25" t="s">
+      <c r="G121" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H121" s="35"/>
+      <c r="H121" s="29"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
@@ -5837,10 +5837,10 @@
       <c r="F122" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G122" s="25" t="s">
+      <c r="G122" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H122" s="35"/>
+      <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
@@ -5859,10 +5859,10 @@
       <c r="F123" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G123" s="25" t="s">
+      <c r="G123" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H123" s="35"/>
+      <c r="H123" s="29"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
@@ -5881,10 +5881,10 @@
       <c r="F124" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="G124" s="25" t="s">
+      <c r="G124" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H124" s="35"/>
+      <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
@@ -5903,10 +5903,10 @@
       <c r="F125" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="G125" s="25" t="s">
+      <c r="G125" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H125" s="35"/>
+      <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="13" t="s">
@@ -5925,10 +5925,10 @@
       <c r="F126" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="G126" s="25" t="s">
+      <c r="G126" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H126" s="35"/>
+      <c r="H126" s="29"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
@@ -5947,10 +5947,10 @@
       <c r="F127" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="G127" s="25" t="s">
+      <c r="G127" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H127" s="35"/>
+      <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A128" s="14" t="s">
@@ -5969,10 +5969,10 @@
       <c r="F128" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="G128" s="25" t="s">
+      <c r="G128" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H128" s="35"/>
+      <c r="H128" s="29"/>
     </row>
     <row r="129" spans="1:8" ht="108" x14ac:dyDescent="0.45">
       <c r="A129" s="14" t="s">
@@ -5991,10 +5991,10 @@
       <c r="F129" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="G129" s="25" t="s">
+      <c r="G129" s="20" t="s">
         <v>656</v>
       </c>
-      <c r="H129" s="35"/>
+      <c r="H129" s="29"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="10" t="s">
@@ -6018,7 +6018,7 @@
       <c r="G130" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H130" s="30" t="s">
+      <c r="H130" s="25" t="s">
         <v>700</v>
       </c>
     </row>
@@ -6039,10 +6039,10 @@
       <c r="F131" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G131" s="25" t="s">
+      <c r="G131" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="H131" s="35"/>
+      <c r="H131" s="29"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="13" t="s">
@@ -6059,10 +6059,10 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="25" t="s">
+      <c r="G132" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H132" s="35"/>
+      <c r="H132" s="29"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="12" t="s">
@@ -6079,10 +6079,10 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="25" t="s">
+      <c r="G133" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="H133" s="35"/>
+      <c r="H133" s="29"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
@@ -6101,10 +6101,10 @@
       <c r="F134" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G134" s="25" t="s">
+      <c r="G134" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="H134" s="35"/>
+      <c r="H134" s="29"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
@@ -6121,10 +6121,10 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="25" t="s">
+      <c r="G135" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="H135" s="35"/>
+      <c r="H135" s="29"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
@@ -6143,10 +6143,10 @@
       <c r="F136" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G136" s="25" t="s">
+      <c r="G136" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="H136" s="35"/>
+      <c r="H136" s="29"/>
     </row>
     <row r="137" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
@@ -6165,10 +6165,10 @@
       <c r="F137" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G137" s="25" t="s">
+      <c r="G137" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="H137" s="35"/>
+      <c r="H137" s="29"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
@@ -6189,10 +6189,10 @@
       <c r="F138" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G138" s="25" t="s">
+      <c r="G138" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="H138" s="35"/>
+      <c r="H138" s="29"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="14" t="s">
@@ -6211,10 +6211,10 @@
       <c r="F139" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G139" s="25" t="s">
+      <c r="G139" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="H139" s="35"/>
+      <c r="H139" s="29"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="14" t="s">
@@ -6233,10 +6233,10 @@
       <c r="F140" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G140" s="25" t="s">
+      <c r="G140" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="H140" s="35"/>
+      <c r="H140" s="29"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
@@ -6255,10 +6255,10 @@
       <c r="F141" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="G141" s="25" t="s">
+      <c r="G141" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="H141" s="35"/>
+      <c r="H141" s="29"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="14" t="s">
@@ -6277,10 +6277,10 @@
       <c r="F142" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="G142" s="25" t="s">
+      <c r="G142" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="H142" s="35"/>
+      <c r="H142" s="29"/>
     </row>
     <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A143" s="15" t="s">
@@ -6299,10 +6299,10 @@
       <c r="F143" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="G143" s="25" t="s">
+      <c r="G143" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="H143" s="35"/>
+      <c r="H143" s="29"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
@@ -6326,7 +6326,7 @@
       <c r="G144" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H144" s="32" t="s">
+      <c r="H144" s="27" t="s">
         <v>700</v>
       </c>
     </row>
@@ -6347,10 +6347,10 @@
       <c r="F145" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G145" s="25" t="s">
+      <c r="G145" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="H145" s="35"/>
+      <c r="H145" s="29"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
@@ -6369,10 +6369,10 @@
       <c r="F146" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G146" s="25" t="s">
+      <c r="G146" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="H146" s="35"/>
+      <c r="H146" s="29"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
@@ -6389,10 +6389,10 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="25" t="s">
+      <c r="G147" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="H147" s="35"/>
+      <c r="H147" s="29"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
@@ -6409,10 +6409,10 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="25" t="s">
+      <c r="G148" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="H148" s="35"/>
+      <c r="H148" s="29"/>
     </row>
     <row r="149" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
@@ -6431,10 +6431,10 @@
       <c r="F149" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="G149" s="25" t="s">
+      <c r="G149" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="H149" s="35"/>
+      <c r="H149" s="29"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="12" t="s">
@@ -6453,10 +6453,10 @@
       <c r="F150" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="G150" s="25" t="s">
+      <c r="G150" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="H150" s="35"/>
+      <c r="H150" s="29"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
@@ -6480,7 +6480,7 @@
       <c r="G151" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H151" s="32" t="s">
+      <c r="H151" s="27" t="s">
         <v>700</v>
       </c>
     </row>
@@ -6501,10 +6501,10 @@
       <c r="F152" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G152" s="25" t="s">
+      <c r="G152" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="H152" s="35"/>
+      <c r="H152" s="29"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="12" t="s">
@@ -6523,10 +6523,10 @@
       <c r="F153" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G153" s="25" t="s">
+      <c r="G153" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="H153" s="35"/>
+      <c r="H153" s="29"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="14" t="s">
@@ -6547,10 +6547,10 @@
       <c r="F154" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G154" s="25" t="s">
+      <c r="G154" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="H154" s="35"/>
+      <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
@@ -6571,10 +6571,10 @@
       <c r="F155" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G155" s="25" t="s">
+      <c r="G155" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="H155" s="35"/>
+      <c r="H155" s="29"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
@@ -6595,10 +6595,10 @@
       <c r="F156" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="G156" s="25" t="s">
+      <c r="G156" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="H156" s="35"/>
+      <c r="H156" s="29"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
@@ -6619,10 +6619,10 @@
       <c r="F157" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="G157" s="25" t="s">
+      <c r="G157" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H157" s="35"/>
+      <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
@@ -6643,10 +6643,10 @@
       <c r="F158" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G158" s="25" t="s">
+      <c r="G158" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H158" s="35"/>
+      <c r="H158" s="29"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="14" t="s">
@@ -6667,10 +6667,10 @@
       <c r="F159" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G159" s="25" t="s">
+      <c r="G159" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H159" s="35"/>
+      <c r="H159" s="29"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
@@ -6691,10 +6691,10 @@
       <c r="F160" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="G160" s="25" t="s">
+      <c r="G160" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H160" s="35"/>
+      <c r="H160" s="29"/>
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
@@ -6715,10 +6715,10 @@
       <c r="F161" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="G161" s="25" t="s">
+      <c r="G161" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H161" s="35"/>
+      <c r="H161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="14" t="s">
@@ -6739,10 +6739,10 @@
       <c r="F162" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G162" s="25" t="s">
+      <c r="G162" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H162" s="35"/>
+      <c r="H162" s="29"/>
     </row>
     <row r="163" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="15" t="s">
@@ -6763,10 +6763,10 @@
       <c r="F163" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G163" s="25" t="s">
+      <c r="G163" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="H163" s="35"/>
+      <c r="H163" s="29"/>
     </row>
     <row r="164" spans="1:10" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="15" t="s">
@@ -6787,10 +6787,10 @@
       <c r="F164" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G164" s="25" t="s">
+      <c r="G164" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H164" s="35"/>
+      <c r="H164" s="29"/>
     </row>
     <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="15" t="s">
@@ -6811,60 +6811,60 @@
       <c r="F165" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G165" s="25" t="s">
+      <c r="G165" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="H165" s="35"/>
+      <c r="H165" s="29"/>
     </row>
     <row r="166" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A166" s="37" t="s">
+      <c r="A166" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="B166" s="38" t="s">
+      <c r="B166" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C166" s="38" t="s">
+      <c r="C166" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D166" s="38" t="s">
+      <c r="D166" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E166" s="38" t="s">
+      <c r="E166" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F166" s="38" t="s">
+      <c r="F166" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="30" t="s">
+      <c r="G166" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H166" s="32" t="s">
+      <c r="H166" s="27" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A167" s="39" t="s">
+      <c r="A167" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="B167" s="40">
+      <c r="B167" s="34">
         <v>120</v>
       </c>
-      <c r="C167" s="40">
+      <c r="C167" s="34">
         <v>57</v>
       </c>
-      <c r="D167" s="40">
+      <c r="D167" s="34">
         <v>40</v>
       </c>
-      <c r="E167" s="41" t="s">
+      <c r="E167" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="F167" s="40" t="s">
+      <c r="F167" s="34" t="s">
         <v>686</v>
       </c>
-      <c r="G167" s="43" t="s">
+      <c r="G167" s="36" t="s">
         <v>379</v>
       </c>
-      <c r="H167" s="42" t="s">
+      <c r="H167" s="43" t="s">
         <v>701</v>
       </c>
     </row>
@@ -6885,8 +6885,8 @@
       <c r="F168" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="G168" s="44"/>
-      <c r="H168" s="19"/>
+      <c r="G168" s="37"/>
+      <c r="H168" s="44"/>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
@@ -6905,8 +6905,8 @@
       <c r="F169" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="G169" s="44"/>
-      <c r="H169" s="19"/>
+      <c r="G169" s="37"/>
+      <c r="H169" s="44"/>
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
@@ -6925,8 +6925,8 @@
       <c r="F170" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="G170" s="44"/>
-      <c r="H170" s="19"/>
+      <c r="G170" s="37"/>
+      <c r="H170" s="44"/>
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
@@ -6945,8 +6945,8 @@
       <c r="F171" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="G171" s="44"/>
-      <c r="H171" s="19"/>
+      <c r="G171" s="37"/>
+      <c r="H171" s="44"/>
     </row>
     <row r="172" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A172" s="12" t="s">
@@ -6965,8 +6965,8 @@
       <c r="F172" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="G172" s="44"/>
-      <c r="H172" s="19"/>
+      <c r="G172" s="37"/>
+      <c r="H172" s="44"/>
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
@@ -6985,9 +6985,9 @@
       <c r="F173" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="G173" s="44"/>
-      <c r="H173" s="19"/>
-      <c r="J173" s="33"/>
+      <c r="G173" s="37"/>
+      <c r="H173" s="44"/>
+      <c r="J173" s="28"/>
     </row>
     <row r="174" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="12" t="s">
@@ -7006,8 +7006,8 @@
       <c r="F174" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="G174" s="44"/>
-      <c r="H174" s="19"/>
+      <c r="G174" s="37"/>
+      <c r="H174" s="44"/>
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
@@ -7026,8 +7026,8 @@
       <c r="F175" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="G175" s="44"/>
-      <c r="H175" s="19"/>
+      <c r="G175" s="37"/>
+      <c r="H175" s="44"/>
     </row>
     <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
@@ -7046,8 +7046,8 @@
       <c r="F176" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G176" s="44"/>
-      <c r="H176" s="19"/>
+      <c r="G176" s="37"/>
+      <c r="H176" s="44"/>
     </row>
     <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A177" s="13" t="s">
@@ -7066,8 +7066,8 @@
       <c r="F177" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="G177" s="44"/>
-      <c r="H177" s="19"/>
+      <c r="G177" s="37"/>
+      <c r="H177" s="44"/>
     </row>
     <row r="178" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
@@ -7086,8 +7086,8 @@
       <c r="F178" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="G178" s="44"/>
-      <c r="H178" s="19"/>
+      <c r="G178" s="37"/>
+      <c r="H178" s="44"/>
     </row>
     <row r="179" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
@@ -7108,8 +7108,8 @@
       <c r="F179" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="G179" s="44"/>
-      <c r="H179" s="19"/>
+      <c r="G179" s="37"/>
+      <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
@@ -7130,8 +7130,8 @@
       <c r="F180" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="G180" s="44"/>
-      <c r="H180" s="19"/>
+      <c r="G180" s="37"/>
+      <c r="H180" s="44"/>
     </row>
     <row r="181" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
@@ -7150,8 +7150,8 @@
       <c r="F181" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="G181" s="44"/>
-      <c r="H181" s="19"/>
+      <c r="G181" s="37"/>
+      <c r="H181" s="44"/>
     </row>
     <row r="182" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" s="17" t="s">
@@ -7166,14 +7166,14 @@
       <c r="D182" s="18">
         <v>130</v>
       </c>
-      <c r="E182" s="36" t="s">
+      <c r="E182" s="30" t="s">
         <v>679</v>
       </c>
       <c r="F182" s="18" t="s">
         <v>699</v>
       </c>
-      <c r="G182" s="45"/>
-      <c r="H182" s="20"/>
+      <c r="G182" s="38"/>
+      <c r="H182" s="45"/>
     </row>
     <row r="186" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30143CDC-BF08-4B15-A546-D217D1FCDEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BB3CE9-6C11-4C9A-BD1C-0DF7E6BCB867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2221,7 +2221,7 @@
   </si>
   <si>
     <t>【地牢介绍】被弃地下城一共有三层，第二层比第一层多了狂热者和狂怒亵渎，然后第三层主要是领主和他的四个小弟；被弃地下城有普通模式和英雄模式，普通模式玩家死亡后可以返回捡尸体，地点冷却时间为8小时，而英雄模式玩家死亡后无法返回，物品将永远丢失，地点冷却时间为4小时
-【英雄模式的减益】英雄模式下的地牢会有4种随机减益，前2种为固定减益，后2种为随机减益
+【英雄模式的减益】英雄模式下的地牢会有4种减益，前2种为固定减益，后2种为随机减益
 （1）一条命：固定减益，死亡后无法返回地下城捡尸体
 （2）瘟疫崛起：固定减益，敌人可以复活
 （3）全速奔跑：随机减益，敌人移动速度增加35%

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BB3CE9-6C11-4C9A-BD1C-0DF7E6BCB867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A1D518-0BB6-4E58-A38C-A37AE54084AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2198,14 +2198,6 @@
     <t>场地机制</t>
   </si>
   <si>
-    <t>【场地机制】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
-【英雄模式玩家增益】玩家生命值增加40点；帐篷敌人不致命；敌人更容易受到火焰/冰冻/衰败伤害；玩家治疗效果提高20%
-【英雄模式玩家减益】无法使用食物、卷轴、狼和猫、任何药水（含投掷型）；回复能力降低3倍；生命值减少40点；防御力降低25%；无法使用陷阱或符文
-【英雄模式敌方强化】敌人生命值和回复能力增强；免疫冰冻、眩晕和恐惧；移动速度提高40%；视野范围增加30%；20%概率使用复活药（两条命）；造成的伤害增加20%；防御力提升25%
-【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
-【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。</t>
-  </si>
-  <si>
     <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，猎头者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，掷斧者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
 【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫
 【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
@@ -2230,6 +2222,40 @@
 （6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
 （7）被感染的空气：随机减益，角色最大生命值降低30
 （8）鹰眼：随机减益，敌人视野增加35%</t>
+  </si>
+  <si>
+    <t>【场地机制】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
+【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
+【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
+【英雄模式玩家增益】
+1.	良好体魄：玩家最大生命值增加40点
+2.	训练警报：帐篷中的敌人没那么致命
+3.	刺骨寒冰：敌人更容易受到寒冷伤害
+4.	炽焰：敌人更容易受到火焰伤害
+5.	衰败：敌人更容易受到衰败伤害
+6.	高效治疗：玩家治疗效果提高20%
+7.	治疗之风：每4秒恢复5生命值
+8.	尖锐尖刺：敌人在攻击你时会受到伤害
+9.	强力重击：玩家攻击造成额外20点伤害
+【英雄模式玩家减益】
+1.	损坏的药水：无法使用药水（包括投掷药水）
+2.	泛黄的卷轴：无法使用卷轴
+3.	胆小的动物：你的恐狼会逃跑，猫咪的被动技能不起作用
+4.	严格饮食：无法使用食物或水
+5.	开放性伤口：受到的治疗效果降低3倍
+6.	被感染的空气：玩家最大生命值减少40点
+7.	生锈护甲：玩家护甲（防御力）降低25%
+8.	无用的陷阱：无法使用陷阱或符文
+【英雄模式敌方强化】
+1.	强健体魄：敌人的生命值和治疗效果提高
+2.	失控的狂怒：敌人免疫冻结、眩晕和恐惧；
+3.	全速奔跑：敌人移动速度提高40%
+4.	警觉的守卫：敌人视野范围增加30%
+5.	绝处逢生：敌人有20%概率避免死亡并恢复生命值（两条命）
+6.	沉重打击：敌人造成的伤害增加20%
+7.	强悍护甲：敌人防御力提升35%
+8.	符文陷阱：地点中的符文数量增加
+9.	超自然反应：敌人有20%的机会躲避攻击</t>
   </si>
 </sst>
 </file>
@@ -3939,7 +3965,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4375,7 +4401,7 @@
         <v>141</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4645,7 +4671,7 @@
         <v>169</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
@@ -6865,7 +6891,7 @@
         <v>379</v>
       </c>
       <c r="H167" s="43" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A1D518-0BB6-4E58-A38C-A37AE54084AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9397AB-0E3B-42CD-9764-7DB02E31083A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2224,9 +2224,10 @@
 （8）鹰眼：随机减益，敌人视野增加35%</t>
   </si>
   <si>
-    <t>【场地机制】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
-【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
+    <t>【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
 【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
+【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
+【英雄模式buff和debuff介绍】英雄模式的增益和减益组合通常为：玩家增益+玩家减益+敌方强化；他们分别的介绍如下：
 【英雄模式玩家增益】
 1.	良好体魄：玩家最大生命值增加40点
 2.	训练警报：帐篷中的敌人没那么致命
@@ -2246,16 +2247,16 @@
 6.	被感染的空气：玩家最大生命值减少40点
 7.	生锈护甲：玩家护甲（防御力）降低25%
 8.	无用的陷阱：无法使用陷阱或符文
+9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧；
 【英雄模式敌方强化】
 1.	强健体魄：敌人的生命值和治疗效果提高
-2.	失控的狂怒：敌人免疫冻结、眩晕和恐惧；
-3.	全速奔跑：敌人移动速度提高40%
-4.	警觉的守卫：敌人视野范围增加30%
-5.	绝处逢生：敌人有20%概率避免死亡并恢复生命值（两条命）
-6.	沉重打击：敌人造成的伤害增加20%
-7.	强悍护甲：敌人防御力提升35%
-8.	符文陷阱：地点中的符文数量增加
-9.	超自然反应：敌人有20%的机会躲避攻击</t>
+2.	全速奔跑：敌人移动速度提高40%
+3.	警觉的守卫：敌人视野范围增加30%
+4.	绝处逢生：敌人有20%概率避免死亡并恢复生命值（两条命）
+5.	沉重打击：敌人造成的伤害增加20%
+6.	强悍护甲：敌人防御力提升35%
+7.	符文陷阱：地点中的符文数量增加
+8.	超自然反应：敌人有20%的机会躲避攻击</t>
   </si>
 </sst>
 </file>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9397AB-0E3B-42CD-9764-7DB02E31083A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F1633E-2DEC-487C-84AB-FBC3D24C6720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2198,32 +2198,6 @@
     <t>场地机制</t>
   </si>
   <si>
-    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，猎头者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，掷斧者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
-【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫
-【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
-（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
-（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
-（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
-【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破</t>
-  </si>
-  <si>
-    <t>【治疗效果降低】矿井内受黑暗力量影响,所有治疗手段效果压到三分之一，圣殿骑士套装可以免疫这个减益
-【玩家死亡】玩家死亡会回到码头，而不是河对岸的城堡，并且可以回去捡尸体
-【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血</t>
-  </si>
-  <si>
-    <t>【地牢介绍】被弃地下城一共有三层，第二层比第一层多了狂热者和狂怒亵渎，然后第三层主要是领主和他的四个小弟；被弃地下城有普通模式和英雄模式，普通模式玩家死亡后可以返回捡尸体，地点冷却时间为8小时，而英雄模式玩家死亡后无法返回，物品将永远丢失，地点冷却时间为4小时
-【英雄模式的减益】英雄模式下的地牢会有4种减益，前2种为固定减益，后2种为随机减益
-（1）一条命：固定减益，死亡后无法返回地下城捡尸体
-（2）瘟疫崛起：固定减益，敌人可以复活
-（3）全速奔跑：随机减益，敌人移动速度增加35%
-（4）超自然反应：随机减益，敌人有15%的机会躲避攻击
-（5）疯子的笑声：随机减益，陷阱数量增加
-（6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
-（7）被感染的空气：随机减益，角色最大生命值降低30
-（8）鹰眼：随机减益，敌人视野增加35%</t>
-  </si>
-  <si>
     <t>【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
 【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
 【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
@@ -2247,7 +2221,7 @@
 6.	被感染的空气：玩家最大生命值减少40点
 7.	生锈护甲：玩家护甲（防御力）降低25%
 8.	无用的陷阱：无法使用陷阱或符文
-9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧；
+9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧
 【英雄模式敌方强化】
 1.	强健体魄：敌人的生命值和治疗效果提高
 2.	全速奔跑：敌人移动速度提高40%
@@ -2257,6 +2231,32 @@
 6.	强悍护甲：敌人防御力提升35%
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有20%的机会躲避攻击</t>
+  </si>
+  <si>
+    <t>【治疗效果降低】矿井内受黑暗力量影响,所有治疗手段效果压到三分之一，圣殿骑士套装可以免疫这个减益。
+【玩家死亡】玩家死亡会回到码头，而不是河对岸的城堡，并且可以回去捡尸体。
+【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血。</t>
+  </si>
+  <si>
+    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，猎头者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，掷斧者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
+【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
+【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
+（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
+（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
+（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
+【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
+  </si>
+  <si>
+    <t>【地牢介绍】被弃地下城一共有三层，第二层比第一层多了狂热者和狂怒亵渎，然后第三层主要是领主和他的四个小弟；被弃地下城有普通模式和英雄模式，普通模式玩家死亡后可以返回捡尸体，地点冷却时间为8小时，而英雄模式玩家死亡后无法返回，物品将永远丢失，地点冷却时间为4小时。
+【英雄模式的减益】英雄模式下的地牢会有4种减益，前2种为固定减益，后2种为随机减益：
+（1）一条命：固定减益，死亡后无法返回地下城捡尸体
+（2）瘟疫崛起：固定减益，敌人可以复活
+（3）全速奔跑：随机减益，敌人移动速度增加35%
+（4）超自然反应：随机减益，敌人有15%的机会躲避攻击
+（5）疯子的笑声：随机减益，陷阱数量增加
+（6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
+（7）被感染的空气：随机减益，角色最大生命值降低30
+（8）鹰眼：随机减益，敌人视野增加35%</t>
   </si>
 </sst>
 </file>
@@ -3966,7 +3966,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4402,7 +4402,7 @@
         <v>141</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -6892,7 +6892,7 @@
         <v>379</v>
       </c>
       <c r="H167" s="43" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F1633E-2DEC-487C-84AB-FBC3D24C6720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9277BA3A-C9CD-4E97-B94D-CED14E09A712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2190,12 +2190,38 @@
 受伤后回血,单次上限100(超出部分每5秒补一次),累计400</t>
   </si>
   <si>
+    <t>场地机制</t>
+  </si>
+  <si>
+    <t>【治疗效果降低】矿井内受黑暗力量影响,所有治疗手段效果压到三分之一，圣殿骑士套装可以免疫这个减益。
+【玩家死亡】玩家死亡会回到码头，而不是河对岸的城堡，并且可以回去捡尸体。
+【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血。</t>
+  </si>
+  <si>
+    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，猎头者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，掷斧者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
+【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
+【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
+（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
+（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
+（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
+【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
+  </si>
+  <si>
+    <t>【地牢介绍】被弃地下城一共有三层，第二层比第一层多了狂热者和狂怒亵渎，然后第三层主要是领主和他的四个小弟；被弃地下城有普通模式和英雄模式，普通模式玩家死亡后可以返回捡尸体，地点冷却时间为8小时，而英雄模式玩家死亡后无法返回，物品将永远丢失，地点冷却时间为4小时。
+【英雄模式的减益】英雄模式下的地牢会有4种减益，前2种为固定减益，后2种为随机减益：
+（1）一条命：固定减益，死亡后无法返回地下城捡尸体
+（2）瘟疫崛起：固定减益，敌人可以复活
+（3）全速奔跑：随机减益，敌人移动速度增加35%
+（4）超自然反应：随机减益，敌人有15%的机会躲避攻击
+（5）疯子的笑声：随机减益，陷阱数量增加
+（6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
+（7）被感染的空气：随机减益，角色最大生命值降低30
+（8）鹰眼：随机减益，敌人视野增加35%</t>
+  </si>
+  <si>
     <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
 复活药1瓶；他的武器可以禁疗；受伤后回血,单次上限100(超出部分每5秒补一次),累计400
-可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；元素伤害减半</t>
-  </si>
-  <si>
-    <t>场地机制</t>
+可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；无元素抗性</t>
   </si>
   <si>
     <t>【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
@@ -2210,7 +2236,7 @@
 5.	衰败：敌人更容易受到衰败伤害
 6.	高效治疗：玩家治疗效果提高20%
 7.	治疗之风：每4秒恢复5生命值
-8.	尖锐尖刺：敌人在攻击你时会受到伤害
+8.	尖锐尖刺：敌人在攻击你时会受到固定10点伤害
 9.	强力重击：玩家攻击造成额外20点伤害
 【英雄模式玩家减益】
 1.	损坏的药水：无法使用药水（包括投掷药水）
@@ -2223,7 +2249,7 @@
 8.	无用的陷阱：无法使用陷阱或符文
 9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧
 【英雄模式敌方强化】
-1.	强健体魄：敌人的生命值和治疗效果提高
+1.	强健体魄：敌人的生命值提高10%，治疗效果也提高
 2.	全速奔跑：敌人移动速度提高40%
 3.	警觉的守卫：敌人视野范围增加30%
 4.	绝处逢生：敌人有20%概率避免死亡并恢复生命值（两条命）
@@ -2231,32 +2257,6 @@
 6.	强悍护甲：敌人防御力提升35%
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有20%的机会躲避攻击</t>
-  </si>
-  <si>
-    <t>【治疗效果降低】矿井内受黑暗力量影响,所有治疗手段效果压到三分之一，圣殿骑士套装可以免疫这个减益。
-【玩家死亡】玩家死亡会回到码头，而不是河对岸的城堡，并且可以回去捡尸体。
-【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血。</t>
-  </si>
-  <si>
-    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，猎头者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，掷斧者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
-【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
-【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
-（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
-（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
-（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
-【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
-  </si>
-  <si>
-    <t>【地牢介绍】被弃地下城一共有三层，第二层比第一层多了狂热者和狂怒亵渎，然后第三层主要是领主和他的四个小弟；被弃地下城有普通模式和英雄模式，普通模式玩家死亡后可以返回捡尸体，地点冷却时间为8小时，而英雄模式玩家死亡后无法返回，物品将永远丢失，地点冷却时间为4小时。
-【英雄模式的减益】英雄模式下的地牢会有4种减益，前2种为固定减益，后2种为随机减益：
-（1）一条命：固定减益，死亡后无法返回地下城捡尸体
-（2）瘟疫崛起：固定减益，敌人可以复活
-（3）全速奔跑：随机减益，敌人移动速度增加35%
-（4）超自然反应：随机减益，敌人有15%的机会躲避攻击
-（5）疯子的笑声：随机减益，陷阱数量增加
-（6）生锈的锁：随机减益，打开宝箱和门所花费的时间增加150%，打开门的范围减小
-（7）被感染的空气：随机减益，角色最大生命值降低30
-（8）鹰眼：随机减益，敌人视野增加35%</t>
   </si>
 </sst>
 </file>
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3308,7 +3308,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3944,7 +3944,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -3966,7 +3966,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4378,7 +4378,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
@@ -4402,7 +4402,7 @@
         <v>141</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4648,7 +4648,7 @@
         <v>6</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -4672,7 +4672,7 @@
         <v>169</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
@@ -4764,7 +4764,7 @@
         <v>6</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -4852,7 +4852,7 @@
         <v>6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
@@ -5146,7 +5146,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
@@ -5778,7 +5778,7 @@
         <v>6</v>
       </c>
       <c r="H118" s="26" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
@@ -6046,7 +6046,7 @@
         <v>6</v>
       </c>
       <c r="H130" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
@@ -6354,7 +6354,7 @@
         <v>6</v>
       </c>
       <c r="H144" s="27" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
@@ -6508,7 +6508,7 @@
         <v>6</v>
       </c>
       <c r="H151" s="27" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
@@ -6866,7 +6866,7 @@
         <v>6</v>
       </c>
       <c r="H166" s="27" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6892,7 +6892,7 @@
         <v>379</v>
       </c>
       <c r="H167" s="43" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -7197,7 +7197,7 @@
         <v>679</v>
       </c>
       <c r="F182" s="18" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="G182" s="38"/>
       <c r="H182" s="45"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9277BA3A-C9CD-4E97-B94D-CED14E09A712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5346800-4C4F-4BDE-8CB3-7BA7F21B8A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="706">
   <si>
     <t>家里</t>
   </si>
@@ -2024,13 +2024,7 @@
     <t>取决于爆炸距离</t>
   </si>
   <si>
-    <t>继母艾莎+5级图的蝙蝠</t>
-  </si>
-  <si>
     <t>继母艾莎</t>
-  </si>
-  <si>
-    <t>继母艾莎；5级图</t>
   </si>
   <si>
     <t>荒废墓穴；继母艾莎；夜晚地窖；
@@ -2257,6 +2251,15 @@
 6.	强悍护甲：敌人防御力提升35%
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有20%的机会躲避攻击</t>
+  </si>
+  <si>
+    <t>继母艾莎蝙蝠</t>
+  </si>
+  <si>
+    <t>5级图的蝙蝠</t>
+  </si>
+  <si>
+    <t>5级图</t>
   </si>
 </sst>
 </file>
@@ -3213,7 +3216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
@@ -3260,7 +3263,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3308,7 +3311,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3415,7 +3418,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>649</v>
+        <v>703</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3431,296 +3434,296 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>24</v>
+        <v>704</v>
       </c>
       <c r="B11" s="2">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="20"/>
+      <c r="F11" s="20" t="s">
+        <v>23</v>
+      </c>
       <c r="G11" s="23" t="s">
-        <v>25</v>
+        <v>705</v>
       </c>
       <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="20"/>
       <c r="G12" s="23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="20"/>
       <c r="G13" s="23" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="D14" s="2">
+        <v>70</v>
+      </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="20" t="s">
-        <v>30</v>
-      </c>
+      <c r="F14" s="20"/>
       <c r="G14" s="23" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
-      <c r="D15" s="2">
-        <v>9</v>
-      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="20"/>
+      <c r="F15" s="20" t="s">
+        <v>30</v>
+      </c>
       <c r="G15" s="23" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
       <c r="D16" s="2">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="20" t="s">
-        <v>34</v>
-      </c>
+      <c r="F16" s="20"/>
       <c r="G16" s="23" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H16" s="29"/>
     </row>
-    <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="20"/>
+      <c r="F17" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="G17" s="23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="2">
+        <v>125</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A19" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B19" s="2">
         <v>95</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C19" s="2">
         <v>23</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
         <v>32</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="20" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G19" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="29"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="12" t="s">
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B20" s="2">
         <v>90</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2">
-        <v>15</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="29"/>
-    </row>
-    <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A20" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="2">
-        <v>70</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>44</v>
+      <c r="D20" s="2">
+        <v>15</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="20" t="s">
-        <v>45</v>
-      </c>
+      <c r="F20" s="20"/>
       <c r="G20" s="23" t="s">
-        <v>652</v>
+        <v>42</v>
       </c>
       <c r="H20" s="29"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
-      <c r="D21" s="2">
-        <v>10</v>
+      <c r="D21" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="20"/>
+      <c r="F21" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="G21" s="23" t="s">
-        <v>47</v>
+        <v>650</v>
       </c>
       <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="2">
+        <v>300</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="29"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" s="2">
-        <v>100</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H22" s="29"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="B23" s="2">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2">
-        <v>90</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>9</v>
@@ -3729,415 +3732,415 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="C25" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B26" s="2">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D26" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>64</v>
+      <c r="F26" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>61</v>
       </c>
       <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D27" s="2">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>64</v>
       </c>
       <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2">
+        <v>300</v>
+      </c>
+      <c r="C28" s="2">
+        <v>47</v>
+      </c>
+      <c r="D28" s="2">
+        <v>70</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="29"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B29" s="2">
         <v>2800</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="29"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="2">
-        <v>1000</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B30" s="2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="C30" s="2">
-        <v>37</v>
-      </c>
-      <c r="D30" s="2">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H30" s="29"/>
     </row>
-    <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B31" s="2">
-        <v>760</v>
+        <v>900</v>
       </c>
       <c r="C31" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A32" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B32" s="2">
-        <v>2000</v>
+        <v>760</v>
       </c>
       <c r="C32" s="2">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D32" s="2">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H32" s="29"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A33" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>646</v>
+    <row r="33" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A33" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C33" s="2">
+        <v>11</v>
       </c>
       <c r="D33" s="2">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="29"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A34" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D34" s="2">
+        <v>24</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G34" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="H33" s="29"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A34" s="10" t="s">
+      <c r="H34" s="29"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A35" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G35" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="2">
-        <v>50</v>
-      </c>
-      <c r="C35" s="2">
-        <v>16</v>
-      </c>
-      <c r="D35" s="2">
-        <v>10</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" s="46" t="s">
-        <v>702</v>
+      <c r="H35" s="11" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B36" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C36" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D36" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" s="47"/>
+        <v>90</v>
+      </c>
+      <c r="H36" s="46" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B37" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C37" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H37" s="47"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B38" s="2">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D38" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H38" s="47"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B39" s="2">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="C39" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="F39" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="G39" s="20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H39" s="47"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B40" s="2">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>648</v>
+        <v>30</v>
+      </c>
+      <c r="D40" s="2">
+        <v>51</v>
       </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
-        <v>101</v>
-      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H40" s="47"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B41" s="2">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="C41" s="2">
-        <v>44</v>
-      </c>
-      <c r="D41" s="2">
-        <v>60</v>
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>648</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="F41" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="G41" s="20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H41" s="47"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B42" s="2">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D42" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H42" s="47"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="2">
+        <v>100</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="H42" s="47"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B43" s="2">
-        <v>400</v>
-      </c>
-      <c r="C43" s="2">
-        <v>44</v>
-      </c>
-      <c r="D43" s="2">
-        <v>60</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>109</v>
       </c>
       <c r="H43" s="47"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>684</v>
+        <v>107</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4146,55 +4149,55 @@
         <v>44</v>
       </c>
       <c r="D44" s="2">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H44" s="47"/>
     </row>
-    <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B45" s="2">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D45" s="2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H45" s="47"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B46" s="2">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="C46" s="2">
+        <v>52</v>
+      </c>
+      <c r="D46" s="2">
         <v>60</v>
-      </c>
-      <c r="D46" s="2">
-        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G46" s="20" t="s">
         <v>115</v>
@@ -4203,602 +4206,604 @@
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
-        <v>118</v>
+        <v>680</v>
       </c>
       <c r="B47" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C47" s="2">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D47" s="2">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G47" s="20" t="s">
         <v>115</v>
       </c>
       <c r="H47" s="47"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A48" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B48" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="C48" s="2">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D48" s="2">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="H48" s="47"/>
     </row>
-    <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A49" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>124</v>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A49" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" s="2">
+        <v>600</v>
+      </c>
+      <c r="C49" s="2">
+        <v>55</v>
       </c>
       <c r="D49" s="2">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="H49" s="47"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A50" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="2">
-        <v>1750</v>
-      </c>
-      <c r="C50" s="2">
-        <v>42</v>
+        <v>122</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D50" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H50" s="47"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B51" s="2">
-        <v>900</v>
+        <v>1750</v>
       </c>
       <c r="C51" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D51" s="2">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H51" s="47"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B52" s="2">
-        <v>1750</v>
+        <v>900</v>
       </c>
       <c r="C52" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D52" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H52" s="47"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B53" s="2">
-        <v>1600</v>
+        <v>1750</v>
       </c>
       <c r="C53" s="2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D53" s="2">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H53" s="47"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A54" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1600</v>
+      </c>
+      <c r="C54" s="2">
+        <v>55</v>
+      </c>
+      <c r="D54" s="2">
+        <v>72</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="G54" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H53" s="48"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A54" s="10" t="s">
+      <c r="H54" s="48"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A55" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H54" s="11" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A55" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B55" s="2">
-        <v>180</v>
-      </c>
-      <c r="C55" s="2">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>50</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="H55" s="46" t="s">
-        <v>701</v>
+      <c r="H55" s="11" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B56" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="H56" s="47"/>
+        <v>141</v>
+      </c>
+      <c r="H56" s="46" t="s">
+        <v>699</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B57" s="2">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
       </c>
       <c r="D57" s="2">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H57" s="47"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B58" s="2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
       </c>
       <c r="D58" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H58" s="47"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B59" s="2">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H59" s="47"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B60" s="2">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="C60" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D60" s="2">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H60" s="47"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B61" s="2">
         <v>350</v>
       </c>
       <c r="C61" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D61" s="2">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H61" s="47"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A62" s="13" t="s">
-        <v>157</v>
+      <c r="A62" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="B62" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="C62" s="2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D62" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="H62" s="47"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B63" s="2">
         <v>300</v>
       </c>
       <c r="C63" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D63" s="2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H63" s="47"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="13" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B64" s="2">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="C64" s="2">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="D64" s="2">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H64" s="47"/>
     </row>
-    <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
-      <c r="A65" s="15" t="s">
-        <v>165</v>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A65" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="B65" s="2">
-        <v>10000</v>
+        <v>175</v>
       </c>
       <c r="C65" s="2">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>677</v>
+        <v>93</v>
+      </c>
+      <c r="D65" s="2">
+        <v>65</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>685</v>
+        <v>164</v>
       </c>
       <c r="G65" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H65" s="47"/>
+    </row>
+    <row r="66" spans="1:8" ht="162" x14ac:dyDescent="0.45">
+      <c r="A66" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B66" s="2">
+        <v>10000</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="G66" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="H65" s="48"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A66" s="10" t="s">
+      <c r="H66" s="48"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A67" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D67" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G67" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H66" s="25" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A67" s="12" t="s">
+      <c r="H67" s="25" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A68" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B68" s="2">
         <v>335</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C68" s="2">
         <v>48</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D68" s="2">
         <v>100</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="G67" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="H67" s="49" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A68" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B68" s="2">
-        <v>450</v>
-      </c>
-      <c r="C68" s="2">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2">
-        <v>500</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="H68" s="47"/>
-    </row>
-    <row r="69" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A69" s="13" t="s">
-        <v>172</v>
+      <c r="H68" s="49" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A69" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="B69" s="2">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D69" s="2">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>169</v>
       </c>
       <c r="H69" s="47"/>
     </row>
-    <row r="70" spans="1:8" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A70" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B70" s="2">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="C70" s="2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D70" s="2">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>169</v>
       </c>
       <c r="H70" s="47"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A71" s="10" t="s">
+    <row r="71" spans="1:8" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C71" s="2">
+        <v>42</v>
+      </c>
+      <c r="D71" s="2">
+        <v>200</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H71" s="47"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A72" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B72" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C72" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D72" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G72" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H71" s="26" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A72" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B72" s="2">
-        <v>60</v>
-      </c>
-      <c r="C72" s="2">
-        <v>0</v>
-      </c>
-      <c r="D72" s="2">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H72" s="29"/>
+      <c r="H72" s="26" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B73" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C73" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D73" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
@@ -4809,92 +4814,88 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B74" s="2">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C74" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D74" s="2">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E74" s="2"/>
-      <c r="F74" s="2" t="s">
-        <v>180</v>
-      </c>
+      <c r="F74" s="2"/>
       <c r="G74" s="20" t="s">
         <v>176</v>
       </c>
       <c r="H74" s="29"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" s="2">
+        <v>30</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="H75" s="29"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A76" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B76" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C76" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D76" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G76" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H75" s="11" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A76" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B76" s="2">
-        <v>800</v>
-      </c>
-      <c r="C76" s="2">
-        <v>64</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G76" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H76" s="29"/>
+      <c r="H76" s="11" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B77" s="2">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="C77" s="2">
-        <v>23</v>
-      </c>
-      <c r="D77" s="2">
-        <v>30</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>187</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G77" s="20" t="s">
         <v>185</v>
@@ -4903,22 +4904,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B78" s="2">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="C78" s="2">
         <v>23</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>191</v>
+      <c r="D78" s="2">
+        <v>30</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G78" s="20" t="s">
         <v>185</v>
@@ -4927,20 +4928,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B79" s="2">
         <v>800</v>
       </c>
       <c r="C79" s="2">
-        <v>78</v>
-      </c>
-      <c r="D79" s="2">
-        <v>70</v>
-      </c>
-      <c r="E79" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>191</v>
+      </c>
       <c r="F79" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>185</v>
@@ -4949,20 +4952,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+      <c r="B80" s="2">
+        <v>800</v>
       </c>
       <c r="C80" s="2">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D80" s="2">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G80" s="20" t="s">
         <v>185</v>
@@ -4971,20 +4974,20 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>666</v>
+        <v>195</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
       </c>
       <c r="D81" s="2">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G81" s="20" t="s">
         <v>185</v>
@@ -4993,20 +4996,20 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C82" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D82" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G82" s="20" t="s">
         <v>185</v>
@@ -5014,21 +5017,21 @@
       <c r="H82" s="29"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A83" s="16" t="s">
-        <v>204</v>
+      <c r="A83" s="12" t="s">
+        <v>665</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C83" s="2">
-        <v>55</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>206</v>
+        <v>24</v>
+      </c>
+      <c r="D83" s="2">
+        <v>64</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G83" s="20" t="s">
         <v>185</v>
@@ -5037,20 +5040,20 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="16" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C84" s="2">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G84" s="20" t="s">
         <v>185</v>
@@ -5059,7 +5062,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>209</v>
@@ -5067,133 +5070,135 @@
       <c r="C85" s="2">
         <v>38</v>
       </c>
-      <c r="D85" s="2">
-        <v>125</v>
+      <c r="D85" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G85" s="20" t="s">
         <v>185</v>
       </c>
       <c r="H85" s="29"/>
     </row>
-    <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A86" s="15" t="s">
-        <v>214</v>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A86" s="16" t="s">
+        <v>212</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C86" s="2">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D86" s="2">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G86" s="20" t="s">
         <v>185</v>
       </c>
       <c r="H86" s="29"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="B87" s="2">
+        <v>214</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C87" s="2">
+        <v>60</v>
+      </c>
+      <c r="D87" s="2">
         <v>250</v>
-      </c>
-      <c r="C87" s="2">
-        <v>0</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G87" s="20" t="s">
         <v>185</v>
       </c>
       <c r="H87" s="29"/>
     </row>
-    <row r="88" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="10" t="s">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A88" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="2">
+        <v>250</v>
+      </c>
+      <c r="C88" s="2">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="H88" s="29"/>
+    </row>
+    <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B89" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C89" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D89" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E89" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F89" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G89" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H88" s="25" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A89" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B89" s="2">
-        <v>25</v>
-      </c>
-      <c r="C89" s="2">
-        <v>0</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G89" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="H89" s="29"/>
+      <c r="H89" s="25" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B90" s="2">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="C90" s="2">
-        <v>55</v>
-      </c>
-      <c r="D90" s="2">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
+      <c r="F90" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G90" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H90" s="29"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -5202,18 +5207,18 @@
         <v>55</v>
       </c>
       <c r="D91" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H91" s="29"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -5222,7 +5227,7 @@
         <v>55</v>
       </c>
       <c r="D92" s="2">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -5233,7 +5238,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -5242,7 +5247,7 @@
         <v>55</v>
       </c>
       <c r="D93" s="2">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
@@ -5253,210 +5258,208 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B94" s="2">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C94" s="2">
-        <v>0</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>229</v>
+        <v>55</v>
+      </c>
+      <c r="D94" s="2">
+        <v>59</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="F94" s="2"/>
       <c r="G94" s="20" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H94" s="29"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B95" s="2">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C95" s="2">
-        <v>37</v>
-      </c>
-      <c r="D95" s="2">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
+      <c r="F95" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="G95" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H95" s="29"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B96" s="2">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="C96" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D96" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E96" s="2"/>
-      <c r="F96" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="F96" s="2"/>
       <c r="G96" s="20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H96" s="29"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B97" s="2">
-        <v>2000</v>
+        <v>60</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
       </c>
       <c r="D97" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
+      <c r="F97" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="G97" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H97" s="29"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B98" s="2">
-        <v>550</v>
+        <v>2000</v>
       </c>
       <c r="C98" s="2">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D98" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H98" s="29"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B99" s="2">
-        <v>40</v>
+        <v>550</v>
       </c>
       <c r="C99" s="2">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>242</v>
+        <v>63</v>
+      </c>
+      <c r="D99" s="2">
+        <v>70</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="20" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D100" s="2">
-        <v>62</v>
+        <v>241</v>
+      </c>
+      <c r="B100" s="2">
+        <v>40</v>
+      </c>
+      <c r="C100" s="2">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="E100" s="2"/>
-      <c r="F100" s="2" t="s">
-        <v>245</v>
-      </c>
+      <c r="F100" s="2"/>
       <c r="G100" s="20" t="s">
         <v>243</v>
       </c>
       <c r="H100" s="29"/>
     </row>
-    <row r="101" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="B101" s="2">
-        <v>150</v>
-      </c>
-      <c r="C101" s="2">
-        <v>23</v>
+        <v>244</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="D101" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H101" s="29"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B102" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="C102" s="2">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="D102" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B103" s="2">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="C103" s="2">
         <v>74</v>
       </c>
       <c r="D103" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>251</v>
@@ -5464,99 +5467,101 @@
       <c r="H103" s="29"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A104" s="13" t="s">
-        <v>254</v>
+      <c r="A104" s="12" t="s">
+        <v>252</v>
       </c>
       <c r="B104" s="2">
-        <v>300</v>
+        <v>185</v>
       </c>
       <c r="C104" s="2">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>646</v>
+        <v>74</v>
+      </c>
+      <c r="D104" s="2">
+        <v>50</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H104" s="29"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="13" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B105" s="2">
         <v>300</v>
       </c>
       <c r="C105" s="2">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="H105" s="29"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A106" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B106" s="2">
+        <v>300</v>
+      </c>
+      <c r="C106" s="2">
         <v>30</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D106" s="2">
         <v>40</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="H105" s="29"/>
-    </row>
-    <row r="106" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A106" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B106" s="2">
-        <v>500</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D106" s="2">
-        <v>36</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H106" s="29"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C107" s="2">
-        <v>0</v>
+        <v>259</v>
+      </c>
+      <c r="B107" s="2">
+        <v>500</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="D107" s="2">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H107" s="29"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>635</v>
+      <c r="C108" s="2">
+        <v>0</v>
       </c>
       <c r="D108" s="2">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -5567,7 +5572,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>635</v>
@@ -5575,8 +5580,8 @@
       <c r="C109" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>635</v>
+      <c r="D109" s="2">
+        <v>72</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5586,568 +5591,568 @@
       <c r="H109" s="29"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B110" s="2">
-        <v>300</v>
-      </c>
-      <c r="C110" s="2">
-        <v>20</v>
-      </c>
-      <c r="D110" s="2">
-        <v>20</v>
+      <c r="A110" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="20" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H110" s="29"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A111" s="14" t="s">
-        <v>268</v>
+      <c r="A111" s="13" t="s">
+        <v>266</v>
       </c>
       <c r="B111" s="2">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C111" s="2">
         <v>20</v>
       </c>
       <c r="D111" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H111" s="29"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A112" s="15" t="s">
-        <v>270</v>
+      <c r="A112" s="14" t="s">
+        <v>268</v>
       </c>
       <c r="B112" s="2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="C112" s="2">
         <v>20</v>
       </c>
       <c r="D112" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="H112" s="29"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B113" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C113" s="2">
+        <v>20</v>
+      </c>
+      <c r="D113" s="2">
+        <v>29</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="H112" s="29"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A113" s="14" t="s">
+      <c r="H113" s="29"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B114" s="2">
         <v>450</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C114" s="2">
         <v>69</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G113" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="H113" s="29"/>
-    </row>
-    <row r="114" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A114" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="B114" s="2">
-        <v>2500</v>
-      </c>
-      <c r="C114" s="2">
-        <v>23</v>
-      </c>
-      <c r="D114" s="2">
-        <v>55</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="H114" s="29"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B115" s="2">
-        <v>9000</v>
+        <v>2500</v>
       </c>
       <c r="C115" s="2">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D115" s="2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="H115" s="29"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B116" s="2">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="C116" s="2">
-        <v>0</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>281</v>
+        <v>54</v>
+      </c>
+      <c r="D116" s="2">
+        <v>40</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="H116" s="29"/>
     </row>
-    <row r="117" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A117" s="15" t="s">
-        <v>650</v>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" s="14" t="s">
+        <v>280</v>
       </c>
       <c r="B117" s="2">
-        <v>1700</v>
+        <v>10500</v>
       </c>
       <c r="C117" s="2">
-        <v>67</v>
-      </c>
-      <c r="D117" s="2">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G117" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="H117" s="29"/>
+    </row>
+    <row r="118" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A118" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="B118" s="2">
+        <v>1700</v>
+      </c>
+      <c r="C118" s="2">
+        <v>67</v>
+      </c>
+      <c r="D118" s="2">
+        <v>90</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G117" s="20" t="s">
+      <c r="G118" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="H117" s="29"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A118" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="B118" s="4" t="s">
+      <c r="H118" s="29"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="B119" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C119" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D119" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="E119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F119" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G118" s="11" t="s">
+      <c r="G119" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H118" s="26" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A119" s="12" t="s">
-        <v>668</v>
-      </c>
-      <c r="B119" s="2">
-        <v>75</v>
-      </c>
-      <c r="C119" s="2">
-        <v>0</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="G119" s="20" t="s">
-        <v>656</v>
-      </c>
-      <c r="H119" s="29"/>
+      <c r="H119" s="26" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B120" s="2">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
       </c>
-      <c r="D120" s="2">
-        <v>5</v>
+      <c r="D120" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H120" s="29"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B121" s="2">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="C121" s="2">
         <v>0</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>654</v>
+      <c r="D121" s="2">
+        <v>5</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H121" s="29"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>292</v>
+        <v>668</v>
       </c>
       <c r="B122" s="2">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C122" s="2">
-        <v>24</v>
-      </c>
-      <c r="D122" s="2">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B123" s="2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C123" s="2">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D123" s="2">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H123" s="29"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>671</v>
+        <v>294</v>
       </c>
       <c r="B124" s="2">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="C124" s="2">
-        <v>0</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>654</v>
+        <v>48</v>
+      </c>
+      <c r="D124" s="2">
+        <v>130</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B125" s="2">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C125" s="2">
         <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A126" s="13" t="s">
-        <v>658</v>
+      <c r="A126" s="12" t="s">
+        <v>670</v>
       </c>
       <c r="B126" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C126" s="2">
-        <v>9</v>
-      </c>
-      <c r="D126" s="2">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="G126" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="H126" s="29"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A127" s="13" t="s">
         <v>656</v>
       </c>
-      <c r="H126" s="29"/>
-    </row>
-    <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A127" s="13" t="s">
-        <v>662</v>
-      </c>
       <c r="B127" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C127" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A128" s="14" t="s">
-        <v>664</v>
+      <c r="A128" s="13" t="s">
+        <v>660</v>
       </c>
       <c r="B128" s="2">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C128" s="2">
-        <v>66</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>646</v>
+        <v>24</v>
+      </c>
+      <c r="D128" s="2">
+        <v>35</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H128" s="29"/>
     </row>
-    <row r="129" spans="1:8" ht="108" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A129" s="14" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="B129" s="2">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="C129" s="2">
-        <v>58</v>
-      </c>
-      <c r="D129" s="2">
-        <v>120</v>
+        <v>66</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H129" s="29"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A130" s="10" t="s">
+    <row r="130" spans="1:8" ht="108" x14ac:dyDescent="0.45">
+      <c r="A130" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="B130" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C130" s="2">
+        <v>58</v>
+      </c>
+      <c r="D130" s="2">
+        <v>120</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="H130" s="29"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A131" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B131" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C131" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D131" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="E131" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="F131" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G130" s="11" t="s">
+      <c r="G131" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H130" s="25" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="12" t="s">
+      <c r="H131" s="25" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B132" s="2">
         <v>50</v>
-      </c>
-      <c r="C131" s="2">
-        <v>0</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G131" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="H131" s="29"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A132" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B132" s="2">
-        <v>900</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
       </c>
-      <c r="D132" s="2">
-        <v>20</v>
+      <c r="D132" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
+      <c r="F132" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="G132" s="20" t="s">
-        <v>72</v>
+        <v>290</v>
       </c>
       <c r="H132" s="29"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A133" s="12" t="s">
-        <v>295</v>
+      <c r="A133" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="B133" s="2">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>635</v>
+      <c r="D133" s="2">
+        <v>20</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="20" t="s">
-        <v>296</v>
+        <v>72</v>
       </c>
       <c r="H133" s="29"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B134" s="2">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
       </c>
-      <c r="D134" s="2">
-        <v>5</v>
+      <c r="D134" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="E134" s="2"/>
-      <c r="F134" s="2" t="s">
-        <v>298</v>
-      </c>
+      <c r="F134" s="2"/>
       <c r="G134" s="20" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H134" s="29"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B135" s="2">
-        <v>200</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>635</v>
+        <v>45</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2">
+        <v>5</v>
       </c>
       <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
+      <c r="F135" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="G135" s="20" t="s">
         <v>299</v>
       </c>
@@ -6155,66 +6160,62 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B136" s="2">
-        <v>600</v>
-      </c>
-      <c r="C136" s="2">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>635</v>
       </c>
       <c r="E136" s="2"/>
-      <c r="F136" s="2" t="s">
-        <v>302</v>
-      </c>
+      <c r="F136" s="2"/>
       <c r="G136" s="20" t="s">
         <v>299</v>
       </c>
       <c r="H136" s="29"/>
     </row>
-    <row r="137" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B137" s="2">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="C137" s="2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>635</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H137" s="29"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A138" s="13" t="s">
-        <v>306</v>
+    <row r="138" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A138" s="12" t="s">
+        <v>303</v>
       </c>
       <c r="B138" s="2">
         <v>1500</v>
       </c>
       <c r="C138" s="2">
-        <v>48</v>
-      </c>
-      <c r="D138" s="2">
-        <v>100</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>307</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G138" s="20" t="s">
         <v>305</v>
@@ -6222,179 +6223,181 @@
       <c r="H138" s="29"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A139" s="14" t="s">
-        <v>309</v>
+      <c r="A139" s="13" t="s">
+        <v>306</v>
       </c>
       <c r="B139" s="2">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="C139" s="2">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D139" s="2">
-        <v>9</v>
-      </c>
-      <c r="E139" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>307</v>
+      </c>
       <c r="F139" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="H139" s="29"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B140" s="2">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="C140" s="2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D140" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="G140" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H140" s="29"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B141" s="2">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="C141" s="2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D141" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H141" s="29"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="14" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B142" s="2">
-        <v>720</v>
+        <v>150</v>
       </c>
       <c r="C142" s="2">
         <v>0</v>
       </c>
       <c r="D142" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G142" s="20" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A143" s="15" t="s">
-        <v>320</v>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A143" s="14" t="s">
+        <v>317</v>
       </c>
       <c r="B143" s="2">
-        <v>2000</v>
+        <v>720</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
       <c r="D143" s="2">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G143" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="H143" s="29"/>
+    </row>
+    <row r="144" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A144" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2">
+        <v>57</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="G143" s="20" t="s">
+      <c r="G144" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="H143" s="29"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A144" s="10" t="s">
+      <c r="H144" s="29"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A145" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B145" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C145" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D145" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E144" s="4" t="s">
+      <c r="E145" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F144" s="4" t="s">
+      <c r="F145" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="11" t="s">
+      <c r="G145" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H144" s="27" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A145" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="B145" s="2">
-        <v>400</v>
-      </c>
-      <c r="C145" s="2">
-        <v>0</v>
-      </c>
-      <c r="D145" s="2">
-        <v>99</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="G145" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="H145" s="29"/>
+      <c r="H145" s="27" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B146" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="C146" s="2">
         <v>0</v>
       </c>
-      <c r="D146" s="2" t="s">
-        <v>646</v>
+      <c r="D146" s="2">
+        <v>99</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G146" s="20" t="s">
         <v>322</v>
@@ -6403,36 +6406,38 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B147" s="2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C147" s="2">
         <v>0</v>
       </c>
-      <c r="D147" s="2">
-        <v>14</v>
+      <c r="D147" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
+      <c r="F147" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="G147" s="20" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H147" s="29"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B148" s="2">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="C148" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D148" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -6441,147 +6446,143 @@
       </c>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="2">
+        <v>180</v>
+      </c>
+      <c r="C149" s="2">
+        <v>15</v>
+      </c>
+      <c r="D149" s="2">
+        <v>54</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="H149" s="29"/>
+    </row>
+    <row r="150" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A150" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B150" s="2">
         <v>40</v>
-      </c>
-      <c r="C149" s="2">
-        <v>0</v>
-      </c>
-      <c r="D149" s="2">
-        <v>5</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G149" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="H149" s="29"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A150" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B150" s="2">
-        <v>100</v>
       </c>
       <c r="C150" s="2">
         <v>0</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>646</v>
+      <c r="D150" s="2">
+        <v>5</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G150" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="H150" s="29"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A151" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="2">
+        <v>100</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="G150" s="20" t="s">
+      <c r="G151" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="H150" s="29"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A151" s="10" t="s">
+      <c r="H151" s="29"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A152" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B152" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C152" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D152" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="E152" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="F152" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G151" s="11" t="s">
+      <c r="G152" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H151" s="27" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A152" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C152" s="2">
-        <v>0</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="G152" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="H152" s="29"/>
+      <c r="H152" s="27" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>635</v>
+        <v>341</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G153" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="H153" s="29"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A154" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G153" s="20" t="s">
+      <c r="G154" s="20" t="s">
         <v>337</v>
-      </c>
-      <c r="H153" s="29"/>
-    </row>
-    <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A154" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G154" s="20" t="s">
-        <v>350</v>
       </c>
       <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>345</v>
@@ -6590,13 +6591,13 @@
         <v>346</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>348</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G155" s="20" t="s">
         <v>350</v>
@@ -6605,7 +6606,7 @@
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>345</v>
@@ -6620,7 +6621,7 @@
         <v>348</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G156" s="20" t="s">
         <v>350</v>
@@ -6629,7 +6630,7 @@
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>345</v>
@@ -6644,16 +6645,16 @@
         <v>348</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
-        <v>633</v>
+        <v>356</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>345</v>
@@ -6668,7 +6669,7 @@
         <v>348</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G158" s="20" t="s">
         <v>358</v>
@@ -6677,7 +6678,7 @@
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="14" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>345</v>
@@ -6692,7 +6693,7 @@
         <v>348</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G159" s="20" t="s">
         <v>358</v>
@@ -6701,7 +6702,7 @@
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>345</v>
@@ -6716,7 +6717,7 @@
         <v>348</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G160" s="20" t="s">
         <v>358</v>
@@ -6725,7 +6726,7 @@
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>345</v>
@@ -6740,7 +6741,7 @@
         <v>348</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G161" s="20" t="s">
         <v>358</v>
@@ -6749,7 +6750,7 @@
     </row>
     <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="14" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>345</v>
@@ -6764,453 +6765,477 @@
         <v>348</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G162" s="20" t="s">
         <v>358</v>
       </c>
       <c r="H162" s="29"/>
     </row>
-    <row r="163" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A163" s="15" t="s">
+    <row r="163" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A163" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G163" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="H163" s="29"/>
+    </row>
+    <row r="164" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A164" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B164" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D164" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="E164" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F163" s="2" t="s">
+      <c r="F164" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G163" s="20" t="s">
+      <c r="G164" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="H163" s="29"/>
-    </row>
-    <row r="164" spans="1:10" ht="54" x14ac:dyDescent="0.45">
-      <c r="A164" s="15" t="s">
+      <c r="H164" s="29"/>
+    </row>
+    <row r="165" spans="1:10" ht="54" x14ac:dyDescent="0.45">
+      <c r="A165" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B165" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C165" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="D165" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E164" s="6" t="s">
+      <c r="E165" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="F164" s="2" t="s">
+      <c r="F165" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G164" s="20" t="s">
+      <c r="G165" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="H164" s="29"/>
-    </row>
-    <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A165" s="15" t="s">
+      <c r="H165" s="29"/>
+    </row>
+    <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A166" s="15" t="s">
         <v>634</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B166" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="E165" s="8" t="s">
+      <c r="E166" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="F165" s="2" t="s">
+      <c r="F166" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G165" s="20" t="s">
+      <c r="G166" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="H165" s="29"/>
-    </row>
-    <row r="166" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A166" s="31" t="s">
+      <c r="H166" s="29"/>
+    </row>
+    <row r="167" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A167" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="B166" s="32" t="s">
+      <c r="B167" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C166" s="32" t="s">
+      <c r="C167" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D166" s="32" t="s">
+      <c r="D167" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E166" s="32" t="s">
+      <c r="E167" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F166" s="32" t="s">
+      <c r="F167" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="25" t="s">
+      <c r="G167" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H166" s="27" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A167" s="33" t="s">
+      <c r="H167" s="27" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A168" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="B167" s="34">
+      <c r="B168" s="34">
         <v>120</v>
       </c>
-      <c r="C167" s="34">
+      <c r="C168" s="34">
         <v>57</v>
       </c>
-      <c r="D167" s="34">
+      <c r="D168" s="34">
         <v>40</v>
       </c>
-      <c r="E167" s="35" t="s">
+      <c r="E168" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="F167" s="34" t="s">
-        <v>686</v>
-      </c>
-      <c r="G167" s="36" t="s">
+      <c r="F168" s="34" t="s">
+        <v>684</v>
+      </c>
+      <c r="G168" s="36" t="s">
         <v>379</v>
       </c>
-      <c r="H167" s="43" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A168" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="B168" s="2">
-        <v>120</v>
-      </c>
-      <c r="C168" s="2">
-        <v>62</v>
-      </c>
-      <c r="D168" s="2">
-        <v>270</v>
-      </c>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="G168" s="37"/>
-      <c r="H168" s="44"/>
+      <c r="H168" s="43" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B169" s="2">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C169" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D169" s="2">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
       </c>
       <c r="C170" s="2">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D170" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
       </c>
       <c r="C171" s="2">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D171" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
     </row>
-    <row r="172" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
       </c>
       <c r="C172" s="2">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D172" s="2">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
       </c>
       <c r="C173" s="2">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D173" s="2">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
-      <c r="J173" s="28"/>
-    </row>
-    <row r="174" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    </row>
+    <row r="174" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
       </c>
       <c r="C174" s="2">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D174" s="2">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
+      <c r="J174" s="28"/>
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B175" s="2">
         <v>200</v>
       </c>
       <c r="C175" s="2">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D175" s="2">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
     </row>
     <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B176" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C176" s="2">
-        <v>55</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>646</v>
+        <v>77</v>
+      </c>
+      <c r="D176" s="2">
+        <v>70</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>399</v>
+        <v>692</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
     </row>
-    <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A177" s="13" t="s">
-        <v>400</v>
+    <row r="177" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A177" s="12" t="s">
+        <v>398</v>
       </c>
       <c r="B177" s="2">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C177" s="2">
-        <v>86</v>
-      </c>
-      <c r="D177" s="2">
-        <v>83</v>
+        <v>55</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>695</v>
+        <v>399</v>
       </c>
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
     </row>
     <row r="178" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B178" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C178" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D178" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
     </row>
-    <row r="179" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B179" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C179" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D179" s="2">
-        <v>64</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>678</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
-    <row r="180" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B180" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C180" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D180" s="2">
-        <v>60</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>407</v>
+        <v>64</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>676</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
     </row>
-    <row r="181" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>681</v>
+        <v>406</v>
       </c>
       <c r="B181" s="2">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="C181" s="2">
-        <v>0</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E181" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="D181" s="2">
+        <v>60</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>407</v>
+      </c>
       <c r="F181" s="2" t="s">
-        <v>409</v>
+        <v>696</v>
       </c>
       <c r="G181" s="37"/>
       <c r="H181" s="44"/>
     </row>
-    <row r="182" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A182" s="17" t="s">
-        <v>680</v>
-      </c>
-      <c r="B182" s="18">
+    <row r="182" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A182" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="B182" s="2">
         <v>500</v>
       </c>
-      <c r="C182" s="18">
+      <c r="C182" s="2">
+        <v>0</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G182" s="37"/>
+      <c r="H182" s="44"/>
+    </row>
+    <row r="183" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A183" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="B183" s="18">
+        <v>500</v>
+      </c>
+      <c r="C183" s="18">
         <v>87</v>
       </c>
-      <c r="D182" s="18">
+      <c r="D183" s="18">
         <v>130</v>
       </c>
-      <c r="E182" s="30" t="s">
-        <v>679</v>
-      </c>
-      <c r="F182" s="18" t="s">
-        <v>703</v>
-      </c>
-      <c r="G182" s="38"/>
-      <c r="H182" s="45"/>
-    </row>
-    <row r="186" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="E183" s="30" t="s">
+        <v>677</v>
+      </c>
+      <c r="F183" s="18" t="s">
+        <v>701</v>
+      </c>
+      <c r="G183" s="38"/>
+      <c r="H183" s="45"/>
+    </row>
+    <row r="187" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="G167:G182"/>
+    <mergeCell ref="G168:G183"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="H167:H182"/>
-    <mergeCell ref="H35:H53"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="H55:H65"/>
+    <mergeCell ref="H168:H183"/>
+    <mergeCell ref="H36:H54"/>
+    <mergeCell ref="H68:H71"/>
+    <mergeCell ref="H56:H66"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5346800-4C4F-4BDE-8CB3-7BA7F21B8A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3C8D7D-0990-410B-8B6A-3F6F6639F3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2105,10 +2105,6 @@
 2.噩梦之斩：释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕；
 3.低语触碰：低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）；
 不是魔王</t>
-  </si>
-  <si>
-    <t>120（近战）
-180（远程）</t>
   </si>
   <si>
     <t>15 冰</t>
@@ -2260,6 +2256,10 @@
   </si>
   <si>
     <t>5级图</t>
+  </si>
+  <si>
+    <t>120~1480（近战）
+180（远程）</t>
   </si>
 </sst>
 </file>
@@ -3220,7 +3220,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
-    <col min="2" max="4" width="16" style="5" customWidth="1"/>
+    <col min="2" max="3" width="16" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19" style="5" customWidth="1"/>
     <col min="5" max="5" width="12" style="5" customWidth="1"/>
     <col min="6" max="6" width="68.796875" style="5" customWidth="1"/>
     <col min="7" max="7" width="32.06640625" style="5" customWidth="1"/>
@@ -3263,7 +3264,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3311,7 +3312,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3418,7 +3419,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3440,7 +3441,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B11" s="2">
         <v>85</v>
@@ -3456,7 +3457,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H11" s="29"/>
     </row>
@@ -3969,7 +3970,7 @@
         <v>6</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -3991,7 +3992,7 @@
         <v>90</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
@@ -4162,7 +4163,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B45" s="2">
         <v>400</v>
@@ -4184,7 +4185,7 @@
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B46" s="2">
         <v>450</v>
@@ -4206,7 +4207,7 @@
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B47" s="2">
         <v>300</v>
@@ -4403,7 +4404,7 @@
         <v>6</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4427,7 +4428,7 @@
         <v>141</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
@@ -4639,11 +4640,11 @@
         <v>0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>675</v>
+        <v>705</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>138</v>
@@ -4673,7 +4674,7 @@
         <v>6</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -4697,7 +4698,7 @@
         <v>169</v>
       </c>
       <c r="H68" s="49" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.45">
@@ -4789,7 +4790,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
@@ -4877,7 +4878,7 @@
         <v>6</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
@@ -5171,7 +5172,7 @@
         <v>6</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
@@ -5803,7 +5804,7 @@
         <v>6</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
@@ -6071,7 +6072,7 @@
         <v>6</v>
       </c>
       <c r="H131" s="25" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
@@ -6379,7 +6380,7 @@
         <v>6</v>
       </c>
       <c r="H145" s="27" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
@@ -6533,7 +6534,7 @@
         <v>6</v>
       </c>
       <c r="H152" s="27" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
@@ -6891,7 +6892,7 @@
         <v>6</v>
       </c>
       <c r="H167" s="27" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6911,13 +6912,13 @@
         <v>191</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G168" s="36" t="s">
         <v>379</v>
       </c>
       <c r="H168" s="43" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6935,7 +6936,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
@@ -6955,7 +6956,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
@@ -6975,7 +6976,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
@@ -6995,7 +6996,7 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
@@ -7015,7 +7016,7 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
@@ -7035,7 +7036,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7056,7 +7057,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
@@ -7076,7 +7077,7 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
@@ -7116,7 +7117,7 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
@@ -7136,7 +7137,7 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
@@ -7155,10 +7156,10 @@
         <v>64</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
@@ -7180,14 +7181,14 @@
         <v>407</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G181" s="37"/>
       <c r="H181" s="44"/>
     </row>
     <row r="182" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B182" s="2">
         <v>500</v>
@@ -7207,7 +7208,7 @@
     </row>
     <row r="183" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A183" s="17" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B183" s="18">
         <v>500</v>
@@ -7219,10 +7220,10 @@
         <v>130</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F183" s="18" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G183" s="38"/>
       <c r="H183" s="45"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3C8D7D-0990-410B-8B6A-3F6F6639F3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0839A026-A885-4669-A00D-5F48D5BC315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,9 +187,6 @@
     <t>不定; &lt;70.8</t>
   </si>
   <si>
-    <t>不定; &lt;59</t>
-  </si>
-  <si>
     <t>在低生命值有可能会逃走</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
   </si>
   <si>
     <t>不定; &lt;77.9</t>
-  </si>
-  <si>
-    <t>不定; &lt;81</t>
   </si>
   <si>
     <t>可以稍微回血；在低生命值有可能会逃走</t>
@@ -2260,6 +2254,12 @@
   <si>
     <t>120~1480（近战）
 180（远程）</t>
+  </si>
+  <si>
+    <t>不定;≤81</t>
+  </si>
+  <si>
+    <t>不定; ≤81</t>
   </si>
 </sst>
 </file>
@@ -3231,7 +3231,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="39" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3264,7 +3264,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="20" t="s">
@@ -3312,7 +3312,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3419,7 +3419,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3435,13 +3435,13 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B11" s="2">
         <v>85</v>
@@ -3457,7 +3457,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H11" s="29"/>
     </row>
@@ -3663,7 +3663,7 @@
         <v>45</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H21" s="29"/>
     </row>
@@ -3698,33 +3698,33 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>704</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="23" t="s">
         <v>51</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>52</v>
       </c>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2">
         <v>100</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>705</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>9</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2">
         <v>90</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G25" s="23" t="s">
         <v>9</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2">
         <v>140</v>
@@ -3768,16 +3768,16 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2">
         <v>200</v>
@@ -3790,16 +3790,16 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2">
         <v>300</v>
@@ -3812,16 +3812,16 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2">
         <v>2800</v>
@@ -3830,18 +3830,18 @@
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30" s="2">
         <v>1000</v>
@@ -3852,16 +3852,16 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B31" s="2">
         <v>900</v>
@@ -3874,16 +3874,16 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A32" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B32" s="2">
         <v>760</v>
@@ -3896,16 +3896,16 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H32" s="29"/>
     </row>
     <row r="33" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A33" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B33" s="2">
         <v>2000</v>
@@ -3918,38 +3918,38 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H33" s="29"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D34" s="2">
         <v>24</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H34" s="29"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1</v>
@@ -3970,12 +3970,12 @@
         <v>6</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B36" s="2">
         <v>50</v>
@@ -3989,15 +3989,15 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2">
         <v>55</v>
@@ -4011,13 +4011,13 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H37" s="47"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B38" s="2">
         <v>50</v>
@@ -4031,13 +4031,13 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H38" s="47"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B39" s="2">
         <v>65</v>
@@ -4050,16 +4050,16 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H39" s="47"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B40" s="2">
         <v>175</v>
@@ -4073,13 +4073,13 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H40" s="47"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B41" s="2">
         <v>10</v>
@@ -4088,20 +4088,20 @@
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H41" s="47"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B42" s="2">
         <v>400</v>
@@ -4115,13 +4115,13 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="20" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H42" s="47"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B43" s="2">
         <v>100</v>
@@ -4135,13 +4135,13 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H43" s="47"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4154,16 +4154,16 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H44" s="47"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B45" s="2">
         <v>400</v>
@@ -4176,16 +4176,16 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H45" s="47"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B46" s="2">
         <v>450</v>
@@ -4198,16 +4198,16 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H46" s="47"/>
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B47" s="2">
         <v>300</v>
@@ -4220,16 +4220,16 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H47" s="47"/>
     </row>
     <row r="48" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A48" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B48" s="2">
         <v>400</v>
@@ -4242,16 +4242,16 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H48" s="47"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B49" s="2">
         <v>600</v>
@@ -4264,38 +4264,38 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H49" s="47"/>
     </row>
     <row r="50" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A50" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="D50" s="2">
         <v>150</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H50" s="47"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B51" s="2">
         <v>1750</v>
@@ -4308,16 +4308,16 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H51" s="47"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B52" s="2">
         <v>900</v>
@@ -4330,16 +4330,16 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H52" s="47"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B53" s="2">
         <v>1750</v>
@@ -4352,16 +4352,16 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H53" s="47"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B54" s="2">
         <v>1600</v>
@@ -4374,16 +4374,16 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H54" s="48"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1</v>
@@ -4404,12 +4404,12 @@
         <v>6</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B56" s="2">
         <v>180</v>
@@ -4422,18 +4422,18 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B57" s="2">
         <v>90</v>
@@ -4446,16 +4446,16 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H57" s="47"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B58" s="2">
         <v>200</v>
@@ -4468,16 +4468,16 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H58" s="47"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B59" s="2">
         <v>180</v>
@@ -4490,16 +4490,16 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H59" s="47"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B60" s="2">
         <v>250</v>
@@ -4512,16 +4512,16 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H60" s="47"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B61" s="2">
         <v>350</v>
@@ -4534,16 +4534,16 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H61" s="47"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B62" s="2">
         <v>350</v>
@@ -4556,16 +4556,16 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H62" s="47"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B63" s="2">
         <v>300</v>
@@ -4578,16 +4578,16 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H63" s="47"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B64" s="2">
         <v>300</v>
@@ -4600,16 +4600,16 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H64" s="47"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B65" s="2">
         <v>175</v>
@@ -4622,16 +4622,16 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H65" s="47"/>
     </row>
     <row r="66" spans="1:8" ht="162" x14ac:dyDescent="0.45">
       <c r="A66" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B66" s="2">
         <v>10000</v>
@@ -4640,20 +4640,20 @@
         <v>0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H66" s="48"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>1</v>
@@ -4674,12 +4674,12 @@
         <v>6</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B68" s="2">
         <v>335</v>
@@ -4692,18 +4692,18 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H68" s="49" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A69" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B69" s="2">
         <v>450</v>
@@ -4716,16 +4716,16 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H69" s="47"/>
     </row>
     <row r="70" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A70" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B70" s="2">
         <v>550</v>
@@ -4738,16 +4738,16 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H70" s="47"/>
     </row>
     <row r="71" spans="1:8" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B71" s="2">
         <v>1000</v>
@@ -4760,16 +4760,16 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H71" s="47"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>1</v>
@@ -4790,12 +4790,12 @@
         <v>6</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B73" s="2">
         <v>60</v>
@@ -4809,13 +4809,13 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H73" s="29"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B74" s="2">
         <v>70</v>
@@ -4829,13 +4829,13 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H74" s="29"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B75" s="2">
         <v>30</v>
@@ -4848,16 +4848,16 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H75" s="29"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>1</v>
@@ -4878,12 +4878,12 @@
         <v>6</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B77" s="2">
         <v>800</v>
@@ -4892,20 +4892,20 @@
         <v>64</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H77" s="29"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B78" s="2">
         <v>700</v>
@@ -4917,19 +4917,19 @@
         <v>30</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H78" s="29"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B79" s="2">
         <v>800</v>
@@ -4938,22 +4938,22 @@
         <v>23</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="G79" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H79" s="29"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B80" s="2">
         <v>800</v>
@@ -4966,19 +4966,19 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H80" s="29"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -4988,19 +4988,19 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H81" s="29"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -5010,19 +5010,19 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H82" s="29"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="12" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C83" s="2">
         <v>24</v>
@@ -5032,63 +5032,63 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H83" s="29"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C84" s="2">
         <v>55</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H84" s="29"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C85" s="2">
         <v>38</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H85" s="29"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C86" s="2">
         <v>38</v>
@@ -5098,19 +5098,19 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H86" s="29"/>
     </row>
     <row r="87" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C87" s="2">
         <v>60</v>
@@ -5120,16 +5120,16 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H87" s="29"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B88" s="2">
         <v>250</v>
@@ -5138,20 +5138,20 @@
         <v>0</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H88" s="29"/>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>1</v>
@@ -5172,12 +5172,12 @@
         <v>6</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B90" s="2">
         <v>25</v>
@@ -5186,20 +5186,20 @@
         <v>0</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H90" s="29"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -5213,13 +5213,13 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H91" s="29"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -5233,13 +5233,13 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H92" s="29"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -5253,13 +5253,13 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H93" s="29"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B94" s="2">
         <v>400</v>
@@ -5273,13 +5273,13 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H94" s="29"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B95" s="2">
         <v>200</v>
@@ -5288,20 +5288,20 @@
         <v>0</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H95" s="29"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B96" s="2">
         <v>400</v>
@@ -5315,13 +5315,13 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H96" s="29"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B97" s="2">
         <v>60</v>
@@ -5334,16 +5334,16 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H97" s="29"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B98" s="2">
         <v>2000</v>
@@ -5357,13 +5357,13 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H98" s="29"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B99" s="2">
         <v>550</v>
@@ -5377,13 +5377,13 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B100" s="2">
         <v>40</v>
@@ -5392,40 +5392,40 @@
         <v>0</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H100" s="29"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D101" s="2">
         <v>62</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B102" s="2">
         <v>150</v>
@@ -5438,16 +5438,16 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B103" s="2">
         <v>110</v>
@@ -5460,16 +5460,16 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H103" s="29"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B104" s="2">
         <v>185</v>
@@ -5482,16 +5482,16 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H104" s="29"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B105" s="2">
         <v>300</v>
@@ -5500,20 +5500,20 @@
         <v>0</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H105" s="29"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B106" s="2">
         <v>300</v>
@@ -5527,19 +5527,19 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H106" s="29"/>
     </row>
     <row r="107" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B107" s="2">
         <v>500</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D107" s="2">
         <v>36</v>
@@ -5547,16 +5547,16 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H107" s="29"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -5567,19 +5567,19 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H108" s="29"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D109" s="2">
         <v>72</v>
@@ -5587,33 +5587,33 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H109" s="29"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H110" s="29"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B111" s="2">
         <v>300</v>
@@ -5627,13 +5627,13 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H111" s="29"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B112" s="2">
         <v>600</v>
@@ -5647,13 +5647,13 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H112" s="29"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B113" s="2">
         <v>1000</v>
@@ -5667,13 +5667,13 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H113" s="29"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B114" s="2">
         <v>450</v>
@@ -5682,20 +5682,20 @@
         <v>69</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H114" s="29"/>
     </row>
     <row r="115" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B115" s="2">
         <v>2500</v>
@@ -5708,16 +5708,16 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H115" s="29"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B116" s="2">
         <v>9000</v>
@@ -5730,16 +5730,16 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H116" s="29"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B117" s="2">
         <v>10500</v>
@@ -5748,20 +5748,20 @@
         <v>0</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H117" s="29"/>
     </row>
     <row r="118" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A118" s="15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B118" s="2">
         <v>1700</v>
@@ -5774,16 +5774,16 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>1</v>
@@ -5804,12 +5804,12 @@
         <v>6</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B120" s="2">
         <v>75</v>
@@ -5818,20 +5818,20 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H120" s="29"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B121" s="2">
         <v>45</v>
@@ -5844,16 +5844,16 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H121" s="29"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B122" s="2">
         <v>100</v>
@@ -5862,20 +5862,20 @@
         <v>0</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -5888,16 +5888,16 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H123" s="29"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B124" s="2">
         <v>300</v>
@@ -5910,16 +5910,16 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B125" s="2">
         <v>150</v>
@@ -5928,20 +5928,20 @@
         <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -5950,20 +5950,20 @@
         <v>0</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H126" s="29"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B127" s="2">
         <v>215</v>
@@ -5976,16 +5976,16 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A128" s="13" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B128" s="2">
         <v>200</v>
@@ -5998,16 +5998,16 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H128" s="29"/>
     </row>
     <row r="129" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A129" s="14" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B129" s="2">
         <v>600</v>
@@ -6016,20 +6016,20 @@
         <v>66</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H129" s="29"/>
     </row>
     <row r="130" spans="1:8" ht="108" x14ac:dyDescent="0.45">
       <c r="A130" s="14" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B130" s="2">
         <v>2000</v>
@@ -6042,16 +6042,16 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G130" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H130" s="29"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>1</v>
@@ -6072,12 +6072,12 @@
         <v>6</v>
       </c>
       <c r="H131" s="25" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B132" s="2">
         <v>50</v>
@@ -6086,20 +6086,20 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G132" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H132" s="29"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B133" s="2">
         <v>900</v>
@@ -6113,13 +6113,13 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H133" s="29"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B134" s="2">
         <v>100</v>
@@ -6128,18 +6128,18 @@
         <v>0</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H134" s="29"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B135" s="2">
         <v>45</v>
@@ -6152,36 +6152,36 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H135" s="29"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B136" s="2">
         <v>200</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H136" s="29"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B137" s="2">
         <v>600</v>
@@ -6190,20 +6190,20 @@
         <v>0</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H137" s="29"/>
     </row>
     <row r="138" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A138" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B138" s="2">
         <v>1500</v>
@@ -6212,20 +6212,20 @@
         <v>52</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G138" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H138" s="29"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B139" s="2">
         <v>1500</v>
@@ -6237,19 +6237,19 @@
         <v>100</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H139" s="29"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="14" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B140" s="2">
         <v>1000</v>
@@ -6262,16 +6262,16 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G140" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H140" s="29"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B141" s="2">
         <v>750</v>
@@ -6284,16 +6284,16 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H141" s="29"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B142" s="2">
         <v>150</v>
@@ -6306,16 +6306,16 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G142" s="20" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H142" s="29"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" s="14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B143" s="2">
         <v>720</v>
@@ -6328,16 +6328,16 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H143" s="29"/>
     </row>
     <row r="144" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A144" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B144" s="2">
         <v>2000</v>
@@ -6350,16 +6350,16 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G144" s="20" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H144" s="29"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>1</v>
@@ -6380,12 +6380,12 @@
         <v>6</v>
       </c>
       <c r="H145" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B146" s="2">
         <v>400</v>
@@ -6398,16 +6398,16 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G146" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H146" s="29"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B147" s="2">
         <v>80</v>
@@ -6416,20 +6416,20 @@
         <v>0</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H147" s="29"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B148" s="2">
         <v>70</v>
@@ -6443,13 +6443,13 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H148" s="29"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B149" s="2">
         <v>180</v>
@@ -6463,13 +6463,13 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H149" s="29"/>
     </row>
     <row r="150" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B150" s="2">
         <v>40</v>
@@ -6482,16 +6482,16 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G150" s="20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H150" s="29"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B151" s="2">
         <v>100</v>
@@ -6500,20 +6500,20 @@
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H151" s="29"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>1</v>
@@ -6534,344 +6534,344 @@
         <v>6</v>
       </c>
       <c r="H152" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C153" s="2">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H153" s="29"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G154" s="20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="D155" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E155" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E155" s="6" t="s">
+      <c r="F155" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G155" s="20" t="s">
         <v>348</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G155" s="20" t="s">
-        <v>350</v>
       </c>
       <c r="H155" s="29"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E156" s="6" t="s">
+      <c r="G156" s="20" t="s">
         <v>348</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G156" s="20" t="s">
-        <v>350</v>
       </c>
       <c r="H156" s="29"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C157" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E157" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E157" s="6" t="s">
+      <c r="F157" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G157" s="20" t="s">
         <v>348</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="G157" s="20" t="s">
-        <v>350</v>
       </c>
       <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G158" s="20" t="s">
         <v>356</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G158" s="20" t="s">
-        <v>358</v>
       </c>
       <c r="H158" s="29"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="14" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C159" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E159" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="F159" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H159" s="29"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C160" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E160" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="F160" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H160" s="29"/>
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C161" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E161" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="F161" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="14" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C162" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E162" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="F162" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G162" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H162" s="29"/>
     </row>
     <row r="163" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C163" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E163" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="F163" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H163" s="29"/>
     </row>
     <row r="164" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A164" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="D164" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E164" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="F164" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="E164" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="G164" s="20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H164" s="29"/>
     </row>
     <row r="165" spans="1:10" ht="54" x14ac:dyDescent="0.45">
       <c r="A165" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="D165" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E165" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="F165" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D165" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E165" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="G165" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H165" s="29"/>
     </row>
     <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="15" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G166" s="20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H166" s="29"/>
     </row>
     <row r="167" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A167" s="31" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B167" s="32" t="s">
         <v>1</v>
@@ -6892,12 +6892,12 @@
         <v>6</v>
       </c>
       <c r="H167" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="33" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B168" s="34">
         <v>120</v>
@@ -6909,21 +6909,21 @@
         <v>40</v>
       </c>
       <c r="E168" s="35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G168" s="36" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H168" s="43" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B169" s="2">
         <v>120</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6956,14 +6956,14 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
@@ -6976,14 +6976,14 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
     </row>
     <row r="172" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
@@ -6996,14 +6996,14 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
@@ -7016,14 +7016,14 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
     </row>
     <row r="174" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" s="12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B175" s="2">
         <v>200</v>
@@ -7057,14 +7057,14 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
     </row>
     <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B176" s="2">
         <v>200</v>
@@ -7077,14 +7077,14 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
     </row>
     <row r="177" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B177" s="2">
         <v>120</v>
@@ -7093,18 +7093,18 @@
         <v>55</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
     </row>
     <row r="178" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B178" s="2">
         <v>200</v>
@@ -7117,14 +7117,14 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
     </row>
     <row r="179" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B179" s="2">
         <v>250</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B180" s="2">
         <v>200</v>
@@ -7156,17 +7156,17 @@
         <v>64</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
     </row>
     <row r="181" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B181" s="2">
         <v>250</v>
@@ -7178,17 +7178,17 @@
         <v>60</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G181" s="37"/>
       <c r="H181" s="44"/>
     </row>
     <row r="182" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B182" s="2">
         <v>500</v>
@@ -7197,18 +7197,18 @@
         <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G182" s="37"/>
       <c r="H182" s="44"/>
     </row>
     <row r="183" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A183" s="17" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B183" s="18">
         <v>500</v>
@@ -7220,10 +7220,10 @@
         <v>130</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F183" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G183" s="38"/>
       <c r="H183" s="45"/>
@@ -7257,24 +7257,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -7283,15 +7283,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -7300,32 +7300,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -7334,7 +7334,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -7351,15 +7351,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -7368,15 +7368,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -7385,7 +7385,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -7393,7 +7393,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -7402,15 +7402,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -7419,7 +7419,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -7436,7 +7436,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -7444,214 +7444,214 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -7660,491 +7660,491 @@
         <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>5</v>
@@ -8153,2778 +8153,2778 @@
         <v>39</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0839A026-A885-4669-A00D-5F48D5BC315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED2B63C-F10E-472F-B570-9C5ECB5732A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2120,13 +2120,6 @@
   </si>
   <si>
     <t>领主第一个小弟-阿托鲁斯</t>
-  </si>
-  <si>
-    <t>普通攻击：距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
-钩索：出现预警范围，短暂蓄力后若未脱离范围则被勾到卡恩身边并受到500点物理伤害。若被勾路径上有铁蒺藜，则受到额外伤害。
-净化：当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
-饮血：距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
-震地：卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒；是魔王</t>
   </si>
   <si>
     <t>武器：冰弓（冻伤20）；减速；保持距离；元素伤害减半；受伤后回血,单次上限40(超出部分每5秒补一次),累计200</t>
@@ -2260,6 +2253,13 @@
   </si>
   <si>
     <t>不定; ≤81</t>
+  </si>
+  <si>
+    <t>【普通攻击】距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
+【钩索】出现预警范围，短暂蓄力后若未脱离范围则被勾到卡恩身边并受到500点物理伤害。若被勾路径上有铁蒺藜，则受到额外伤害。
+【净化】当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
+【饮血】距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
+【飞天大操】卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒</t>
   </si>
 </sst>
 </file>
@@ -3264,7 +3264,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3312,7 +3312,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3419,7 +3419,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B11" s="2">
         <v>85</v>
@@ -3457,7 +3457,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H11" s="29"/>
     </row>
@@ -3698,7 +3698,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3720,7 +3720,7 @@
         <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="20" t="s">
@@ -3970,7 +3970,7 @@
         <v>6</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -3992,7 +3992,7 @@
         <v>88</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
@@ -4404,7 +4404,7 @@
         <v>6</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4428,7 +4428,7 @@
         <v>139</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
@@ -4640,11 +4640,11 @@
         <v>0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>136</v>
@@ -4674,7 +4674,7 @@
         <v>6</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -4698,7 +4698,7 @@
         <v>167</v>
       </c>
       <c r="H68" s="49" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.45">
@@ -4790,7 +4790,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
@@ -4878,7 +4878,7 @@
         <v>6</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
@@ -5172,7 +5172,7 @@
         <v>6</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
@@ -5804,7 +5804,7 @@
         <v>6</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
@@ -6072,7 +6072,7 @@
         <v>6</v>
       </c>
       <c r="H131" s="25" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
@@ -6380,7 +6380,7 @@
         <v>6</v>
       </c>
       <c r="H145" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
@@ -6534,7 +6534,7 @@
         <v>6</v>
       </c>
       <c r="H152" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
@@ -6892,7 +6892,7 @@
         <v>6</v>
       </c>
       <c r="H167" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6912,13 +6912,13 @@
         <v>189</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G168" s="36" t="s">
         <v>377</v>
       </c>
       <c r="H168" s="43" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
@@ -7159,7 +7159,7 @@
         <v>673</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
@@ -7181,7 +7181,7 @@
         <v>405</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G181" s="37"/>
       <c r="H181" s="44"/>
@@ -7223,7 +7223,7 @@
         <v>674</v>
       </c>
       <c r="F183" s="18" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G183" s="38"/>
       <c r="H183" s="45"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED2B63C-F10E-472F-B570-9C5ECB5732A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D222BA2-D00E-4AD9-B56B-A06977E2EA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="707">
   <si>
     <t>家里</t>
   </si>
@@ -2092,13 +2092,6 @@
   </si>
   <si>
     <t>低语噩梦</t>
-  </si>
-  <si>
-    <t>免疫冰伤，受到双倍火伤；
-1.灵魂复苏：释放超大范围圆形斩击，若命中则造成140点物理伤害，并召唤3个被遗忘的灵魂；
-2.噩梦之斩：释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕；
-3.低语触碰：低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）；
-不是魔王</t>
   </si>
   <si>
     <t>15 冰</t>
@@ -2260,6 +2253,17 @@
 【净化】当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
 【饮血】距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
 【飞天大操】卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒</t>
+  </si>
+  <si>
+    <t>免疫冰伤，受到双倍火伤；不是魔王
+【灵魂复苏】释放超大范围圆形斩击，若命中则造成140点物理伤害，并召唤3个被遗忘的灵魂
+【噩梦之斩】释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕
+【低语触碰】低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）</t>
+  </si>
+  <si>
+    <t>【砸地】中心385(普)/500(英)，外圈105-165(普)/130-210(英)
+【三连批】240(普)/300(英)
+【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙(生命值&lt;80%、60%、45%、25% 时)</t>
   </si>
 </sst>
 </file>
@@ -3264,7 +3268,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3312,7 +3316,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3419,7 +3423,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3441,7 +3445,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B11" s="2">
         <v>85</v>
@@ -3457,7 +3461,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H11" s="29"/>
     </row>
@@ -3698,7 +3702,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3720,7 +3724,7 @@
         <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="20" t="s">
@@ -3970,7 +3974,7 @@
         <v>6</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -3992,7 +3996,7 @@
         <v>88</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
@@ -4163,7 +4167,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B45" s="2">
         <v>400</v>
@@ -4185,7 +4189,7 @@
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B46" s="2">
         <v>450</v>
@@ -4207,7 +4211,7 @@
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B47" s="2">
         <v>300</v>
@@ -4286,7 +4290,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>123</v>
+        <v>706</v>
       </c>
       <c r="G50" s="20" t="s">
         <v>113</v>
@@ -4404,7 +4408,7 @@
         <v>6</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4428,7 +4432,7 @@
         <v>139</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
@@ -4640,11 +4644,11 @@
         <v>0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>136</v>
@@ -4674,7 +4678,7 @@
         <v>6</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -4698,7 +4702,7 @@
         <v>167</v>
       </c>
       <c r="H68" s="49" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.45">
@@ -4790,7 +4794,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
@@ -4878,7 +4882,7 @@
         <v>6</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
@@ -5172,7 +5176,7 @@
         <v>6</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
@@ -5804,7 +5808,7 @@
         <v>6</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
@@ -6027,7 +6031,7 @@
       </c>
       <c r="H129" s="29"/>
     </row>
-    <row r="130" spans="1:8" ht="108" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A130" s="14" t="s">
         <v>671</v>
       </c>
@@ -6042,7 +6046,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>672</v>
+        <v>705</v>
       </c>
       <c r="G130" s="20" t="s">
         <v>652</v>
@@ -6072,7 +6076,7 @@
         <v>6</v>
       </c>
       <c r="H131" s="25" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
@@ -6380,7 +6384,7 @@
         <v>6</v>
       </c>
       <c r="H145" s="27" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
@@ -6534,7 +6538,7 @@
         <v>6</v>
       </c>
       <c r="H152" s="27" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
@@ -6892,7 +6896,7 @@
         <v>6</v>
       </c>
       <c r="H167" s="27" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6912,13 +6916,13 @@
         <v>189</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G168" s="36" t="s">
         <v>377</v>
       </c>
       <c r="H168" s="43" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
@@ -6956,7 +6960,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
@@ -6976,7 +6980,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
@@ -6996,7 +7000,7 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
@@ -7016,7 +7020,7 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
@@ -7036,7 +7040,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7057,7 +7061,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
@@ -7077,7 +7081,7 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
@@ -7117,7 +7121,7 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
@@ -7137,7 +7141,7 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
@@ -7156,10 +7160,10 @@
         <v>64</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
@@ -7181,14 +7185,14 @@
         <v>405</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G181" s="37"/>
       <c r="H181" s="44"/>
     </row>
     <row r="182" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B182" s="2">
         <v>500</v>
@@ -7208,7 +7212,7 @@
     </row>
     <row r="183" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A183" s="17" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B183" s="18">
         <v>500</v>
@@ -7220,10 +7224,10 @@
         <v>130</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F183" s="18" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G183" s="38"/>
       <c r="H183" s="45"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D222BA2-D00E-4AD9-B56B-A06977E2EA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D43E600-5D97-4443-9186-D1927A48A4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2261,7 +2261,7 @@
 【低语触碰】低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）</t>
   </si>
   <si>
-    <t>【砸地】中心385(普)/500(英)，外圈105-165(普)/130-210(英)
+    <t>【砸地】中心385(普)/500-700(英)，外圈105-165(普)/130-210(英)
 【三连批】240(普)/300(英)
 【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙(生命值&lt;80%、60%、45%、25% 时)</t>
   </si>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D43E600-5D97-4443-9186-D1927A48A4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33708455-308D-4C32-B731-6C42CACBF1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2263,7 +2263,7 @@
   <si>
     <t>【砸地】中心385(普)/500-700(英)，外圈105-165(普)/130-210(英)
 【三连批】240(普)/300(英)
-【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙(生命值&lt;80%、60%、45%、25% 时)</t>
+【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙，分别在领主生命值&lt;80%，60%，45%，25% 的时候</t>
   </si>
 </sst>
 </file>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33708455-308D-4C32-B731-6C42CACBF1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470D125E-00F2-4BCC-8535-BDC994E4771C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2194,6 +2194,43 @@
 可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；无元素抗性</t>
   </si>
   <si>
+    <t>继母艾莎蝙蝠</t>
+  </si>
+  <si>
+    <t>5级图的蝙蝠</t>
+  </si>
+  <si>
+    <t>5级图</t>
+  </si>
+  <si>
+    <t>120~1480（近战）
+180（远程）</t>
+  </si>
+  <si>
+    <t>不定;≤81</t>
+  </si>
+  <si>
+    <t>不定; ≤81</t>
+  </si>
+  <si>
+    <t>【普通攻击】距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
+【钩索】出现预警范围，短暂蓄力后若未脱离范围则被勾到卡恩身边并受到500点物理伤害。若被勾路径上有铁蒺藜，则受到额外伤害。
+【净化】当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
+【饮血】距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
+【飞天大操】卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒</t>
+  </si>
+  <si>
+    <t>免疫冰伤，受到双倍火伤；不是魔王
+【灵魂复苏】释放超大范围圆形斩击，若命中则造成140点物理伤害，并召唤3个被遗忘的灵魂
+【噩梦之斩】释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕
+【低语触碰】低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）</t>
+  </si>
+  <si>
+    <t>【砸地】中心385(普)/500-700(英)，外圈105-165(普)/130-210(英)
+【三连批】240(普)/300(英)
+【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙，分别在领主生命值&lt;80%，60%，45%，25% 的时候</t>
+  </si>
+  <si>
     <t>【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
 【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
 【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
@@ -2203,7 +2240,7 @@
 2.	训练警报：帐篷中的敌人没那么致命
 3.	刺骨寒冰：敌人更容易受到寒冷伤害
 4.	炽焰：敌人更容易受到火焰伤害
-5.	衰败：敌人更容易受到衰败伤害
+5.	衰败之触：敌人更容易受到衰败伤害
 6.	高效治疗：玩家治疗效果提高20%
 7.	治疗之风：每4秒恢复5生命值
 8.	尖锐尖刺：敌人在攻击你时会受到固定10点伤害
@@ -2227,43 +2264,6 @@
 6.	强悍护甲：敌人防御力提升35%
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有20%的机会躲避攻击</t>
-  </si>
-  <si>
-    <t>继母艾莎蝙蝠</t>
-  </si>
-  <si>
-    <t>5级图的蝙蝠</t>
-  </si>
-  <si>
-    <t>5级图</t>
-  </si>
-  <si>
-    <t>120~1480（近战）
-180（远程）</t>
-  </si>
-  <si>
-    <t>不定;≤81</t>
-  </si>
-  <si>
-    <t>不定; ≤81</t>
-  </si>
-  <si>
-    <t>【普通攻击】距离它较近时，使用斧头近战攻击；距离它较远时，会投掷斧头攻击。近战状态的攻击能給卡恩叠加狂怒效果，每层狂怒均会提升卡恩的近战、远程攻击速度与80点近战伤害，狂怒持续10秒，可叠加，每层独立计时。远程状态下能减慢玩家的奔跑速度。
-【钩索】出现预警范围，短暂蓄力后若未脱离范围则被勾到卡恩身边并受到500点物理伤害。若被勾路径上有铁蒺藜，则受到额外伤害。
-【净化】当身上有负面状态（中毒，诅咒，抑制，流血，禁疗等）时，解除所有负面状态并恢复400点生命值。这个技能有一段冷却时间。
-【饮血】距离卡恩较远时，卡恩可能会开始饮血恢复生命值，每段恢复150点生命，可用攻击打断（注意：恐狼、dot伤害无法打断）。
-【飞天大操】卡恩跳走，落地区域有预警。落地时若未脱离预警范围则受到20点真实伤害，并被眩晕5秒</t>
-  </si>
-  <si>
-    <t>免疫冰伤，受到双倍火伤；不是魔王
-【灵魂复苏】释放超大范围圆形斩击，若命中则造成140点物理伤害，并召唤3个被遗忘的灵魂
-【噩梦之斩】释放超大半径范围扇形斩击，造成170点物理伤害，并对你造成3秒恐惧或2秒眩晕
-【低语触碰】低语噩梦在进行普通攻击时，有概率降低你3秒攻击和奔跑速度（可叠加，每层独立计时）</t>
-  </si>
-  <si>
-    <t>【砸地】中心385(普)/500-700(英)，外圈105-165(普)/130-210(英)
-【三连批】240(普)/300(英)
-【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙，分别在领主生命值&lt;80%，60%，45%，25% 的时候</t>
   </si>
 </sst>
 </file>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B11" s="2">
         <v>85</v>
@@ -3461,7 +3461,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H11" s="29"/>
     </row>
@@ -3702,7 +3702,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3724,7 +3724,7 @@
         <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="20" t="s">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G50" s="20" t="s">
         <v>113</v>
@@ -4644,11 +4644,11 @@
         <v>0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>136</v>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G130" s="20" t="s">
         <v>652</v>
@@ -6922,7 +6922,7 @@
         <v>377</v>
       </c>
       <c r="H168" s="43" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470D125E-00F2-4BCC-8535-BDC994E4771C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7A2A18-BBD1-45C5-9847-9D653902EAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="706">
   <si>
     <t>家里</t>
   </si>
@@ -2192,15 +2192,6 @@
     <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
 复活药1瓶；他的武器可以禁疗；受伤后回血,单次上限100(超出部分每5秒补一次),累计400
 可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；无元素抗性</t>
-  </si>
-  <si>
-    <t>继母艾莎蝙蝠</t>
-  </si>
-  <si>
-    <t>5级图的蝙蝠</t>
-  </si>
-  <si>
-    <t>5级图</t>
   </si>
   <si>
     <t>120~1480（近战）
@@ -2264,6 +2255,12 @@
 6.	强悍护甲：敌人防御力提升35%
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有20%的机会躲避攻击</t>
+  </si>
+  <si>
+    <t>蝙蝠</t>
+  </si>
+  <si>
+    <t>继母艾莎；1-5级图</t>
   </si>
 </sst>
 </file>
@@ -3423,7 +3420,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3439,296 +3436,296 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>647</v>
+        <v>705</v>
       </c>
       <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>698</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="20" t="s">
-        <v>23</v>
-      </c>
+      <c r="F11" s="20"/>
       <c r="G11" s="23" t="s">
-        <v>699</v>
+        <v>25</v>
       </c>
       <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="20"/>
       <c r="G12" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C13" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="20"/>
       <c r="G13" s="23" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="20"/>
+      <c r="F14" s="20" t="s">
+        <v>30</v>
+      </c>
       <c r="G14" s="23" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2">
+        <v>9</v>
+      </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="20" t="s">
-        <v>30</v>
-      </c>
+      <c r="F15" s="20"/>
       <c r="G15" s="23" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
       <c r="D16" s="2">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="20"/>
+      <c r="F16" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="G16" s="23" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H16" s="29"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="20" t="s">
-        <v>34</v>
-      </c>
+      <c r="F17" s="20"/>
       <c r="G17" s="23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2">
+        <v>90</v>
+      </c>
+      <c r="C19" s="2">
         <v>0</v>
       </c>
-      <c r="D18" s="2">
-        <v>20</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="29"/>
-    </row>
-    <row r="19" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A19" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="2">
-        <v>95</v>
-      </c>
-      <c r="C19" s="2">
-        <v>23</v>
-      </c>
       <c r="D19" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="F19" s="20"/>
       <c r="G19" s="23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H19" s="29"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
-      <c r="D20" s="2">
-        <v>15</v>
+      <c r="D20" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="20"/>
+      <c r="F20" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="G20" s="23" t="s">
-        <v>42</v>
+        <v>648</v>
       </c>
       <c r="H20" s="29"/>
     </row>
-    <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>44</v>
+      <c r="D21" s="2">
+        <v>10</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="20" t="s">
-        <v>45</v>
-      </c>
+      <c r="F21" s="20"/>
       <c r="G21" s="23" t="s">
-        <v>648</v>
+        <v>47</v>
       </c>
       <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2">
-        <v>300</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>698</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="20"/>
+      <c r="F22" s="20" t="s">
+        <v>50</v>
+      </c>
       <c r="G22" s="23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="12" t="s">
-        <v>48</v>
+      <c r="A23" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="B23" s="2">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2">
-        <v>100</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>702</v>
+        <v>90</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>10</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>9</v>
@@ -3737,415 +3734,415 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="C25" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D25" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B26" s="2">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>59</v>
+      <c r="F26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>62</v>
       </c>
       <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C27" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D27" s="2">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>65</v>
       </c>
       <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2">
-        <v>300</v>
+        <v>2800</v>
       </c>
       <c r="C28" s="2">
-        <v>47</v>
-      </c>
-      <c r="D28" s="2">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" s="13" t="s">
-        <v>66</v>
+      <c r="A29" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="B29" s="2">
-        <v>2800</v>
+        <v>1000</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="G29" s="20" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B30" s="2">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D30" s="2">
+        <v>35</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H30" s="29"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A31" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B31" s="2">
-        <v>900</v>
+        <v>760</v>
       </c>
       <c r="C31" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A32" s="14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B32" s="2">
-        <v>760</v>
+        <v>2000</v>
       </c>
       <c r="C32" s="2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D32" s="2">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H32" s="29"/>
     </row>
-    <row r="33" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A33" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C33" s="2">
-        <v>11</v>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A33" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="D33" s="2">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H33" s="29"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A34" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D34" s="2">
-        <v>24</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" s="29"/>
+      <c r="A34" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>692</v>
+      <c r="A35" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="2">
+        <v>50</v>
+      </c>
+      <c r="C35" s="2">
+        <v>16</v>
+      </c>
+      <c r="D35" s="2">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" s="46" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B36" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="H36" s="46" t="s">
-        <v>695</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="H36" s="47"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B37" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C37" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D37" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H37" s="47"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B38" s="2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C38" s="2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="F38" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="G38" s="20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H38" s="47"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B39" s="2">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="C39" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D39" s="2">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H39" s="47"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B40" s="2">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="C40" s="2">
-        <v>30</v>
-      </c>
-      <c r="D40" s="2">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="G40" s="20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H40" s="47"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B41" s="2">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>646</v>
+        <v>44</v>
+      </c>
+      <c r="D41" s="2">
+        <v>60</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H41" s="47"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B42" s="2">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="C42" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H42" s="47"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" s="12" t="s">
-        <v>103</v>
+      <c r="A43" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="B43" s="2">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C43" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D43" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="G43" s="20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H43" s="47"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>105</v>
+        <v>678</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4154,55 +4151,55 @@
         <v>44</v>
       </c>
       <c r="D44" s="2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H44" s="47"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B45" s="2">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C45" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H45" s="47"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B46" s="2">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D46" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G46" s="20" t="s">
         <v>113</v>
@@ -4211,516 +4208,516 @@
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="13" t="s">
-        <v>676</v>
+        <v>116</v>
       </c>
       <c r="B47" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D47" s="2">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G47" s="20" t="s">
         <v>113</v>
       </c>
       <c r="H47" s="47"/>
     </row>
-    <row r="48" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B48" s="2">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C48" s="2">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="H48" s="47"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B49" s="2">
-        <v>600</v>
-      </c>
-      <c r="C49" s="2">
-        <v>55</v>
+    <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A49" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="D49" s="2">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>119</v>
+        <v>702</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="H49" s="47"/>
     </row>
-    <row r="50" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1750</v>
+      </c>
+      <c r="C50" s="2">
+        <v>42</v>
       </c>
       <c r="D50" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>705</v>
+        <v>125</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H50" s="47"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B51" s="2">
-        <v>1750</v>
+        <v>900</v>
       </c>
       <c r="C51" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D51" s="2">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H51" s="47"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B52" s="2">
-        <v>900</v>
+        <v>1750</v>
       </c>
       <c r="C52" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D52" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H52" s="47"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B53" s="2">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="C53" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D53" s="2">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H53" s="47"/>
+        <v>135</v>
+      </c>
+      <c r="H53" s="48"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A54" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B54" s="2">
-        <v>1600</v>
-      </c>
-      <c r="C54" s="2">
-        <v>55</v>
-      </c>
-      <c r="D54" s="2">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="H54" s="48"/>
+      <c r="A54" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A55" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>692</v>
+      <c r="A55" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="2">
+        <v>180</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2">
+        <v>50</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H55" s="46" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B56" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="H56" s="46" t="s">
-        <v>694</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H56" s="47"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B57" s="2">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
       </c>
       <c r="D57" s="2">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H57" s="47"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B58" s="2">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
       </c>
       <c r="D58" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H58" s="47"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B59" s="2">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H59" s="47"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B60" s="2">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="C60" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D60" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H60" s="47"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B61" s="2">
         <v>350</v>
       </c>
       <c r="C61" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D61" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H61" s="47"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A62" s="12" t="s">
-        <v>153</v>
+      <c r="A62" s="13" t="s">
+        <v>155</v>
       </c>
       <c r="B62" s="2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C62" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D62" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="H62" s="47"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B63" s="2">
         <v>300</v>
       </c>
       <c r="C63" s="2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D63" s="2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H63" s="47"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B64" s="2">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="C64" s="2">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D64" s="2">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H64" s="47"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A65" s="13" t="s">
-        <v>161</v>
+    <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
+      <c r="A65" s="15" t="s">
+        <v>163</v>
       </c>
       <c r="B65" s="2">
-        <v>175</v>
+        <v>10000</v>
       </c>
       <c r="C65" s="2">
-        <v>93</v>
-      </c>
-      <c r="D65" s="2">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>697</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>162</v>
+        <v>700</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="H65" s="47"/>
-    </row>
-    <row r="66" spans="1:8" ht="162" x14ac:dyDescent="0.45">
-      <c r="A66" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" s="2">
-        <v>10000</v>
-      </c>
-      <c r="C66" s="2">
+        <v>136</v>
+      </c>
+      <c r="H65" s="48"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A66" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H66" s="25" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A67" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67" s="2">
+        <v>335</v>
+      </c>
+      <c r="C67" s="2">
+        <v>48</v>
+      </c>
+      <c r="D67" s="2">
+        <v>100</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A68" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B68" s="2">
+        <v>450</v>
+      </c>
+      <c r="C68" s="2">
         <v>0</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="H66" s="48"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A67" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H67" s="25" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A68" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="B68" s="2">
-        <v>335</v>
-      </c>
-      <c r="C68" s="2">
-        <v>48</v>
-      </c>
       <c r="D68" s="2">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="H68" s="49" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A69" s="12" t="s">
-        <v>168</v>
+      <c r="H68" s="47"/>
+    </row>
+    <row r="69" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A69" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="B69" s="2">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D69" s="2">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>167</v>
@@ -4729,20 +4726,20 @@
     </row>
     <row r="70" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A70" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B70" s="2">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="C70" s="2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D70" s="2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>167</v>
@@ -4750,65 +4747,63 @@
       <c r="H70" s="47"/>
     </row>
     <row r="71" spans="1:8" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B71" s="2">
-        <v>1000</v>
-      </c>
-      <c r="C71" s="2">
-        <v>42</v>
-      </c>
-      <c r="D71" s="2">
-        <v>200</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="G71" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="H71" s="47"/>
+      <c r="A71" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H71" s="26" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B72" s="2">
+        <v>60</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2">
+        <v>10</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>692</v>
-      </c>
+      <c r="H72" s="29"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B73" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C73" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D73" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
@@ -4819,88 +4814,92 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B74" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C74" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D74" s="2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="F74" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="G74" s="20" t="s">
         <v>174</v>
       </c>
       <c r="H74" s="29"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A75" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B75" s="2">
-        <v>30</v>
-      </c>
-      <c r="C75" s="2">
-        <v>0</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="A75" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G75" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H75" s="29"/>
+      <c r="E75" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A76" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G76" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H76" s="11" t="s">
-        <v>692</v>
-      </c>
+      <c r="A76" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B76" s="2">
+        <v>800</v>
+      </c>
+      <c r="C76" s="2">
+        <v>64</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="H76" s="29"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B77" s="2">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="C77" s="2">
-        <v>64</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E77" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="D77" s="2">
+        <v>30</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="F77" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G77" s="20" t="s">
         <v>183</v>
@@ -4909,22 +4908,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B78" s="2">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="C78" s="2">
         <v>23</v>
       </c>
-      <c r="D78" s="2">
-        <v>30</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>185</v>
+      <c r="D78" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G78" s="20" t="s">
         <v>183</v>
@@ -4933,22 +4932,20 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B79" s="2">
         <v>800</v>
       </c>
       <c r="C79" s="2">
-        <v>23</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>189</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D79" s="2">
+        <v>70</v>
+      </c>
+      <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>183</v>
@@ -4957,20 +4954,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B80" s="2">
-        <v>800</v>
+        <v>193</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C80" s="2">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D80" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G80" s="20" t="s">
         <v>183</v>
@@ -4979,20 +4976,20 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>193</v>
+        <v>662</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
       </c>
       <c r="D81" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G81" s="20" t="s">
         <v>183</v>
@@ -5001,20 +4998,20 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C82" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D82" s="2">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G82" s="20" t="s">
         <v>183</v>
@@ -5022,21 +5019,21 @@
       <c r="H82" s="29"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A83" s="12" t="s">
-        <v>663</v>
+      <c r="A83" s="16" t="s">
+        <v>202</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C83" s="2">
-        <v>24</v>
-      </c>
-      <c r="D83" s="2">
-        <v>64</v>
+        <v>55</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G83" s="20" t="s">
         <v>183</v>
@@ -5045,20 +5042,20 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="16" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C84" s="2">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G84" s="20" t="s">
         <v>183</v>
@@ -5067,7 +5064,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>207</v>
@@ -5075,56 +5072,56 @@
       <c r="C85" s="2">
         <v>38</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>208</v>
+      <c r="D85" s="2">
+        <v>125</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G85" s="20" t="s">
         <v>183</v>
       </c>
       <c r="H85" s="29"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A86" s="16" t="s">
-        <v>210</v>
+    <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A86" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C86" s="2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D86" s="2">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G86" s="20" t="s">
         <v>183</v>
       </c>
       <c r="H86" s="29"/>
     </row>
-    <row r="87" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
+      </c>
+      <c r="B87" s="2">
+        <v>250</v>
       </c>
       <c r="C87" s="2">
-        <v>60</v>
-      </c>
-      <c r="D87" s="2">
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G87" s="20" t="s">
         <v>183</v>
@@ -5132,78 +5129,76 @@
       <c r="H87" s="29"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A88" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="B88" s="2">
-        <v>250</v>
-      </c>
-      <c r="C88" s="2">
+      <c r="A88" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H88" s="25" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="2">
+        <v>25</v>
+      </c>
+      <c r="C89" s="2">
         <v>0</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G88" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="H88" s="29"/>
-    </row>
-    <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H89" s="25" t="s">
-        <v>692</v>
-      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="H89" s="29"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B90" s="2">
-        <v>25</v>
+        <v>400</v>
       </c>
       <c r="C90" s="2">
-        <v>0</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>644</v>
+        <v>55</v>
+      </c>
+      <c r="D90" s="2">
+        <v>26</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="F90" s="2"/>
       <c r="G90" s="20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H90" s="29"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -5212,18 +5207,18 @@
         <v>55</v>
       </c>
       <c r="D91" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="20" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H91" s="29"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -5232,7 +5227,7 @@
         <v>55</v>
       </c>
       <c r="D92" s="2">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
@@ -5243,7 +5238,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -5252,7 +5247,7 @@
         <v>55</v>
       </c>
       <c r="D93" s="2">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
@@ -5263,143 +5258,145 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B94" s="2">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C94" s="2">
-        <v>55</v>
-      </c>
-      <c r="D94" s="2">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
+      <c r="F94" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="G94" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H94" s="29"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B95" s="2">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C95" s="2">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>227</v>
+        <v>37</v>
+      </c>
+      <c r="D95" s="2">
+        <v>34</v>
       </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="2" t="s">
-        <v>228</v>
-      </c>
+      <c r="F95" s="2"/>
       <c r="G95" s="20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H95" s="29"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B96" s="2">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="C96" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D96" s="2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
+      <c r="F96" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="G96" s="20" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H96" s="29"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B97" s="2">
-        <v>60</v>
+        <v>2000</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
       </c>
       <c r="D97" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E97" s="2"/>
-      <c r="F97" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="F97" s="2"/>
       <c r="G97" s="20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H97" s="29"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B98" s="2">
-        <v>2000</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D98" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H98" s="29"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B99" s="2">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="C99" s="2">
-        <v>63</v>
-      </c>
-      <c r="D99" s="2">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B100" s="2">
-        <v>40</v>
-      </c>
-      <c r="C100" s="2">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D100" s="2">
+        <v>62</v>
       </c>
       <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
+      <c r="F100" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="G100" s="20" t="s">
         <v>241</v>
       </c>
@@ -5407,64 +5404,64 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>633</v>
+        <v>244</v>
+      </c>
+      <c r="B101" s="2">
+        <v>150</v>
+      </c>
+      <c r="C101" s="2">
+        <v>23</v>
       </c>
       <c r="D101" s="2">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B102" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="C102" s="2">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D102" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B103" s="2">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="C103" s="2">
         <v>74</v>
       </c>
       <c r="D103" s="2">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>249</v>
@@ -5472,101 +5469,99 @@
       <c r="H103" s="29"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A104" s="12" t="s">
-        <v>250</v>
+      <c r="A104" s="13" t="s">
+        <v>252</v>
       </c>
       <c r="B104" s="2">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="C104" s="2">
-        <v>74</v>
-      </c>
-      <c r="D104" s="2">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H104" s="29"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="13" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B105" s="2">
         <v>300</v>
       </c>
       <c r="C105" s="2">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>644</v>
+        <v>30</v>
+      </c>
+      <c r="D105" s="2">
+        <v>40</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="2" t="s">
-        <v>253</v>
-      </c>
+      <c r="F105" s="2"/>
       <c r="G105" s="20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H105" s="29"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A106" s="13" t="s">
-        <v>255</v>
+    <row r="106" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A106" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="B106" s="2">
-        <v>300</v>
-      </c>
-      <c r="C106" s="2">
-        <v>30</v>
+        <v>500</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="D106" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H106" s="29"/>
     </row>
-    <row r="107" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="B107" s="2">
-        <v>500</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0</v>
       </c>
       <c r="D107" s="2">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H107" s="29"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="C108" s="2">
-        <v>0</v>
+      <c r="C108" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="D108" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -5577,7 +5572,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>633</v>
@@ -5585,8 +5580,8 @@
       <c r="C109" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D109" s="2">
-        <v>72</v>
+      <c r="D109" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5596,237 +5591,239 @@
       <c r="H109" s="29"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>633</v>
+      <c r="A110" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B110" s="2">
+        <v>300</v>
+      </c>
+      <c r="C110" s="2">
+        <v>20</v>
+      </c>
+      <c r="D110" s="2">
+        <v>20</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H110" s="29"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A111" s="13" t="s">
-        <v>264</v>
+      <c r="A111" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="B111" s="2">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C111" s="2">
         <v>20</v>
       </c>
       <c r="D111" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H111" s="29"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A112" s="14" t="s">
-        <v>266</v>
+      <c r="A112" s="15" t="s">
+        <v>268</v>
       </c>
       <c r="B112" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C112" s="2">
         <v>20</v>
       </c>
       <c r="D112" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H112" s="29"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A113" s="15" t="s">
-        <v>268</v>
+      <c r="A113" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="B113" s="2">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="C113" s="2">
-        <v>20</v>
-      </c>
-      <c r="D113" s="2">
-        <v>29</v>
+        <v>69</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
+      <c r="F113" s="2" t="s">
+        <v>271</v>
+      </c>
       <c r="G113" s="20" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H113" s="29"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A114" s="14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B114" s="2">
-        <v>450</v>
+        <v>2500</v>
       </c>
       <c r="C114" s="2">
-        <v>69</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>644</v>
+        <v>23</v>
+      </c>
+      <c r="D114" s="2">
+        <v>55</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="H114" s="29"/>
     </row>
-    <row r="115" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B115" s="2">
-        <v>2500</v>
+        <v>9000</v>
       </c>
       <c r="C115" s="2">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D115" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="H115" s="29"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B116" s="2">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="C116" s="2">
-        <v>54</v>
-      </c>
-      <c r="D116" s="2">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H116" s="29"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A117" s="14" t="s">
-        <v>278</v>
+    <row r="117" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A117" s="15" t="s">
+        <v>647</v>
       </c>
       <c r="B117" s="2">
-        <v>10500</v>
+        <v>1700</v>
       </c>
       <c r="C117" s="2">
-        <v>0</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>279</v>
+        <v>67</v>
+      </c>
+      <c r="D117" s="2">
+        <v>90</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H117" s="29"/>
     </row>
-    <row r="118" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A118" s="15" t="s">
-        <v>647</v>
-      </c>
-      <c r="B118" s="2">
-        <v>1700</v>
-      </c>
-      <c r="C118" s="2">
-        <v>67</v>
-      </c>
-      <c r="D118" s="2">
-        <v>90</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="G118" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="H118" s="29"/>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G118" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H118" s="26" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A119" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G119" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H119" s="26" t="s">
-        <v>692</v>
-      </c>
+      <c r="A119" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="B119" s="2">
+        <v>75</v>
+      </c>
+      <c r="C119" s="2">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G119" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="H119" s="29"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B120" s="2">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>650</v>
+      <c r="D120" s="2">
+        <v>5</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G120" s="20" t="s">
         <v>652</v>
@@ -5835,20 +5832,20 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B121" s="2">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="C121" s="2">
         <v>0</v>
       </c>
-      <c r="D121" s="2">
-        <v>5</v>
+      <c r="D121" s="2" t="s">
+        <v>650</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G121" s="20" t="s">
         <v>652</v>
@@ -5857,20 +5854,20 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>666</v>
+        <v>290</v>
       </c>
       <c r="B122" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C122" s="2">
-        <v>0</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>650</v>
+        <v>24</v>
+      </c>
+      <c r="D122" s="2">
+        <v>25</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G122" s="20" t="s">
         <v>652</v>
@@ -5879,16 +5876,16 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B123" s="2">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="C123" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D123" s="2">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
@@ -5901,20 +5898,20 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>292</v>
+        <v>667</v>
       </c>
       <c r="B124" s="2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C124" s="2">
-        <v>48</v>
-      </c>
-      <c r="D124" s="2">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>650</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="G124" s="20" t="s">
         <v>652</v>
@@ -5923,10 +5920,10 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B125" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C125" s="2">
         <v>0</v>
@@ -5936,7 +5933,7 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G125" s="20" t="s">
         <v>652</v>
@@ -5944,43 +5941,43 @@
       <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A126" s="12" t="s">
-        <v>668</v>
+      <c r="A126" s="13" t="s">
+        <v>654</v>
       </c>
       <c r="B126" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C126" s="2">
-        <v>0</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>650</v>
+        <v>9</v>
+      </c>
+      <c r="D126" s="2">
+        <v>10</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="G126" s="20" t="s">
         <v>652</v>
       </c>
       <c r="H126" s="29"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B127" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C127" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D127" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="G127" s="20" t="s">
         <v>652</v>
@@ -5988,176 +5985,174 @@
       <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A128" s="13" t="s">
-        <v>658</v>
+      <c r="A128" s="14" t="s">
+        <v>660</v>
       </c>
       <c r="B128" s="2">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C128" s="2">
-        <v>24</v>
-      </c>
-      <c r="D128" s="2">
-        <v>35</v>
+        <v>66</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G128" s="20" t="s">
         <v>652</v>
       </c>
       <c r="H128" s="29"/>
     </row>
-    <row r="129" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A129" s="14" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="B129" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="C129" s="2">
-        <v>66</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>644</v>
+        <v>58</v>
+      </c>
+      <c r="D129" s="2">
+        <v>120</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="G129" s="20" t="s">
         <v>652</v>
       </c>
       <c r="H129" s="29"/>
     </row>
-    <row r="130" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
-      <c r="A130" s="14" t="s">
-        <v>671</v>
-      </c>
-      <c r="B130" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C130" s="2">
-        <v>58</v>
-      </c>
-      <c r="D130" s="2">
-        <v>120</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="G130" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="H130" s="29"/>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A130" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G130" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H130" s="25" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G131" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H131" s="25" t="s">
-        <v>692</v>
-      </c>
+      <c r="A131" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B131" s="2">
+        <v>50</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G131" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="H131" s="29"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A132" s="12" t="s">
-        <v>286</v>
+      <c r="A132" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="B132" s="2">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>644</v>
+      <c r="D132" s="2">
+        <v>20</v>
       </c>
       <c r="E132" s="2"/>
-      <c r="F132" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="F132" s="2"/>
       <c r="G132" s="20" t="s">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="H132" s="29"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A133" s="13" t="s">
-        <v>69</v>
+      <c r="A133" s="12" t="s">
+        <v>293</v>
       </c>
       <c r="B133" s="2">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
-      <c r="D133" s="2">
-        <v>20</v>
+      <c r="D133" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="20" t="s">
-        <v>70</v>
+        <v>294</v>
       </c>
       <c r="H133" s="29"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B134" s="2">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>633</v>
+      <c r="D134" s="2">
+        <v>5</v>
       </c>
       <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
+      <c r="F134" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="G134" s="20" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H134" s="29"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B135" s="2">
-        <v>45</v>
-      </c>
-      <c r="C135" s="2">
-        <v>0</v>
-      </c>
-      <c r="D135" s="2">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="E135" s="2"/>
-      <c r="F135" s="2" t="s">
-        <v>296</v>
-      </c>
+      <c r="F135" s="2"/>
       <c r="G135" s="20" t="s">
         <v>297</v>
       </c>
@@ -6165,62 +6160,66 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B136" s="2">
-        <v>200</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>633</v>
+        <v>600</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>633</v>
       </c>
       <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
+      <c r="F136" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="G136" s="20" t="s">
         <v>297</v>
       </c>
       <c r="H136" s="29"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B137" s="2">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="C137" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>633</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="H137" s="29"/>
     </row>
-    <row r="138" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A138" s="12" t="s">
-        <v>301</v>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A138" s="13" t="s">
+        <v>304</v>
       </c>
       <c r="B138" s="2">
         <v>1500</v>
       </c>
       <c r="C138" s="2">
-        <v>52</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E138" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D138" s="2">
+        <v>100</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>305</v>
+      </c>
       <c r="F138" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G138" s="20" t="s">
         <v>303</v>
@@ -6228,181 +6227,179 @@
       <c r="H138" s="29"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A139" s="13" t="s">
-        <v>304</v>
+      <c r="A139" s="14" t="s">
+        <v>307</v>
       </c>
       <c r="B139" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C139" s="2">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D139" s="2">
-        <v>100</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>305</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H139" s="29"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="14" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B140" s="2">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C140" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D140" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="G140" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H140" s="29"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B141" s="2">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="C141" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D141" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H141" s="29"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B142" s="2">
-        <v>150</v>
+        <v>720</v>
       </c>
       <c r="C142" s="2">
         <v>0</v>
       </c>
       <c r="D142" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G142" s="20" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A143" s="14" t="s">
-        <v>315</v>
+    <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A143" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="B143" s="2">
-        <v>720</v>
+        <v>2000</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
       <c r="D143" s="2">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H143" s="29"/>
     </row>
-    <row r="144" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A144" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="B144" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C144" s="2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A144" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G144" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H144" s="27" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A145" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="2">
+        <v>400</v>
+      </c>
+      <c r="C145" s="2">
         <v>0</v>
       </c>
-      <c r="D144" s="2">
-        <v>57</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G144" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="H144" s="29"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A145" s="10" t="s">
+      <c r="D145" s="2">
+        <v>99</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G145" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="B145" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G145" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H145" s="27" t="s">
-        <v>692</v>
-      </c>
+      <c r="H145" s="29"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B146" s="2">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="C146" s="2">
         <v>0</v>
       </c>
-      <c r="D146" s="2">
-        <v>99</v>
+      <c r="D146" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G146" s="20" t="s">
         <v>320</v>
@@ -6411,38 +6408,36 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B147" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C147" s="2">
         <v>0</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>644</v>
+      <c r="D147" s="2">
+        <v>14</v>
       </c>
       <c r="E147" s="2"/>
-      <c r="F147" s="2" t="s">
-        <v>324</v>
-      </c>
+      <c r="F147" s="2"/>
       <c r="G147" s="20" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H147" s="29"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B148" s="2">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C148" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D148" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -6451,143 +6446,147 @@
       </c>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B149" s="2">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="C149" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D149" s="2">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
+      <c r="F149" s="2" t="s">
+        <v>329</v>
+      </c>
       <c r="G149" s="20" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H149" s="29"/>
     </row>
-    <row r="150" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="12" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B150" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C150" s="2">
         <v>0</v>
       </c>
-      <c r="D150" s="2">
-        <v>5</v>
+      <c r="D150" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G150" s="20" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="H150" s="29"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A151" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B151" s="2">
-        <v>100</v>
-      </c>
-      <c r="C151" s="2">
+      <c r="A151" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H151" s="27" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A152" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C152" s="2">
         <v>0</v>
       </c>
-      <c r="D151" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G151" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="H151" s="29"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A152" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H152" s="27" t="s">
-        <v>692</v>
-      </c>
+      <c r="D152" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G152" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="H152" s="29"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C153" s="2">
-        <v>0</v>
+        <v>633</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="H153" s="29"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A154" s="12" t="s">
-        <v>336</v>
+    <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A154" s="14" t="s">
+        <v>342</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>633</v>
+        <v>343</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>633</v>
+        <v>344</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E154" s="2"/>
+        <v>634</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>346</v>
+      </c>
       <c r="F154" s="2" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="G154" s="20" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>343</v>
@@ -6596,13 +6595,13 @@
         <v>344</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>346</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G155" s="20" t="s">
         <v>348</v>
@@ -6611,7 +6610,7 @@
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>343</v>
@@ -6626,7 +6625,7 @@
         <v>346</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G156" s="20" t="s">
         <v>348</v>
@@ -6635,7 +6634,7 @@
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>343</v>
@@ -6650,16 +6649,16 @@
         <v>346</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
-        <v>354</v>
+        <v>631</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>343</v>
@@ -6674,7 +6673,7 @@
         <v>346</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G158" s="20" t="s">
         <v>356</v>
@@ -6683,7 +6682,7 @@
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="14" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>343</v>
@@ -6698,7 +6697,7 @@
         <v>346</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G159" s="20" t="s">
         <v>356</v>
@@ -6707,7 +6706,7 @@
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>343</v>
@@ -6722,7 +6721,7 @@
         <v>346</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G160" s="20" t="s">
         <v>356</v>
@@ -6731,7 +6730,7 @@
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>343</v>
@@ -6746,7 +6745,7 @@
         <v>346</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G161" s="20" t="s">
         <v>356</v>
@@ -6755,7 +6754,7 @@
     </row>
     <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="14" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>343</v>
@@ -6770,277 +6769,273 @@
         <v>346</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G162" s="20" t="s">
         <v>356</v>
       </c>
       <c r="H162" s="29"/>
     </row>
-    <row r="163" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A163" s="14" t="s">
-        <v>630</v>
+    <row r="163" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A163" s="15" t="s">
+        <v>367</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>346</v>
+        <v>637</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G163" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="H163" s="29"/>
+    </row>
+    <row r="164" spans="1:10" ht="54" x14ac:dyDescent="0.45">
+      <c r="A164" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G164" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="H163" s="29"/>
-    </row>
-    <row r="164" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A164" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="E164" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="G164" s="20" t="s">
-        <v>341</v>
-      </c>
       <c r="H164" s="29"/>
     </row>
-    <row r="165" spans="1:10" ht="54" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="15" t="s">
-        <v>372</v>
+        <v>632</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>373</v>
+        <v>633</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>374</v>
+        <v>633</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E165" s="6" t="s">
-        <v>375</v>
+        <v>633</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>639</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="H165" s="29"/>
     </row>
-    <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A166" s="15" t="s">
-        <v>632</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E166" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G166" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="H166" s="29"/>
-    </row>
-    <row r="167" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A167" s="31" t="s">
+    <row r="166" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A166" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="B167" s="32" t="s">
+      <c r="B166" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C167" s="32" t="s">
+      <c r="C166" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D167" s="32" t="s">
+      <c r="D166" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E167" s="32" t="s">
+      <c r="E166" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F167" s="32" t="s">
+      <c r="F166" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G167" s="25" t="s">
+      <c r="G166" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H167" s="27" t="s">
+      <c r="H166" s="27" t="s">
         <v>692</v>
       </c>
     </row>
+    <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A167" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="B167" s="34">
+        <v>120</v>
+      </c>
+      <c r="C167" s="34">
+        <v>57</v>
+      </c>
+      <c r="D167" s="34">
+        <v>40</v>
+      </c>
+      <c r="E167" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="F167" s="34" t="s">
+        <v>679</v>
+      </c>
+      <c r="G167" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="H167" s="43" t="s">
+        <v>703</v>
+      </c>
+    </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A168" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="B168" s="34">
+      <c r="A168" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B168" s="2">
         <v>120</v>
       </c>
-      <c r="C168" s="34">
-        <v>57</v>
-      </c>
-      <c r="D168" s="34">
-        <v>40</v>
-      </c>
-      <c r="E168" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="F168" s="34" t="s">
-        <v>679</v>
-      </c>
-      <c r="G168" s="36" t="s">
-        <v>377</v>
-      </c>
-      <c r="H168" s="43" t="s">
-        <v>706</v>
-      </c>
+      <c r="C168" s="2">
+        <v>62</v>
+      </c>
+      <c r="D168" s="2">
+        <v>270</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G168" s="37"/>
+      <c r="H168" s="44"/>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B169" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C169" s="2">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D169" s="2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
       </c>
       <c r="C170" s="2">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D170" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
       </c>
       <c r="C171" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D171" s="2">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
     </row>
     <row r="172" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
       </c>
       <c r="C172" s="2">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D172" s="2">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
       </c>
       <c r="C173" s="2">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D173" s="2">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
     </row>
     <row r="174" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" s="12" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
       </c>
       <c r="C174" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D174" s="2">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7048,199 +7043,180 @@
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B175" s="2">
         <v>200</v>
       </c>
       <c r="C175" s="2">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D175" s="2">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
     </row>
     <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B176" s="2">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C176" s="2">
-        <v>77</v>
-      </c>
-      <c r="D176" s="2">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>644</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>687</v>
+        <v>397</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
     </row>
-    <row r="177" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A177" s="12" t="s">
-        <v>396</v>
+    <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A177" s="13" t="s">
+        <v>398</v>
       </c>
       <c r="B177" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C177" s="2">
-        <v>55</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>644</v>
+        <v>86</v>
+      </c>
+      <c r="D177" s="2">
+        <v>83</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>397</v>
+        <v>688</v>
       </c>
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
     </row>
     <row r="178" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B178" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C178" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D178" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
     </row>
-    <row r="179" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B179" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C179" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D179" s="2">
-        <v>100</v>
-      </c>
-      <c r="E179" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>672</v>
+      </c>
       <c r="F179" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
-    <row r="180" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B180" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C180" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D180" s="2">
-        <v>64</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>672</v>
+        <v>60</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>405</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
     </row>
-    <row r="181" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>404</v>
+        <v>675</v>
       </c>
       <c r="B181" s="2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="C181" s="2">
-        <v>83</v>
-      </c>
-      <c r="D181" s="2">
-        <v>60</v>
-      </c>
-      <c r="E181" s="9" t="s">
-        <v>405</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E181" s="2"/>
       <c r="F181" s="2" t="s">
-        <v>691</v>
+        <v>407</v>
       </c>
       <c r="G181" s="37"/>
       <c r="H181" s="44"/>
     </row>
-    <row r="182" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A182" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="B182" s="2">
+    <row r="182" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A182" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="B182" s="18">
         <v>500</v>
       </c>
-      <c r="C182" s="2">
-        <v>0</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G182" s="37"/>
-      <c r="H182" s="44"/>
-    </row>
-    <row r="183" spans="1:8" ht="69.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A183" s="17" t="s">
-        <v>674</v>
-      </c>
-      <c r="B183" s="18">
-        <v>500</v>
-      </c>
-      <c r="C183" s="18">
+      <c r="C182" s="18">
         <v>87</v>
       </c>
-      <c r="D183" s="18">
+      <c r="D182" s="18">
         <v>130</v>
       </c>
-      <c r="E183" s="30" t="s">
+      <c r="E182" s="30" t="s">
         <v>673</v>
       </c>
-      <c r="F183" s="18" t="s">
+      <c r="F182" s="18" t="s">
         <v>696</v>
       </c>
-      <c r="G183" s="38"/>
-      <c r="H183" s="45"/>
-    </row>
+      <c r="G182" s="38"/>
+      <c r="H182" s="45"/>
+    </row>
+    <row r="183" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="187" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="G168:G183"/>
+    <mergeCell ref="G167:G182"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="H168:H183"/>
-    <mergeCell ref="H36:H54"/>
-    <mergeCell ref="H68:H71"/>
-    <mergeCell ref="H56:H66"/>
+    <mergeCell ref="H167:H182"/>
+    <mergeCell ref="H35:H53"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="H55:H65"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7A2A18-BBD1-45C5-9847-9D653902EAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572AF024-571C-4414-AFC2-10B9E643F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="707">
   <si>
     <t>家里</t>
   </si>
@@ -2261,6 +2261,9 @@
   </si>
   <si>
     <t>继母艾莎；1-5级图</t>
+  </si>
+  <si>
+    <t>毁灭战士的头</t>
   </si>
 </sst>
 </file>
@@ -4746,7 +4749,7 @@
       </c>
       <c r="H70" s="47"/>
     </row>
-    <row r="71" spans="1:8" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
         <v>174</v>
       </c>
@@ -5108,7 +5111,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>215</v>
+        <v>706</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572AF024-571C-4414-AFC2-10B9E643F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D69BCA7-ACD7-4A90-BF87-65D3FF39ABC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="706">
   <si>
     <t>家里</t>
   </si>
@@ -750,9 +750,6 @@
   </si>
   <si>
     <t>仆人</t>
-  </si>
-  <si>
-    <t>骷髅图虔诚事件</t>
   </si>
   <si>
     <t>马克思的记忆“过去的幽灵”</t>
@@ -3235,7 +3232,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="39" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3268,7 +3265,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3282,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="20" t="s">
@@ -3316,7 +3313,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3423,7 +3420,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3439,7 +3436,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H10" s="29"/>
     </row>
@@ -3645,7 +3642,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H20" s="29"/>
     </row>
@@ -3680,7 +3677,7 @@
         <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="20" t="s">
@@ -3702,7 +3699,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3912,10 +3909,10 @@
         <v>83</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3952,7 +3949,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -3974,7 +3971,7 @@
         <v>88</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4070,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4145,7 +4142,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4167,7 +4164,7 @@
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -4189,7 +4186,7 @@
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4268,7 +4265,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>113</v>
@@ -4386,7 +4383,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
@@ -4410,7 +4407,7 @@
         <v>139</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4622,11 +4619,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G65" s="20" t="s">
         <v>136</v>
@@ -4656,7 +4653,7 @@
         <v>6</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -4674,13 +4671,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>167</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
@@ -4698,7 +4695,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>167</v>
@@ -4720,7 +4717,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>167</v>
@@ -4742,7 +4739,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>167</v>
@@ -4772,7 +4769,7 @@
         <v>6</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -4860,7 +4857,7 @@
         <v>6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
@@ -4979,7 +4976,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>197</v>
@@ -5001,7 +4998,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>200</v>
@@ -5111,7 +5108,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -5120,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -5154,7 +5151,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -5168,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -5325,231 +5322,231 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B97" s="2">
-        <v>2000</v>
+        <v>550</v>
       </c>
       <c r="C97" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D97" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H97" s="29"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B98" s="2">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="C98" s="2">
-        <v>63</v>
-      </c>
-      <c r="D98" s="2">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H98" s="29"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B99" s="2">
-        <v>40</v>
-      </c>
-      <c r="C99" s="2">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D99" s="2">
+        <v>62</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G99" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="20" t="s">
-        <v>241</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>633</v>
+        <v>243</v>
+      </c>
+      <c r="B100" s="2">
+        <v>150</v>
+      </c>
+      <c r="C100" s="2">
+        <v>23</v>
       </c>
       <c r="D100" s="2">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H100" s="29"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B101" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="C101" s="2">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D101" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B102" s="2">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="C102" s="2">
         <v>74</v>
       </c>
       <c r="D102" s="2">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G102" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="G102" s="20" t="s">
-        <v>249</v>
-      </c>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A103" s="12" t="s">
-        <v>250</v>
+      <c r="A103" s="13" t="s">
+        <v>251</v>
       </c>
       <c r="B103" s="2">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="C103" s="2">
-        <v>74</v>
-      </c>
-      <c r="D103" s="2">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H103" s="29"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="13" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
       </c>
       <c r="C104" s="2">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>644</v>
+        <v>30</v>
+      </c>
+      <c r="D104" s="2">
+        <v>40</v>
       </c>
       <c r="E104" s="2"/>
-      <c r="F104" s="2" t="s">
-        <v>253</v>
-      </c>
+      <c r="F104" s="2"/>
       <c r="G104" s="20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H104" s="29"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A105" s="13" t="s">
-        <v>255</v>
+    <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A105" s="12" t="s">
+        <v>256</v>
       </c>
       <c r="B105" s="2">
-        <v>300</v>
-      </c>
-      <c r="C105" s="2">
-        <v>30</v>
+        <v>500</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="D105" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H105" s="29"/>
     </row>
-    <row r="106" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="B106" s="2">
-        <v>500</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0</v>
       </c>
       <c r="D106" s="2">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H106" s="29"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C107" s="2">
-        <v>0</v>
+        <v>632</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="D107" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H107" s="29"/>
     </row>
@@ -5558,256 +5555,258 @@
         <v>262</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D108" s="2">
-        <v>72</v>
+        <v>632</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H108" s="29"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>633</v>
+      <c r="B109" s="2">
+        <v>300</v>
+      </c>
+      <c r="C109" s="2">
+        <v>20</v>
+      </c>
+      <c r="D109" s="2">
+        <v>20</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H109" s="29"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110" s="13" t="s">
-        <v>264</v>
+      <c r="A110" s="14" t="s">
+        <v>265</v>
       </c>
       <c r="B110" s="2">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C110" s="2">
         <v>20</v>
       </c>
       <c r="D110" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H110" s="29"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A111" s="14" t="s">
-        <v>266</v>
+      <c r="A111" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="B111" s="2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C111" s="2">
         <v>20</v>
       </c>
       <c r="D111" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H111" s="29"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A112" s="15" t="s">
-        <v>268</v>
+      <c r="A112" s="14" t="s">
+        <v>269</v>
       </c>
       <c r="B112" s="2">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="C112" s="2">
-        <v>20</v>
-      </c>
-      <c r="D112" s="2">
-        <v>29</v>
+        <v>69</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
+      <c r="F112" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="G112" s="20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H112" s="29"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A113" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B113" s="2">
-        <v>450</v>
+        <v>2500</v>
       </c>
       <c r="C113" s="2">
-        <v>69</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>644</v>
+        <v>23</v>
+      </c>
+      <c r="D113" s="2">
+        <v>55</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="H113" s="29"/>
     </row>
-    <row r="114" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B114" s="2">
-        <v>2500</v>
+        <v>9000</v>
       </c>
       <c r="C114" s="2">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D114" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="H114" s="29"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B115" s="2">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="C115" s="2">
-        <v>54</v>
-      </c>
-      <c r="D115" s="2">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H115" s="29"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A116" s="14" t="s">
-        <v>278</v>
+    <row r="116" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A116" s="15" t="s">
+        <v>646</v>
       </c>
       <c r="B116" s="2">
-        <v>10500</v>
+        <v>1700</v>
       </c>
       <c r="C116" s="2">
-        <v>0</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>279</v>
+        <v>67</v>
+      </c>
+      <c r="D116" s="2">
+        <v>90</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H116" s="29"/>
     </row>
-    <row r="117" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A117" s="15" t="s">
-        <v>647</v>
-      </c>
-      <c r="B117" s="2">
-        <v>1700</v>
-      </c>
-      <c r="C117" s="2">
-        <v>67</v>
-      </c>
-      <c r="D117" s="2">
-        <v>90</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="G117" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="H117" s="29"/>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G117" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H117" s="26" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="B118" s="2">
+        <v>75</v>
+      </c>
+      <c r="C118" s="2">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B118" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G118" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H118" s="26" t="s">
-        <v>692</v>
-      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G118" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
         <v>664</v>
       </c>
       <c r="B119" s="2">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C119" s="2">
         <v>0</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>650</v>
+      <c r="D119" s="2">
+        <v>5</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G119" s="20" t="s">
         <v>651</v>
-      </c>
-      <c r="G119" s="20" t="s">
-        <v>652</v>
       </c>
       <c r="H119" s="29"/>
     </row>
@@ -5816,86 +5815,86 @@
         <v>665</v>
       </c>
       <c r="B120" s="2">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
       </c>
-      <c r="D120" s="2">
-        <v>5</v>
+      <c r="D120" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H120" s="29"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>666</v>
+        <v>289</v>
       </c>
       <c r="B121" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C121" s="2">
-        <v>0</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>650</v>
+        <v>24</v>
+      </c>
+      <c r="D121" s="2">
+        <v>25</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H121" s="29"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B122" s="2">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="C122" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D122" s="2">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>292</v>
+        <v>666</v>
       </c>
       <c r="B123" s="2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C123" s="2">
-        <v>48</v>
-      </c>
-      <c r="D123" s="2">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H123" s="29"/>
     </row>
@@ -5904,240 +5903,238 @@
         <v>667</v>
       </c>
       <c r="B124" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
         <v>669</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A125" s="12" t="s">
-        <v>668</v>
+      <c r="A125" s="13" t="s">
+        <v>653</v>
       </c>
       <c r="B125" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C125" s="2">
-        <v>0</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>650</v>
+        <v>9</v>
+      </c>
+      <c r="D125" s="2">
+        <v>10</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H125" s="29"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="13" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B126" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C126" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D126" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H126" s="29"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A127" s="13" t="s">
-        <v>658</v>
+      <c r="A127" s="14" t="s">
+        <v>659</v>
       </c>
       <c r="B127" s="2">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C127" s="2">
-        <v>24</v>
-      </c>
-      <c r="D127" s="2">
-        <v>35</v>
+        <v>66</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H127" s="29"/>
     </row>
-    <row r="128" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="14" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="B128" s="2">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="C128" s="2">
-        <v>66</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>644</v>
+        <v>58</v>
+      </c>
+      <c r="D128" s="2">
+        <v>120</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>661</v>
+        <v>700</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H128" s="29"/>
     </row>
-    <row r="129" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
-      <c r="A129" s="14" t="s">
-        <v>671</v>
-      </c>
-      <c r="B129" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C129" s="2">
-        <v>58</v>
-      </c>
-      <c r="D129" s="2">
-        <v>120</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="G129" s="20" t="s">
-        <v>652</v>
-      </c>
-      <c r="H129" s="29"/>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A129" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G129" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H129" s="25" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G130" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H130" s="25" t="s">
-        <v>692</v>
-      </c>
+      <c r="B130" s="2">
+        <v>50</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="H130" s="29"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="12" t="s">
-        <v>286</v>
+      <c r="A131" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="B131" s="2">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>644</v>
+      <c r="D131" s="2">
+        <v>20</v>
       </c>
       <c r="E131" s="2"/>
-      <c r="F131" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="F131" s="2"/>
       <c r="G131" s="20" t="s">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="H131" s="29"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A132" s="13" t="s">
-        <v>69</v>
+      <c r="A132" s="12" t="s">
+        <v>292</v>
       </c>
       <c r="B132" s="2">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
       </c>
-      <c r="D132" s="2">
-        <v>20</v>
+      <c r="D132" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="20" t="s">
-        <v>70</v>
+        <v>293</v>
       </c>
       <c r="H132" s="29"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B133" s="2">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>633</v>
+      <c r="D133" s="2">
+        <v>5</v>
       </c>
       <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
+      <c r="F133" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="G133" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H133" s="29"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B134" s="2">
-        <v>45</v>
-      </c>
-      <c r="C134" s="2">
-        <v>0</v>
-      </c>
-      <c r="D134" s="2">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="E134" s="2"/>
-      <c r="F134" s="2" t="s">
+      <c r="F134" s="2"/>
+      <c r="G134" s="20" t="s">
         <v>296</v>
-      </c>
-      <c r="G134" s="20" t="s">
-        <v>297</v>
       </c>
       <c r="H134" s="29"/>
     </row>
@@ -6146,540 +6143,544 @@
         <v>298</v>
       </c>
       <c r="B135" s="2">
-        <v>200</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>633</v>
+        <v>600</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
+      <c r="F135" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="G135" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H135" s="29"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B136" s="2">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="C136" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G136" s="20" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H136" s="29"/>
     </row>
-    <row r="137" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A137" s="12" t="s">
-        <v>301</v>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A137" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
       </c>
       <c r="C137" s="2">
-        <v>52</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E137" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D137" s="2">
+        <v>100</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="F137" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G137" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="G137" s="20" t="s">
-        <v>303</v>
-      </c>
       <c r="H137" s="29"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A138" s="13" t="s">
-        <v>304</v>
+      <c r="A138" s="14" t="s">
+        <v>306</v>
       </c>
       <c r="B138" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C138" s="2">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D138" s="2">
-        <v>100</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>305</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G138" s="20" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H138" s="29"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B139" s="2">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="C139" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D139" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H139" s="29"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B140" s="2">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="C140" s="2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D140" s="2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="G140" s="20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H140" s="29"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B141" s="2">
-        <v>150</v>
+        <v>720</v>
       </c>
       <c r="C141" s="2">
         <v>0</v>
       </c>
       <c r="D141" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H141" s="29"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A142" s="14" t="s">
-        <v>315</v>
+    <row r="142" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A142" s="15" t="s">
+        <v>317</v>
       </c>
       <c r="B142" s="2">
-        <v>720</v>
+        <v>2000</v>
       </c>
       <c r="C142" s="2">
         <v>0</v>
       </c>
       <c r="D142" s="2">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G142" s="20" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="H142" s="29"/>
     </row>
-    <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A143" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="B143" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C143" s="2">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A143" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G143" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H143" s="27" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A144" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="2">
+        <v>400</v>
+      </c>
+      <c r="C144" s="2">
         <v>0</v>
       </c>
-      <c r="D143" s="2">
-        <v>57</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" s="2" t="s">
+      <c r="D144" s="2">
+        <v>99</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G144" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="G143" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="H143" s="29"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A144" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G144" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H144" s="27" t="s">
-        <v>692</v>
-      </c>
+      <c r="H144" s="29"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B145" s="2">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
-      <c r="D145" s="2">
-        <v>99</v>
+      <c r="D145" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H145" s="29"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B146" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C146" s="2">
         <v>0</v>
       </c>
-      <c r="D146" s="2" t="s">
-        <v>644</v>
+      <c r="D146" s="2">
+        <v>14</v>
       </c>
       <c r="E146" s="2"/>
-      <c r="F146" s="2" t="s">
-        <v>324</v>
-      </c>
+      <c r="F146" s="2"/>
       <c r="G146" s="20" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H146" s="29"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B147" s="2">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="C147" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D147" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H147" s="29"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
         <v>327</v>
       </c>
       <c r="B148" s="2">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="C148" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D148" s="2">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
+      <c r="F148" s="2" t="s">
+        <v>328</v>
+      </c>
       <c r="G148" s="20" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H148" s="29"/>
     </row>
-    <row r="149" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B149" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C149" s="2">
         <v>0</v>
       </c>
-      <c r="D149" s="2">
-        <v>5</v>
+      <c r="D149" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="H149" s="29"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A150" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B150" s="2">
-        <v>100</v>
-      </c>
-      <c r="C150" s="2">
+      <c r="A150" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G150" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H150" s="27" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A151" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C151" s="2">
         <v>0</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G150" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="H150" s="29"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A151" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G151" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H151" s="27" t="s">
-        <v>692</v>
-      </c>
+      <c r="D151" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G151" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="H151" s="29"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C152" s="2">
-        <v>0</v>
+        <v>632</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G152" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H152" s="29"/>
+    </row>
+    <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="A153" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="H152" s="29"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A153" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="B153" s="2" t="s">
-        <v>633</v>
+        <v>342</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>633</v>
+        <v>343</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E153" s="2"/>
+      <c r="E153" s="6" t="s">
+        <v>345</v>
+      </c>
       <c r="F153" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H153" s="29"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F154" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G154" s="20" t="s">
         <v>347</v>
-      </c>
-      <c r="G154" s="20" t="s">
-        <v>348</v>
       </c>
       <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D155" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H155" s="29"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D156" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G156" s="20" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="H156" s="29"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
-        <v>354</v>
+        <v>630</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D157" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F157" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G157" s="20" t="s">
         <v>355</v>
-      </c>
-      <c r="G157" s="20" t="s">
-        <v>356</v>
       </c>
       <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G158" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H158" s="29"/>
     </row>
@@ -6688,22 +6689,22 @@
         <v>627</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H159" s="29"/>
     </row>
@@ -6712,22 +6713,22 @@
         <v>628</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H160" s="29"/>
     </row>
@@ -6736,185 +6737,181 @@
         <v>629</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H161" s="29"/>
     </row>
-    <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A162" s="14" t="s">
-        <v>630</v>
+    <row r="162" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="A162" s="15" t="s">
+        <v>366</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E162" s="6" t="s">
-        <v>346</v>
+      <c r="E162" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G162" s="20" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="H162" s="29"/>
     </row>
-    <row r="163" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:10" ht="54" x14ac:dyDescent="0.45">
       <c r="A163" s="15" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="E163" s="7" t="s">
-        <v>370</v>
+      <c r="E163" s="6" t="s">
+        <v>374</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="H163" s="29"/>
     </row>
-    <row r="164" spans="1:10" ht="54" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="15" t="s">
-        <v>372</v>
+        <v>631</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>373</v>
+        <v>632</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>374</v>
+        <v>632</v>
       </c>
       <c r="D164" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E164" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="E164" s="6" t="s">
-        <v>375</v>
-      </c>
       <c r="F164" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G164" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H164" s="29"/>
+    </row>
+    <row r="165" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A165" s="31" t="s">
         <v>376</v>
       </c>
-      <c r="G164" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="H164" s="29"/>
-    </row>
-    <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A165" s="15" t="s">
-        <v>632</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E165" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G165" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="H165" s="29"/>
-    </row>
-    <row r="166" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A166" s="31" t="s">
+      <c r="B165" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C165" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D165" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="E165" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F165" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G165" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H165" s="27" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+      <c r="A166" s="33" t="s">
         <v>377</v>
       </c>
-      <c r="B166" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C166" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D166" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E166" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F166" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="G166" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="H166" s="27" t="s">
-        <v>692</v>
+      <c r="B166" s="34">
+        <v>120</v>
+      </c>
+      <c r="C166" s="34">
+        <v>57</v>
+      </c>
+      <c r="D166" s="34">
+        <v>40</v>
+      </c>
+      <c r="E166" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="F166" s="34" t="s">
+        <v>678</v>
+      </c>
+      <c r="G166" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="H166" s="43" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A167" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="B167" s="34">
+      <c r="A167" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B167" s="2">
         <v>120</v>
       </c>
-      <c r="C167" s="34">
-        <v>57</v>
-      </c>
-      <c r="D167" s="34">
-        <v>40</v>
-      </c>
-      <c r="E167" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="F167" s="34" t="s">
+      <c r="C167" s="2">
+        <v>62</v>
+      </c>
+      <c r="D167" s="2">
+        <v>270</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="G167" s="36" t="s">
-        <v>377</v>
-      </c>
-      <c r="H167" s="43" t="s">
-        <v>703</v>
-      </c>
+      <c r="G167" s="37"/>
+      <c r="H167" s="44"/>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B168" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C168" s="2">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D168" s="2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
@@ -6925,16 +6922,16 @@
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B169" s="2">
         <v>200</v>
       </c>
       <c r="C169" s="2">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D169" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
@@ -6945,16 +6942,16 @@
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
       </c>
       <c r="C170" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D170" s="2">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
@@ -6965,16 +6962,16 @@
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
       </c>
       <c r="C171" s="2">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D171" s="2">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
@@ -6985,16 +6982,16 @@
     </row>
     <row r="172" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
       </c>
       <c r="C172" s="2">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D172" s="2">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
@@ -7005,16 +7002,16 @@
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
       </c>
       <c r="C173" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D173" s="2">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
@@ -7025,16 +7022,16 @@
     </row>
     <row r="174" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" s="12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
       </c>
       <c r="C174" s="2">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D174" s="2">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
@@ -7046,56 +7043,56 @@
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B175" s="2">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C175" s="2">
-        <v>77</v>
-      </c>
-      <c r="D175" s="2">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>687</v>
+        <v>396</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
     </row>
-    <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.45">
-      <c r="A176" s="12" t="s">
-        <v>396</v>
+    <row r="176" spans="1:10" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="A176" s="13" t="s">
+        <v>397</v>
       </c>
       <c r="B176" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C176" s="2">
-        <v>55</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>644</v>
+        <v>86</v>
+      </c>
+      <c r="D176" s="2">
+        <v>83</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>397</v>
+        <v>687</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
     </row>
     <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A177" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B177" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C177" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D177" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
@@ -7104,41 +7101,43 @@
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
     </row>
-    <row r="178" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B178" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C178" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D178" s="2">
-        <v>100</v>
-      </c>
-      <c r="E178" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>671</v>
+      </c>
       <c r="F178" s="2" t="s">
         <v>689</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
     </row>
-    <row r="179" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B179" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C179" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D179" s="2">
-        <v>64</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>672</v>
+        <v>60</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>404</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>690</v>
@@ -7146,77 +7145,55 @@
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
-    <row r="180" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>404</v>
+        <v>674</v>
       </c>
       <c r="B180" s="2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="C180" s="2">
-        <v>83</v>
-      </c>
-      <c r="D180" s="2">
-        <v>60</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>405</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E180" s="2"/>
       <c r="F180" s="2" t="s">
-        <v>691</v>
+        <v>406</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
     </row>
-    <row r="181" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A181" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="B181" s="2">
+    <row r="181" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A181" s="17" t="s">
+        <v>673</v>
+      </c>
+      <c r="B181" s="18">
         <v>500</v>
       </c>
-      <c r="C181" s="2">
-        <v>0</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G181" s="37"/>
-      <c r="H181" s="44"/>
-    </row>
-    <row r="182" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A182" s="17" t="s">
-        <v>674</v>
-      </c>
-      <c r="B182" s="18">
-        <v>500</v>
-      </c>
-      <c r="C182" s="18">
+      <c r="C181" s="18">
         <v>87</v>
       </c>
-      <c r="D182" s="18">
+      <c r="D181" s="18">
         <v>130</v>
       </c>
-      <c r="E182" s="30" t="s">
-        <v>673</v>
-      </c>
-      <c r="F182" s="18" t="s">
-        <v>696</v>
-      </c>
-      <c r="G182" s="38"/>
-      <c r="H182" s="45"/>
+      <c r="E181" s="30" t="s">
+        <v>672</v>
+      </c>
+      <c r="F181" s="18" t="s">
+        <v>695</v>
+      </c>
+      <c r="G181" s="38"/>
+      <c r="H181" s="45"/>
     </row>
     <row r="183" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="187" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="G167:G182"/>
+    <mergeCell ref="G166:G181"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="H167:H182"/>
+    <mergeCell ref="H166:H181"/>
     <mergeCell ref="H35:H53"/>
     <mergeCell ref="H67:H70"/>
     <mergeCell ref="H55:H65"/>
@@ -7240,24 +7217,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -7266,15 +7243,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -7283,32 +7260,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -7317,7 +7294,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -7325,7 +7302,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -7334,15 +7311,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -7351,15 +7328,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -7368,7 +7345,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -7376,7 +7353,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -7385,15 +7362,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -7402,7 +7379,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -7410,7 +7387,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -7419,7 +7396,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -7427,7 +7404,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
@@ -7436,15 +7413,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
@@ -7453,15 +7430,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>57</v>
@@ -7470,7 +7447,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>58</v>
@@ -7478,7 +7455,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>60</v>
@@ -7487,15 +7464,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -7504,15 +7481,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>63</v>
@@ -7521,7 +7498,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>64</v>
@@ -7529,7 +7506,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
@@ -7538,15 +7515,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -7555,15 +7532,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -7572,7 +7549,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>75</v>
@@ -7580,7 +7557,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>77</v>
@@ -7589,15 +7566,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>77</v>
@@ -7606,7 +7583,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>78</v>
@@ -7614,7 +7591,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>80</v>
@@ -7623,15 +7600,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>80</v>
@@ -7648,7 +7625,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
@@ -7657,15 +7634,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>91</v>
@@ -7674,15 +7651,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>96</v>
@@ -7691,15 +7668,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>101</v>
@@ -7708,15 +7685,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>105</v>
@@ -7725,15 +7702,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>108</v>
@@ -7742,15 +7719,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>108</v>
@@ -7767,7 +7744,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>108</v>
@@ -7776,7 +7753,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>110</v>
@@ -7784,7 +7761,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>111</v>
@@ -7793,15 +7770,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>111</v>
@@ -7810,7 +7787,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>112</v>
@@ -7818,7 +7795,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>114</v>
@@ -7827,15 +7804,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>114</v>
@@ -7844,7 +7821,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>115</v>
@@ -7852,7 +7829,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>116</v>
@@ -7861,15 +7838,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>116</v>
@@ -7878,7 +7855,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>117</v>
@@ -7886,7 +7863,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>118</v>
@@ -7895,15 +7872,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>120</v>
@@ -7912,7 +7889,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>122</v>
@@ -7920,7 +7897,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>120</v>
@@ -7929,7 +7906,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>123</v>
@@ -7937,7 +7914,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>124</v>
@@ -7946,15 +7923,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>124</v>
@@ -7963,7 +7940,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>125</v>
@@ -7971,7 +7948,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>127</v>
@@ -7980,15 +7957,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>127</v>
@@ -7997,15 +7974,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>130</v>
@@ -8014,15 +7991,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>130</v>
@@ -8031,15 +8008,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>133</v>
@@ -8048,15 +8025,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>133</v>
@@ -8065,15 +8042,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>133</v>
@@ -8082,7 +8059,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>134</v>
@@ -8090,7 +8067,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>137</v>
@@ -8099,15 +8076,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>140</v>
@@ -8116,7 +8093,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>141</v>
@@ -8124,7 +8101,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>143</v>
@@ -8141,7 +8118,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>148</v>
@@ -8150,7 +8127,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>149</v>
@@ -8158,7 +8135,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>151</v>
@@ -8167,15 +8144,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>153</v>
@@ -8184,15 +8161,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>155</v>
@@ -8201,15 +8178,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>158</v>
@@ -8218,15 +8195,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>158</v>
@@ -8235,7 +8212,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>159</v>
@@ -8243,7 +8220,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>161</v>
@@ -8252,15 +8229,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>161</v>
@@ -8269,7 +8246,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>162</v>
@@ -8277,24 +8254,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>165</v>
@@ -8303,15 +8280,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>165</v>
@@ -8320,7 +8297,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>166</v>
@@ -8328,7 +8305,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>168</v>
@@ -8337,7 +8314,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>169</v>
@@ -8345,7 +8322,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>170</v>
@@ -8354,15 +8331,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>170</v>
@@ -8371,7 +8348,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>171</v>
@@ -8379,7 +8356,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>172</v>
@@ -8388,15 +8365,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>172</v>
@@ -8405,7 +8382,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>173</v>
@@ -8413,262 +8390,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>176</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>202</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>206</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>218</v>
@@ -8677,7 +8654,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>219</v>
@@ -8685,7 +8662,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>220</v>
@@ -8694,15 +8671,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>222</v>
@@ -8711,15 +8688,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>224</v>
@@ -8728,15 +8705,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>225</v>
@@ -8745,15 +8722,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>226</v>
@@ -8762,7 +8739,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>228</v>
@@ -8770,7 +8747,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>230</v>
@@ -8779,508 +8756,508 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D105" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>69</v>
@@ -9289,245 +9266,245 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D124" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>78</v>
@@ -9535,1379 +9512,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D144" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D145" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D207" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D214" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D69BCA7-ACD7-4A90-BF87-65D3FF39ABC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB5BD78-C251-411D-BF3B-E1D7BD5B28BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1992,18 +1992,6 @@
   </si>
   <si>
     <t>待测 衰败</t>
-  </si>
-  <si>
-    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.嗜血。攻击时能恢复等同于其所造成的伤害的生命值。2.破甲。攻击时无视玩家部分护甲。</t>
-  </si>
-  <si>
-    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.投掷炸弹。对玩家所在区域投掷炸弹，投掷时有前摇和预警，若被命中则受到500点物理伤害并被眩晕。2.自爆。死亡时自爆，对附近造成750点伤害。3.走位。会主动远离玩家，跟玩家拉开距离</t>
-  </si>
-  <si>
-    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.普通攻击。距离它较近时使用近战攻击；距离较远时使用远程攻击，远程攻击有概率对玩家造成恐惧效果。2.流血。造成持续55秒的流血效果（可叠加），共20段流血伤害（8）。3.呼唤。呼叫附近的矿工和工兵。4.召唤。随机召唤一个骷髅战士(200HP)攻击玩家。</t>
-  </si>
-  <si>
-    <t>受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；1.不稳。骨傀儡约每2秒受到50点真实伤害，约每10秒恢复250点生命值。若骨傀儡被冻结，则它将无法恢复生命值。2.加速。骨傀儡造成的伤害降低100点（快速攻击100），但是攻击速度大大提高。3.重组。骨傀儡死后将在一段时间内复活，无法彻底杀死；可闪避，降低玩家攻速；击败后会清除仇恨值并回归原位置。</t>
   </si>
   <si>
     <t>无</t>
@@ -2261,6 +2249,30 @@
   </si>
   <si>
     <t>毁灭战士的头</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；可闪避，降低玩家攻速；击败后会清除仇恨值并回归原位置。
+【不稳】骨傀儡约每2秒受到50点真实伤害，约每10秒恢复250点生命值。若骨傀儡被冻结，则它将无法恢复生命值。
+【加速】骨傀儡造成的伤害降低100点（快速攻击100），但是攻击速度大大提高。
+【重组】骨傀儡死后将在一段时间内复活，无法彻底杀死。</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
+【普通攻击】距离它较近时使用近战攻击；距离较远时使用远程攻击，远程攻击有概率对玩家造成恐惧效果。
+【流血】造成持续55秒的流血效果（可叠加），共20段流血伤害（8）。
+【呼唤】呼叫附近的矿工和工兵。
+【召唤】随机召唤一个骷髅战士(200HP)攻击玩家。</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
+【投掷炸弹】对玩家所在区域投掷炸弹，投掷时有前摇和预警，若被命中则受到500点物理伤害并被眩晕。
+【自爆】死亡时自爆，对附近造成750点伤害。
+【走位】会主动远离玩家，跟玩家拉开距离。</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
+【嗜血】攻击时能恢复等同于其所造成的伤害的生命值。
+【破甲】攻击时无视玩家部分护甲。</t>
   </si>
 </sst>
 </file>
@@ -3265,7 +3277,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3279,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="20" t="s">
@@ -3313,7 +3325,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3420,7 +3432,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3436,7 +3448,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="H10" s="29"/>
     </row>
@@ -3642,7 +3654,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="H20" s="29"/>
     </row>
@@ -3677,7 +3689,7 @@
         <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="20" t="s">
@@ -3699,7 +3711,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3909,10 +3921,10 @@
         <v>83</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3949,7 +3961,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -3971,7 +3983,7 @@
         <v>88</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4067,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4142,7 +4154,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4164,7 +4176,7 @@
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -4186,7 +4198,7 @@
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4265,7 +4277,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>113</v>
@@ -4383,7 +4395,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
@@ -4407,7 +4419,7 @@
         <v>139</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4619,11 +4631,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="G65" s="20" t="s">
         <v>136</v>
@@ -4653,10 +4665,10 @@
         <v>6</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A67" s="12" t="s">
         <v>165</v>
       </c>
@@ -4671,16 +4683,16 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>639</v>
+        <v>705</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>167</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
         <v>168</v>
       </c>
@@ -4695,14 +4707,14 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>640</v>
+        <v>704</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>167</v>
       </c>
       <c r="H68" s="47"/>
     </row>
-    <row r="69" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" ht="81" x14ac:dyDescent="0.45">
       <c r="A69" s="13" t="s">
         <v>170</v>
       </c>
@@ -4717,14 +4729,14 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>641</v>
+        <v>703</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>167</v>
       </c>
       <c r="H69" s="47"/>
     </row>
-    <row r="70" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A70" s="13" t="s">
         <v>172</v>
       </c>
@@ -4739,7 +4751,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>642</v>
+        <v>702</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>167</v>
@@ -4769,7 +4781,7 @@
         <v>6</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -4857,7 +4869,7 @@
         <v>6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
@@ -4976,7 +4988,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>197</v>
@@ -4998,7 +5010,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>200</v>
@@ -5108,7 +5120,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -5117,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -5151,7 +5163,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -5165,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -5459,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
@@ -5641,7 +5653,7 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
@@ -5652,7 +5664,7 @@
       </c>
       <c r="H112" s="29"/>
     </row>
-    <row r="113" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" ht="54.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="14" t="s">
         <v>272</v>
       </c>
@@ -5720,7 +5732,7 @@
     </row>
     <row r="116" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A116" s="15" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -5742,7 +5754,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -5763,12 +5775,12 @@
         <v>6</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="12" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -5777,20 +5789,20 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -5803,16 +5815,16 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H119" s="29"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -5821,14 +5833,14 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H120" s="29"/>
     </row>
@@ -5847,10 +5859,10 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H121" s="29"/>
     </row>
@@ -5869,16 +5881,16 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -5887,20 +5899,20 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H123" s="29"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -5909,20 +5921,20 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="13" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -5935,16 +5947,16 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="13" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -5957,16 +5969,16 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H126" s="29"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -5975,20 +5987,20 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="14" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -6001,10 +6013,10 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="H128" s="29"/>
     </row>
@@ -6031,7 +6043,7 @@
         <v>6</v>
       </c>
       <c r="H129" s="25" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
@@ -6045,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
@@ -6339,7 +6351,7 @@
         <v>6</v>
       </c>
       <c r="H143" s="27" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
@@ -6375,7 +6387,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -6459,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -6493,7 +6505,7 @@
         <v>6</v>
       </c>
       <c r="H150" s="27" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
@@ -6851,7 +6863,7 @@
         <v>6</v>
       </c>
       <c r="H165" s="27" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6871,13 +6883,13 @@
         <v>189</v>
       </c>
       <c r="F166" s="34" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="G166" s="36" t="s">
         <v>376</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
@@ -6895,7 +6907,7 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="G167" s="37"/>
       <c r="H167" s="44"/>
@@ -6915,7 +6927,7 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="G168" s="37"/>
       <c r="H168" s="44"/>
@@ -6935,7 +6947,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
@@ -6955,7 +6967,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
@@ -6975,7 +6987,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
@@ -6995,7 +7007,7 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
@@ -7015,7 +7027,7 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
@@ -7035,7 +7047,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7052,7 +7064,7 @@
         <v>55</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
@@ -7076,7 +7088,7 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
@@ -7096,7 +7108,7 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
@@ -7115,10 +7127,10 @@
         <v>64</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
@@ -7140,14 +7152,14 @@
         <v>404</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B180" s="2">
         <v>500</v>
@@ -7156,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2" t="s">
@@ -7167,7 +7179,7 @@
     </row>
     <row r="181" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A181" s="17" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B181" s="18">
         <v>500</v>
@@ -7179,10 +7191,10 @@
         <v>130</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F181" s="18" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="G181" s="38"/>
       <c r="H181" s="45"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB5BD78-C251-411D-BF3B-E1D7BD5B28BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A853668F-494B-406F-B6B9-EBB09B265072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="707">
   <si>
     <t>家里</t>
   </si>
@@ -756,9 +756,6 @@
   </si>
   <si>
     <t>主线第四章：过去的鬼魂</t>
-  </si>
-  <si>
-    <t>梦魇</t>
   </si>
   <si>
     <t>14-27</t>
@@ -2273,6 +2270,12 @@
     <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
 【嗜血】攻击时能恢复等同于其所造成的伤害的生命值。
 【破甲】攻击时无视玩家部分护甲。</t>
+  </si>
+  <si>
+    <t>噩梦</t>
+  </si>
+  <si>
+    <t>永恒噩梦</t>
   </si>
 </sst>
 </file>
@@ -3244,7 +3247,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="39" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3277,7 +3280,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3291,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="20" t="s">
@@ -3325,7 +3328,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3432,7 +3435,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3448,7 +3451,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H10" s="29"/>
     </row>
@@ -3654,7 +3657,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H20" s="29"/>
     </row>
@@ -3689,7 +3692,7 @@
         <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="20" t="s">
@@ -3711,7 +3714,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3921,10 +3924,10 @@
         <v>83</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3961,7 +3964,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -3983,7 +3986,7 @@
         <v>88</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4079,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4154,7 +4157,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4176,7 +4179,7 @@
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -4198,7 +4201,7 @@
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4277,7 +4280,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>113</v>
@@ -4395,7 +4398,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
@@ -4419,7 +4422,7 @@
         <v>139</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4631,11 +4634,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G65" s="20" t="s">
         <v>136</v>
@@ -4665,7 +4668,7 @@
         <v>6</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
@@ -4683,13 +4686,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>167</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
@@ -4707,7 +4710,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>167</v>
@@ -4729,7 +4732,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>167</v>
@@ -4751,7 +4754,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>167</v>
@@ -4781,7 +4784,7 @@
         <v>6</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -4869,7 +4872,7 @@
         <v>6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
@@ -4988,7 +4991,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>197</v>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>200</v>
@@ -5120,7 +5123,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -5129,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -5163,7 +5166,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -5177,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -5354,7 +5357,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>238</v>
+        <v>705</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -5363,40 +5366,40 @@
         <v>0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H98" s="29"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>241</v>
+        <v>706</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>632</v>
+        <v>639</v>
+      </c>
+      <c r="C99" s="2">
+        <v>0</v>
       </c>
       <c r="D99" s="2">
         <v>62</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H99" s="29"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B100" s="2">
         <v>150</v>
@@ -5409,16 +5412,16 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G100" s="20" t="s">
         <v>244</v>
-      </c>
-      <c r="G100" s="20" t="s">
-        <v>245</v>
       </c>
       <c r="H100" s="29"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B101" s="2">
         <v>110</v>
@@ -5431,16 +5434,16 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G101" s="20" t="s">
         <v>247</v>
-      </c>
-      <c r="G101" s="20" t="s">
-        <v>248</v>
       </c>
       <c r="H101" s="29"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B102" s="2">
         <v>185</v>
@@ -5453,16 +5456,16 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H102" s="29"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B103" s="2">
         <v>300</v>
@@ -5471,20 +5474,20 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G103" s="20" t="s">
         <v>252</v>
-      </c>
-      <c r="G103" s="20" t="s">
-        <v>253</v>
       </c>
       <c r="H103" s="29"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
@@ -5498,19 +5501,19 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H104" s="29"/>
     </row>
     <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A105" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B105" s="2">
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -5518,16 +5521,16 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H105" s="29"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -5538,19 +5541,19 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H106" s="29"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D107" s="2">
         <v>72</v>
@@ -5558,33 +5561,33 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H107" s="29"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H108" s="29"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B109" s="2">
         <v>300</v>
@@ -5598,13 +5601,13 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H109" s="29"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B110" s="2">
         <v>600</v>
@@ -5618,13 +5621,13 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H110" s="29"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B111" s="2">
         <v>1000</v>
@@ -5638,13 +5641,13 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H111" s="29"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B112" s="2">
         <v>450</v>
@@ -5653,20 +5656,20 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G112" s="20" t="s">
         <v>270</v>
-      </c>
-      <c r="G112" s="20" t="s">
-        <v>271</v>
       </c>
       <c r="H112" s="29"/>
     </row>
     <row r="113" spans="1:8" ht="54.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B113" s="2">
         <v>2500</v>
@@ -5679,16 +5682,16 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H113" s="29"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B114" s="2">
         <v>9000</v>
@@ -5701,16 +5704,16 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G114" s="20" t="s">
         <v>275</v>
-      </c>
-      <c r="G114" s="20" t="s">
-        <v>276</v>
       </c>
       <c r="H114" s="29"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B115" s="2">
         <v>10500</v>
@@ -5719,20 +5722,20 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G115" s="20" t="s">
         <v>279</v>
-      </c>
-      <c r="G115" s="20" t="s">
-        <v>280</v>
       </c>
       <c r="H115" s="29"/>
     </row>
     <row r="116" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A116" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -5745,16 +5748,16 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G116" s="20" t="s">
         <v>282</v>
-      </c>
-      <c r="G116" s="20" t="s">
-        <v>283</v>
       </c>
       <c r="H116" s="29"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -5775,12 +5778,12 @@
         <v>6</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="12" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -5789,20 +5792,20 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="G118" s="20" t="s">
         <v>646</v>
-      </c>
-      <c r="G118" s="20" t="s">
-        <v>647</v>
       </c>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -5815,16 +5818,16 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H119" s="29"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -5833,20 +5836,20 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H120" s="29"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B121" s="2">
         <v>150</v>
@@ -5859,16 +5862,16 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H121" s="29"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B122" s="2">
         <v>300</v>
@@ -5881,16 +5884,16 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -5899,20 +5902,20 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H123" s="29"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -5921,20 +5924,20 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -5947,16 +5950,16 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -5969,16 +5972,16 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H126" s="29"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -5987,20 +5990,20 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="14" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -6013,16 +6016,16 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H128" s="29"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>1</v>
@@ -6043,12 +6046,12 @@
         <v>6</v>
       </c>
       <c r="H129" s="25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B130" s="2">
         <v>50</v>
@@ -6057,14 +6060,14 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G130" s="20" t="s">
         <v>286</v>
-      </c>
-      <c r="G130" s="20" t="s">
-        <v>287</v>
       </c>
       <c r="H130" s="29"/>
     </row>
@@ -6090,7 +6093,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B132" s="2">
         <v>100</v>
@@ -6099,18 +6102,18 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H132" s="29"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B133" s="2">
         <v>45</v>
@@ -6123,36 +6126,36 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G133" s="20" t="s">
         <v>295</v>
-      </c>
-      <c r="G133" s="20" t="s">
-        <v>296</v>
       </c>
       <c r="H133" s="29"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B134" s="2">
         <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H134" s="29"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B135" s="2">
         <v>600</v>
@@ -6161,20 +6164,20 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H135" s="29"/>
     </row>
     <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B136" s="2">
         <v>1500</v>
@@ -6183,20 +6186,20 @@
         <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G136" s="20" t="s">
         <v>301</v>
-      </c>
-      <c r="G136" s="20" t="s">
-        <v>302</v>
       </c>
       <c r="H136" s="29"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
@@ -6208,19 +6211,19 @@
         <v>100</v>
       </c>
       <c r="E137" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="G137" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H137" s="29"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B138" s="2">
         <v>1000</v>
@@ -6233,16 +6236,16 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G138" s="20" t="s">
         <v>307</v>
-      </c>
-      <c r="G138" s="20" t="s">
-        <v>308</v>
       </c>
       <c r="H138" s="29"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B139" s="2">
         <v>750</v>
@@ -6258,13 +6261,13 @@
         <v>78</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H139" s="29"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B140" s="2">
         <v>150</v>
@@ -6277,16 +6280,16 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G140" s="20" t="s">
         <v>312</v>
-      </c>
-      <c r="G140" s="20" t="s">
-        <v>313</v>
       </c>
       <c r="H140" s="29"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B141" s="2">
         <v>720</v>
@@ -6299,16 +6302,16 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G141" s="20" t="s">
         <v>315</v>
-      </c>
-      <c r="G141" s="20" t="s">
-        <v>316</v>
       </c>
       <c r="H141" s="29"/>
     </row>
     <row r="142" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B142" s="2">
         <v>2000</v>
@@ -6321,16 +6324,16 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G142" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H142" s="29"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>1</v>
@@ -6351,12 +6354,12 @@
         <v>6</v>
       </c>
       <c r="H143" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B144" s="2">
         <v>400</v>
@@ -6369,16 +6372,16 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G144" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H144" s="29"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B145" s="2">
         <v>80</v>
@@ -6387,20 +6390,20 @@
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H145" s="29"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B146" s="2">
         <v>70</v>
@@ -6414,13 +6417,13 @@
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H146" s="29"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B147" s="2">
         <v>180</v>
@@ -6434,13 +6437,13 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H147" s="29"/>
     </row>
     <row r="148" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B148" s="2">
         <v>40</v>
@@ -6453,16 +6456,16 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G148" s="20" t="s">
         <v>328</v>
-      </c>
-      <c r="G148" s="20" t="s">
-        <v>329</v>
       </c>
       <c r="H148" s="29"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B149" s="2">
         <v>100</v>
@@ -6471,20 +6474,20 @@
         <v>0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H149" s="29"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>1</v>
@@ -6505,344 +6508,344 @@
         <v>6</v>
       </c>
       <c r="H150" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G151" s="20" t="s">
         <v>339</v>
-      </c>
-      <c r="G151" s="20" t="s">
-        <v>340</v>
       </c>
       <c r="H151" s="29"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G152" s="20" t="s">
         <v>333</v>
-      </c>
-      <c r="G152" s="20" t="s">
-        <v>334</v>
       </c>
       <c r="H152" s="29"/>
     </row>
     <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D153" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E153" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="20" t="s">
         <v>346</v>
-      </c>
-      <c r="G153" s="20" t="s">
-        <v>347</v>
       </c>
       <c r="H153" s="29"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G154" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="G155" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H155" s="29"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="G156" s="20" t="s">
         <v>354</v>
-      </c>
-      <c r="G156" s="20" t="s">
-        <v>355</v>
       </c>
       <c r="H156" s="29"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D157" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G158" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H158" s="29"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="14" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H159" s="29"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H160" s="29"/>
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A162" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C162" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="D162" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E162" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E162" s="7" t="s">
+      <c r="F162" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="F162" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="G162" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H162" s="29"/>
     </row>
     <row r="163" spans="1:10" ht="54" x14ac:dyDescent="0.45">
       <c r="A163" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E163" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="E163" s="6" t="s">
+      <c r="F163" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="G163" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H163" s="29"/>
     </row>
     <row r="164" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>632</v>
-      </c>
       <c r="C164" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F164" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G164" s="20" t="s">
         <v>333</v>
-      </c>
-      <c r="G164" s="20" t="s">
-        <v>334</v>
       </c>
       <c r="H164" s="29"/>
     </row>
     <row r="165" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A165" s="31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B165" s="32" t="s">
         <v>1</v>
@@ -6863,12 +6866,12 @@
         <v>6</v>
       </c>
       <c r="H165" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B166" s="34">
         <v>120</v>
@@ -6883,18 +6886,18 @@
         <v>189</v>
       </c>
       <c r="F166" s="34" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G166" s="36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B167" s="2">
         <v>120</v>
@@ -6907,14 +6910,14 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G167" s="37"/>
       <c r="H167" s="44"/>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B168" s="2">
         <v>200</v>
@@ -6927,14 +6930,14 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G168" s="37"/>
       <c r="H168" s="44"/>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B169" s="2">
         <v>200</v>
@@ -6947,14 +6950,14 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6967,14 +6970,14 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
@@ -6987,14 +6990,14 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
     </row>
     <row r="172" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
@@ -7007,14 +7010,14 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
@@ -7027,14 +7030,14 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
     </row>
     <row r="174" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
@@ -7047,7 +7050,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7055,7 +7058,7 @@
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B175" s="2">
         <v>120</v>
@@ -7064,18 +7067,18 @@
         <v>55</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
     </row>
     <row r="176" spans="1:10" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A176" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B176" s="2">
         <v>200</v>
@@ -7088,14 +7091,14 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
     </row>
     <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A177" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B177" s="2">
         <v>250</v>
@@ -7108,14 +7111,14 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
     </row>
     <row r="178" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B178" s="2">
         <v>200</v>
@@ -7127,17 +7130,17 @@
         <v>64</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
     </row>
     <row r="179" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B179" s="2">
         <v>250</v>
@@ -7149,17 +7152,17 @@
         <v>60</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B180" s="2">
         <v>500</v>
@@ -7168,18 +7171,18 @@
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
     </row>
     <row r="181" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A181" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B181" s="18">
         <v>500</v>
@@ -7191,10 +7194,10 @@
         <v>130</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F181" s="18" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G181" s="38"/>
       <c r="H181" s="45"/>
@@ -7229,24 +7232,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -7255,15 +7258,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -7272,32 +7275,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -7306,7 +7309,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -7314,7 +7317,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -7323,15 +7326,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -7340,15 +7343,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -7357,7 +7360,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -7365,7 +7368,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -7374,15 +7377,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -7391,7 +7394,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -7399,7 +7402,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -7408,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -7416,7 +7419,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
@@ -7425,15 +7428,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
@@ -7442,15 +7445,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>57</v>
@@ -7459,7 +7462,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>58</v>
@@ -7467,7 +7470,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>60</v>
@@ -7476,15 +7479,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -7493,15 +7496,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>63</v>
@@ -7510,7 +7513,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>64</v>
@@ -7518,7 +7521,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
@@ -7527,15 +7530,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -7544,15 +7547,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -7561,7 +7564,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>75</v>
@@ -7569,7 +7572,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>77</v>
@@ -7578,15 +7581,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>77</v>
@@ -7595,7 +7598,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>78</v>
@@ -7603,7 +7606,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>80</v>
@@ -7612,15 +7615,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>80</v>
@@ -7637,7 +7640,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
@@ -7646,15 +7649,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>91</v>
@@ -7663,15 +7666,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>96</v>
@@ -7680,15 +7683,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>101</v>
@@ -7697,15 +7700,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>105</v>
@@ -7714,15 +7717,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>108</v>
@@ -7731,15 +7734,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>108</v>
@@ -7756,7 +7759,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>108</v>
@@ -7765,7 +7768,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>110</v>
@@ -7773,7 +7776,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>111</v>
@@ -7782,15 +7785,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>111</v>
@@ -7799,7 +7802,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>112</v>
@@ -7807,7 +7810,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>114</v>
@@ -7816,15 +7819,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>114</v>
@@ -7833,7 +7836,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>115</v>
@@ -7841,7 +7844,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>116</v>
@@ -7850,15 +7853,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>116</v>
@@ -7867,7 +7870,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>117</v>
@@ -7875,7 +7878,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>118</v>
@@ -7884,15 +7887,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>120</v>
@@ -7901,7 +7904,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>122</v>
@@ -7909,7 +7912,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>120</v>
@@ -7918,7 +7921,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>123</v>
@@ -7926,7 +7929,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>124</v>
@@ -7935,15 +7938,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>124</v>
@@ -7952,7 +7955,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>125</v>
@@ -7960,7 +7963,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>127</v>
@@ -7969,15 +7972,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>127</v>
@@ -7986,15 +7989,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>130</v>
@@ -8003,15 +8006,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>130</v>
@@ -8020,15 +8023,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>133</v>
@@ -8037,15 +8040,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>133</v>
@@ -8054,15 +8057,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>133</v>
@@ -8071,7 +8074,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>134</v>
@@ -8079,7 +8082,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>137</v>
@@ -8088,15 +8091,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>140</v>
@@ -8105,7 +8108,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>141</v>
@@ -8113,7 +8116,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>143</v>
@@ -8130,7 +8133,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>148</v>
@@ -8139,7 +8142,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>149</v>
@@ -8147,7 +8150,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>151</v>
@@ -8156,15 +8159,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>153</v>
@@ -8173,15 +8176,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>155</v>
@@ -8190,15 +8193,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>158</v>
@@ -8207,15 +8210,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>158</v>
@@ -8224,7 +8227,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>159</v>
@@ -8232,7 +8235,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>161</v>
@@ -8241,15 +8244,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>161</v>
@@ -8258,7 +8261,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>162</v>
@@ -8266,24 +8269,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>165</v>
@@ -8292,15 +8295,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>165</v>
@@ -8309,7 +8312,7 @@
         <v>5</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>166</v>
@@ -8317,7 +8320,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>168</v>
@@ -8326,7 +8329,7 @@
         <v>5</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>169</v>
@@ -8334,7 +8337,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>170</v>
@@ -8343,15 +8346,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>170</v>
@@ -8360,7 +8363,7 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>171</v>
@@ -8368,7 +8371,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>172</v>
@@ -8377,15 +8380,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>172</v>
@@ -8394,7 +8397,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>173</v>
@@ -8402,262 +8405,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>176</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>202</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>206</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>218</v>
@@ -8666,7 +8669,7 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>219</v>
@@ -8674,7 +8677,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>220</v>
@@ -8683,15 +8686,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>222</v>
@@ -8700,15 +8703,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>224</v>
@@ -8717,15 +8720,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>225</v>
@@ -8734,15 +8737,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>226</v>
@@ -8751,7 +8754,7 @@
         <v>5</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>228</v>
@@ -8759,7 +8762,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>230</v>
@@ -8768,508 +8771,508 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D105" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>69</v>
@@ -9278,245 +9281,245 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D124" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>78</v>
@@ -9524,1379 +9527,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D144" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D145" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D207" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D214" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A853668F-494B-406F-B6B9-EBB09B265072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0AC8ED-953F-43BC-A8D6-84D679A84E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="715">
   <si>
     <t>家里</t>
   </si>
@@ -1042,9 +1042,6 @@
   </si>
   <si>
     <t>衰败之女弗拉格纳</t>
-  </si>
-  <si>
-    <t>数据待补充</t>
   </si>
   <si>
     <t>沼泽中心</t>
@@ -1986,9 +1983,6 @@
   </si>
   <si>
     <t>15，20，35</t>
-  </si>
-  <si>
-    <t>待测 衰败</t>
   </si>
   <si>
     <t>无</t>
@@ -2204,6 +2198,45 @@
 【小弟出场顺序】召唤阿托鲁斯、郭隆德、吉杜尔和亚龙，分别在领主生命值&lt;80%，60%，45%，25% 的时候</t>
   </si>
   <si>
+    <t>蝙蝠</t>
+  </si>
+  <si>
+    <t>继母艾莎；1-5级图</t>
+  </si>
+  <si>
+    <t>毁灭战士的头</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；可闪避，降低玩家攻速；击败后会清除仇恨值并回归原位置。
+【不稳】骨傀儡约每2秒受到50点真实伤害，约每10秒恢复250点生命值。若骨傀儡被冻结，则它将无法恢复生命值。
+【加速】骨傀儡造成的伤害降低100点（快速攻击100），但是攻击速度大大提高。
+【重组】骨傀儡死后将在一段时间内复活，无法彻底杀死。</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
+【普通攻击】距离它较近时使用近战攻击；距离较远时使用远程攻击，远程攻击有概率对玩家造成恐惧效果。
+【流血】造成持续55秒的流血效果（可叠加），共20段流血伤害（8）。
+【呼唤】呼叫附近的矿工和工兵。
+【召唤】随机召唤一个骷髅战士(200HP)攻击玩家。</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
+【投掷炸弹】对玩家所在区域投掷炸弹，投掷时有前摇和预警，若被命中则受到500点物理伤害并被眩晕。
+【自爆】死亡时自爆，对附近造成750点伤害。
+【走位】会主动远离玩家，跟玩家拉开距离。</t>
+  </si>
+  <si>
+    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
+【嗜血】攻击时能恢复等同于其所造成的伤害的生命值。
+【破甲】攻击时无视玩家部分护甲。</t>
+  </si>
+  <si>
+    <t>噩梦</t>
+  </si>
+  <si>
+    <t>永恒噩梦</t>
+  </si>
+  <si>
     <t>【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
 【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
 【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
@@ -2211,9 +2244,9 @@
 【英雄模式玩家增益】
 1.	良好体魄：玩家最大生命值增加40点
 2.	训练警报：帐篷中的敌人没那么致命
-3.	刺骨寒冰：敌人更容易受到寒冷伤害
-4.	炽焰：敌人更容易受到火焰伤害
-5.	衰败之触：敌人更容易受到衰败伤害
+3.	刺骨寒冰：敌人更容易受到寒冷伤害（+50%）
+4.	炽焰：敌人更容易受到火焰伤害（+50%）
+5.	衰败之触：敌人更容易受到衰败伤害（+50%）
 6.	高效治疗：玩家治疗效果提高20%
 7.	治疗之风：每4秒恢复5生命值
 8.	尖锐尖刺：敌人在攻击你时会受到固定10点伤害
@@ -2239,43 +2272,44 @@
 8.	超自然反应：敌人有20%的机会躲避攻击</t>
   </si>
   <si>
-    <t>蝙蝠</t>
-  </si>
-  <si>
-    <t>继母艾莎；1-5级图</t>
-  </si>
-  <si>
-    <t>毁灭战士的头</t>
-  </si>
-  <si>
-    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害；可闪避，降低玩家攻速；击败后会清除仇恨值并回归原位置。
-【不稳】骨傀儡约每2秒受到50点真实伤害，约每10秒恢复250点生命值。若骨傀儡被冻结，则它将无法恢复生命值。
-【加速】骨傀儡造成的伤害降低100点（快速攻击100），但是攻击速度大大提高。
-【重组】骨傀儡死后将在一段时间内复活，无法彻底杀死。</t>
-  </si>
-  <si>
-    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
-【普通攻击】距离它较近时使用近战攻击；距离较远时使用远程攻击，远程攻击有概率对玩家造成恐惧效果。
-【流血】造成持续55秒的流血效果（可叠加），共20段流血伤害（8）。
-【呼唤】呼叫附近的矿工和工兵。
-【召唤】随机召唤一个骷髅战士(200HP)攻击玩家。</t>
-  </si>
-  <si>
-    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
-【投掷炸弹】对玩家所在区域投掷炸弹，投掷时有前摇和预警，若被命中则受到500点物理伤害并被眩晕。
-【自爆】死亡时自爆，对附近造成750点伤害。
-【走位】会主动远离玩家，跟玩家拉开距离。</t>
-  </si>
-  <si>
-    <t>【特性】受到1.5倍衰败伤害，1倍火焰伤害，0.5倍寒冷伤害。
-【嗜血】攻击时能恢复等同于其所造成的伤害的生命值。
-【破甲】攻击时无视玩家部分护甲。</t>
-  </si>
-  <si>
-    <t>噩梦</t>
-  </si>
-  <si>
-    <t>永恒噩梦</t>
+    <t>800，2500，5000</t>
+  </si>
+  <si>
+    <t>10，19，60 衰败</t>
+  </si>
+  <si>
+    <t>25，55，85</t>
+  </si>
+  <si>
+    <t>0，0，4.5</t>
+  </si>
+  <si>
+    <t>10，29，40</t>
+  </si>
+  <si>
+    <t>3，10，20</t>
+  </si>
+  <si>
+    <t>3，9，17 衰败</t>
+  </si>
+  <si>
+    <t>【特性】衰败之女受到1.5倍元素伤害；在受到一定伤害之后会瞬移到四个角落中的其中一个法阵
+【技能介绍】弗拉格纳有两个主要技能，第一个是衰败之球，当人物远离弗拉格纳时她就会触发这个技能，触发技能时，弗拉格纳站在原地向四周发射大量衰败之球；第二个技能是衰败地刺，在近战过程当中概率触发，触发该技能时地面会出现预示范围；下面则是这两个技能分别在普通，英雄，传奇模式下的伤害区别：
+【衰败之球】
+普通模式：26衰败伤+15物理伤
+英雄模式：57衰败伤+40物理伤
+传奇模式：待测
+【衰败地刺】
+普通模式：20衰败伤+30物理伤+9流血*5下
+英雄模式：96衰败伤+50物理伤+9流血*5下
+传奇模式：待测</t>
+  </si>
+  <si>
+    <t>18，23，60</t>
+  </si>
+  <si>
+    <t>地图会不断刷新侍女，上限3个
+普通模式25一刀死；英雄模式55一刀死；传奇模式90一刀死</t>
   </si>
 </sst>
 </file>
@@ -3247,7 +3281,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="39" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3280,7 +3314,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -3294,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="20" t="s">
@@ -3328,7 +3362,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -3435,7 +3469,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B10" s="2">
         <v>85</v>
@@ -3451,7 +3485,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="H10" s="29"/>
     </row>
@@ -3657,7 +3691,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H20" s="29"/>
     </row>
@@ -3692,7 +3726,7 @@
         <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="20" t="s">
@@ -3714,7 +3748,7 @@
         <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="20" t="s">
@@ -3924,10 +3958,10 @@
         <v>83</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -3964,7 +3998,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -3986,7 +4020,7 @@
         <v>88</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -4082,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
@@ -4157,7 +4191,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -4179,7 +4213,7 @@
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="13" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -4201,7 +4235,7 @@
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="13" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -4280,7 +4314,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>113</v>
@@ -4398,7 +4432,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
@@ -4422,7 +4456,7 @@
         <v>139</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.45">
@@ -4634,11 +4668,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G65" s="20" t="s">
         <v>136</v>
@@ -4668,7 +4702,7 @@
         <v>6</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
@@ -4686,13 +4720,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>167</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
@@ -4710,7 +4744,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>167</v>
@@ -4732,7 +4766,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>167</v>
@@ -4754,7 +4788,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>167</v>
@@ -4784,7 +4818,7 @@
         <v>6</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -4872,7 +4906,7 @@
         <v>6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
@@ -4991,7 +5025,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="12" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>197</v>
@@ -5013,7 +5047,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="12" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>200</v>
@@ -5123,7 +5157,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="15" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -5132,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -5166,7 +5200,7 @@
         <v>6</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -5180,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -5357,7 +5391,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="12" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -5377,10 +5411,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="12" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -5474,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
@@ -5530,7 +5564,7 @@
         <v>258</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -5550,10 +5584,10 @@
         <v>260</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D107" s="2">
         <v>72</v>
@@ -5570,13 +5604,13 @@
         <v>261</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -5656,7 +5690,7 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
@@ -5735,7 +5769,7 @@
     </row>
     <row r="116" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A116" s="15" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -5757,7 +5791,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -5778,12 +5812,12 @@
         <v>6</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="12" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -5792,20 +5826,20 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H118" s="29"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="12" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -5818,16 +5852,16 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H119" s="29"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="12" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -5836,14 +5870,14 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H120" s="29"/>
     </row>
@@ -5862,10 +5896,10 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H121" s="29"/>
     </row>
@@ -5884,16 +5918,16 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G122" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H122" s="29"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -5902,20 +5936,20 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H123" s="29"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="12" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -5924,20 +5958,20 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G124" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H124" s="29"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="13" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -5950,16 +5984,16 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H125" s="29"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -5972,16 +6006,16 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H126" s="29"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -5990,20 +6024,20 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H127" s="29"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="14" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -6016,10 +6050,10 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H128" s="29"/>
     </row>
@@ -6046,7 +6080,7 @@
         <v>6</v>
       </c>
       <c r="H129" s="25" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
@@ -6060,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
@@ -6102,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
@@ -6141,10 +6175,10 @@
         <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
@@ -6164,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
@@ -6186,7 +6220,7 @@
         <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
@@ -6354,7 +6388,7 @@
         <v>6</v>
       </c>
       <c r="H143" s="27" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
@@ -6390,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -6474,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -6487,7 +6521,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>1</v>
@@ -6508,344 +6542,346 @@
         <v>6</v>
       </c>
       <c r="H150" s="27" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G151" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="G151" s="20" t="s">
-        <v>339</v>
-      </c>
       <c r="H151" s="29"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>631</v>
+        <v>707</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>631</v>
+        <v>708</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="E152" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>711</v>
+      </c>
       <c r="F152" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="G152" s="20" t="s">
         <v>332</v>
-      </c>
-      <c r="G152" s="20" t="s">
-        <v>333</v>
       </c>
       <c r="H152" s="29"/>
     </row>
     <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D153" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E153" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="20" t="s">
         <v>345</v>
-      </c>
-      <c r="G153" s="20" t="s">
-        <v>346</v>
       </c>
       <c r="H153" s="29"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G154" s="20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H154" s="29"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="G155" s="20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H155" s="29"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="G156" s="20" t="s">
         <v>353</v>
-      </c>
-      <c r="G156" s="20" t="s">
-        <v>354</v>
       </c>
       <c r="H156" s="29"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D157" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H157" s="29"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="14" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G158" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H158" s="29"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="14" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H159" s="29"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G160" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H160" s="29"/>
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A162" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C162" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="D162" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E162" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="E162" s="7" t="s">
+      <c r="F162" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F162" s="2" t="s">
-        <v>369</v>
-      </c>
       <c r="G162" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H162" s="29"/>
     </row>
     <row r="163" spans="1:10" ht="54" x14ac:dyDescent="0.45">
       <c r="A163" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E163" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E163" s="6" t="s">
+      <c r="F163" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="G163" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H163" s="29"/>
     </row>
-    <row r="164" spans="1:10" ht="27" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:10" ht="202.5" x14ac:dyDescent="0.45">
       <c r="A164" s="15" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>631</v>
+        <v>705</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>631</v>
+        <v>713</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>631</v>
+        <v>709</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>637</v>
+        <v>706</v>
       </c>
       <c r="F164" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="G164" s="20" t="s">
         <v>332</v>
-      </c>
-      <c r="G164" s="20" t="s">
-        <v>333</v>
       </c>
       <c r="H164" s="29"/>
     </row>
     <row r="165" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A165" s="31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B165" s="32" t="s">
         <v>1</v>
@@ -6866,12 +6902,12 @@
         <v>6</v>
       </c>
       <c r="H165" s="27" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B166" s="34">
         <v>120</v>
@@ -6886,18 +6922,18 @@
         <v>189</v>
       </c>
       <c r="F166" s="34" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G166" s="36" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B167" s="2">
         <v>120</v>
@@ -6910,14 +6946,14 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G167" s="37"/>
       <c r="H167" s="44"/>
     </row>
     <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B168" s="2">
         <v>200</v>
@@ -6930,14 +6966,14 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G168" s="37"/>
       <c r="H168" s="44"/>
     </row>
     <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B169" s="2">
         <v>200</v>
@@ -6950,14 +6986,14 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G169" s="37"/>
       <c r="H169" s="44"/>
     </row>
     <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B170" s="2">
         <v>200</v>
@@ -6970,14 +7006,14 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="44"/>
     </row>
     <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B171" s="2">
         <v>200</v>
@@ -6990,14 +7026,14 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G171" s="37"/>
       <c r="H171" s="44"/>
     </row>
     <row r="172" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B172" s="2">
         <v>200</v>
@@ -7010,14 +7046,14 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G172" s="37"/>
       <c r="H172" s="44"/>
     </row>
     <row r="173" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B173" s="2">
         <v>200</v>
@@ -7030,14 +7066,14 @@
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G173" s="37"/>
       <c r="H173" s="44"/>
     </row>
     <row r="174" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B174" s="2">
         <v>200</v>
@@ -7050,7 +7086,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G174" s="37"/>
       <c r="H174" s="44"/>
@@ -7058,7 +7094,7 @@
     </row>
     <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B175" s="2">
         <v>120</v>
@@ -7067,18 +7103,18 @@
         <v>55</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G175" s="37"/>
       <c r="H175" s="44"/>
     </row>
     <row r="176" spans="1:10" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A176" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B176" s="2">
         <v>200</v>
@@ -7091,14 +7127,14 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G176" s="37"/>
       <c r="H176" s="44"/>
     </row>
     <row r="177" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A177" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B177" s="2">
         <v>250</v>
@@ -7111,14 +7147,14 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G177" s="37"/>
       <c r="H177" s="44"/>
     </row>
     <row r="178" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A178" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B178" s="2">
         <v>200</v>
@@ -7130,17 +7166,17 @@
         <v>64</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G178" s="37"/>
       <c r="H178" s="44"/>
     </row>
     <row r="179" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B179" s="2">
         <v>250</v>
@@ -7152,17 +7188,17 @@
         <v>60</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G179" s="37"/>
       <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B180" s="2">
         <v>500</v>
@@ -7171,18 +7207,18 @@
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G180" s="37"/>
       <c r="H180" s="44"/>
     </row>
     <row r="181" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A181" s="17" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B181" s="18">
         <v>500</v>
@@ -7194,10 +7230,10 @@
         <v>130</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F181" s="18" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G181" s="38"/>
       <c r="H181" s="45"/>
@@ -7232,24 +7268,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -7258,15 +7294,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>17</v>
@@ -7275,32 +7311,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -7309,7 +7345,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -7317,7 +7353,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -7326,15 +7362,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>28</v>
@@ -7343,15 +7379,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
@@ -7360,7 +7396,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
@@ -7368,7 +7404,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -7377,15 +7413,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>43</v>
@@ -7394,7 +7430,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>45</v>
@@ -7402,7 +7438,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -7411,7 +7447,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -7419,7 +7455,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
@@ -7428,15 +7464,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
@@ -7445,15 +7481,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>57</v>
@@ -7462,7 +7498,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>58</v>
@@ -7470,7 +7506,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>60</v>
@@ -7479,15 +7515,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>63</v>
@@ -7496,15 +7532,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>63</v>
@@ -7513,7 +7549,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>64</v>
@@ -7521,7 +7557,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>69</v>
@@ -7530,15 +7566,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -7547,15 +7583,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -7564,7 +7600,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>75</v>
@@ -7572,7 +7608,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>77</v>
@@ -7581,15 +7617,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>77</v>
@@ -7598,7 +7634,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>78</v>
@@ -7606,7 +7642,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>80</v>
@@ -7615,15 +7651,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>80</v>
@@ -7640,7 +7676,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
@@ -7649,15 +7685,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>91</v>
@@ -7666,15 +7702,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>96</v>
@@ -7683,15 +7719,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>101</v>
@@ -7700,15 +7736,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>105</v>
@@ -7717,15 +7753,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>108</v>
@@ -7734,15 +7770,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>108</v>
@@ -7759,7 +7795,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>108</v>
@@ -7768,7 +7804,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>110</v>
@@ -7776,7 +7812,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>111</v>
@@ -7785,15 +7821,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>111</v>
@@ -7802,7 +7838,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>112</v>
@@ -7810,7 +7846,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>114</v>
@@ -7819,15 +7855,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>114</v>
@@ -7836,7 +7872,7 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>115</v>
@@ -7844,7 +7880,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>116</v>
@@ -7853,15 +7889,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>116</v>
@@ -7870,7 +7906,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>117</v>
@@ -7878,7 +7914,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>118</v>
@@ -7887,15 +7923,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>120</v>
@@ -7904,7 +7940,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>122</v>
@@ -7912,7 +7948,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>120</v>
@@ -7921,7 +7957,7 @@
         <v>5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>123</v>
@@ -7929,7 +7965,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>124</v>
@@ -7938,15 +7974,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>124</v>
@@ -7955,7 +7991,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>125</v>
@@ -7963,7 +7999,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>127</v>
@@ -7972,15 +8008,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>127</v>
@@ -7989,15 +8025,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>130</v>
@@ -8006,15 +8042,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>130</v>
@@ -8023,15 +8059,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>133</v>
@@ -8040,15 +8076,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>133</v>
@@ -8057,15 +8093,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>133</v>
@@ -8074,7 +8110,7 @@
         <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>134</v>
@@ -8082,7 +8118,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>137</v>
@@ -8091,15 +8127,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>140</v>
@@ -8108,7 +8144,7 @@
         <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>141</v>
@@ -8116,7 +8152,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>143</v>
@@ -8133,7 +8169,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>148</v>
@@ -8142,7 +8178,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>149</v>
@@ -8150,7 +8186,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>151</v>
@@ -8159,15 +8195,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>153</v>
@@ -8176,15 +8212,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>155</v>
@@ -8193,15 +8229,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>158</v>
@@ -8210,15 +8246,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>158</v>
@@ -8227,7 +8263,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>159</v>
@@ -8235,7 +8271,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>161</v>
@@ -8244,15 +8280,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>161</v>
@@ -8261,7 +8297,7 @@
